--- a/testdata/formulas/formula-suite.xlsx
+++ b/testdata/formulas/formula-suite.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="1563">
   <si>
     <t xml:space="preserve">apple</t>
   </si>
@@ -2601,6 +2601,2112 @@
   </si>
   <si>
     <t xml:space="preserve">=1/0+NA()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TRUNC(8.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TRUNC(-8.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TRUNC(3.14159,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TRUNC(1234.5,-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TRUNC(C1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CEILING.MATH(6.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CEILING.MATH(-5.5,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CEILING.MATH(-5.5,2,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CEILING.MATH(6.3,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CEILING.MATH(24.3,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR.MATH(6.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR.MATH(-5.5,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR.MATH(-5.5,2,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR.MATH(24.3,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR(3.7,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR(-2.5,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR(-2.5,-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR(2.5,-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FLOOR(3,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MROUND(10,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MROUND(-10,-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MROUND(1.3,0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MROUND(5,-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MROUND(7,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EXP(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EXP(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EXP(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EXP(A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EXP(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LN(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LN(EXP(2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LN(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LN(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LN(A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG(100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG(8,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG(10,10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG(5,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG10(1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG10(0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG10(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOG10(A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIGN(-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIGN(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIGN(C1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIGN(C2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIGN(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AND(RAND()&gt;=0,RAND()&lt;1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INT(RAND())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RAND()&lt;&gt;RAND()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IF(RAND()&lt;1,"ok","bad")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANDBETWEEN(5,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AND(RANDBETWEEN(1,6)&gt;=1,RANDBETWEEN(1,6)&lt;=6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANDBETWEEN(3,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANDBETWEEN(-2,-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMSQ(3,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMSQ(A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMSQ(C1:C3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMSQ(A1:A2,B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMSQ(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SQRTPI(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SQRTPI(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SQRTPI(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SQRTPI(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACT(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACT(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACT(5.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACT(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACT(171)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACTDOUBLE(6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACTDOUBLE(7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACTDOUBLE(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FACTDOUBLE(-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COMBIN(8,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COMBIN(5,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COMBIN(5,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COMBIN(3,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COMBIN(10.9,2.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERMUT(5,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERMUT(3,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERMUT(3,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERMUT(2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GCD(24,36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GCD(5,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GCD(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GCD(-1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GCD(7.9,14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LCM(4,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LCM(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LCM(0,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LCM(-1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUOTIENT(7,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUOTIENT(-7,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUOTIENT(5,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUOTIENT(C1,A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EVEN(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EVEN(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EVEN(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EVEN(1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EVEN(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ODD(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ODD(-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ODD(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ODD(1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ODD(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIN(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIN(PI()/2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIN(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SIN(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COS(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COS(PI())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COS(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COS(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TAN(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TAN(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TAN(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TAN(A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ASIN(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ASIN(0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ASIN(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ASIN(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ACOS(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ACOS(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ACOS(0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ACOS(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN(1000000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN2(1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN2(-1,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN2(0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ATAN2(1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SINH(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SINH(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SINH(-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SINH(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COSH(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COSH(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COSH(-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COSH(H2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TANH(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TANH(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TANH(-0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TANH(100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEGREES(PI())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEGREES(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEGREES(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEGREES(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RADIANS(180)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RADIANS(90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RADIANS(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RADIANS(-45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2MY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2MY2(A1:A3,A4:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2MY2(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2MY2(A1:A3,H1:H3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2PY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2PY2(A1:A3,A4:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2PY2(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMX2PY2(F1:F2,A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMXMY2(A1:A3,A4:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMXMY2(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMXMY2(F1:F2,A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTBLANK(D1:D6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTBLANK(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTBLANK(D3:D4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTBLANK(J1:J4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMIFS(A1:A6,B1:B6,"*a*")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMIFS(A1:A6,A1:A6,"&gt;2",A1:A6,"&lt;5")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMIFS(C1:C6,A1:A6,"&gt;=3")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMIFS(A1:A6,A1:A6,"&gt;2",B1:B3,"x")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMIFS(F1:F4,A1:A4,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMIFS(A1:A2,H1:H2,"#N/A")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTIFS(A1:A6,"&gt;2")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTIFS(A1:A6,"&gt;2",C1:C6,"&lt;50")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTIFS(B1:B6,"?????")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTIFS(A1:A6,"&gt;2",B1:B5,"a*")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTIFS(D1:D6,"")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNTIFS(A1:A6,"&lt;&gt;3",A1:A6,"&lt;&gt;4")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIFS(A1:A6,A1:A6,"&gt;2")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIFS(C1:C6,A1:A6,"&lt;=3")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIFS(A1:A6,A1:A6,"&gt;10")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIFS(A1:A6,B1:B6,"*e*")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIF(A1:A6,"&gt;3")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIF(B1:B6,"*e*",A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIF(A1:A6,"&gt;10")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIF(C1:C6,"&lt;&gt;0")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGEIF(F1:F4,"&gt;=200")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MAXIFS(C1:C6,A1:A6,"&lt;=4")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MAXIFS(A1:A6,B1:B6,"*e*")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MAXIFS(A1:A6,A1:A6,"&gt;10")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MAXIFS(C1:C6,A1:A6,"&gt;=2",A1:A6,"&lt;=3")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINIFS(C1:C6,A1:A6,"&lt;=4")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINIFS(A1:A6,B1:B6,"*e*")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINIFS(A1:A6,A1:A6,"&gt;10")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINIFS(C1:C6,A1:A6,"&gt;=3")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MEDIAN(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MEDIAN(1,2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MEDIAN(C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MEDIAN(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MEDIAN(A1:A2,H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MEDIAN(A1:A5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE(1,2,2,3,3,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE(2,2,3,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE({1,2,2,3})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE.SNGL(1,2,2,3,3,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE.SNGL(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE.SNGL(2,2,3,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MODE.SNGL(B1:B3,5,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR(1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.S(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.S(C1:C4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.S(A1,H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.S(A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.P(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.P(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.P(C1:C4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VAR.P(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VARP(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VARP(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VARP(1,2,3,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=VARP(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV(1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.S(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.S(C1:C4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.S(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.S(A1,H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.P(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.P(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.P(C1:C4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEV.P(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEVP(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEVP(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEVP(1,2,3,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=STDEVP(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LARGE(A1:A6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LARGE(A1:A6,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LARGE(C1:C6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LARGE(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LARGE(A1:A6,1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SMALL(A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SMALL(C1:C6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SMALL(B1:B6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SMALL(A1:A6,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK(3,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK(3,A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK(9,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK(100,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.EQ(100,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.EQ(1,A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.EQ(9,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.EQ(0,C1:C6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.AVG(3,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.AVG(1,A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.AVG(9,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANK.AVG(100,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE(A1:A6,0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE(A1:A6,0.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE(A1:A6,1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.INC(A1:A6,0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.INC(C1:C6,0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.INC(A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.INC(B1:B3,0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.EXC(A1:A6,0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.EXC(A1:A6,0.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.EXC(A1:A6,0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTILE.EXC(A1:A6,0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE(A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE(A1:A6,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE(A1:A6,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.INC(A1:A6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.INC(C1:C6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.INC(A1:A6,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.INC(A1:A6,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.EXC(A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.EXC(A1:A6,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.EXC(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=QUARTILE.EXC(A1:A6,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK(A1:A6,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK(A1:A6,3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK(A1:A6,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK(A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK.INC(A1:A6,2.5,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK.INC(A1:A6,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK.INC(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PERCENTRANK.INC(C1:C6,10.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CORREL(A1:A4,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CORREL(A1:A4,{4;3;2;1})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CORREL(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CORREL(A1:A1,F1:F1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CORREL(A1:A6,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVAR(A1:A4,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVAR(A1:A6,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVAR(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVAR(B1:B3,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.P(A1:A4,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.P(A1:A6,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.P(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.P(B1:B3,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.S(A1:A4,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.S(A1:A6,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.S(A1:A3,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COVARIANCE.S(A1:A1,F1:F1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLOPE(F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLOPE(C1:C6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLOPE(F1:F4,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLOPE(F1:F4,{1;1;1;1})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INTERCEPT(F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INTERCEPT(C1:C6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INTERCEPT(F1:F4,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INTERCEPT(F1:F4,{1;1;1;1})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RSQ(F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RSQ(C1:C6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RSQ(F1:F4,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RSQ(F1:F4,{1;1;1;1})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST(5,F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST(7,C1:C6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST(5,F1:F4,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST(B1,F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST.LINEAR(10,F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST.LINEAR(0,C1:C6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST.LINEAR(5,F1:F4,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FORECAST.LINEAR(2.5,F1:F4,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TREND(F1:F4,A1:A4,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(TREND(F1:F4,A1:A4,A5:A6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TREND(F1:F4),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TREND(F1:F4,A1:A4,5,FALSE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TREND(A1:A4,F1:F4,250)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GEOMEAN(1,2,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GEOMEAN(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GEOMEAN(C1:C3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=GEOMEAN(B1:B2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HARMEAN(1,2,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HARMEAN(A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HARMEAN(C1:C3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HARMEAN(B1:B2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEVSQ(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEVSQ(1,2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEVSQ(C1:C4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DEVSQ(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVEDEV(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVEDEV(1,2,3,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVEDEV(C1:C4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVEDEV(B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PMT(0.08/12,10,10000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PMT(0,10,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PMT(0.05,5,1000,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PMT(0.05,0,100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PMT(0.06,12,-5000,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FV(0.06/12,10,-200,-500,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FV(0,10,-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FV(0.05,5,-100,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FV(0.1,2,0,-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PV(0.08/12,240,500)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PV(0,5,-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PV(0.05,10,-100,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PV(0.05,10,0,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPER(0.12/12,-100,-1000,10000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPER(0,-100,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPER(0.05,-100,1000,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPER(0.01,0,100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IPMT(0.1/12,1,36,8000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IPMT(0.1/12,3,36,8000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IPMT(0.1,3,3,8000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IPMT(0.1/12,1,36,8000,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IPMT(0.05,0,3,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IPMT(0.05,2,3,1000,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PPMT(0.1/12,1,24,2000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PPMT(0.08,10,10,200000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PPMT(0.05,2,3,1000,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PPMT(0.05,4,3,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPV(0.1,-10000,3000,4200,6800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPV(0.1,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPV(-1,1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NPV(0.08,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(IRR({-70000,12000,15000,18000,21000,26000}),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(IRR({-100,110}),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IRR({1,2,3})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(IRR({-1000,300,400,500},0.2),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(RATE(48,-200,8000),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(RATE(10,0,-100,200),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RATE(0,-100,1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(RATE(12,-100,1000),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLN(30000,7500,10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLN(100,0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLN(100,10,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SLN(F1,0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SYD(30000,7500,10,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SYD(30000,7500,10,10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SYD(100,0,4,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SYD(100,0,4,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DB(1000000,100000,6,1,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DB(1000000,100000,6,2,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DB(1000000,100000,6,7,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DB(1000000,100000,6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DB(1000,100,5,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DDB(2400,300,10*365,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DDB(2400,300,10,1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DDB(2400,300,10,2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DDB(2400,300,10,10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DDB(100,0,5,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EFFECT(0.0525,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EFFECT(0.1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EFFECT(0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EFFECT(0.1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NOMINAL(0.053543,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NOMINAL(0.1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NOMINAL(0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NOMINAL(0.1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MIRR({1,2,3},0.1,0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROUND(MIRR({-100,50,60},0.05,0.05),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MIRR({-100,-50},0.1,0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFS(A1&gt;5,"a",A1&gt;0,"b")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFS(FALSE,1,TRUE,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFS(FALSE,1,FALSE,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFS(TRUE,1,1/0,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFS(A1,"x")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SWITCH(2,1,"a",2,"b","z")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SWITCH(9,1,"a",2,"b","z")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SWITCH(9,1,"a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SWITCH("B","a",1,"b",2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SWITCH(A3,1,"one",3,"three")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFNA(H2,"x")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFNA(H1,"x")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFNA(5,"x")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFNA(MATCH(9,A1:A6,0),0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XOR(TRUE,FALSE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XOR(TRUE,TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XOR(TRUE,TRUE,TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XOR(1,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XOR(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISLOGICAL(TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISLOGICAL(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISLOGICAL("TRUE")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISLOGICAL(1=1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISEVEN(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISEVEN(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISEVEN(-2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISEVEN("a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISEVEN(A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISODD(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISODD(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISODD(-3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISODD("a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISODD(A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=N(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=N("a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=N(TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=N(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=N(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=N(A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=T("a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=T(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=T(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=T(H2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=T(TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE("a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE(TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE({1,2})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE(A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE(A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TYPE(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("row",A5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("col",C1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("address",B2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("contents",A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("type",B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("type",A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CELL("type",J9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISERR(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISERR(H2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISERR(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISERR(1/0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISNONTEXT(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISNONTEXT("a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISNONTEXT(J9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISNONTEXT(H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISREF(A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISREF(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISREF(A1:B2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISREF(INDEX(A1:A3,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISREF("A1")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEARCH("an","banana")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEARCH("AN","banana",3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEARCH("b?n","banana")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEARCH("z","banana")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEARCH("a*a","banana")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEARCH("~?","what?")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPLACE("abcdef",3,2,"XY")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPLACE("abc",5,1,"Z")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPLACE("abc",1,0,"Z")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPLACE("abc",0,1,"Z")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPLACE(B1,1,1,"A")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPT("ab",3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPT("x",0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPT("x",-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPT(A1,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REPT("-",2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PROPER("hello world")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PROPER("o'neil mc-donald")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PROPER("2nd place")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PROPER(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=PROPER("ÀB cD")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHAR(65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHAR(97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHAR(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHAR(256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHAR(169)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHAR(233)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CODE("A")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CODE("apple")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CODE("")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CODE("é")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CODE(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICODE("A")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICODE("€")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICODE("")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICODE(B2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICHAR(65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICHAR(8364)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICHAR(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNICHAR(97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CLEAN("a"&amp;CHAR(7)&amp;"b")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CLEAN(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CLEAN("  x ")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CLEAN(A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("1,234.5")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("1.234,5",",",".")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("5%")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("abc")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("1%%")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE("1.5",".",".")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NUMBERVALUE(" 12 ")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FIXED(1234.567,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FIXED(1234.567,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FIXED(-1234.567,2,TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FIXED(0.5,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FIXED(1234567)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FIXED(A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(",",TRUE,B1:B3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN("-",FALSE,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(", ",TRUE,"a","","b")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(",",FALSE,"a","","b")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN("",TRUE,B1:B2,"!")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(",",TRUE,H1,"a")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEVALUE("2024-01-15")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEVALUE("1/15/2024")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEVALUE("2024-12-31")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEVALUE("abc")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEVALUE(5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIMEVALUE("12:00")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIMEVALUE("6:00 PM")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIMEVALUE("18:30:30")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIMEVALUE("xx")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIMEVALUE("2024-01-15 06:00")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIME(12,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIME(25,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIME(0,90,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIME(1,2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TIME(-1,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HOUR(E3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HOUR(0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HOUR("18:30")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HOUR(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINUTE(E3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINUTE("18:30:45")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINUTE(0.7712)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINUTE(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SECOND("18:30:45")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SECOND(0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SECOND(TIME(1,2,3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SECOND(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EDATE(E1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EDATE(DATE(2024,1,31),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EDATE(E1,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EDATE(E1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EDATE(E1,12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EOMONTH(E1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EOMONTH(E1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EOMONTH(E1,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EOMONTH(E2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS(E1,E2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS(E1,E1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY(E1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY(DATE(2024,1,19),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY(E1,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY(E1,5,E1+1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY(E1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY.INTL(E1,1,11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY.INTL(DATE(2024,1,20),1,11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY.INTL(E1,5,"0000011")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WORKDAY.INTL(E1,-2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(DATE(2020,1,15),E1,"Y")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(DATE(2020,1,15),E1,"M")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(DATE(2020,1,15),E1,"D")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(DATE(2023,6,20),E1,"YM")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(DATE(2023,6,20),E1,"YD")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(E1,DATE(2020,1,15),"Y")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DATEDIF(E1,E2,"X")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(E1,E2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(E2,E1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=YEARFRAC(E1,E2,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WEEKNUM(E1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WEEKNUM(E1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WEEKNUM(E2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WEEKNUM(E2,21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WEEKNUM(DATE(2024,1,1),21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WEEKNUM(E1,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISOWEEKNUM(E1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISOWEEKNUM(E2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISOWEEKNUM(DATE(2021,1,3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISOWEEKNUM(DATE(2020,12,31))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISOWEEKNUM(DATE(2016,1,1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(A1:C3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(A:A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS({1,2;3,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(A1:C3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(A:C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(1:1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS({1,2;3,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOOKUP(3,A1:A6,B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOOKUP(3.5,A1:A6,B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOOKUP(0,A1:A6,B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOOKUP(100,A1:A6,B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LOOKUP(2,A1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH(3,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH("cherry",B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH(3.5,A1:A6,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH(3.5,A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH("ch*",B1:B6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH(9,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH(3,A1:A6,0,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XMATCH(3,A1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP(3,A1:A6,B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP(9,A1:A6,B1:B6,"none")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP(9,A1:A6,B1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP(3.5,A1:A6,B1:B6,,-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP("fig",B1:B6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP(4,A1:A6,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=XLOOKUP(3,A1:A6,B1:B5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(A1:XLOOKUP(3,A1:A6,A1:A6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDIRECT("A1")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDIRECT("A"&amp;3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(INDIRECT("A1:A3"))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDIRECT("Other!A1")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDIRECT("R2C1",FALSE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDIRECT("zzz")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDIRECT(B1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=OFFSET(A1,2,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(OFFSET(A1,0,0,3,1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=OFFSET(A1,-1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(OFFSET(A1:A2,1,0))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(OFFSET(A1,0,0,3,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=OFFSET(A1,0,0,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(5,3,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(2,28,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(1,1,1,FALSE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(1,1,1,TRUE,"My Sheet")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ADDRESS(1,1,5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(TRANSPOSE(A1:A3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TRANSPOSE(A1:A3),1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(TRANSPOSE(A1:A6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(TRANSPOSE(A1:C1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TRANSPOSE(A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HYPERLINK("http://x.y","click")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HYPERLINK("http://x.y")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HYPERLINK(B1,"go")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=HYPERLINK("u",A2)</t>
   </si>
   <si>
     <t xml:space="preserve">remote</t>
@@ -2610,13 +4716,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yy\ hh:mm\ AM/PM"/>
     <numFmt numFmtId="168" formatCode="[hh]:mm:ss"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
+    <numFmt numFmtId="170" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="hh:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -2682,7 +4790,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2708,6 +4816,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2834,7 +4950,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L862"/>
+  <dimension ref="A1:L1564"/>
   <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8062,7 +10178,7 @@
       </c>
       <c r="L568" s="4" t="n">
         <f aca="true">NOW()</f>
-        <v>46310.3676440239</v>
+        <v>46310.8757863259</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10709,6 +12825,6324 @@
       <c r="L862" s="0" t="e">
         <f aca="false">1/0+NA()</f>
         <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K863" s="0" t="s">
+        <v>860</v>
+      </c>
+      <c r="L863" s="0" t="n">
+        <f aca="false">TRUNC(8.9)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K864" s="0" t="s">
+        <v>861</v>
+      </c>
+      <c r="L864" s="0" t="n">
+        <f aca="false">TRUNC(-8.9)</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K865" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="L865" s="0" t="n">
+        <f aca="false">TRUNC(3.14159,2)</f>
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K866" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="L866" s="0" t="n">
+        <f aca="false">TRUNC(1234.5,-2)</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K867" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="L867" s="0" t="n">
+        <f aca="false">TRUNC(C1)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K868" s="0" t="s">
+        <v>865</v>
+      </c>
+      <c r="L868" s="0" t="n">
+        <f aca="false">_xlfn.CEILING.MATH(6.3)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K869" s="0" t="s">
+        <v>866</v>
+      </c>
+      <c r="L869" s="0" t="n">
+        <f aca="false">_xlfn.CEILING.MATH(-5.5,2)</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K870" s="0" t="s">
+        <v>867</v>
+      </c>
+      <c r="L870" s="0" t="n">
+        <f aca="false">_xlfn.CEILING.MATH(-5.5,2,1)</f>
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K871" s="0" t="s">
+        <v>868</v>
+      </c>
+      <c r="L871" s="0" t="n">
+        <f aca="false">_xlfn.CEILING.MATH(6.3,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K872" s="0" t="s">
+        <v>869</v>
+      </c>
+      <c r="L872" s="0" t="n">
+        <f aca="false">_xlfn.CEILING.MATH(24.3,5)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K873" s="0" t="s">
+        <v>870</v>
+      </c>
+      <c r="L873" s="0" t="n">
+        <f aca="false">_xlfn.FLOOR.MATH(6.7)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K874" s="0" t="s">
+        <v>871</v>
+      </c>
+      <c r="L874" s="0" t="n">
+        <f aca="false">_xlfn.FLOOR.MATH(-5.5,2)</f>
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K875" s="0" t="s">
+        <v>872</v>
+      </c>
+      <c r="L875" s="0" t="n">
+        <f aca="false">_xlfn.FLOOR.MATH(-5.5,2,1)</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K876" s="0" t="s">
+        <v>873</v>
+      </c>
+      <c r="L876" s="0" t="n">
+        <f aca="false">_xlfn.FLOOR.MATH(24.3,5)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K877" s="0" t="s">
+        <v>874</v>
+      </c>
+      <c r="L877" s="0" t="n">
+        <f aca="false">FLOOR(3.7,2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K878" s="0" t="s">
+        <v>875</v>
+      </c>
+      <c r="L878" s="0" t="n">
+        <f aca="false">FLOOR(-2.5,2)</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K879" s="0" t="s">
+        <v>876</v>
+      </c>
+      <c r="L879" s="0" t="n">
+        <f aca="false">FLOOR(-2.5,-2)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K880" s="0" t="s">
+        <v>877</v>
+      </c>
+      <c r="L880" s="0" t="e">
+        <f aca="false">FLOOR(2.5,-2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K881" s="0" t="s">
+        <v>878</v>
+      </c>
+      <c r="L881" s="0" t="e">
+        <f aca="false">FLOOR(3,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K882" s="0" t="s">
+        <v>879</v>
+      </c>
+      <c r="L882" s="0" t="n">
+        <f aca="false">MROUND(10,3)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K883" s="0" t="s">
+        <v>880</v>
+      </c>
+      <c r="L883" s="0" t="n">
+        <f aca="false">MROUND(-10,-3)</f>
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K884" s="0" t="s">
+        <v>881</v>
+      </c>
+      <c r="L884" s="0" t="n">
+        <f aca="false">MROUND(1.3,0.2)</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K885" s="0" t="s">
+        <v>882</v>
+      </c>
+      <c r="L885" s="0" t="n">
+        <f aca="false">MROUND(5,-2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K886" s="0" t="s">
+        <v>883</v>
+      </c>
+      <c r="L886" s="0" t="n">
+        <f aca="false">MROUND(7,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K887" s="0" t="s">
+        <v>884</v>
+      </c>
+      <c r="L887" s="0" t="n">
+        <f aca="false">EXP(0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K888" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="L888" s="0" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
+      </c>
+    </row>
+    <row r="889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K889" s="0" t="s">
+        <v>886</v>
+      </c>
+      <c r="L889" s="0" t="n">
+        <f aca="false">EXP(-1)</f>
+        <v>0.367879441171442</v>
+      </c>
+    </row>
+    <row r="890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K890" s="0" t="s">
+        <v>887</v>
+      </c>
+      <c r="L890" s="0" t="n">
+        <f aca="false">EXP(A2)</f>
+        <v>7.38905609893065</v>
+      </c>
+    </row>
+    <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K891" s="0" t="s">
+        <v>888</v>
+      </c>
+      <c r="L891" s="0" t="e">
+        <f aca="false">EXP(B1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K892" s="0" t="s">
+        <v>889</v>
+      </c>
+      <c r="L892" s="0" t="n">
+        <f aca="false">LN(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K893" s="0" t="s">
+        <v>890</v>
+      </c>
+      <c r="L893" s="0" t="n">
+        <f aca="false">LN(EXP(2))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K894" s="0" t="s">
+        <v>891</v>
+      </c>
+      <c r="L894" s="0" t="e">
+        <f aca="false">LN(0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K895" s="0" t="s">
+        <v>892</v>
+      </c>
+      <c r="L895" s="0" t="e">
+        <f aca="false">LN(-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K896" s="0" t="s">
+        <v>893</v>
+      </c>
+      <c r="L896" s="0" t="n">
+        <f aca="false">LN(A6)</f>
+        <v>1.79175946922806</v>
+      </c>
+    </row>
+    <row r="897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K897" s="0" t="s">
+        <v>894</v>
+      </c>
+      <c r="L897" s="0" t="n">
+        <f aca="false">LOG(100)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K898" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="L898" s="0" t="n">
+        <f aca="false">LOG(8,2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K899" s="0" t="s">
+        <v>896</v>
+      </c>
+      <c r="L899" s="0" t="n">
+        <f aca="false">LOG(10,10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K900" s="0" t="s">
+        <v>897</v>
+      </c>
+      <c r="L900" s="0" t="e">
+        <f aca="false">LOG(5,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K901" s="0" t="s">
+        <v>898</v>
+      </c>
+      <c r="L901" s="0" t="e">
+        <f aca="false">LOG(-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K902" s="0" t="s">
+        <v>899</v>
+      </c>
+      <c r="L902" s="0" t="n">
+        <f aca="false">LOG10(1000)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K903" s="0" t="s">
+        <v>900</v>
+      </c>
+      <c r="L903" s="0" t="n">
+        <f aca="false">LOG10(0.01)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K904" s="0" t="s">
+        <v>901</v>
+      </c>
+      <c r="L904" s="0" t="e">
+        <f aca="false">LOG10(0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K905" s="0" t="s">
+        <v>902</v>
+      </c>
+      <c r="L905" s="0" t="n">
+        <f aca="false">LOG10(A4)</f>
+        <v>0.602059991327962</v>
+      </c>
+    </row>
+    <row r="906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K906" s="0" t="s">
+        <v>903</v>
+      </c>
+      <c r="L906" s="0" t="n">
+        <f aca="false">SIGN(-5)</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K907" s="0" t="s">
+        <v>904</v>
+      </c>
+      <c r="L907" s="0" t="n">
+        <f aca="false">SIGN(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K908" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="L908" s="0" t="n">
+        <f aca="false">SIGN(C1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K909" s="0" t="s">
+        <v>906</v>
+      </c>
+      <c r="L909" s="0" t="n">
+        <f aca="false">SIGN(C2)</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K910" s="0" t="s">
+        <v>907</v>
+      </c>
+      <c r="L910" s="0" t="e">
+        <f aca="false">SIGN(B1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K911" s="0" t="s">
+        <v>908</v>
+      </c>
+      <c r="L911" s="1" t="b">
+        <f aca="true">AND(RAND()&gt;=0,RAND()&lt;1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K912" s="0" t="s">
+        <v>909</v>
+      </c>
+      <c r="L912" s="0" t="n">
+        <f aca="true">INT(RAND())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K913" s="0" t="s">
+        <v>910</v>
+      </c>
+      <c r="L913" s="1" t="b">
+        <f aca="true">RAND()&lt;&gt;RAND()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K914" s="0" t="s">
+        <v>911</v>
+      </c>
+      <c r="L914" s="0" t="str">
+        <f aca="true">IF(RAND()&lt;1,"ok","bad")</f>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K915" s="0" t="s">
+        <v>912</v>
+      </c>
+      <c r="L915" s="0" t="n">
+        <f aca="false">RANDBETWEEN(5,5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K916" s="0" t="s">
+        <v>913</v>
+      </c>
+      <c r="L916" s="1" t="b">
+        <f aca="false">AND(RANDBETWEEN(1,6)&gt;=1,RANDBETWEEN(1,6)&lt;=6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K917" s="0" t="s">
+        <v>914</v>
+      </c>
+      <c r="L917" s="0" t="e">
+        <f aca="false">RANDBETWEEN(3,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K918" s="0" t="s">
+        <v>915</v>
+      </c>
+      <c r="L918" s="0" t="n">
+        <f aca="false">RANDBETWEEN(-2,-2)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K919" s="0" t="s">
+        <v>916</v>
+      </c>
+      <c r="L919" s="0" t="n">
+        <f aca="false">SUMSQ(3,4)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K920" s="0" t="s">
+        <v>917</v>
+      </c>
+      <c r="L920" s="0" t="n">
+        <f aca="false">SUMSQ(A1:A3)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K921" s="0" t="s">
+        <v>918</v>
+      </c>
+      <c r="L921" s="0" t="n">
+        <f aca="false">SUMSQ(C1:C3)</f>
+        <v>114.25</v>
+      </c>
+    </row>
+    <row r="922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K922" s="0" t="s">
+        <v>919</v>
+      </c>
+      <c r="L922" s="0" t="n">
+        <f aca="false">SUMSQ(A1:A2,B1:B3)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K923" s="0" t="s">
+        <v>920</v>
+      </c>
+      <c r="L923" s="0" t="e">
+        <f aca="false">SUMSQ(H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K924" s="0" t="s">
+        <v>921</v>
+      </c>
+      <c r="L924" s="0" t="n">
+        <f aca="false">SQRTPI(1)</f>
+        <v>1.77245385090552</v>
+      </c>
+    </row>
+    <row r="925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K925" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="L925" s="0" t="n">
+        <f aca="false">SQRTPI(2)</f>
+        <v>2.506628274631</v>
+      </c>
+    </row>
+    <row r="926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K926" s="0" t="s">
+        <v>923</v>
+      </c>
+      <c r="L926" s="0" t="n">
+        <f aca="false">SQRTPI(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K927" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="L927" s="0" t="e">
+        <f aca="false">SQRTPI(-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K928" s="0" t="s">
+        <v>925</v>
+      </c>
+      <c r="L928" s="0" t="n">
+        <f aca="false">FACT(5)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K929" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="L929" s="0" t="n">
+        <f aca="false">FACT(0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K930" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="L930" s="0" t="n">
+        <f aca="false">FACT(5.9)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K931" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="L931" s="0" t="e">
+        <f aca="false">FACT(-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K932" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="L932" s="0" t="e">
+        <f aca="false">FACT(171)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K933" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="L933" s="0" t="n">
+        <f aca="false">FACTDOUBLE(6)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K934" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="L934" s="0" t="n">
+        <f aca="false">FACTDOUBLE(7)</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K935" s="0" t="s">
+        <v>932</v>
+      </c>
+      <c r="L935" s="0" t="n">
+        <f aca="false">FACTDOUBLE(0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K936" s="0" t="s">
+        <v>933</v>
+      </c>
+      <c r="L936" s="0" t="e">
+        <f aca="false">FACTDOUBLE(-2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K937" s="0" t="s">
+        <v>934</v>
+      </c>
+      <c r="L937" s="0" t="n">
+        <f aca="false">COMBIN(8,2)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K938" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="L938" s="0" t="n">
+        <f aca="false">COMBIN(5,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K939" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="L939" s="0" t="n">
+        <f aca="false">COMBIN(5,5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K940" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="L940" s="0" t="e">
+        <f aca="false">COMBIN(3,5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K941" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="L941" s="0" t="n">
+        <f aca="false">COMBIN(10.9,2.5)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K942" s="0" t="s">
+        <v>939</v>
+      </c>
+      <c r="L942" s="0" t="n">
+        <f aca="false">PERMUT(5,2)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K943" s="0" t="s">
+        <v>940</v>
+      </c>
+      <c r="L943" s="0" t="n">
+        <f aca="false">PERMUT(3,3)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K944" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="L944" s="0" t="n">
+        <f aca="false">PERMUT(3,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K945" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="L945" s="0" t="e">
+        <f aca="false">PERMUT(2,3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K946" s="0" t="s">
+        <v>943</v>
+      </c>
+      <c r="L946" s="0" t="n">
+        <f aca="false">GCD(24,36)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K947" s="0" t="s">
+        <v>944</v>
+      </c>
+      <c r="L947" s="0" t="n">
+        <f aca="false">GCD(5,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K948" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="L948" s="0" t="n">
+        <f aca="false">GCD(A1:A6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K949" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="L949" s="0" t="e">
+        <f aca="false">GCD(-1,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K950" s="0" t="s">
+        <v>947</v>
+      </c>
+      <c r="L950" s="0" t="n">
+        <f aca="false">GCD(7.9,14)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K951" s="0" t="s">
+        <v>948</v>
+      </c>
+      <c r="L951" s="0" t="n">
+        <f aca="false">LCM(4,6)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K952" s="0" t="s">
+        <v>949</v>
+      </c>
+      <c r="L952" s="0" t="n">
+        <f aca="false">LCM(A1:A6)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K953" s="0" t="s">
+        <v>950</v>
+      </c>
+      <c r="L953" s="0" t="n">
+        <f aca="false">LCM(0,5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K954" s="0" t="s">
+        <v>951</v>
+      </c>
+      <c r="L954" s="0" t="e">
+        <f aca="false">LCM(-1,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K955" s="0" t="s">
+        <v>952</v>
+      </c>
+      <c r="L955" s="0" t="n">
+        <f aca="false">QUOTIENT(7,2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K956" s="0" t="s">
+        <v>953</v>
+      </c>
+      <c r="L956" s="0" t="n">
+        <f aca="false">QUOTIENT(-7,2)</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K957" s="0" t="s">
+        <v>954</v>
+      </c>
+      <c r="L957" s="0" t="e">
+        <f aca="false">QUOTIENT(5,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K958" s="0" t="s">
+        <v>955</v>
+      </c>
+      <c r="L958" s="0" t="n">
+        <f aca="false">QUOTIENT(C1,A2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K959" s="0" t="s">
+        <v>956</v>
+      </c>
+      <c r="L959" s="0" t="n">
+        <f aca="false">EVEN(3)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K960" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="L960" s="0" t="n">
+        <f aca="false">EVEN(-1)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K961" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="L961" s="0" t="n">
+        <f aca="false">EVEN(2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K962" s="0" t="s">
+        <v>959</v>
+      </c>
+      <c r="L962" s="0" t="n">
+        <f aca="false">EVEN(1.5)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K963" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="L963" s="0" t="n">
+        <f aca="false">EVEN(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K964" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="L964" s="0" t="n">
+        <f aca="false">ODD(2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K965" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="L965" s="0" t="n">
+        <f aca="false">ODD(-2)</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K966" s="0" t="s">
+        <v>963</v>
+      </c>
+      <c r="L966" s="0" t="n">
+        <f aca="false">ODD(3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K967" s="0" t="s">
+        <v>964</v>
+      </c>
+      <c r="L967" s="0" t="n">
+        <f aca="false">ODD(1.5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K968" s="0" t="s">
+        <v>965</v>
+      </c>
+      <c r="L968" s="0" t="n">
+        <f aca="false">ODD(0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K969" s="0" t="s">
+        <v>966</v>
+      </c>
+      <c r="L969" s="0" t="n">
+        <f aca="false">SIN(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K970" s="0" t="s">
+        <v>967</v>
+      </c>
+      <c r="L970" s="0" t="n">
+        <f aca="false">SIN(PI()/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K971" s="0" t="s">
+        <v>968</v>
+      </c>
+      <c r="L971" s="0" t="n">
+        <f aca="false">SIN(1)</f>
+        <v>0.841470984807897</v>
+      </c>
+    </row>
+    <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K972" s="0" t="s">
+        <v>969</v>
+      </c>
+      <c r="L972" s="0" t="e">
+        <f aca="false">SIN(B1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K973" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="L973" s="0" t="n">
+        <f aca="false">COS(0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K974" s="0" t="s">
+        <v>971</v>
+      </c>
+      <c r="L974" s="0" t="n">
+        <f aca="false">COS(PI())</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K975" s="0" t="s">
+        <v>972</v>
+      </c>
+      <c r="L975" s="0" t="n">
+        <f aca="false">COS(1)</f>
+        <v>0.54030230586814</v>
+      </c>
+    </row>
+    <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K976" s="0" t="s">
+        <v>973</v>
+      </c>
+      <c r="L976" s="0" t="e">
+        <f aca="false">COS(H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K977" s="0" t="s">
+        <v>974</v>
+      </c>
+      <c r="L977" s="0" t="n">
+        <f aca="false">TAN(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K978" s="0" t="s">
+        <v>975</v>
+      </c>
+      <c r="L978" s="0" t="n">
+        <f aca="false">TAN(1)</f>
+        <v>1.5574077246549</v>
+      </c>
+    </row>
+    <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K979" s="0" t="s">
+        <v>976</v>
+      </c>
+      <c r="L979" s="0" t="n">
+        <f aca="false">TAN(-1)</f>
+        <v>-1.5574077246549</v>
+      </c>
+    </row>
+    <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K980" s="0" t="s">
+        <v>977</v>
+      </c>
+      <c r="L980" s="0" t="n">
+        <f aca="false">TAN(A2)</f>
+        <v>-2.18503986326152</v>
+      </c>
+    </row>
+    <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K981" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="L981" s="0" t="n">
+        <f aca="false">ASIN(1)</f>
+        <v>1.5707963267949</v>
+      </c>
+    </row>
+    <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K982" s="0" t="s">
+        <v>979</v>
+      </c>
+      <c r="L982" s="0" t="n">
+        <f aca="false">ASIN(0.5)</f>
+        <v>0.523598775598299</v>
+      </c>
+    </row>
+    <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K983" s="0" t="s">
+        <v>980</v>
+      </c>
+      <c r="L983" s="0" t="e">
+        <f aca="false">ASIN(2)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K984" s="0" t="s">
+        <v>981</v>
+      </c>
+      <c r="L984" s="0" t="n">
+        <f aca="false">ASIN(-1)</f>
+        <v>-1.5707963267949</v>
+      </c>
+    </row>
+    <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K985" s="0" t="s">
+        <v>982</v>
+      </c>
+      <c r="L985" s="0" t="n">
+        <f aca="false">ACOS(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K986" s="0" t="s">
+        <v>983</v>
+      </c>
+      <c r="L986" s="0" t="n">
+        <f aca="false">ACOS(-1)</f>
+        <v>3.14159265358979</v>
+      </c>
+    </row>
+    <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K987" s="0" t="s">
+        <v>984</v>
+      </c>
+      <c r="L987" s="0" t="n">
+        <f aca="false">ACOS(0.5)</f>
+        <v>1.0471975511966</v>
+      </c>
+    </row>
+    <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K988" s="0" t="s">
+        <v>985</v>
+      </c>
+      <c r="L988" s="0" t="e">
+        <f aca="false">ACOS(2)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K989" s="0" t="s">
+        <v>986</v>
+      </c>
+      <c r="L989" s="0" t="n">
+        <f aca="false">ATAN(1)</f>
+        <v>0.785398163397448</v>
+      </c>
+    </row>
+    <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K990" s="0" t="s">
+        <v>987</v>
+      </c>
+      <c r="L990" s="0" t="n">
+        <f aca="false">ATAN(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K991" s="0" t="s">
+        <v>988</v>
+      </c>
+      <c r="L991" s="0" t="n">
+        <f aca="false">ATAN(-1)</f>
+        <v>-0.785398163397448</v>
+      </c>
+    </row>
+    <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K992" s="0" t="s">
+        <v>989</v>
+      </c>
+      <c r="L992" s="0" t="n">
+        <f aca="false">ATAN(1000000)</f>
+        <v>1.5707953267949</v>
+      </c>
+    </row>
+    <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K993" s="0" t="s">
+        <v>990</v>
+      </c>
+      <c r="L993" s="0" t="n">
+        <f aca="false">ATAN2(1,1)</f>
+        <v>0.785398163397448</v>
+      </c>
+    </row>
+    <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K994" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="L994" s="0" t="n">
+        <f aca="false">ATAN2(-1,-1)</f>
+        <v>-2.35619449019235</v>
+      </c>
+    </row>
+    <row r="995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K995" s="0" t="s">
+        <v>992</v>
+      </c>
+      <c r="L995" s="0" t="n">
+        <f aca="false">ATAN2(0,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K996" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="L996" s="0" t="n">
+        <f aca="false">ATAN2(1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K997" s="0" t="s">
+        <v>994</v>
+      </c>
+      <c r="L997" s="0" t="n">
+        <f aca="false">SINH(1)</f>
+        <v>1.1752011936438</v>
+      </c>
+    </row>
+    <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K998" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="L998" s="0" t="n">
+        <f aca="false">SINH(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K999" s="0" t="s">
+        <v>996</v>
+      </c>
+      <c r="L999" s="0" t="n">
+        <f aca="false">SINH(-2)</f>
+        <v>-3.62686040784702</v>
+      </c>
+    </row>
+    <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1000" s="0" t="s">
+        <v>997</v>
+      </c>
+      <c r="L1000" s="0" t="e">
+        <f aca="false">SINH(B1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1001" s="0" t="s">
+        <v>998</v>
+      </c>
+      <c r="L1001" s="0" t="n">
+        <f aca="false">COSH(0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1002" s="0" t="s">
+        <v>999</v>
+      </c>
+      <c r="L1002" s="0" t="n">
+        <f aca="false">COSH(1)</f>
+        <v>1.54308063481524</v>
+      </c>
+    </row>
+    <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1003" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L1003" s="0" t="n">
+        <f aca="false">COSH(-2)</f>
+        <v>3.76219569108363</v>
+      </c>
+    </row>
+    <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1004" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L1004" s="0" t="e">
+        <f aca="false">COSH(H2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1005" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L1005" s="0" t="n">
+        <f aca="false">TANH(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1006" s="0" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L1006" s="0" t="n">
+        <f aca="false">TANH(1)</f>
+        <v>0.761594155955765</v>
+      </c>
+    </row>
+    <row r="1007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1007" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L1007" s="0" t="n">
+        <f aca="false">TANH(-0.5)</f>
+        <v>-0.46211715726001</v>
+      </c>
+    </row>
+    <row r="1008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1008" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L1008" s="0" t="n">
+        <f aca="false">TANH(100)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1009" s="0" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L1009" s="0" t="n">
+        <f aca="false">DEGREES(PI())</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1010" s="0" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L1010" s="0" t="n">
+        <f aca="false">DEGREES(1)</f>
+        <v>57.2957795130823</v>
+      </c>
+    </row>
+    <row r="1011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1011" s="0" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L1011" s="0" t="n">
+        <f aca="false">DEGREES(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1012" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L1012" s="0" t="e">
+        <f aca="false">DEGREES(B1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1013" s="0" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L1013" s="0" t="n">
+        <f aca="false">RADIANS(180)</f>
+        <v>3.14159265358979</v>
+      </c>
+    </row>
+    <row r="1014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1014" s="0" t="s">
+        <v>1011</v>
+      </c>
+      <c r="L1014" s="0" t="n">
+        <f aca="false">RADIANS(90)</f>
+        <v>1.5707963267949</v>
+      </c>
+    </row>
+    <row r="1015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1015" s="0" t="s">
+        <v>1012</v>
+      </c>
+      <c r="L1015" s="0" t="n">
+        <f aca="false">RADIANS(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1016" s="0" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L1016" s="0" t="n">
+        <f aca="false">RADIANS(-45)</f>
+        <v>-0.785398163397448</v>
+      </c>
+    </row>
+    <row r="1017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1017" s="0" t="s">
+        <v>1014</v>
+      </c>
+      <c r="L1017" s="0" t="n">
+        <f aca="false">SUMX2MY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="1018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1018" s="0" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L1018" s="0" t="n">
+        <f aca="false">SUMX2MY2(A1:A3,A4:A6)</f>
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="1019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1019" s="0" t="s">
+        <v>1016</v>
+      </c>
+      <c r="L1019" s="0" t="e">
+        <f aca="false">SUMX2MY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1020" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L1020" s="0" t="e">
+        <f aca="false">SUMX2MY2(A1:A3,H1:H3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1021" s="0" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L1021" s="0" t="n">
+        <f aca="false">SUMX2PY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1022" s="0" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L1022" s="0" t="n">
+        <f aca="false">SUMX2PY2(A1:A3,A4:A6)</f>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1023" s="0" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L1023" s="0" t="e">
+        <f aca="false">SUMX2PY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1024" s="0" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L1024" s="0" t="n">
+        <f aca="false">SUMX2PY2(F1:F2,A1:A2)</f>
+        <v>50005</v>
+      </c>
+    </row>
+    <row r="1025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1025" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="L1025" s="0" t="n">
+        <f aca="false">SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1026" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L1026" s="0" t="n">
+        <f aca="false">SUMXMY2(A1:A3,A4:A6)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1027" s="0" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L1027" s="0" t="e">
+        <f aca="false">SUMXMY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1028" s="0" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L1028" s="0" t="n">
+        <f aca="false">SUMXMY2(F1:F2,A1:A2)</f>
+        <v>49005</v>
+      </c>
+    </row>
+    <row r="1029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1029" s="0" t="s">
+        <v>1026</v>
+      </c>
+      <c r="L1029" s="0" t="n">
+        <f aca="false">COUNTBLANK(D1:D6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1030" s="0" t="s">
+        <v>1027</v>
+      </c>
+      <c r="L1030" s="0" t="n">
+        <f aca="false">COUNTBLANK(A1:A6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1031" s="0" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L1031" s="0" t="n">
+        <f aca="false">COUNTBLANK(D3:D4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1032" s="0" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L1032" s="0" t="n">
+        <f aca="false">COUNTBLANK(J1:J4)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1033" s="0" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L1033" s="0" t="n">
+        <f aca="false">SUMIFS(A1:A6,B1:B6,"*a*")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1034" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L1034" s="0" t="n">
+        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",A1:A6,"&lt;5")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1035" s="0" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L1035" s="0" t="n">
+        <f aca="false">SUMIFS(C1:C6,A1:A6,"&gt;=3")</f>
+        <v>1000103.25</v>
+      </c>
+    </row>
+    <row r="1036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1036" s="0" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L1036" s="0" t="e">
+        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",B1:B3,"x")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1037" s="0" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L1037" s="0" t="n">
+        <f aca="false">SUMIFS(F1:F4,A1:A4,2)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1038" s="0" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L1038" s="0" t="n">
+        <f aca="false">SUMIFS(A1:A2,H1:H2,"#N/A")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1039" s="0" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L1039" s="0" t="n">
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1040" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L1040" s="0" t="n">
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2",C1:C6,"&lt;50")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1041" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L1041" s="0" t="n">
+        <f aca="false">COUNTIFS(B1:B6,"?????")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1042" s="0" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L1042" s="0" t="e">
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2",B1:B5,"a*")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1043" s="0" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L1043" s="0" t="n">
+        <f aca="false">COUNTIFS(D1:D6,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1044" s="0" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L1044" s="0" t="n">
+        <f aca="false">COUNTIFS(A1:A6,"&lt;&gt;3",A1:A6,"&lt;&gt;4")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1045" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="L1045" s="0" t="n">
+        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;2")</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="1046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1046" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L1046" s="0" t="n">
+        <f aca="false">AVERAGEIFS(C1:C6,A1:A6,"&lt;=3")</f>
+        <v>2.83333333333333</v>
+      </c>
+    </row>
+    <row r="1047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1047" s="0" t="s">
+        <v>1044</v>
+      </c>
+      <c r="L1047" s="0" t="e">
+        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1048" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="L1048" s="0" t="n">
+        <f aca="false">AVERAGEIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="1049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1049" s="0" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L1049" s="0" t="n">
+        <f aca="false">AVERAGEIF(A1:A6,"&gt;3")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1050" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L1050" s="0" t="n">
+        <f aca="false">AVERAGEIF(B1:B6,"*e*",A1:A6)</f>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="1051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1051" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="L1051" s="0" t="e">
+        <f aca="false">AVERAGEIF(A1:A6,"&gt;10")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1052" s="0" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L1052" s="0" t="n">
+        <f aca="false">AVERAGEIF(C1:C6,"&lt;&gt;0")</f>
+        <v>200022.35</v>
+      </c>
+    </row>
+    <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1053" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L1053" s="0" t="n">
+        <f aca="false">AVERAGEIF(F1:F4,"&gt;=200")</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="1054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1054" s="0" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L1054" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&lt;=4")</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1055" s="0" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L1055" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1056" s="0" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L1056" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1057" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L1057" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&gt;=2",A1:A6,"&lt;=3")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1058" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L1058" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&lt;=4")</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1059" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L1059" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1060" s="0" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L1060" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1061" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="L1061" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&gt;=3")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1062" s="0" t="s">
+        <v>1059</v>
+      </c>
+      <c r="L1062" s="0" t="n">
+        <f aca="false">MEDIAN(A1:A6)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1063" s="0" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L1063" s="0" t="n">
+        <f aca="false">MEDIAN(1,2,3)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1064" s="0" t="s">
+        <v>1061</v>
+      </c>
+      <c r="L1064" s="0" t="n">
+        <f aca="false">MEDIAN(C1:C6)</f>
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="1065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1065" s="0" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L1065" s="0" t="e">
+        <f aca="false">MEDIAN(B1:B3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1066" s="0" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L1066" s="0" t="e">
+        <f aca="false">MEDIAN(A1:A2,H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1067" s="0" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L1067" s="0" t="n">
+        <f aca="false">MEDIAN(A1:A5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1068" s="0" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L1068" s="0" t="n">
+        <f aca="false">MODE(1,2,2,3,3,3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1069" s="0" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L1069" s="0" t="e">
+        <f aca="false">MODE(A1:A6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1070" s="0" t="s">
+        <v>1067</v>
+      </c>
+      <c r="L1070" s="0" t="n">
+        <f aca="false">MODE(2,2,3,3)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1071" s="0" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L1071" s="0" t="n">
+        <f aca="false">MODE({1,2,2,3})</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1072" s="0" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L1072" s="0" t="n">
+        <f aca="false">_xlfn.MODE.SNGL(1,2,2,3,3,3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1073" s="0" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L1073" s="0" t="e">
+        <f aca="false">_xlfn.MODE.SNGL(A1:A6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1074" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L1074" s="0" t="n">
+        <f aca="false">_xlfn.MODE.SNGL(2,2,3,3)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1075" s="0" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L1075" s="0" t="n">
+        <f aca="false">_xlfn.MODE.SNGL(B1:B3,5,5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1076" s="0" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L1076" s="0" t="n">
+        <f aca="false">VAR(A1:A6)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1077" s="0" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L1077" s="0" t="e">
+        <f aca="false">VAR(5)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1078" s="0" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L1078" s="0" t="n">
+        <f aca="false">VAR(1,2)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1079" s="0" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L1079" s="0" t="e">
+        <f aca="false">VAR(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1080" s="0" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L1080" s="0" t="n">
+        <f aca="false">_xlfn.VAR.S(A1:A6)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1081" s="0" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L1081" s="0" t="n">
+        <f aca="false">_xlfn.VAR.S(C1:C4)</f>
+        <v>2390.39583333333</v>
+      </c>
+    </row>
+    <row r="1082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1082" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L1082" s="0" t="e">
+        <f aca="false">_xlfn.VAR.S(A1,H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1083" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L1083" s="0" t="e">
+        <f aca="false">_xlfn.VAR.S(A1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1084" s="0" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L1084" s="0" t="n">
+        <f aca="false">_xlfn.VAR.P(A1:A6)</f>
+        <v>2.91666666666667</v>
+      </c>
+    </row>
+    <row r="1085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1085" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L1085" s="0" t="n">
+        <f aca="false">_xlfn.VAR.P(5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1086" s="0" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L1086" s="0" t="n">
+        <f aca="false">_xlfn.VAR.P(C1:C4)</f>
+        <v>1792.796875</v>
+      </c>
+    </row>
+    <row r="1087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1087" s="0" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L1087" s="0" t="e">
+        <f aca="false">_xlfn.VAR.P(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1088" s="0" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L1088" s="0" t="n">
+        <f aca="false">VARP(A1:A6)</f>
+        <v>2.91666666666667</v>
+      </c>
+    </row>
+    <row r="1089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1089" s="0" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L1089" s="0" t="n">
+        <f aca="false">VARP(5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1090" s="0" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L1090" s="0" t="n">
+        <f aca="false">VARP(1,2,3,4)</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="1091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1091" s="0" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1091" s="0" t="e">
+        <f aca="false">VARP(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1092" s="0" t="s">
+        <v>1089</v>
+      </c>
+      <c r="L1092" s="0" t="n">
+        <f aca="false">STDEV(A1:A6)</f>
+        <v>1.87082869338697</v>
+      </c>
+    </row>
+    <row r="1093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1093" s="0" t="s">
+        <v>1090</v>
+      </c>
+      <c r="L1093" s="0" t="e">
+        <f aca="false">STDEV(5)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1094" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="L1094" s="0" t="n">
+        <f aca="false">STDEV(1,2)</f>
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="1095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1095" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L1095" s="0" t="e">
+        <f aca="false">STDEV(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1096" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="L1096" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.S(A1:A6)</f>
+        <v>1.87082869338697</v>
+      </c>
+    </row>
+    <row r="1097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1097" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L1097" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.S(C1:C4)</f>
+        <v>48.8916744787222</v>
+      </c>
+    </row>
+    <row r="1098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1098" s="0" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L1098" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.S(1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1099" s="0" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L1099" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.S(A1,H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1100" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L1100" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.P(A1:A6)</f>
+        <v>1.70782512765993</v>
+      </c>
+    </row>
+    <row r="1101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1101" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L1101" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.P(5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1102" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="L1102" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.P(C1:C4)</f>
+        <v>42.3414321321327</v>
+      </c>
+    </row>
+    <row r="1103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1103" s="0" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L1103" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.P(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1104" s="0" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L1104" s="0" t="n">
+        <f aca="false">STDEVP(A1:A6)</f>
+        <v>1.70782512765993</v>
+      </c>
+    </row>
+    <row r="1105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1105" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L1105" s="0" t="n">
+        <f aca="false">STDEVP(5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1106" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L1106" s="0" t="n">
+        <f aca="false">STDEVP(1,2,3,4)</f>
+        <v>1.1180339887499</v>
+      </c>
+    </row>
+    <row r="1107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1107" s="0" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L1107" s="0" t="e">
+        <f aca="false">STDEVP(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1108" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L1108" s="0" t="n">
+        <f aca="false">LARGE(A1:A6,2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1109" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L1109" s="0" t="e">
+        <f aca="false">LARGE(A1:A6,7)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1110" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L1110" s="0" t="n">
+        <f aca="false">LARGE(C1:C6,1)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="1111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1111" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="L1111" s="0" t="e">
+        <f aca="false">LARGE(A1:A6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1112" s="0" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L1112" s="0" t="n">
+        <f aca="false">LARGE(A1:A6,1.5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1113" s="0" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L1113" s="0" t="n">
+        <f aca="false">SMALL(A1:A6,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1114" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L1114" s="0" t="n">
+        <f aca="false">SMALL(C1:C6,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1115" s="0" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L1115" s="0" t="e">
+        <f aca="false">SMALL(B1:B6,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1116" s="0" t="s">
+        <v>1113</v>
+      </c>
+      <c r="L1116" s="0" t="n">
+        <f aca="false">SMALL(A1:A6,6)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1117" s="0" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L1117" s="0" t="n">
+        <f aca="false">RANK(3,A1:A6)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1118" s="0" t="s">
+        <v>1115</v>
+      </c>
+      <c r="L1118" s="0" t="n">
+        <f aca="false">RANK(3,A1:A6,1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1119" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L1119" s="0" t="e">
+        <f aca="false">RANK(9,A1:A6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1120" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="L1120" s="0" t="n">
+        <f aca="false">RANK(100,C1:C6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1121" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L1121" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(100,C1:C6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1122" s="0" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L1122" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(1,A1:A6,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1123" s="0" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L1123" s="0" t="e">
+        <f aca="false">_xlfn.RANK.EQ(9,A1:A6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1124" s="0" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L1124" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(0,C1:C6,1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1125" s="0" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L1125" s="0" t="n">
+        <f aca="false">_xlfn.RANK.AVG(3,A1:A6)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1126" s="0" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L1126" s="0" t="n">
+        <f aca="false">_xlfn.RANK.AVG(1,A1:A6,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1127" s="0" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L1127" s="0" t="e">
+        <f aca="false">_xlfn.RANK.AVG(9,A1:A6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1128" s="0" t="s">
+        <v>1125</v>
+      </c>
+      <c r="L1128" s="0" t="n">
+        <f aca="false">_xlfn.RANK.AVG(100,C1:C6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1129" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="L1129" s="0" t="n">
+        <f aca="false">PERCENTILE(A1:A6,0.5)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1130" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L1130" s="0" t="n">
+        <f aca="false">PERCENTILE(A1:A6,0.25)</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="1131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1131" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L1131" s="0" t="n">
+        <f aca="false">PERCENTILE(A1:A6,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1132" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L1132" s="0" t="e">
+        <f aca="false">PERCENTILE(A1:A6,1.5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1133" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L1133" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,0.9)</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="1134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1134" s="0" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L1134" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.INC(C1:C6,0.5)</f>
+        <v>6.875</v>
+      </c>
+    </row>
+    <row r="1135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1135" s="0" t="s">
+        <v>1132</v>
+      </c>
+      <c r="L1135" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,1)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1136" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="L1136" s="0" t="e">
+        <f aca="false">_xlfn.PERCENTILE.INC(B1:B3,0.5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1137" s="0" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L1137" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.5)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1138" s="0" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L1138" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.25)</f>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1139" s="0" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L1139" s="0" t="e">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1140" s="0" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L1140" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.8)</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="1141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1141" s="0" t="s">
+        <v>1138</v>
+      </c>
+      <c r="L1141" s="0" t="n">
+        <f aca="false">QUARTILE(A1:A6,1)</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="1142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1142" s="0" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L1142" s="0" t="n">
+        <f aca="false">QUARTILE(A1:A6,3)</f>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="1143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1143" s="0" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L1143" s="0" t="n">
+        <f aca="false">QUARTILE(A1:A6,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1144" s="0" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L1144" s="0" t="e">
+        <f aca="false">QUARTILE(A1:A6,5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1145" s="0" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L1145" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,2)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1146" s="0" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L1146" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.INC(C1:C6,1)</f>
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="1147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1147" s="0" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L1147" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,4)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1148" s="0" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L1148" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1149" s="0" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L1149" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,1)</f>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1150" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L1150" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,3)</f>
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="1151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1151" s="0" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L1151" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1152" s="0" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L1152" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1153" s="0" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L1153" s="0" t="n">
+        <f aca="false">PERCENTRANK(A1:A6,3)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="1154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1154" s="0" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L1154" s="0" t="n">
+        <f aca="false">PERCENTRANK(A1:A6,3.5)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1155" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L1155" s="0" t="e">
+        <f aca="false">PERCENTRANK(A1:A6,7)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1156" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L1156" s="0" t="n">
+        <f aca="false">PERCENTRANK(A1:A6,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1157" s="0" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L1157" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,2.5,2)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="1158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1158" s="0" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L1158" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1159" s="0" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L1159" s="0" t="e">
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1160" s="0" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L1160" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTRANK.INC(C1:C6,10.5)</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1161" s="0" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L1161" s="0" t="n">
+        <f aca="false">CORREL(A1:A4,F1:F4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1162" s="0" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L1162" s="0" t="n">
+        <f aca="false">CORREL(A1:A4,{4;3;2;1})</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="1163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1163" s="0" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L1163" s="0" t="e">
+        <f aca="false">CORREL(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1164" s="0" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L1164" s="0" t="e">
+        <f aca="false">CORREL(A1,F1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1165" s="0" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L1165" s="0" t="n">
+        <f aca="false">CORREL(A1:A6,C1:C6)</f>
+        <v>0.654676581102423</v>
+      </c>
+    </row>
+    <row r="1166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1166" s="0" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L1166" s="0" t="n">
+        <f aca="false">COVAR(A1:A4,F1:F4)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1167" s="0" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L1167" s="0" t="n">
+        <f aca="false">COVAR(A1:A6,C1:C6)</f>
+        <v>416671.9375</v>
+      </c>
+    </row>
+    <row r="1168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1168" s="0" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L1168" s="0" t="e">
+        <f aca="false">COVAR(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1169" s="0" t="s">
+        <v>1166</v>
+      </c>
+      <c r="L1169" s="0" t="e">
+        <f aca="false">COVAR(B1:B3,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1170" s="0" t="s">
+        <v>1167</v>
+      </c>
+      <c r="L1170" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A4,F1:F4)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1171" s="0" t="s">
+        <v>1168</v>
+      </c>
+      <c r="L1171" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A6,C1:C6)</f>
+        <v>416671.9375</v>
+      </c>
+    </row>
+    <row r="1172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1172" s="0" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L1172" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1173" s="0" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L1173" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.P(B1:B3,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1174" s="0" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L1174" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A4,F1:F4)</f>
+        <v>166.666666666667</v>
+      </c>
+    </row>
+    <row r="1175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1175" s="0" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L1175" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A6,C1:C6)</f>
+        <v>500006.325</v>
+      </c>
+    </row>
+    <row r="1176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1176" s="0" t="s">
+        <v>1173</v>
+      </c>
+      <c r="L1176" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1177" s="0" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L1177" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.S(A1,F1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1178" s="0" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L1178" s="0" t="n">
+        <f aca="false">SLOPE(F1:F4,A1:A4)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1179" s="0" t="s">
+        <v>1176</v>
+      </c>
+      <c r="L1179" s="0" t="n">
+        <f aca="false">SLOPE(C1:C6,A1:A6)</f>
+        <v>142858.95</v>
+      </c>
+    </row>
+    <row r="1180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1180" s="0" t="s">
+        <v>1177</v>
+      </c>
+      <c r="L1180" s="0" t="e">
+        <f aca="false">SLOPE(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1181" s="0" t="s">
+        <v>1178</v>
+      </c>
+      <c r="L1181" s="0" t="e">
+        <f aca="false">SLOPE(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1182" s="0" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L1182" s="0" t="n">
+        <f aca="false">INTERCEPT(F1:F4,A1:A4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1183" s="0" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L1183" s="0" t="n">
+        <f aca="false">INTERCEPT(C1:C6,A1:A6)</f>
+        <v>-333321.033333333</v>
+      </c>
+    </row>
+    <row r="1184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1184" s="0" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L1184" s="0" t="e">
+        <f aca="false">INTERCEPT(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1185" s="0" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L1185" s="0" t="e">
+        <f aca="false">INTERCEPT(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1186" s="0" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L1186" s="0" t="n">
+        <f aca="false">RSQ(F1:F4,A1:A4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1187" s="0" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L1187" s="0" t="n">
+        <f aca="false">RSQ(C1:C6,A1:A6)</f>
+        <v>0.428601425843957</v>
+      </c>
+    </row>
+    <row r="1188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1188" s="0" t="s">
+        <v>1185</v>
+      </c>
+      <c r="L1188" s="0" t="e">
+        <f aca="false">RSQ(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1189" s="0" t="s">
+        <v>1186</v>
+      </c>
+      <c r="L1189" s="0" t="e">
+        <f aca="false">RSQ(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1190" s="0" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L1190" s="0" t="n">
+        <f aca="false">FORECAST(5,F1:F4,A1:A4)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1191" s="0" t="s">
+        <v>1188</v>
+      </c>
+      <c r="L1191" s="0" t="n">
+        <f aca="false">FORECAST(7,C1:C6,A1:A6)</f>
+        <v>666691.616666667</v>
+      </c>
+    </row>
+    <row r="1192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1192" s="0" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1192" s="0" t="e">
+        <f aca="false">FORECAST(5,F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1193" s="0" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L1193" s="0" t="e">
+        <f aca="false">FORECAST(B1,F1:F4,A1:A4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1194" s="0" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L1194" s="0" t="n">
+        <f aca="false">_xlfn.FORECAST.LINEAR(10,F1:F4,A1:A4)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1195" s="0" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L1195" s="0" t="n">
+        <f aca="false">_xlfn.FORECAST.LINEAR(0,C1:C6,A1:A6)</f>
+        <v>-333321.033333333</v>
+      </c>
+    </row>
+    <row r="1196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1196" s="0" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L1196" s="0" t="e">
+        <f aca="false">_xlfn.FORECAST.LINEAR(5,F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1197" s="0" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L1197" s="0" t="n">
+        <f aca="false">_xlfn.FORECAST.LINEAR(2.5,F1:F4,A1:A4)</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1198" s="0" t="s">
+        <v>1195</v>
+      </c>
+      <c r="L1198" s="0" t="n">
+        <f aca="false">TREND(F1:F4,A1:A4,5)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1199" s="0" t="s">
+        <v>1196</v>
+      </c>
+      <c r="L1199" s="0" t="n">
+        <f aca="false">SUM(TREND(F1:F4,A1:A4,A5:A6))</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="1200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1200" s="0" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L1200" s="0" t="n">
+        <f aca="false">INDEX(TREND(F1:F4),2)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1201" s="0" t="s">
+        <v>1198</v>
+      </c>
+      <c r="L1201" s="0" t="n">
+        <f aca="false">TREND(F1:F4,A1:A4,5,FALSE())</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1202" s="0" t="s">
+        <v>1199</v>
+      </c>
+      <c r="L1202" s="0" t="n">
+        <f aca="false">TREND(A1:A4,F1:F4,250)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="1203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1203" s="0" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L1203" s="0" t="n">
+        <f aca="false">GEOMEAN(1,2,4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1204" s="0" t="s">
+        <v>1201</v>
+      </c>
+      <c r="L1204" s="0" t="n">
+        <f aca="false">GEOMEAN(A1:A6)</f>
+        <v>2.99379516552391</v>
+      </c>
+    </row>
+    <row r="1205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1205" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L1205" s="0" t="e">
+        <f aca="false">GEOMEAN(C1:C3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1206" s="0" t="s">
+        <v>1203</v>
+      </c>
+      <c r="L1206" s="0" t="e">
+        <f aca="false">GEOMEAN(B1:B2)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="1207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1207" s="0" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L1207" s="0" t="n">
+        <f aca="false">HARMEAN(1,2,4)</f>
+        <v>1.71428571428571</v>
+      </c>
+    </row>
+    <row r="1208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1208" s="0" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L1208" s="0" t="n">
+        <f aca="false">HARMEAN(A1:A3)</f>
+        <v>1.63636363636364</v>
+      </c>
+    </row>
+    <row r="1209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1209" s="0" t="s">
+        <v>1206</v>
+      </c>
+      <c r="L1209" s="0" t="e">
+        <f aca="false">HARMEAN(C1:C3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1210" s="0" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L1210" s="0" t="e">
+        <f aca="false">HARMEAN(B1:B2)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="1211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1211" s="0" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L1211" s="0" t="n">
+        <f aca="false">DEVSQ(A1:A6)</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="1212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1212" s="0" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L1212" s="0" t="n">
+        <f aca="false">DEVSQ(1,2,3)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1213" s="0" t="s">
+        <v>1210</v>
+      </c>
+      <c r="L1213" s="0" t="n">
+        <f aca="false">DEVSQ(C1:C4)</f>
+        <v>7171.1875</v>
+      </c>
+    </row>
+    <row r="1214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1214" s="0" t="s">
+        <v>1211</v>
+      </c>
+      <c r="L1214" s="0" t="e">
+        <f aca="false">DEVSQ(B1:B3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1215" s="0" t="s">
+        <v>1212</v>
+      </c>
+      <c r="L1215" s="0" t="n">
+        <f aca="false">AVEDEV(A1:A6)</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1216" s="0" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L1216" s="0" t="n">
+        <f aca="false">AVEDEV(1,2,3,4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1217" s="0" t="s">
+        <v>1214</v>
+      </c>
+      <c r="L1217" s="0" t="n">
+        <f aca="false">AVEDEV(C1:C4)</f>
+        <v>36.4375</v>
+      </c>
+    </row>
+    <row r="1218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1218" s="0" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L1218" s="0" t="e">
+        <f aca="false">AVEDEV(B1:B3)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="1219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1219" s="0" t="s">
+        <v>1216</v>
+      </c>
+      <c r="L1219" s="7" t="n">
+        <f aca="false">PMT(0.08/12,10,10000)</f>
+        <v>-1037.03208935915</v>
+      </c>
+    </row>
+    <row r="1220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1220" s="0" t="s">
+        <v>1217</v>
+      </c>
+      <c r="L1220" s="7" t="n">
+        <f aca="false">PMT(0,10,1000)</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1221" s="0" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L1221" s="7" t="n">
+        <f aca="false">PMT(0.05,5,1000,0,1)</f>
+        <v>-219.975998217398</v>
+      </c>
+    </row>
+    <row r="1222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1222" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="L1222" s="7" t="e">
+        <f aca="false">PMT(0.05,0,100)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="1223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1223" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="L1223" s="7" t="n">
+        <f aca="false">PMT(0.06,12,-5000,1000)</f>
+        <v>537.108117522654</v>
+      </c>
+    </row>
+    <row r="1224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1224" s="0" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L1224" s="7" t="n">
+        <f aca="false">FV(0.06/12,10,-200,-500,1)</f>
+        <v>2581.40337406014</v>
+      </c>
+    </row>
+    <row r="1225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1225" s="0" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L1225" s="7" t="n">
+        <f aca="false">FV(0,10,-100)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1226" s="0" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L1226" s="7" t="n">
+        <f aca="false">FV(0.05,5,-100,0,0)</f>
+        <v>552.563125000001</v>
+      </c>
+    </row>
+    <row r="1227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1227" s="0" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L1227" s="7" t="n">
+        <f aca="false">FV(0.1,2,0,-100)</f>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1228" s="0" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L1228" s="7" t="n">
+        <f aca="false">PV(0.08/12,240,500)</f>
+        <v>-59777.1458511878</v>
+      </c>
+    </row>
+    <row r="1229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1229" s="0" t="s">
+        <v>1226</v>
+      </c>
+      <c r="L1229" s="7" t="n">
+        <f aca="false">PV(0,5,-10)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1230" s="0" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L1230" s="7" t="n">
+        <f aca="false">PV(0.05,10,-100,0,1)</f>
+        <v>810.782167564406</v>
+      </c>
+    </row>
+    <row r="1231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1231" s="0" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L1231" s="7" t="n">
+        <f aca="false">PV(0.05,10,0,1000)</f>
+        <v>-613.913253540759</v>
+      </c>
+    </row>
+    <row r="1232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1232" s="0" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L1232" s="0" t="n">
+        <f aca="false">NPER(0.12/12,-100,-1000,10000)</f>
+        <v>60.0821228537617</v>
+      </c>
+    </row>
+    <row r="1233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1233" s="0" t="s">
+        <v>1230</v>
+      </c>
+      <c r="L1233" s="0" t="n">
+        <f aca="false">NPER(0,-100,1000)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1234" s="0" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L1234" s="0" t="n">
+        <f aca="false">NPER(0.05,-100,1000,0,1)</f>
+        <v>13.2532278981381</v>
+      </c>
+    </row>
+    <row r="1235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1235" s="0" t="s">
+        <v>1232</v>
+      </c>
+      <c r="L1235" s="0" t="e">
+        <f aca="false">NPER(0.01,0,100)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="1236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1236" s="0" t="s">
+        <v>1233</v>
+      </c>
+      <c r="L1236" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,1,36,8000)</f>
+        <v>-66.6666666666667</v>
+      </c>
+    </row>
+    <row r="1237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1237" s="0" t="s">
+        <v>1234</v>
+      </c>
+      <c r="L1237" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,3,36,8000)</f>
+        <v>-63.4621895664547</v>
+      </c>
+    </row>
+    <row r="1238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1238" s="0" t="s">
+        <v>1235</v>
+      </c>
+      <c r="L1238" s="7" t="n">
+        <f aca="false">IPMT(0.1,3,3,8000)</f>
+        <v>-292.447129909365</v>
+      </c>
+    </row>
+    <row r="1239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1239" s="0" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L1239" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,1,36,8000,0,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1240" s="0" t="s">
+        <v>1237</v>
+      </c>
+      <c r="L1240" s="7" t="e">
+        <f aca="false">IPMT(0.05,0,3,1000)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1241" s="0" t="s">
+        <v>1238</v>
+      </c>
+      <c r="L1241" s="7" t="n">
+        <f aca="false">IPMT(0.05,2,3,1000,0,1)</f>
+        <v>-32.5138778747026</v>
+      </c>
+    </row>
+    <row r="1242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1242" s="0" t="s">
+        <v>1239</v>
+      </c>
+      <c r="L1242" s="7" t="n">
+        <f aca="false">PPMT(0.1/12,1,24,2000)</f>
+        <v>-75.6231860083664</v>
+      </c>
+    </row>
+    <row r="1243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1243" s="0" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L1243" s="7" t="n">
+        <f aca="false">PPMT(0.08,10,10,200000)</f>
+        <v>-27598.0534624214</v>
+      </c>
+    </row>
+    <row r="1244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1244" s="0" t="s">
+        <v>1241</v>
+      </c>
+      <c r="L1244" s="7" t="n">
+        <f aca="false">PPMT(0.05,2,3,1000,0,1)</f>
+        <v>-317.208564631245</v>
+      </c>
+    </row>
+    <row r="1245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1245" s="0" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L1245" s="7" t="e">
+        <f aca="false">PPMT(0.05,4,3,1000)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1246" s="0" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L1246" s="7" t="n">
+        <f aca="false">NPV(0.1,-10000,3000,4200,6800)</f>
+        <v>1188.44341233522</v>
+      </c>
+    </row>
+    <row r="1247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1247" s="0" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L1247" s="7" t="n">
+        <f aca="false">NPV(0.1,A1:A3)</f>
+        <v>4.81592787377911</v>
+      </c>
+    </row>
+    <row r="1248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1248" s="0" t="s">
+        <v>1245</v>
+      </c>
+      <c r="L1248" s="7" t="e">
+        <f aca="false">NPV(-1,1,2)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="1249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1249" s="0" t="s">
+        <v>1246</v>
+      </c>
+      <c r="L1249" s="7" t="n">
+        <f aca="false">NPV(0.08,F1:F4)</f>
+        <v>796.221970077581</v>
+      </c>
+    </row>
+    <row r="1250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1250" s="0" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L1250" s="0" t="n">
+        <f aca="false">ROUND(IRR({-70000,12000,15000,18000,21000,26000}),6)</f>
+        <v>0.086631</v>
+      </c>
+    </row>
+    <row r="1251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1251" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L1251" s="0" t="n">
+        <f aca="false">ROUND(IRR({-100,110}),6)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1252" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="L1252" s="6" t="e">
+        <f aca="false">IRR({1,2,3})</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1253" s="0" t="s">
+        <v>1250</v>
+      </c>
+      <c r="L1253" s="0" t="n">
+        <f aca="false">ROUND(IRR({-1000,300,400,500},0.2),6)</f>
+        <v>0.088963</v>
+      </c>
+    </row>
+    <row r="1254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1254" s="0" t="s">
+        <v>1251</v>
+      </c>
+      <c r="L1254" s="0" t="n">
+        <f aca="false">ROUND(RATE(48,-200,8000),6)</f>
+        <v>0.007701</v>
+      </c>
+    </row>
+    <row r="1255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1255" s="0" t="s">
+        <v>1252</v>
+      </c>
+      <c r="L1255" s="0" t="n">
+        <f aca="false">ROUND(RATE(10,0,-100,200),6)</f>
+        <v>0.071773</v>
+      </c>
+    </row>
+    <row r="1256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1256" s="0" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L1256" s="6" t="e">
+        <f aca="false">RATE(0,-100,1000)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1257" s="0" t="s">
+        <v>1254</v>
+      </c>
+      <c r="L1257" s="0" t="n">
+        <f aca="false">ROUND(RATE(12,-100,1000),6)</f>
+        <v>0.029229</v>
+      </c>
+    </row>
+    <row r="1258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1258" s="0" t="s">
+        <v>1255</v>
+      </c>
+      <c r="L1258" s="7" t="n">
+        <f aca="false">SLN(30000,7500,10)</f>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="1259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1259" s="0" t="s">
+        <v>1256</v>
+      </c>
+      <c r="L1259" s="7" t="n">
+        <f aca="false">SLN(100,0,4)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1260" s="0" t="s">
+        <v>1257</v>
+      </c>
+      <c r="L1260" s="7" t="e">
+        <f aca="false">SLN(100,10,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1261" s="0" t="s">
+        <v>1258</v>
+      </c>
+      <c r="L1261" s="7" t="n">
+        <f aca="false">SLN(F1,0,4)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1262" s="0" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L1262" s="7" t="n">
+        <f aca="false">SYD(30000,7500,10,1)</f>
+        <v>4090.90909090909</v>
+      </c>
+    </row>
+    <row r="1263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1263" s="0" t="s">
+        <v>1260</v>
+      </c>
+      <c r="L1263" s="7" t="n">
+        <f aca="false">SYD(30000,7500,10,10)</f>
+        <v>409.090909090909</v>
+      </c>
+    </row>
+    <row r="1264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1264" s="0" t="s">
+        <v>1261</v>
+      </c>
+      <c r="L1264" s="7" t="n">
+        <f aca="false">SYD(100,0,4,5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1265" s="0" t="s">
+        <v>1262</v>
+      </c>
+      <c r="L1265" s="7" t="n">
+        <f aca="false">SYD(100,0,4,0)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1266" s="0" t="s">
+        <v>1263</v>
+      </c>
+      <c r="L1266" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,1,7)</f>
+        <v>186083.333333333</v>
+      </c>
+    </row>
+    <row r="1267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1267" s="0" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L1267" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,2,7)</f>
+        <v>259639.416666667</v>
+      </c>
+    </row>
+    <row r="1268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1268" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L1268" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,7,7)</f>
+        <v>15845.0984738481</v>
+      </c>
+    </row>
+    <row r="1269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1269" s="0" t="s">
+        <v>1266</v>
+      </c>
+      <c r="L1269" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,1)</f>
+        <v>319000</v>
+      </c>
+    </row>
+    <row r="1270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1270" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="L1270" s="7" t="n">
+        <f aca="false">DB(1000,100,5,6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1271" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L1271" s="7" t="n">
+        <f aca="false">DDB(2400,300,10*365,1)</f>
+        <v>1.31506849315065</v>
+      </c>
+    </row>
+    <row r="1272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1272" s="0" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L1272" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,1,2)</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="1273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1273" s="0" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L1273" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,2,2)</f>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1274" s="0" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L1274" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,10)</f>
+        <v>22.1225472000002</v>
+      </c>
+    </row>
+    <row r="1275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1275" s="0" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L1275" s="7" t="e">
+        <f aca="false">DDB(100,0,5,6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1276" s="0" t="s">
+        <v>1273</v>
+      </c>
+      <c r="L1276" s="6" t="n">
+        <f aca="false">EFFECT(0.0525,4)</f>
+        <v>0.0535426673707582</v>
+      </c>
+    </row>
+    <row r="1277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1277" s="0" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L1277" s="6" t="n">
+        <f aca="false">EFFECT(0.1,1)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1278" s="0" t="s">
+        <v>1275</v>
+      </c>
+      <c r="L1278" s="6" t="n">
+        <f aca="false">EFFECT(0,4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1279" s="0" t="s">
+        <v>1276</v>
+      </c>
+      <c r="L1279" s="6" t="e">
+        <f aca="false">EFFECT(0.1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1280" s="0" t="s">
+        <v>1277</v>
+      </c>
+      <c r="L1280" s="6" t="n">
+        <f aca="false">NOMINAL(0.053543,4)</f>
+        <v>0.052500319868356</v>
+      </c>
+    </row>
+    <row r="1281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1281" s="0" t="s">
+        <v>1278</v>
+      </c>
+      <c r="L1281" s="6" t="n">
+        <f aca="false">NOMINAL(0.1,1)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="1282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1282" s="0" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L1282" s="6" t="e">
+        <f aca="false">NOMINAL(0,4)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1283" s="0" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L1283" s="6" t="e">
+        <f aca="false">NOMINAL(0.1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1284" s="0" t="s">
+        <v>1281</v>
+      </c>
+      <c r="L1284" s="0" t="n">
+        <f aca="false">ROUND(MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12),6)</f>
+        <v>0.126094</v>
+      </c>
+    </row>
+    <row r="1285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1285" s="0" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L1285" s="6" t="e">
+        <f aca="false">MIRR({1,2,3},0.1,0.1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1286" s="0" t="s">
+        <v>1283</v>
+      </c>
+      <c r="L1286" s="0" t="n">
+        <f aca="false">ROUND(MIRR({-100,50,60},0.05,0.05),6)</f>
+        <v>0.06066</v>
+      </c>
+    </row>
+    <row r="1287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1287" s="0" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L1287" s="6" t="e">
+        <f aca="false">MIRR({-100,-50},0.1,0.1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1288" s="0" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L1288" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
+        <v>b</v>
+      </c>
+    </row>
+    <row r="1289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1289" s="0" t="s">
+        <v>1286</v>
+      </c>
+      <c r="L1289" s="0" t="n">
+        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1290" s="0" t="s">
+        <v>1287</v>
+      </c>
+      <c r="L1290" s="0" t="e">
+        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1291" s="0" t="s">
+        <v>1288</v>
+      </c>
+      <c r="L1291" s="0" t="n">
+        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1292" s="0" t="s">
+        <v>1289</v>
+      </c>
+      <c r="L1292" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1,"x")</f>
+        <v>x</v>
+      </c>
+    </row>
+    <row r="1293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1293" s="0" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L1293" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
+        <v>b</v>
+      </c>
+    </row>
+    <row r="1294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1294" s="0" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L1294" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
+        <v>z</v>
+      </c>
+    </row>
+    <row r="1295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1295" s="0" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L1295" s="0" t="e">
+        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1296" s="0" t="s">
+        <v>1293</v>
+      </c>
+      <c r="L1296" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1297" s="0" t="s">
+        <v>1294</v>
+      </c>
+      <c r="L1297" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
+        <v>three</v>
+      </c>
+    </row>
+    <row r="1298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1298" s="0" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L1298" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(H2,"x")</f>
+        <v>x</v>
+      </c>
+    </row>
+    <row r="1299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1299" s="0" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L1299" s="0" t="e">
+        <f aca="false">_xlfn.IFNA(H1,"x")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1300" s="0" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L1300" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(5,"x")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1301" s="0" t="s">
+        <v>1298</v>
+      </c>
+      <c r="L1301" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1302" s="0" t="s">
+        <v>1299</v>
+      </c>
+      <c r="L1302" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1303" s="0" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L1303" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1304" s="0" t="s">
+        <v>1301</v>
+      </c>
+      <c r="L1304" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1305" s="0" t="s">
+        <v>1302</v>
+      </c>
+      <c r="L1305" s="1" t="b">
+        <f aca="false">_xlfn.XOR(1,0,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1306" s="0" t="s">
+        <v>1303</v>
+      </c>
+      <c r="L1306" s="1" t="e">
+        <f aca="false">_xlfn.XOR(H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1307" s="0" t="s">
+        <v>1304</v>
+      </c>
+      <c r="L1307" s="1" t="b">
+        <f aca="false">ISLOGICAL(TRUE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1308" s="0" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L1308" s="1" t="b">
+        <f aca="false">ISLOGICAL(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1309" s="0" t="s">
+        <v>1306</v>
+      </c>
+      <c r="L1309" s="1" t="b">
+        <f aca="false">ISLOGICAL("TRUE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1310" s="0" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L1310" s="1" t="b">
+        <f aca="false">ISLOGICAL(1=1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1311" s="0" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L1311" s="1" t="b">
+        <f aca="false">ISEVEN(2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1312" s="0" t="s">
+        <v>1309</v>
+      </c>
+      <c r="L1312" s="1" t="b">
+        <f aca="false">ISEVEN(3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1313" s="0" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L1313" s="1" t="b">
+        <f aca="false">ISEVEN(-2.9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1314" s="0" t="s">
+        <v>1311</v>
+      </c>
+      <c r="L1314" s="1" t="e">
+        <f aca="false">ISEVEN("a")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1315" s="0" t="s">
+        <v>1312</v>
+      </c>
+      <c r="L1315" s="1" t="b">
+        <f aca="false">ISEVEN(A2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1316" s="0" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L1316" s="1" t="b">
+        <f aca="false">ISODD(2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1317" s="0" t="s">
+        <v>1314</v>
+      </c>
+      <c r="L1317" s="1" t="b">
+        <f aca="false">ISODD(3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1318" s="0" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L1318" s="1" t="b">
+        <f aca="false">ISODD(-3.5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1319" s="0" t="s">
+        <v>1316</v>
+      </c>
+      <c r="L1319" s="1" t="e">
+        <f aca="false">ISODD("a")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1320" s="0" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L1320" s="1" t="b">
+        <f aca="false">ISODD(A1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1321" s="0" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L1321" s="0" t="n">
+        <f aca="false">N(5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1322" s="0" t="s">
+        <v>1319</v>
+      </c>
+      <c r="L1322" s="0" t="n">
+        <f aca="false">N("a")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1323" s="0" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L1323" s="0" t="n">
+        <f aca="false">N(TRUE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1324" s="0" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L1324" s="0" t="e">
+        <f aca="false">N(H1)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1325" s="0" t="s">
+        <v>1322</v>
+      </c>
+      <c r="L1325" s="0" t="n">
+        <f aca="false">N(B1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1326" s="0" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L1326" s="0" t="n">
+        <f aca="false">N(A3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1327" s="0" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L1327" s="0" t="str">
+        <f aca="false">T("a")</f>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1328" s="0" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L1328" s="0" t="str">
+        <f aca="false">T(5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1329" s="0" t="s">
+        <v>1326</v>
+      </c>
+      <c r="L1329" s="0" t="str">
+        <f aca="false">T(B1)</f>
+        <v>apple</v>
+      </c>
+    </row>
+    <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1330" s="0" t="s">
+        <v>1327</v>
+      </c>
+      <c r="L1330" s="0" t="e">
+        <f aca="false">T(H2)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1331" s="0" t="s">
+        <v>1328</v>
+      </c>
+      <c r="L1331" s="0" t="str">
+        <f aca="false">T(TRUE())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1332" s="0" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L1332" s="0" t="n">
+        <f aca="false">TYPE(1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1333" s="0" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L1333" s="0" t="n">
+        <f aca="false">TYPE("a")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1334" s="0" t="s">
+        <v>1331</v>
+      </c>
+      <c r="L1334" s="0" t="n">
+        <f aca="false">TYPE(TRUE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1335" s="0" t="s">
+        <v>1332</v>
+      </c>
+      <c r="L1335" s="0" t="n">
+        <f aca="false">TYPE(H1)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1336" s="0" t="s">
+        <v>1333</v>
+      </c>
+      <c r="L1336" s="0" t="n">
+        <f aca="false">TYPE({1,2})</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1337" s="0" t="s">
+        <v>1334</v>
+      </c>
+      <c r="L1337" s="0" t="e">
+        <f aca="false">TYPE(A1:A2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1338" s="0" t="s">
+        <v>1335</v>
+      </c>
+      <c r="L1338" s="0" t="n">
+        <f aca="false">TYPE(A1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1339" s="0" t="s">
+        <v>1336</v>
+      </c>
+      <c r="L1339" s="0" t="n">
+        <f aca="false">TYPE(B1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1340" s="0" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L1340" s="0" t="n">
+        <f aca="true">CELL("row",A5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1341" s="0" t="s">
+        <v>1338</v>
+      </c>
+      <c r="L1341" s="0" t="n">
+        <f aca="true">CELL("col",C1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1342" s="0" t="s">
+        <v>1339</v>
+      </c>
+      <c r="L1342" s="0" t="str">
+        <f aca="true">CELL("address",B2)</f>
+        <v>$B$2</v>
+      </c>
+    </row>
+    <row r="1343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1343" s="0" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L1343" s="0" t="n">
+        <f aca="true">CELL("contents",A3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1344" s="0" t="s">
+        <v>1341</v>
+      </c>
+      <c r="L1344" s="0" t="str">
+        <f aca="true">CELL("type",B1)</f>
+        <v>l</v>
+      </c>
+    </row>
+    <row r="1345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1345" s="0" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L1345" s="0" t="str">
+        <f aca="true">CELL("type",A1)</f>
+        <v>v</v>
+      </c>
+    </row>
+    <row r="1346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1346" s="0" t="s">
+        <v>1343</v>
+      </c>
+      <c r="L1346" s="0" t="str">
+        <f aca="true">CELL("type",J9)</f>
+        <v>b</v>
+      </c>
+    </row>
+    <row r="1347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1347" s="0" t="s">
+        <v>1344</v>
+      </c>
+      <c r="L1347" s="1" t="b">
+        <f aca="false">ISERR(H1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1348" s="0" t="s">
+        <v>1345</v>
+      </c>
+      <c r="L1348" s="1" t="b">
+        <f aca="false">ISERR(H2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1349" s="0" t="s">
+        <v>1346</v>
+      </c>
+      <c r="L1349" s="1" t="b">
+        <f aca="false">ISERR(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1350" s="0" t="s">
+        <v>1347</v>
+      </c>
+      <c r="L1350" s="1" t="b">
+        <f aca="false">ISERR(1/0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1351" s="0" t="s">
+        <v>1348</v>
+      </c>
+      <c r="L1351" s="1" t="b">
+        <f aca="false">ISNONTEXT(1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1352" s="0" t="s">
+        <v>1349</v>
+      </c>
+      <c r="L1352" s="1" t="b">
+        <f aca="false">ISNONTEXT("a")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1353" s="0" t="s">
+        <v>1350</v>
+      </c>
+      <c r="L1353" s="1" t="b">
+        <f aca="false">ISNONTEXT(J9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1354" s="0" t="s">
+        <v>1351</v>
+      </c>
+      <c r="L1354" s="1" t="b">
+        <f aca="false">ISNONTEXT(H1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1355" s="0" t="s">
+        <v>1352</v>
+      </c>
+      <c r="L1355" s="1" t="b">
+        <f aca="false">ISREF(A1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1356" s="0" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L1356" s="1" t="b">
+        <f aca="false">ISREF(1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1357" s="0" t="s">
+        <v>1354</v>
+      </c>
+      <c r="L1357" s="1" t="b">
+        <f aca="false">ISREF(A1:B2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1358" s="0" t="s">
+        <v>1355</v>
+      </c>
+      <c r="L1358" s="1" t="b">
+        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1359" s="0" t="s">
+        <v>1356</v>
+      </c>
+      <c r="L1359" s="1" t="b">
+        <f aca="false">ISREF("A1")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1360" s="0" t="s">
+        <v>1357</v>
+      </c>
+      <c r="L1360" s="0" t="n">
+        <f aca="false">SEARCH("an","banana")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1361" s="0" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L1361" s="0" t="n">
+        <f aca="false">SEARCH("AN","banana",3)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1362" s="0" t="s">
+        <v>1359</v>
+      </c>
+      <c r="L1362" s="0" t="n">
+        <f aca="false">SEARCH("b?n","banana")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1363" s="0" t="s">
+        <v>1360</v>
+      </c>
+      <c r="L1363" s="0" t="e">
+        <f aca="false">SEARCH("z","banana")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1364" s="0" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L1364" s="0" t="n">
+        <f aca="false">SEARCH("a*a","banana")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1365" s="0" t="s">
+        <v>1362</v>
+      </c>
+      <c r="L1365" s="0" t="n">
+        <f aca="false">SEARCH("~?","what?")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1366" s="0" t="s">
+        <v>1363</v>
+      </c>
+      <c r="L1366" s="0" t="str">
+        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
+        <v>abXYef</v>
+      </c>
+    </row>
+    <row r="1367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1367" s="0" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L1367" s="0" t="str">
+        <f aca="false">REPLACE("abc",5,1,"Z")</f>
+        <v>abcZ</v>
+      </c>
+    </row>
+    <row r="1368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1368" s="0" t="s">
+        <v>1365</v>
+      </c>
+      <c r="L1368" s="0" t="str">
+        <f aca="false">REPLACE("abc",1,0,"Z")</f>
+        <v>Zabc</v>
+      </c>
+    </row>
+    <row r="1369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1369" s="0" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L1369" s="0" t="e">
+        <f aca="false">REPLACE("abc",0,1,"Z")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1370" s="0" t="s">
+        <v>1367</v>
+      </c>
+      <c r="L1370" s="0" t="str">
+        <f aca="false">REPLACE(B1,1,1,"A")</f>
+        <v>Apple</v>
+      </c>
+    </row>
+    <row r="1371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1371" s="0" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L1371" s="0" t="str">
+        <f aca="false">REPT("ab",3)</f>
+        <v>ababab</v>
+      </c>
+    </row>
+    <row r="1372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1372" s="0" t="s">
+        <v>1369</v>
+      </c>
+      <c r="L1372" s="0" t="str">
+        <f aca="false">REPT("x",0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1373" s="0" t="s">
+        <v>1370</v>
+      </c>
+      <c r="L1373" s="0" t="e">
+        <f aca="false">REPT("x",-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1374" s="0" t="s">
+        <v>1371</v>
+      </c>
+      <c r="L1374" s="0" t="str">
+        <f aca="false">REPT(A1,3)</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1375" s="0" t="s">
+        <v>1372</v>
+      </c>
+      <c r="L1375" s="0" t="str">
+        <f aca="false">REPT("-",2.9)</f>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1376" s="0" t="s">
+        <v>1373</v>
+      </c>
+      <c r="L1376" s="0" t="str">
+        <f aca="false">PROPER("hello world")</f>
+        <v>Hello World</v>
+      </c>
+    </row>
+    <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1377" s="0" t="s">
+        <v>1374</v>
+      </c>
+      <c r="L1377" s="0" t="str">
+        <f aca="false">PROPER("o'neil mc-donald")</f>
+        <v>O'Neil Mc-Donald</v>
+      </c>
+    </row>
+    <row r="1378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1378" s="0" t="s">
+        <v>1375</v>
+      </c>
+      <c r="L1378" s="0" t="str">
+        <f aca="false">PROPER("2nd place")</f>
+        <v>2Nd Place</v>
+      </c>
+    </row>
+    <row r="1379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1379" s="0" t="s">
+        <v>1376</v>
+      </c>
+      <c r="L1379" s="0" t="str">
+        <f aca="false">PROPER(B1)</f>
+        <v>Apple</v>
+      </c>
+    </row>
+    <row r="1380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1380" s="0" t="s">
+        <v>1377</v>
+      </c>
+      <c r="L1380" s="0" t="str">
+        <f aca="false">PROPER("ÀB cD")</f>
+        <v>Àb Cd</v>
+      </c>
+    </row>
+    <row r="1381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1381" s="0" t="s">
+        <v>1378</v>
+      </c>
+      <c r="L1381" s="0" t="str">
+        <f aca="false">CHAR(65)</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1382" s="0" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L1382" s="0" t="str">
+        <f aca="false">CHAR(97)</f>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="1383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1383" s="0" t="s">
+        <v>1380</v>
+      </c>
+      <c r="L1383" s="0" t="str">
+        <f aca="false">CHAR(0)</f>
+        <v>_x0000_</v>
+      </c>
+    </row>
+    <row r="1384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1384" s="0" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L1384" s="0" t="e">
+        <f aca="false">CHAR(256)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1385" s="0" t="s">
+        <v>1382</v>
+      </c>
+      <c r="L1385" s="0" t="str">
+        <f aca="false">CHAR(169)</f>
+        <v>�</v>
+      </c>
+    </row>
+    <row r="1386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1386" s="0" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L1386" s="0" t="str">
+        <f aca="false">CHAR(233)</f>
+        <v>�</v>
+      </c>
+    </row>
+    <row r="1387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1387" s="0" t="s">
+        <v>1384</v>
+      </c>
+      <c r="L1387" s="0" t="n">
+        <f aca="false">CODE("A")</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1388" s="0" t="s">
+        <v>1385</v>
+      </c>
+      <c r="L1388" s="0" t="n">
+        <f aca="false">CODE("apple")</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1389" s="0" t="s">
+        <v>1386</v>
+      </c>
+      <c r="L1389" s="0" t="n">
+        <f aca="false">CODE("")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1390" s="0" t="s">
+        <v>1387</v>
+      </c>
+      <c r="L1390" s="0" t="n">
+        <f aca="false">CODE("é")</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1391" s="0" t="s">
+        <v>1388</v>
+      </c>
+      <c r="L1391" s="0" t="n">
+        <f aca="false">CODE(B1)</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1392" s="0" t="s">
+        <v>1389</v>
+      </c>
+      <c r="L1392" s="0" t="n">
+        <f aca="false">_xlfn.UNICODE("A")</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1393" s="0" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L1393" s="0" t="n">
+        <f aca="false">_xlfn.UNICODE("€")</f>
+        <v>8364</v>
+      </c>
+    </row>
+    <row r="1394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1394" s="0" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L1394" s="0" t="e">
+        <f aca="false">_xlfn.UNICODE("")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1395" s="0" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L1395" s="0" t="n">
+        <f aca="false">_xlfn.UNICODE(B2)</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1396" s="0" t="s">
+        <v>1393</v>
+      </c>
+      <c r="L1396" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(65)</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="1397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1397" s="0" t="s">
+        <v>1394</v>
+      </c>
+      <c r="L1397" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(8364)</f>
+        <v>€</v>
+      </c>
+    </row>
+    <row r="1398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1398" s="0" t="s">
+        <v>1395</v>
+      </c>
+      <c r="L1398" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(0)</f>
+        <v>_x0000_</v>
+      </c>
+    </row>
+    <row r="1399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1399" s="0" t="s">
+        <v>1396</v>
+      </c>
+      <c r="L1399" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(97)</f>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="1400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1400" s="0" t="s">
+        <v>1397</v>
+      </c>
+      <c r="L1400" s="0" t="str">
+        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
+        <v>ab</v>
+      </c>
+    </row>
+    <row r="1401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1401" s="0" t="s">
+        <v>1398</v>
+      </c>
+      <c r="L1401" s="0" t="str">
+        <f aca="false">CLEAN(B1)</f>
+        <v>apple</v>
+      </c>
+    </row>
+    <row r="1402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1402" s="0" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L1402" s="0" t="str">
+        <f aca="false">CLEAN("  x ")</f>
+        <v>  x </v>
+      </c>
+    </row>
+    <row r="1403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1403" s="0" t="s">
+        <v>1400</v>
+      </c>
+      <c r="L1403" s="0" t="str">
+        <f aca="false">CLEAN(A1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1404" s="0" t="s">
+        <v>1401</v>
+      </c>
+      <c r="L1404" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1405" s="0" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L1405" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
+        <v>1234.5</v>
+      </c>
+    </row>
+    <row r="1406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1406" s="0" t="s">
+        <v>1403</v>
+      </c>
+      <c r="L1406" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="1407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1407" s="0" t="s">
+        <v>1404</v>
+      </c>
+      <c r="L1407" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1408" s="0" t="s">
+        <v>1405</v>
+      </c>
+      <c r="L1408" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1409" s="0" t="s">
+        <v>1406</v>
+      </c>
+      <c r="L1409" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="1410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1410" s="0" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L1410" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1411" s="0" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L1411" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1412" s="0" t="s">
+        <v>1409</v>
+      </c>
+      <c r="L1412" s="0" t="str">
+        <f aca="false">FIXED(1234.567,1)</f>
+        <v>1,234.6</v>
+      </c>
+    </row>
+    <row r="1413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1413" s="0" t="s">
+        <v>1410</v>
+      </c>
+      <c r="L1413" s="0" t="str">
+        <f aca="false">FIXED(1234.567,-1)</f>
+        <v>1,230</v>
+      </c>
+    </row>
+    <row r="1414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1414" s="0" t="s">
+        <v>1411</v>
+      </c>
+      <c r="L1414" s="0" t="str">
+        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
+        <v>-1234.57</v>
+      </c>
+    </row>
+    <row r="1415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1415" s="0" t="s">
+        <v>1412</v>
+      </c>
+      <c r="L1415" s="0" t="str">
+        <f aca="false">FIXED(0.5,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1416" s="0" t="s">
+        <v>1413</v>
+      </c>
+      <c r="L1416" s="0" t="str">
+        <f aca="false">FIXED(1234567)</f>
+        <v>1,234,567.00</v>
+      </c>
+    </row>
+    <row r="1417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1417" s="0" t="s">
+        <v>1414</v>
+      </c>
+      <c r="L1417" s="0" t="str">
+        <f aca="false">FIXED(A1)</f>
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="1418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1418" s="0" t="s">
+        <v>1415</v>
+      </c>
+      <c r="L1418" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
+        <v>apple,banana,cherry</v>
+      </c>
+    </row>
+    <row r="1419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1419" s="0" t="s">
+        <v>1416</v>
+      </c>
+      <c r="L1419" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
+        <v>1-2-3</v>
+      </c>
+    </row>
+    <row r="1420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1420" s="0" t="s">
+        <v>1417</v>
+      </c>
+      <c r="L1420" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
+        <v>a, b</v>
+      </c>
+    </row>
+    <row r="1421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1421" s="0" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L1421" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
+        <v>a,,b</v>
+      </c>
+    </row>
+    <row r="1422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1422" s="0" t="s">
+        <v>1419</v>
+      </c>
+      <c r="L1422" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
+        <v>applebanana!</v>
+      </c>
+    </row>
+    <row r="1423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1423" s="0" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L1423" s="0" t="e">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="1424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1424" s="0" t="s">
+        <v>1421</v>
+      </c>
+      <c r="L1424" s="0" t="n">
+        <f aca="false">DATEVALUE("2024-01-15")</f>
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="1425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1425" s="0" t="s">
+        <v>1422</v>
+      </c>
+      <c r="L1425" s="0" t="n">
+        <f aca="false">DATEVALUE("1/15/2024")</f>
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="1426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1426" s="0" t="s">
+        <v>1423</v>
+      </c>
+      <c r="L1426" s="0" t="n">
+        <f aca="false">DATEVALUE("2024-12-31")</f>
+        <v>45657</v>
+      </c>
+    </row>
+    <row r="1427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1427" s="0" t="s">
+        <v>1424</v>
+      </c>
+      <c r="L1427" s="0" t="e">
+        <f aca="false">DATEVALUE("abc")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1428" s="0" t="s">
+        <v>1425</v>
+      </c>
+      <c r="L1428" s="0" t="e">
+        <f aca="false">DATEVALUE(5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1429" s="0" t="s">
+        <v>1426</v>
+      </c>
+      <c r="L1429" s="0" t="n">
+        <f aca="false">TIMEVALUE("12:00")</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1430" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="L1430" s="0" t="n">
+        <f aca="false">TIMEVALUE("6:00 PM")</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="1431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1431" s="0" t="s">
+        <v>1428</v>
+      </c>
+      <c r="L1431" s="0" t="n">
+        <f aca="false">TIMEVALUE("18:30:30")</f>
+        <v>0.771180555555556</v>
+      </c>
+    </row>
+    <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1432" s="0" t="s">
+        <v>1429</v>
+      </c>
+      <c r="L1432" s="0" t="e">
+        <f aca="false">TIMEVALUE("xx")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1433" s="0" t="s">
+        <v>1430</v>
+      </c>
+      <c r="L1433" s="0" t="n">
+        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1434" s="0" t="s">
+        <v>1431</v>
+      </c>
+      <c r="L1434" s="8" t="n">
+        <f aca="false">TIME(12,0,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1435" s="0" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L1435" s="8" t="n">
+        <f aca="false">TIME(25,0,0)</f>
+        <v>0.0416666666666667</v>
+      </c>
+    </row>
+    <row r="1436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1436" s="0" t="s">
+        <v>1433</v>
+      </c>
+      <c r="L1436" s="8" t="n">
+        <f aca="false">TIME(0,90,0)</f>
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="1437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1437" s="0" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L1437" s="8" t="n">
+        <f aca="false">TIME(1,2,3)</f>
+        <v>0.0430902777777778</v>
+      </c>
+    </row>
+    <row r="1438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1438" s="0" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L1438" s="8" t="e">
+        <f aca="false">TIME(-1,0,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1439" s="0" t="s">
+        <v>1436</v>
+      </c>
+      <c r="L1439" s="0" t="n">
+        <f aca="false">HOUR(E3)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1440" s="0" t="s">
+        <v>1437</v>
+      </c>
+      <c r="L1440" s="0" t="n">
+        <f aca="false">HOUR(0.5)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1441" s="0" t="s">
+        <v>1438</v>
+      </c>
+      <c r="L1441" s="0" t="n">
+        <f aca="false">HOUR("18:30")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1442" s="0" t="s">
+        <v>1439</v>
+      </c>
+      <c r="L1442" s="0" t="n">
+        <f aca="false">HOUR(-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1443" s="0" t="s">
+        <v>1440</v>
+      </c>
+      <c r="L1443" s="0" t="n">
+        <f aca="false">MINUTE(E3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1444" s="0" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1444" s="0" t="n">
+        <f aca="false">MINUTE("18:30:45")</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1445" s="0" t="s">
+        <v>1442</v>
+      </c>
+      <c r="L1445" s="0" t="n">
+        <f aca="false">MINUTE(0.7712)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1446" s="0" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L1446" s="0" t="n">
+        <f aca="false">MINUTE(-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1447" s="0" t="s">
+        <v>1444</v>
+      </c>
+      <c r="L1447" s="0" t="n">
+        <f aca="false">SECOND("18:30:45")</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1448" s="0" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L1448" s="0" t="n">
+        <f aca="false">SECOND(0.5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1449" s="0" t="s">
+        <v>1446</v>
+      </c>
+      <c r="L1449" s="0" t="n">
+        <f aca="false">SECOND(TIME(1,2,3))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1450" s="0" t="s">
+        <v>1447</v>
+      </c>
+      <c r="L1450" s="0" t="n">
+        <f aca="false">SECOND(-1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1451" s="0" t="s">
+        <v>1448</v>
+      </c>
+      <c r="L1451" s="0" t="n">
+        <f aca="false">EDATE(E1,1)</f>
+        <v>45337</v>
+      </c>
+    </row>
+    <row r="1452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1452" s="0" t="s">
+        <v>1449</v>
+      </c>
+      <c r="L1452" s="0" t="n">
+        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
+        <v>45351</v>
+      </c>
+    </row>
+    <row r="1453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1453" s="0" t="s">
+        <v>1450</v>
+      </c>
+      <c r="L1453" s="0" t="n">
+        <f aca="false">EDATE(E1,-1)</f>
+        <v>45275</v>
+      </c>
+    </row>
+    <row r="1454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1454" s="0" t="s">
+        <v>1451</v>
+      </c>
+      <c r="L1454" s="0" t="n">
+        <f aca="false">EDATE(E1,0)</f>
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="1455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1455" s="0" t="s">
+        <v>1452</v>
+      </c>
+      <c r="L1455" s="0" t="n">
+        <f aca="false">EDATE(E1,12)</f>
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="1456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1456" s="0" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L1456" s="0" t="n">
+        <f aca="false">EOMONTH(E1,0)</f>
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="1457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1457" s="0" t="s">
+        <v>1454</v>
+      </c>
+      <c r="L1457" s="0" t="n">
+        <f aca="false">EOMONTH(E1,1)</f>
+        <v>45351</v>
+      </c>
+    </row>
+    <row r="1458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1458" s="0" t="s">
+        <v>1455</v>
+      </c>
+      <c r="L1458" s="0" t="n">
+        <f aca="false">EOMONTH(E1,-1)</f>
+        <v>45291</v>
+      </c>
+    </row>
+    <row r="1459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1459" s="0" t="s">
+        <v>1456</v>
+      </c>
+      <c r="L1459" s="0" t="n">
+        <f aca="false">EOMONTH(E2,2)</f>
+        <v>45716</v>
+      </c>
+    </row>
+    <row r="1460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1460" s="0" t="s">
+        <v>1457</v>
+      </c>
+      <c r="L1460" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1461" s="0" t="s">
+        <v>1458</v>
+      </c>
+      <c r="L1461" s="0" t="n">
+        <f aca="false">NETWORKDAYS(E1,E2)</f>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="1462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1462" s="0" t="s">
+        <v>1459</v>
+      </c>
+      <c r="L1462" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1463" s="0" t="s">
+        <v>1460</v>
+      </c>
+      <c r="L1463" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="1464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1464" s="0" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L1464" s="0" t="n">
+        <f aca="false">NETWORKDAYS(E1,E1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1465" s="0" t="s">
+        <v>1462</v>
+      </c>
+      <c r="L1465" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1466" s="0" t="s">
+        <v>1463</v>
+      </c>
+      <c r="L1466" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1467" s="0" t="s">
+        <v>1464</v>
+      </c>
+      <c r="L1467" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1468" s="0" t="s">
+        <v>1465</v>
+      </c>
+      <c r="L1468" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1469" s="0" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L1469" s="0" t="e">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1470" s="0" t="s">
+        <v>1467</v>
+      </c>
+      <c r="L1470" s="0" t="n">
+        <f aca="false">WORKDAY(E1,1)</f>
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="1471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1471" s="0" t="s">
+        <v>1468</v>
+      </c>
+      <c r="L1471" s="0" t="n">
+        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
+        <v>45313</v>
+      </c>
+    </row>
+    <row r="1472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1472" s="0" t="s">
+        <v>1469</v>
+      </c>
+      <c r="L1472" s="0" t="n">
+        <f aca="false">WORKDAY(E1,-1)</f>
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="1473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1473" s="0" t="s">
+        <v>1470</v>
+      </c>
+      <c r="L1473" s="0" t="n">
+        <f aca="false">WORKDAY(E1,5,E1+1)</f>
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="1474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1474" s="0" t="s">
+        <v>1471</v>
+      </c>
+      <c r="L1474" s="0" t="n">
+        <f aca="false">WORKDAY(E1,0)</f>
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="1475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1475" s="0" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L1475" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="1476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1476" s="0" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L1476" s="3" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
+        <v>45313</v>
+      </c>
+    </row>
+    <row r="1477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1477" s="0" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L1477" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
+        <v>45313</v>
+      </c>
+    </row>
+    <row r="1478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1478" s="0" t="s">
+        <v>1475</v>
+      </c>
+      <c r="L1478" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="1479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1479" s="0" t="s">
+        <v>1476</v>
+      </c>
+      <c r="L1479" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1480" s="0" t="s">
+        <v>1477</v>
+      </c>
+      <c r="L1480" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1481" s="0" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L1481" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1482" s="0" t="s">
+        <v>1479</v>
+      </c>
+      <c r="L1482" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1483" s="0" t="s">
+        <v>1480</v>
+      </c>
+      <c r="L1483" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1484" s="0" t="s">
+        <v>1481</v>
+      </c>
+      <c r="L1484" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1485" s="0" t="s">
+        <v>1482</v>
+      </c>
+      <c r="L1485" s="0" t="e">
+        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1486" s="0" t="s">
+        <v>1483</v>
+      </c>
+      <c r="L1486" s="0" t="e">
+        <f aca="false">DATEDIF(E1,E2,"X")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1487" s="0" t="s">
+        <v>1484</v>
+      </c>
+      <c r="L1487" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1488" s="0" t="s">
+        <v>1485</v>
+      </c>
+      <c r="L1488" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
+        <v>0.495890410958904</v>
+      </c>
+    </row>
+    <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1489" s="0" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L1489" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
+        <v>0.502777777777778</v>
+      </c>
+    </row>
+    <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1490" s="0" t="s">
+        <v>1487</v>
+      </c>
+      <c r="L1490" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
+        <v>0.495890410958904</v>
+      </c>
+    </row>
+    <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1491" s="0" t="s">
+        <v>1488</v>
+      </c>
+      <c r="L1491" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1492" s="0" t="s">
+        <v>1489</v>
+      </c>
+      <c r="L1492" s="0" t="n">
+        <f aca="false">YEARFRAC(E1,E2)</f>
+        <v>0.961111111111111</v>
+      </c>
+    </row>
+    <row r="1493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1493" s="0" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L1493" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
+        <v>3.99835796387521</v>
+      </c>
+    </row>
+    <row r="1494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1494" s="0" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L1494" s="0" t="n">
+        <f aca="false">YEARFRAC(E2,E1)</f>
+        <v>0.961111111111111</v>
+      </c>
+    </row>
+    <row r="1495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1495" s="0" t="s">
+        <v>1492</v>
+      </c>
+      <c r="L1495" s="0" t="e">
+        <f aca="false">YEARFRAC(E1,E2,5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1496" s="0" t="s">
+        <v>1493</v>
+      </c>
+      <c r="L1496" s="0" t="n">
+        <f aca="false">WEEKNUM(E1,1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1497" s="0" t="s">
+        <v>1494</v>
+      </c>
+      <c r="L1497" s="0" t="n">
+        <f aca="false">WEEKNUM(E1,2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1498" s="0" t="s">
+        <v>1495</v>
+      </c>
+      <c r="L1498" s="0" t="n">
+        <f aca="false">WEEKNUM(E2,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1499" s="0" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L1499" s="0" t="n">
+        <f aca="false">WEEKNUM(E2,21)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1500" s="0" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L1500" s="0" t="n">
+        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1501" s="0" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L1501" s="0" t="e">
+        <f aca="false">WEEKNUM(E1,3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1502" s="0" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L1502" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1503" s="0" t="s">
+        <v>1500</v>
+      </c>
+      <c r="L1503" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1504" s="0" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L1504" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1505" s="0" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L1505" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1506" s="0" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L1506" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1507" s="0" t="s">
+        <v>1504</v>
+      </c>
+      <c r="L1507" s="0" t="n">
+        <f aca="false">ROWS(A1:A6)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1508" s="0" t="s">
+        <v>1505</v>
+      </c>
+      <c r="L1508" s="0" t="n">
+        <f aca="false">ROWS(A1:C3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1509" s="0" t="s">
+        <v>1506</v>
+      </c>
+      <c r="L1509" s="0" t="n">
+        <f aca="false">ROWS(A:A)</f>
+        <v>1048576</v>
+      </c>
+    </row>
+    <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1510" s="0" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L1510" s="0" t="n">
+        <f aca="false">ROWS({1,2;3,4})</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1511" s="0" t="s">
+        <v>1508</v>
+      </c>
+      <c r="L1511" s="0" t="n">
+        <f aca="false">COLUMNS(A1:C3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1512" s="0" t="s">
+        <v>1509</v>
+      </c>
+      <c r="L1512" s="0" t="n">
+        <f aca="false">COLUMNS(A:C)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1513" s="0" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L1513" s="0" t="n">
+        <f aca="false">COLUMNS(1:1)</f>
+        <v>16384</v>
+      </c>
+    </row>
+    <row r="1514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1514" s="0" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L1514" s="0" t="n">
+        <f aca="false">COLUMNS({1,2;3,4})</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1515" s="0" t="s">
+        <v>1512</v>
+      </c>
+      <c r="L1515" s="0" t="str">
+        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1516" s="0" t="s">
+        <v>1513</v>
+      </c>
+      <c r="L1516" s="0" t="str">
+        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1517" s="0" t="s">
+        <v>1514</v>
+      </c>
+      <c r="L1517" s="0" t="e">
+        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1518" s="0" t="s">
+        <v>1515</v>
+      </c>
+      <c r="L1518" s="0" t="str">
+        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
+        <v>fig</v>
+      </c>
+    </row>
+    <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1519" s="0" t="s">
+        <v>1516</v>
+      </c>
+      <c r="L1519" s="0" t="str">
+        <f aca="false">LOOKUP(2,A1:B6)</f>
+        <v>banana</v>
+      </c>
+    </row>
+    <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1520" s="0" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L1520" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1521" s="0" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L1521" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1522" s="0" t="s">
+        <v>1519</v>
+      </c>
+      <c r="L1522" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1523" s="0" t="s">
+        <v>1520</v>
+      </c>
+      <c r="L1523" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1524" s="0" t="s">
+        <v>1521</v>
+      </c>
+      <c r="L1524" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1525" s="0" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L1525" s="0" t="e">
+        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1526" s="0" t="s">
+        <v>1523</v>
+      </c>
+      <c r="L1526" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1527" s="0" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L1527" s="0" t="e">
+        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1528" s="0" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L1528" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1529" s="0" t="s">
+        <v>1526</v>
+      </c>
+      <c r="L1529" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
+        <v>none</v>
+      </c>
+    </row>
+    <row r="1530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1530" s="0" t="s">
+        <v>1527</v>
+      </c>
+      <c r="L1530" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1531" s="0" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L1531" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1532" s="0" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L1532" s="0" t="n">
+        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1533" s="0" t="s">
+        <v>1530</v>
+      </c>
+      <c r="L1533" s="0" t="n">
+        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1534" s="0" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L1534" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1535" s="0" t="s">
+        <v>1532</v>
+      </c>
+      <c r="L1535" s="0" t="n">
+        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1536" s="0" t="s">
+        <v>1533</v>
+      </c>
+      <c r="L1536" s="0" t="n">
+        <f aca="true">INDIRECT("A1")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1537" s="0" t="s">
+        <v>1534</v>
+      </c>
+      <c r="L1537" s="0" t="n">
+        <f aca="true">INDIRECT("A"&amp;3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1538" s="0" t="s">
+        <v>1535</v>
+      </c>
+      <c r="L1538" s="0" t="n">
+        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1539" s="0" t="s">
+        <v>1536</v>
+      </c>
+      <c r="L1539" s="0" t="n">
+        <f aca="true">INDIRECT("Other!A1")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1540" s="0" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L1540" s="0" t="n">
+        <f aca="true">INDIRECT("R2C1",FALSE())</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1541" s="0" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L1541" s="0" t="e">
+        <f aca="true">INDIRECT("zzz")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1542" s="0" t="s">
+        <v>1539</v>
+      </c>
+      <c r="L1542" s="0" t="e">
+        <f aca="true">INDIRECT(B1)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="1543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1543" s="0" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L1543" s="0" t="str">
+        <f aca="true">OFFSET(A1,2,1)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1544" s="0" t="s">
+        <v>1541</v>
+      </c>
+      <c r="L1544" s="0" t="n">
+        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1545" s="0" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L1545" s="0" t="e">
+        <f aca="true">OFFSET(A1,-1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1546" s="0" t="s">
+        <v>1543</v>
+      </c>
+      <c r="L1546" s="0" t="n">
+        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1547" s="0" t="s">
+        <v>1544</v>
+      </c>
+      <c r="L1547" s="0" t="n">
+        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1548" s="0" t="s">
+        <v>1545</v>
+      </c>
+      <c r="L1548" s="0" t="e">
+        <f aca="true">OFFSET(A1,0,0,0,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1549" s="0" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L1549" s="0" t="str">
+        <f aca="false">ADDRESS(1,1)</f>
+        <v>$A$1</v>
+      </c>
+    </row>
+    <row r="1550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1550" s="0" t="s">
+        <v>1547</v>
+      </c>
+      <c r="L1550" s="0" t="str">
+        <f aca="false">ADDRESS(5,3,4)</f>
+        <v>C5</v>
+      </c>
+    </row>
+    <row r="1551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1551" s="0" t="s">
+        <v>1548</v>
+      </c>
+      <c r="L1551" s="0" t="str">
+        <f aca="false">ADDRESS(2,28,2)</f>
+        <v>AB$2</v>
+      </c>
+    </row>
+    <row r="1552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1552" s="0" t="s">
+        <v>1549</v>
+      </c>
+      <c r="L1552" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
+        <v>R1C1</v>
+      </c>
+    </row>
+    <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1553" s="0" t="s">
+        <v>1550</v>
+      </c>
+      <c r="L1553" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
+        <v>'My Sheet'.$A$1</v>
+      </c>
+    </row>
+    <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1554" s="0" t="s">
+        <v>1551</v>
+      </c>
+      <c r="L1554" s="0" t="e">
+        <f aca="false">ADDRESS(0,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1555" s="0" t="s">
+        <v>1552</v>
+      </c>
+      <c r="L1555" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,5)</f>
+        <v>$A$1</v>
+      </c>
+    </row>
+    <row r="1556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1556" s="0" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L1556" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1557" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L1557" s="0" t="n">
+        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1558" s="0" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L1558" s="0" t="n">
+        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1559" s="0" t="s">
+        <v>1556</v>
+      </c>
+      <c r="L1559" s="0" t="n">
+        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1560" s="0" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L1560" s="0" t="n">
+        <f aca="false">TRANSPOSE(A1:A3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1561" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="L1561" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y","click")</f>
+        <v>click</v>
+      </c>
+    </row>
+    <row r="1562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1562" s="0" t="s">
+        <v>1559</v>
+      </c>
+      <c r="L1562" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y")</f>
+        <v>http://x.y</v>
+      </c>
+    </row>
+    <row r="1563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1563" s="0" t="s">
+        <v>1560</v>
+      </c>
+      <c r="L1563" s="0" t="str">
+        <f aca="false">HYPERLINK(B1,"go")</f>
+        <v>go</v>
+      </c>
+    </row>
+    <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1564" s="0" t="s">
+        <v>1561</v>
+      </c>
+      <c r="L1564" s="0" t="n">
+        <f aca="false">HYPERLINK("u",A2)</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10735,7 +19169,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>860</v>
+        <v>1562</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/formulas/formula-suite.xlsx
+++ b/testdata/formulas/formula-suite.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="1577">
   <si>
     <t xml:space="preserve">apple</t>
   </si>
@@ -3087,6 +3087,48 @@
   </si>
   <si>
     <t xml:space="preserve">=SUMX2PY2(F1:F2,A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(9,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(109,A1:A6,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(1,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(2,A1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(103,A1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(4,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(105,C1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(6,A1:A4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(7,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(108,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(10,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(111,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(9,A1:A3,H1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUBTOTAL(9.9,A1:A3)</t>
   </si>
   <si>
     <t xml:space="preserve">=SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</t>
@@ -4950,7 +4992,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1564"/>
+  <dimension ref="A1:L1578"/>
   <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10178,7 +10220,7 @@
       </c>
       <c r="L568" s="4" t="n">
         <f aca="true">NOW()</f>
-        <v>46310.8757863259</v>
+        <v>46310.9071510982</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14290,8 +14332,8 @@
         <v>1022</v>
       </c>
       <c r="L1025" s="0" t="n">
-        <f aca="false">SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
-        <v>79</v>
+        <f aca="false">SUBTOTAL(9,A1:A6)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="1026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14299,17 +14341,17 @@
         <v>1023</v>
       </c>
       <c r="L1026" s="0" t="n">
-        <f aca="false">SUMXMY2(A1:A3,A4:A6)</f>
-        <v>27</v>
+        <f aca="false">SUBTOTAL(109,A1:A6,C1:C6)</f>
+        <v>1000132.75</v>
       </c>
     </row>
     <row r="1027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1027" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="L1027" s="0" t="e">
-        <f aca="false">SUMXMY2(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1027" s="0" t="n">
+        <f aca="false">SUBTOTAL(1,C1:C6)</f>
+        <v>166685.291666667</v>
       </c>
     </row>
     <row r="1028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14317,8 +14359,8 @@
         <v>1025</v>
       </c>
       <c r="L1028" s="0" t="n">
-        <f aca="false">SUMXMY2(F1:F2,A1:A2)</f>
-        <v>49005</v>
+        <f aca="false">SUBTOTAL(2,A1:B6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14326,8 +14368,8 @@
         <v>1026</v>
       </c>
       <c r="L1029" s="0" t="n">
-        <f aca="false">COUNTBLANK(D1:D6)</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(103,A1:B6)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14335,8 +14377,8 @@
         <v>1027</v>
       </c>
       <c r="L1030" s="0" t="n">
-        <f aca="false">COUNTBLANK(A1:A6)</f>
-        <v>0</v>
+        <f aca="false">SUBTOTAL(4,C1:C6)</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="1031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14344,8 +14386,8 @@
         <v>1028</v>
       </c>
       <c r="L1031" s="0" t="n">
-        <f aca="false">COUNTBLANK(D3:D4)</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(105,C1:C6)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="1032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14353,8 +14395,8 @@
         <v>1029</v>
       </c>
       <c r="L1032" s="0" t="n">
-        <f aca="false">COUNTBLANK(J1:J4)</f>
-        <v>4</v>
+        <f aca="false">SUBTOTAL(6,A1:A4)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="1033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14362,8 +14404,8 @@
         <v>1030</v>
       </c>
       <c r="L1033" s="0" t="n">
-        <f aca="false">SUMIFS(A1:A6,B1:B6,"*a*")</f>
-        <v>7</v>
+        <f aca="false">SUBTOTAL(7,A1:A6)</f>
+        <v>1.87082869338697</v>
       </c>
     </row>
     <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14371,8 +14413,8 @@
         <v>1031</v>
       </c>
       <c r="L1034" s="0" t="n">
-        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",A1:A6,"&lt;5")</f>
-        <v>7</v>
+        <f aca="false">SUBTOTAL(108,A1:A6)</f>
+        <v>1.70782512765993</v>
       </c>
     </row>
     <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14380,26 +14422,26 @@
         <v>1032</v>
       </c>
       <c r="L1035" s="0" t="n">
-        <f aca="false">SUMIFS(C1:C6,A1:A6,"&gt;=3")</f>
-        <v>1000103.25</v>
+        <f aca="false">SUBTOTAL(10,F1:F4)</f>
+        <v>16666.6666666667</v>
       </c>
     </row>
     <row r="1036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1036" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="L1036" s="0" t="e">
-        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",B1:B3,"x")</f>
-        <v>#VALUE!</v>
+      <c r="L1036" s="0" t="n">
+        <f aca="false">SUBTOTAL(111,F1:F4)</f>
+        <v>12500</v>
       </c>
     </row>
     <row r="1037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1037" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="L1037" s="0" t="n">
-        <f aca="false">SUMIFS(F1:F4,A1:A4,2)</f>
-        <v>200</v>
+      <c r="L1037" s="0" t="e">
+        <f aca="false">SUBTOTAL(9,A1:A3,H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14407,8 +14449,8 @@
         <v>1035</v>
       </c>
       <c r="L1038" s="0" t="n">
-        <f aca="false">SUMIFS(A1:A2,H1:H2,"#N/A")</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(9.9,A1:A3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14416,8 +14458,8 @@
         <v>1036</v>
       </c>
       <c r="L1039" s="0" t="n">
-        <f aca="false">COUNTIFS(A1:A6,"&gt;2")</f>
-        <v>4</v>
+        <f aca="false">SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>79</v>
       </c>
     </row>
     <row r="1040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14425,26 +14467,26 @@
         <v>1037</v>
       </c>
       <c r="L1040" s="0" t="n">
-        <f aca="false">COUNTIFS(A1:A6,"&gt;2",C1:C6,"&lt;50")</f>
-        <v>2</v>
+        <f aca="false">SUMXMY2(A1:A3,A4:A6)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="1041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1041" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="L1041" s="0" t="n">
-        <f aca="false">COUNTIFS(B1:B6,"?????")</f>
-        <v>1</v>
+      <c r="L1041" s="0" t="e">
+        <f aca="false">SUMXMY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1042" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="L1042" s="0" t="e">
-        <f aca="false">COUNTIFS(A1:A6,"&gt;2",B1:B5,"a*")</f>
-        <v>#VALUE!</v>
+      <c r="L1042" s="0" t="n">
+        <f aca="false">SUMXMY2(F1:F2,A1:A2)</f>
+        <v>49005</v>
       </c>
     </row>
     <row r="1043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14452,7 +14494,7 @@
         <v>1040</v>
       </c>
       <c r="L1043" s="0" t="n">
-        <f aca="false">COUNTIFS(D1:D6,"")</f>
+        <f aca="false">COUNTBLANK(D1:D6)</f>
         <v>2</v>
       </c>
     </row>
@@ -14461,8 +14503,8 @@
         <v>1041</v>
       </c>
       <c r="L1044" s="0" t="n">
-        <f aca="false">COUNTIFS(A1:A6,"&lt;&gt;3",A1:A6,"&lt;&gt;4")</f>
-        <v>4</v>
+        <f aca="false">COUNTBLANK(A1:A6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14470,8 +14512,8 @@
         <v>1042</v>
       </c>
       <c r="L1045" s="0" t="n">
-        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;2")</f>
-        <v>4.5</v>
+        <f aca="false">COUNTBLANK(D3:D4)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14479,17 +14521,17 @@
         <v>1043</v>
       </c>
       <c r="L1046" s="0" t="n">
-        <f aca="false">AVERAGEIFS(C1:C6,A1:A6,"&lt;=3")</f>
-        <v>2.83333333333333</v>
+        <f aca="false">COUNTBLANK(J1:J4)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1047" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="L1047" s="0" t="e">
-        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;10")</f>
-        <v>#DIV/0!</v>
+      <c r="L1047" s="0" t="n">
+        <f aca="false">SUMIFS(A1:A6,B1:B6,"*a*")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14497,8 +14539,8 @@
         <v>1045</v>
       </c>
       <c r="L1048" s="0" t="n">
-        <f aca="false">AVERAGEIFS(A1:A6,B1:B6,"*e*")</f>
-        <v>3.25</v>
+        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",A1:A6,"&lt;5")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14506,26 +14548,26 @@
         <v>1046</v>
       </c>
       <c r="L1049" s="0" t="n">
-        <f aca="false">AVERAGEIF(A1:A6,"&gt;3")</f>
-        <v>5</v>
+        <f aca="false">SUMIFS(C1:C6,A1:A6,"&gt;=3")</f>
+        <v>1000103.25</v>
       </c>
     </row>
     <row r="1050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1050" s="0" t="s">
         <v>1047</v>
       </c>
-      <c r="L1050" s="0" t="n">
-        <f aca="false">AVERAGEIF(B1:B6,"*e*",A1:A6)</f>
-        <v>3.25</v>
+      <c r="L1050" s="0" t="e">
+        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",B1:B3,"x")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1051" s="0" t="s">
         <v>1048</v>
       </c>
-      <c r="L1051" s="0" t="e">
-        <f aca="false">AVERAGEIF(A1:A6,"&gt;10")</f>
-        <v>#DIV/0!</v>
+      <c r="L1051" s="0" t="n">
+        <f aca="false">SUMIFS(F1:F4,A1:A4,2)</f>
+        <v>200</v>
       </c>
     </row>
     <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14533,8 +14575,8 @@
         <v>1049</v>
       </c>
       <c r="L1052" s="0" t="n">
-        <f aca="false">AVERAGEIF(C1:C6,"&lt;&gt;0")</f>
-        <v>200022.35</v>
+        <f aca="false">SUMIFS(A1:A2,H1:H2,"#N/A")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14542,8 +14584,8 @@
         <v>1050</v>
       </c>
       <c r="L1053" s="0" t="n">
-        <f aca="false">AVERAGEIF(F1:F4,"&gt;=200")</f>
-        <v>300</v>
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14551,8 +14593,8 @@
         <v>1051</v>
       </c>
       <c r="L1054" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&lt;=4")</f>
-        <v>100</v>
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2",C1:C6,"&lt;50")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14560,17 +14602,17 @@
         <v>1052</v>
       </c>
       <c r="L1055" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(A1:A6,B1:B6,"*e*")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(B1:B6,"?????")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1056" s="0" t="s">
         <v>1053</v>
       </c>
-      <c r="L1056" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(A1:A6,A1:A6,"&gt;10")</f>
-        <v>0</v>
+      <c r="L1056" s="0" t="e">
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2",B1:B5,"a*")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14578,8 +14620,8 @@
         <v>1054</v>
       </c>
       <c r="L1057" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&gt;=2",A1:A6,"&lt;=3")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(D1:D6,"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14587,8 +14629,8 @@
         <v>1055</v>
       </c>
       <c r="L1058" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&lt;=4")</f>
-        <v>-2</v>
+        <f aca="false">COUNTIFS(A1:A6,"&lt;&gt;3",A1:A6,"&lt;&gt;4")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14596,8 +14638,8 @@
         <v>1056</v>
       </c>
       <c r="L1059" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(A1:A6,B1:B6,"*e*")</f>
-        <v>1</v>
+        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;2")</f>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14605,17 +14647,17 @@
         <v>1057</v>
       </c>
       <c r="L1060" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(A1:A6,A1:A6,"&gt;10")</f>
-        <v>0</v>
+        <f aca="false">AVERAGEIFS(C1:C6,A1:A6,"&lt;=3")</f>
+        <v>2.83333333333333</v>
       </c>
     </row>
     <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1061" s="0" t="s">
         <v>1058</v>
       </c>
-      <c r="L1061" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&gt;=3")</f>
-        <v>0</v>
+      <c r="L1061" s="0" t="e">
+        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14623,8 +14665,8 @@
         <v>1059</v>
       </c>
       <c r="L1062" s="0" t="n">
-        <f aca="false">MEDIAN(A1:A6)</f>
-        <v>3.5</v>
+        <f aca="false">AVERAGEIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>3.25</v>
       </c>
     </row>
     <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14632,8 +14674,8 @@
         <v>1060</v>
       </c>
       <c r="L1063" s="0" t="n">
-        <f aca="false">MEDIAN(1,2,3)</f>
-        <v>2</v>
+        <f aca="false">AVERAGEIF(A1:A6,"&gt;3")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14641,8 +14683,8 @@
         <v>1061</v>
       </c>
       <c r="L1064" s="0" t="n">
-        <f aca="false">MEDIAN(C1:C6)</f>
-        <v>6.875</v>
+        <f aca="false">AVERAGEIF(B1:B6,"*e*",A1:A6)</f>
+        <v>3.25</v>
       </c>
     </row>
     <row r="1065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14650,17 +14692,17 @@
         <v>1062</v>
       </c>
       <c r="L1065" s="0" t="e">
-        <f aca="false">MEDIAN(B1:B3)</f>
-        <v>#VALUE!</v>
+        <f aca="false">AVERAGEIF(A1:A6,"&gt;10")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1066" s="0" t="s">
         <v>1063</v>
       </c>
-      <c r="L1066" s="0" t="e">
-        <f aca="false">MEDIAN(A1:A2,H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1066" s="0" t="n">
+        <f aca="false">AVERAGEIF(C1:C6,"&lt;&gt;0")</f>
+        <v>200022.35</v>
       </c>
     </row>
     <row r="1067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14668,8 +14710,8 @@
         <v>1064</v>
       </c>
       <c r="L1067" s="0" t="n">
-        <f aca="false">MEDIAN(A1:A5)</f>
-        <v>3</v>
+        <f aca="false">AVERAGEIF(F1:F4,"&gt;=200")</f>
+        <v>300</v>
       </c>
     </row>
     <row r="1068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14677,17 +14719,17 @@
         <v>1065</v>
       </c>
       <c r="L1068" s="0" t="n">
-        <f aca="false">MODE(1,2,2,3,3,3)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&lt;=4")</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1069" s="0" t="s">
         <v>1066</v>
       </c>
-      <c r="L1069" s="0" t="e">
-        <f aca="false">MODE(A1:A6)</f>
-        <v>#VALUE!</v>
+      <c r="L1069" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14695,8 +14737,8 @@
         <v>1067</v>
       </c>
       <c r="L1070" s="0" t="n">
-        <f aca="false">MODE(2,2,3,3)</f>
-        <v>2</v>
+        <f aca="false">_xlfn.MAXIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14704,8 +14746,8 @@
         <v>1068</v>
       </c>
       <c r="L1071" s="0" t="n">
-        <f aca="false">MODE({1,2,2,3})</f>
-        <v>2</v>
+        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&gt;=2",A1:A6,"&lt;=3")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14713,17 +14755,17 @@
         <v>1069</v>
       </c>
       <c r="L1072" s="0" t="n">
-        <f aca="false">_xlfn.MODE.SNGL(1,2,2,3,3,3)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&lt;=4")</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="1073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1073" s="0" t="s">
         <v>1070</v>
       </c>
-      <c r="L1073" s="0" t="e">
-        <f aca="false">_xlfn.MODE.SNGL(A1:A6)</f>
-        <v>#VALUE!</v>
+      <c r="L1073" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14731,8 +14773,8 @@
         <v>1071</v>
       </c>
       <c r="L1074" s="0" t="n">
-        <f aca="false">_xlfn.MODE.SNGL(2,2,3,3)</f>
-        <v>2</v>
+        <f aca="false">_xlfn.MINIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14740,8 +14782,8 @@
         <v>1072</v>
       </c>
       <c r="L1075" s="0" t="n">
-        <f aca="false">_xlfn.MODE.SNGL(B1:B3,5,5)</f>
-        <v>5</v>
+        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&gt;=3")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14749,7 +14791,7 @@
         <v>1073</v>
       </c>
       <c r="L1076" s="0" t="n">
-        <f aca="false">VAR(A1:A6)</f>
+        <f aca="false">MEDIAN(A1:A6)</f>
         <v>3.5</v>
       </c>
     </row>
@@ -14757,9 +14799,9 @@
       <c r="K1077" s="0" t="s">
         <v>1074</v>
       </c>
-      <c r="L1077" s="0" t="e">
-        <f aca="false">VAR(5)</f>
-        <v>#DIV/0!</v>
+      <c r="L1077" s="0" t="n">
+        <f aca="false">MEDIAN(1,2,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14767,8 +14809,8 @@
         <v>1075</v>
       </c>
       <c r="L1078" s="0" t="n">
-        <f aca="false">VAR(1,2)</f>
-        <v>0.5</v>
+        <f aca="false">MEDIAN(C1:C6)</f>
+        <v>6.875</v>
       </c>
     </row>
     <row r="1079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14776,17 +14818,17 @@
         <v>1076</v>
       </c>
       <c r="L1079" s="0" t="e">
-        <f aca="false">VAR(B1:B3)</f>
-        <v>#DIV/0!</v>
+        <f aca="false">MEDIAN(B1:B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1080" s="0" t="s">
         <v>1077</v>
       </c>
-      <c r="L1080" s="0" t="n">
-        <f aca="false">_xlfn.VAR.S(A1:A6)</f>
-        <v>3.5</v>
+      <c r="L1080" s="0" t="e">
+        <f aca="false">MEDIAN(A1:A2,H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14794,17 +14836,17 @@
         <v>1078</v>
       </c>
       <c r="L1081" s="0" t="n">
-        <f aca="false">_xlfn.VAR.S(C1:C4)</f>
-        <v>2390.39583333333</v>
+        <f aca="false">MEDIAN(A1:A5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1082" s="0" t="s">
         <v>1079</v>
       </c>
-      <c r="L1082" s="0" t="e">
-        <f aca="false">_xlfn.VAR.S(A1,H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1082" s="0" t="n">
+        <f aca="false">MODE(1,2,2,3,3,3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14812,8 +14854,8 @@
         <v>1080</v>
       </c>
       <c r="L1083" s="0" t="e">
-        <f aca="false">_xlfn.VAR.S(A1)</f>
-        <v>#DIV/0!</v>
+        <f aca="false">MODE(A1:A6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14821,8 +14863,8 @@
         <v>1081</v>
       </c>
       <c r="L1084" s="0" t="n">
-        <f aca="false">_xlfn.VAR.P(A1:A6)</f>
-        <v>2.91666666666667</v>
+        <f aca="false">MODE(2,2,3,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14830,8 +14872,8 @@
         <v>1082</v>
       </c>
       <c r="L1085" s="0" t="n">
-        <f aca="false">_xlfn.VAR.P(5)</f>
-        <v>0</v>
+        <f aca="false">MODE({1,2,2,3})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14839,8 +14881,8 @@
         <v>1083</v>
       </c>
       <c r="L1086" s="0" t="n">
-        <f aca="false">_xlfn.VAR.P(C1:C4)</f>
-        <v>1792.796875</v>
+        <f aca="false">_xlfn.MODE.SNGL(1,2,2,3,3,3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14848,8 +14890,8 @@
         <v>1084</v>
       </c>
       <c r="L1087" s="0" t="e">
-        <f aca="false">_xlfn.VAR.P(B1:B3)</f>
-        <v>#DIV/0!</v>
+        <f aca="false">_xlfn.MODE.SNGL(A1:A6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14857,8 +14899,8 @@
         <v>1085</v>
       </c>
       <c r="L1088" s="0" t="n">
-        <f aca="false">VARP(A1:A6)</f>
-        <v>2.91666666666667</v>
+        <f aca="false">_xlfn.MODE.SNGL(2,2,3,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14866,8 +14908,8 @@
         <v>1086</v>
       </c>
       <c r="L1089" s="0" t="n">
-        <f aca="false">VARP(5)</f>
-        <v>0</v>
+        <f aca="false">_xlfn.MODE.SNGL(B1:B3,5,5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14875,8 +14917,8 @@
         <v>1087</v>
       </c>
       <c r="L1090" s="0" t="n">
-        <f aca="false">VARP(1,2,3,4)</f>
-        <v>1.25</v>
+        <f aca="false">VAR(A1:A6)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14884,7 +14926,7 @@
         <v>1088</v>
       </c>
       <c r="L1091" s="0" t="e">
-        <f aca="false">VARP(B1:B3)</f>
+        <f aca="false">VAR(5)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14893,8 +14935,8 @@
         <v>1089</v>
       </c>
       <c r="L1092" s="0" t="n">
-        <f aca="false">STDEV(A1:A6)</f>
-        <v>1.87082869338697</v>
+        <f aca="false">VAR(1,2)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14902,7 +14944,7 @@
         <v>1090</v>
       </c>
       <c r="L1093" s="0" t="e">
-        <f aca="false">STDEV(5)</f>
+        <f aca="false">VAR(B1:B3)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -14911,53 +14953,53 @@
         <v>1091</v>
       </c>
       <c r="L1094" s="0" t="n">
-        <f aca="false">STDEV(1,2)</f>
-        <v>0.707106781186548</v>
+        <f aca="false">_xlfn.VAR.S(A1:A6)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1095" s="0" t="s">
         <v>1092</v>
       </c>
-      <c r="L1095" s="0" t="e">
-        <f aca="false">STDEV(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1095" s="0" t="n">
+        <f aca="false">_xlfn.VAR.S(C1:C4)</f>
+        <v>2390.39583333333</v>
       </c>
     </row>
     <row r="1096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1096" s="0" t="s">
         <v>1093</v>
       </c>
-      <c r="L1096" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.S(A1:A6)</f>
-        <v>1.87082869338697</v>
+      <c r="L1096" s="0" t="e">
+        <f aca="false">_xlfn.VAR.S(A1,H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1097" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="L1097" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.S(C1:C4)</f>
-        <v>48.8916744787222</v>
+      <c r="L1097" s="0" t="e">
+        <f aca="false">_xlfn.VAR.S(A1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1098" s="0" t="s">
         <v>1095</v>
       </c>
-      <c r="L1098" s="0" t="e">
-        <f aca="false">_xlfn.STDEV.S(1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1098" s="0" t="n">
+        <f aca="false">_xlfn.VAR.P(A1:A6)</f>
+        <v>2.91666666666667</v>
       </c>
     </row>
     <row r="1099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1099" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="L1099" s="0" t="e">
-        <f aca="false">_xlfn.STDEV.S(A1,H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1099" s="0" t="n">
+        <f aca="false">_xlfn.VAR.P(5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14965,17 +15007,17 @@
         <v>1097</v>
       </c>
       <c r="L1100" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.P(A1:A6)</f>
-        <v>1.70782512765993</v>
+        <f aca="false">_xlfn.VAR.P(C1:C4)</f>
+        <v>1792.796875</v>
       </c>
     </row>
     <row r="1101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1101" s="0" t="s">
         <v>1098</v>
       </c>
-      <c r="L1101" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.P(5)</f>
-        <v>0</v>
+      <c r="L1101" s="0" t="e">
+        <f aca="false">_xlfn.VAR.P(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14983,17 +15025,17 @@
         <v>1099</v>
       </c>
       <c r="L1102" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.P(C1:C4)</f>
-        <v>42.3414321321327</v>
+        <f aca="false">VARP(A1:A6)</f>
+        <v>2.91666666666667</v>
       </c>
     </row>
     <row r="1103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1103" s="0" t="s">
         <v>1100</v>
       </c>
-      <c r="L1103" s="0" t="e">
-        <f aca="false">_xlfn.STDEV.P(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1103" s="0" t="n">
+        <f aca="false">VARP(5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15001,17 +15043,17 @@
         <v>1101</v>
       </c>
       <c r="L1104" s="0" t="n">
-        <f aca="false">STDEVP(A1:A6)</f>
-        <v>1.70782512765993</v>
+        <f aca="false">VARP(1,2,3,4)</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="1105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1105" s="0" t="s">
         <v>1102</v>
       </c>
-      <c r="L1105" s="0" t="n">
-        <f aca="false">STDEVP(5)</f>
-        <v>0</v>
+      <c r="L1105" s="0" t="e">
+        <f aca="false">VARP(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15019,8 +15061,8 @@
         <v>1103</v>
       </c>
       <c r="L1106" s="0" t="n">
-        <f aca="false">STDEVP(1,2,3,4)</f>
-        <v>1.1180339887499</v>
+        <f aca="false">STDEV(A1:A6)</f>
+        <v>1.87082869338697</v>
       </c>
     </row>
     <row r="1107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15028,7 +15070,7 @@
         <v>1104</v>
       </c>
       <c r="L1107" s="0" t="e">
-        <f aca="false">STDEVP(B1:B3)</f>
+        <f aca="false">STDEV(5)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15037,8 +15079,8 @@
         <v>1105</v>
       </c>
       <c r="L1108" s="0" t="n">
-        <f aca="false">LARGE(A1:A6,2)</f>
-        <v>5</v>
+        <f aca="false">STDEV(1,2)</f>
+        <v>0.707106781186548</v>
       </c>
     </row>
     <row r="1109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15046,8 +15088,8 @@
         <v>1106</v>
       </c>
       <c r="L1109" s="0" t="e">
-        <f aca="false">LARGE(A1:A6,7)</f>
-        <v>#VALUE!</v>
+        <f aca="false">STDEV(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15055,35 +15097,35 @@
         <v>1107</v>
       </c>
       <c r="L1110" s="0" t="n">
-        <f aca="false">LARGE(C1:C6,1)</f>
-        <v>1000000</v>
+        <f aca="false">_xlfn.STDEV.S(A1:A6)</f>
+        <v>1.87082869338697</v>
       </c>
     </row>
     <row r="1111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1111" s="0" t="s">
         <v>1108</v>
       </c>
-      <c r="L1111" s="0" t="e">
-        <f aca="false">LARGE(A1:A6,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1111" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.S(C1:C4)</f>
+        <v>48.8916744787222</v>
       </c>
     </row>
     <row r="1112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1112" s="0" t="s">
         <v>1109</v>
       </c>
-      <c r="L1112" s="0" t="n">
-        <f aca="false">LARGE(A1:A6,1.5)</f>
-        <v>5</v>
+      <c r="L1112" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.S(1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1113" s="0" t="s">
         <v>1110</v>
       </c>
-      <c r="L1113" s="0" t="n">
-        <f aca="false">SMALL(A1:A6,1)</f>
-        <v>1</v>
+      <c r="L1113" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.S(A1,H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15091,17 +15133,17 @@
         <v>1111</v>
       </c>
       <c r="L1114" s="0" t="n">
-        <f aca="false">SMALL(C1:C6,2)</f>
-        <v>0</v>
+        <f aca="false">_xlfn.STDEV.P(A1:A6)</f>
+        <v>1.70782512765993</v>
       </c>
     </row>
     <row r="1115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1115" s="0" t="s">
         <v>1112</v>
       </c>
-      <c r="L1115" s="0" t="e">
-        <f aca="false">SMALL(B1:B6,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1115" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.P(5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15109,17 +15151,17 @@
         <v>1113</v>
       </c>
       <c r="L1116" s="0" t="n">
-        <f aca="false">SMALL(A1:A6,6)</f>
-        <v>6</v>
+        <f aca="false">_xlfn.STDEV.P(C1:C4)</f>
+        <v>42.3414321321327</v>
       </c>
     </row>
     <row r="1117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1117" s="0" t="s">
         <v>1114</v>
       </c>
-      <c r="L1117" s="0" t="n">
-        <f aca="false">RANK(3,A1:A6)</f>
-        <v>4</v>
+      <c r="L1117" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.P(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15127,17 +15169,17 @@
         <v>1115</v>
       </c>
       <c r="L1118" s="0" t="n">
-        <f aca="false">RANK(3,A1:A6,1)</f>
-        <v>3</v>
+        <f aca="false">STDEVP(A1:A6)</f>
+        <v>1.70782512765993</v>
       </c>
     </row>
     <row r="1119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1119" s="0" t="s">
         <v>1116</v>
       </c>
-      <c r="L1119" s="0" t="e">
-        <f aca="false">RANK(9,A1:A6)</f>
-        <v>#N/A</v>
+      <c r="L1119" s="0" t="n">
+        <f aca="false">STDEVP(5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15145,17 +15187,17 @@
         <v>1117</v>
       </c>
       <c r="L1120" s="0" t="n">
-        <f aca="false">RANK(100,C1:C6)</f>
-        <v>2</v>
+        <f aca="false">STDEVP(1,2,3,4)</f>
+        <v>1.1180339887499</v>
       </c>
     </row>
     <row r="1121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1121" s="0" t="s">
         <v>1118</v>
       </c>
-      <c r="L1121" s="0" t="n">
-        <f aca="false">_xlfn.RANK.EQ(100,C1:C6)</f>
-        <v>2</v>
+      <c r="L1121" s="0" t="e">
+        <f aca="false">STDEVP(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15163,8 +15205,8 @@
         <v>1119</v>
       </c>
       <c r="L1122" s="0" t="n">
-        <f aca="false">_xlfn.RANK.EQ(1,A1:A6,1)</f>
-        <v>1</v>
+        <f aca="false">LARGE(A1:A6,2)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15172,8 +15214,8 @@
         <v>1120</v>
       </c>
       <c r="L1123" s="0" t="e">
-        <f aca="false">_xlfn.RANK.EQ(9,A1:A6)</f>
-        <v>#N/A</v>
+        <f aca="false">LARGE(A1:A6,7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15181,17 +15223,17 @@
         <v>1121</v>
       </c>
       <c r="L1124" s="0" t="n">
-        <f aca="false">_xlfn.RANK.EQ(0,C1:C6,1)</f>
-        <v>2</v>
+        <f aca="false">LARGE(C1:C6,1)</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="1125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1125" s="0" t="s">
         <v>1122</v>
       </c>
-      <c r="L1125" s="0" t="n">
-        <f aca="false">_xlfn.RANK.AVG(3,A1:A6)</f>
-        <v>4</v>
+      <c r="L1125" s="0" t="e">
+        <f aca="false">LARGE(A1:A6,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15199,17 +15241,17 @@
         <v>1123</v>
       </c>
       <c r="L1126" s="0" t="n">
-        <f aca="false">_xlfn.RANK.AVG(1,A1:A6,1)</f>
-        <v>1</v>
+        <f aca="false">LARGE(A1:A6,1.5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1127" s="0" t="s">
         <v>1124</v>
       </c>
-      <c r="L1127" s="0" t="e">
-        <f aca="false">_xlfn.RANK.AVG(9,A1:A6)</f>
-        <v>#N/A</v>
+      <c r="L1127" s="0" t="n">
+        <f aca="false">SMALL(A1:A6,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15217,17 +15259,17 @@
         <v>1125</v>
       </c>
       <c r="L1128" s="0" t="n">
-        <f aca="false">_xlfn.RANK.AVG(100,C1:C6)</f>
-        <v>2</v>
+        <f aca="false">SMALL(C1:C6,2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1129" s="0" t="s">
         <v>1126</v>
       </c>
-      <c r="L1129" s="0" t="n">
-        <f aca="false">PERCENTILE(A1:A6,0.5)</f>
-        <v>3.5</v>
+      <c r="L1129" s="0" t="e">
+        <f aca="false">SMALL(B1:B6,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15235,8 +15277,8 @@
         <v>1127</v>
       </c>
       <c r="L1130" s="0" t="n">
-        <f aca="false">PERCENTILE(A1:A6,0.25)</f>
-        <v>2.25</v>
+        <f aca="false">SMALL(A1:A6,6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15244,26 +15286,26 @@
         <v>1128</v>
       </c>
       <c r="L1131" s="0" t="n">
-        <f aca="false">PERCENTILE(A1:A6,0)</f>
-        <v>1</v>
+        <f aca="false">RANK(3,A1:A6)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1132" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="L1132" s="0" t="e">
-        <f aca="false">PERCENTILE(A1:A6,1.5)</f>
-        <v>#VALUE!</v>
+      <c r="L1132" s="0" t="n">
+        <f aca="false">RANK(3,A1:A6,1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1133" s="0" t="s">
         <v>1130</v>
       </c>
-      <c r="L1133" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,0.9)</f>
-        <v>5.5</v>
+      <c r="L1133" s="0" t="e">
+        <f aca="false">RANK(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15271,8 +15313,8 @@
         <v>1131</v>
       </c>
       <c r="L1134" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.INC(C1:C6,0.5)</f>
-        <v>6.875</v>
+        <f aca="false">RANK(100,C1:C6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15280,26 +15322,26 @@
         <v>1132</v>
       </c>
       <c r="L1135" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,1)</f>
-        <v>6</v>
+        <f aca="false">_xlfn.RANK.EQ(100,C1:C6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1136" s="0" t="s">
         <v>1133</v>
       </c>
-      <c r="L1136" s="0" t="e">
-        <f aca="false">_xlfn.PERCENTILE.INC(B1:B3,0.5)</f>
-        <v>#VALUE!</v>
+      <c r="L1136" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(1,A1:A6,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1137" s="0" t="s">
         <v>1134</v>
       </c>
-      <c r="L1137" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.5)</f>
-        <v>3.5</v>
+      <c r="L1137" s="0" t="e">
+        <f aca="false">_xlfn.RANK.EQ(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15307,17 +15349,17 @@
         <v>1135</v>
       </c>
       <c r="L1138" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.25)</f>
-        <v>1.75</v>
+        <f aca="false">_xlfn.RANK.EQ(0,C1:C6,1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1139" s="0" t="s">
         <v>1136</v>
       </c>
-      <c r="L1139" s="0" t="e">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.1)</f>
-        <v>#VALUE!</v>
+      <c r="L1139" s="0" t="n">
+        <f aca="false">_xlfn.RANK.AVG(3,A1:A6)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15325,17 +15367,17 @@
         <v>1137</v>
       </c>
       <c r="L1140" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.8)</f>
-        <v>5.6</v>
+        <f aca="false">_xlfn.RANK.AVG(1,A1:A6,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1141" s="0" t="s">
         <v>1138</v>
       </c>
-      <c r="L1141" s="0" t="n">
-        <f aca="false">QUARTILE(A1:A6,1)</f>
-        <v>2.25</v>
+      <c r="L1141" s="0" t="e">
+        <f aca="false">_xlfn.RANK.AVG(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15343,8 +15385,8 @@
         <v>1139</v>
       </c>
       <c r="L1142" s="0" t="n">
-        <f aca="false">QUARTILE(A1:A6,3)</f>
-        <v>4.75</v>
+        <f aca="false">_xlfn.RANK.AVG(100,C1:C6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15352,17 +15394,17 @@
         <v>1140</v>
       </c>
       <c r="L1143" s="0" t="n">
-        <f aca="false">QUARTILE(A1:A6,0)</f>
-        <v>1</v>
+        <f aca="false">PERCENTILE(A1:A6,0.5)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1144" s="0" t="s">
         <v>1141</v>
       </c>
-      <c r="L1144" s="0" t="e">
-        <f aca="false">QUARTILE(A1:A6,5)</f>
-        <v>#VALUE!</v>
+      <c r="L1144" s="0" t="n">
+        <f aca="false">PERCENTILE(A1:A6,0.25)</f>
+        <v>2.25</v>
       </c>
     </row>
     <row r="1145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15370,17 +15412,17 @@
         <v>1142</v>
       </c>
       <c r="L1145" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,2)</f>
-        <v>3.5</v>
+        <f aca="false">PERCENTILE(A1:A6,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1146" s="0" t="s">
         <v>1143</v>
       </c>
-      <c r="L1146" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.INC(C1:C6,1)</f>
-        <v>0.8125</v>
+      <c r="L1146" s="0" t="e">
+        <f aca="false">PERCENTILE(A1:A6,1.5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15388,17 +15430,17 @@
         <v>1144</v>
       </c>
       <c r="L1147" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,4)</f>
-        <v>6</v>
+        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,0.9)</f>
+        <v>5.5</v>
       </c>
     </row>
     <row r="1148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1148" s="0" t="s">
         <v>1145</v>
       </c>
-      <c r="L1148" s="0" t="e">
-        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,-1)</f>
-        <v>#VALUE!</v>
+      <c r="L1148" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.INC(C1:C6,0.5)</f>
+        <v>6.875</v>
       </c>
     </row>
     <row r="1149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15406,44 +15448,44 @@
         <v>1146</v>
       </c>
       <c r="L1149" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,1)</f>
-        <v>1.75</v>
+        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,1)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1150" s="0" t="s">
         <v>1147</v>
       </c>
-      <c r="L1150" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,3)</f>
-        <v>5.25</v>
+      <c r="L1150" s="0" t="e">
+        <f aca="false">_xlfn.PERCENTILE.INC(B1:B3,0.5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1151" s="0" t="s">
         <v>1148</v>
       </c>
-      <c r="L1151" s="0" t="e">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1151" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.5)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1152" s="0" t="s">
         <v>1149</v>
       </c>
-      <c r="L1152" s="0" t="e">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,4)</f>
-        <v>#VALUE!</v>
+      <c r="L1152" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.25)</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="1153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1153" s="0" t="s">
         <v>1150</v>
       </c>
-      <c r="L1153" s="0" t="n">
-        <f aca="false">PERCENTRANK(A1:A6,3)</f>
-        <v>0.4</v>
+      <c r="L1153" s="0" t="e">
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15451,17 +15493,17 @@
         <v>1151</v>
       </c>
       <c r="L1154" s="0" t="n">
-        <f aca="false">PERCENTRANK(A1:A6,3.5)</f>
-        <v>0.5</v>
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.8)</f>
+        <v>5.6</v>
       </c>
     </row>
     <row r="1155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1155" s="0" t="s">
         <v>1152</v>
       </c>
-      <c r="L1155" s="0" t="e">
-        <f aca="false">PERCENTRANK(A1:A6,7)</f>
-        <v>#VALUE!</v>
+      <c r="L1155" s="0" t="n">
+        <f aca="false">QUARTILE(A1:A6,1)</f>
+        <v>2.25</v>
       </c>
     </row>
     <row r="1156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15469,8 +15511,8 @@
         <v>1153</v>
       </c>
       <c r="L1156" s="0" t="n">
-        <f aca="false">PERCENTRANK(A1:A6,1)</f>
-        <v>0</v>
+        <f aca="false">QUARTILE(A1:A6,3)</f>
+        <v>4.75</v>
       </c>
     </row>
     <row r="1157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15478,26 +15520,26 @@
         <v>1154</v>
       </c>
       <c r="L1157" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,2.5,2)</f>
-        <v>0.3</v>
+        <f aca="false">QUARTILE(A1:A6,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1158" s="0" t="s">
         <v>1155</v>
       </c>
-      <c r="L1158" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,6)</f>
-        <v>1</v>
+      <c r="L1158" s="0" t="e">
+        <f aca="false">QUARTILE(A1:A6,5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1159" s="0" t="s">
         <v>1156</v>
       </c>
-      <c r="L1159" s="0" t="e">
-        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1159" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,2)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15505,8 +15547,8 @@
         <v>1157</v>
       </c>
       <c r="L1160" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTRANK.INC(C1:C6,10.5)</f>
-        <v>0.6</v>
+        <f aca="false">_xlfn.QUARTILE.INC(C1:C6,1)</f>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="1161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15514,53 +15556,53 @@
         <v>1158</v>
       </c>
       <c r="L1161" s="0" t="n">
-        <f aca="false">CORREL(A1:A4,F1:F4)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,4)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1162" s="0" t="s">
         <v>1159</v>
       </c>
-      <c r="L1162" s="0" t="n">
-        <f aca="false">CORREL(A1:A4,{4;3;2;1})</f>
-        <v>-1</v>
+      <c r="L1162" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1163" s="0" t="s">
         <v>1160</v>
       </c>
-      <c r="L1163" s="0" t="e">
-        <f aca="false">CORREL(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1163" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,1)</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="1164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1164" s="0" t="s">
         <v>1161</v>
       </c>
-      <c r="L1164" s="0" t="e">
-        <f aca="false">CORREL(A1,F1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1164" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,3)</f>
+        <v>5.25</v>
       </c>
     </row>
     <row r="1165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1165" s="0" t="s">
         <v>1162</v>
       </c>
-      <c r="L1165" s="0" t="n">
-        <f aca="false">CORREL(A1:A6,C1:C6)</f>
-        <v>0.654676581102423</v>
+      <c r="L1165" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1166" s="0" t="s">
         <v>1163</v>
       </c>
-      <c r="L1166" s="0" t="n">
-        <f aca="false">COVAR(A1:A4,F1:F4)</f>
-        <v>125</v>
+      <c r="L1166" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15568,17 +15610,17 @@
         <v>1164</v>
       </c>
       <c r="L1167" s="0" t="n">
-        <f aca="false">COVAR(A1:A6,C1:C6)</f>
-        <v>416671.9375</v>
+        <f aca="false">PERCENTRANK(A1:A6,3)</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="1168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1168" s="0" t="s">
         <v>1165</v>
       </c>
-      <c r="L1168" s="0" t="e">
-        <f aca="false">COVAR(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1168" s="0" t="n">
+        <f aca="false">PERCENTRANK(A1:A6,3.5)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15586,7 +15628,7 @@
         <v>1166</v>
       </c>
       <c r="L1169" s="0" t="e">
-        <f aca="false">COVAR(B1:B3,A1:A3)</f>
+        <f aca="false">PERCENTRANK(A1:A6,7)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15595,8 +15637,8 @@
         <v>1167</v>
       </c>
       <c r="L1170" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.P(A1:A4,F1:F4)</f>
-        <v>125</v>
+        <f aca="false">PERCENTRANK(A1:A6,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15604,17 +15646,17 @@
         <v>1168</v>
       </c>
       <c r="L1171" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.P(A1:A6,C1:C6)</f>
-        <v>416671.9375</v>
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,2.5,2)</f>
+        <v>0.3</v>
       </c>
     </row>
     <row r="1172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1172" s="0" t="s">
         <v>1169</v>
       </c>
-      <c r="L1172" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.P(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1172" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15622,7 +15664,7 @@
         <v>1170</v>
       </c>
       <c r="L1173" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.P(B1:B3,A1:A3)</f>
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15631,8 +15673,8 @@
         <v>1171</v>
       </c>
       <c r="L1174" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.S(A1:A4,F1:F4)</f>
-        <v>166.666666666667</v>
+        <f aca="false">_xlfn.PERCENTRANK.INC(C1:C6,10.5)</f>
+        <v>0.6</v>
       </c>
     </row>
     <row r="1175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15640,17 +15682,17 @@
         <v>1172</v>
       </c>
       <c r="L1175" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.S(A1:A6,C1:C6)</f>
-        <v>500006.325</v>
+        <f aca="false">CORREL(A1:A4,F1:F4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1176" s="0" t="s">
         <v>1173</v>
       </c>
-      <c r="L1176" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.S(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1176" s="0" t="n">
+        <f aca="false">CORREL(A1:A4,{4;3;2;1})</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="1177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15658,7 +15700,7 @@
         <v>1174</v>
       </c>
       <c r="L1177" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.S(A1,F1)</f>
+        <f aca="false">CORREL(A1:A3,A1:A4)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15666,9 +15708,9 @@
       <c r="K1178" s="0" t="s">
         <v>1175</v>
       </c>
-      <c r="L1178" s="0" t="n">
-        <f aca="false">SLOPE(F1:F4,A1:A4)</f>
-        <v>100</v>
+      <c r="L1178" s="0" t="e">
+        <f aca="false">CORREL(A1,F1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15676,161 +15718,161 @@
         <v>1176</v>
       </c>
       <c r="L1179" s="0" t="n">
-        <f aca="false">SLOPE(C1:C6,A1:A6)</f>
-        <v>142858.95</v>
+        <f aca="false">CORREL(A1:A6,C1:C6)</f>
+        <v>0.654676581102423</v>
       </c>
     </row>
     <row r="1180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1180" s="0" t="s">
         <v>1177</v>
       </c>
-      <c r="L1180" s="0" t="e">
-        <f aca="false">SLOPE(F1:F4,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1180" s="0" t="n">
+        <f aca="false">COVAR(A1:A4,F1:F4)</f>
+        <v>125</v>
       </c>
     </row>
     <row r="1181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1181" s="0" t="s">
         <v>1178</v>
       </c>
-      <c r="L1181" s="0" t="e">
-        <f aca="false">SLOPE(F1:F4,{1;1;1;1})</f>
-        <v>#DIV/0!</v>
+      <c r="L1181" s="0" t="n">
+        <f aca="false">COVAR(A1:A6,C1:C6)</f>
+        <v>416671.9375</v>
       </c>
     </row>
     <row r="1182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1182" s="0" t="s">
         <v>1179</v>
       </c>
-      <c r="L1182" s="0" t="n">
-        <f aca="false">INTERCEPT(F1:F4,A1:A4)</f>
-        <v>0</v>
+      <c r="L1182" s="0" t="e">
+        <f aca="false">COVAR(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1183" s="0" t="s">
         <v>1180</v>
       </c>
-      <c r="L1183" s="0" t="n">
-        <f aca="false">INTERCEPT(C1:C6,A1:A6)</f>
-        <v>-333321.033333333</v>
+      <c r="L1183" s="0" t="e">
+        <f aca="false">COVAR(B1:B3,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1184" s="0" t="s">
         <v>1181</v>
       </c>
-      <c r="L1184" s="0" t="e">
-        <f aca="false">INTERCEPT(F1:F4,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1184" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A4,F1:F4)</f>
+        <v>125</v>
       </c>
     </row>
     <row r="1185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1185" s="0" t="s">
         <v>1182</v>
       </c>
-      <c r="L1185" s="0" t="e">
-        <f aca="false">INTERCEPT(F1:F4,{1;1;1;1})</f>
-        <v>#DIV/0!</v>
+      <c r="L1185" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A6,C1:C6)</f>
+        <v>416671.9375</v>
       </c>
     </row>
     <row r="1186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1186" s="0" t="s">
         <v>1183</v>
       </c>
-      <c r="L1186" s="0" t="n">
-        <f aca="false">RSQ(F1:F4,A1:A4)</f>
-        <v>1</v>
+      <c r="L1186" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1187" s="0" t="s">
         <v>1184</v>
       </c>
-      <c r="L1187" s="0" t="n">
-        <f aca="false">RSQ(C1:C6,A1:A6)</f>
-        <v>0.428601425843957</v>
+      <c r="L1187" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.P(B1:B3,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1188" s="0" t="s">
         <v>1185</v>
       </c>
-      <c r="L1188" s="0" t="e">
-        <f aca="false">RSQ(F1:F4,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1188" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A4,F1:F4)</f>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="1189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1189" s="0" t="s">
         <v>1186</v>
       </c>
-      <c r="L1189" s="0" t="e">
-        <f aca="false">RSQ(F1:F4,{1;1;1;1})</f>
-        <v>#DIV/0!</v>
+      <c r="L1189" s="0" t="n">
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A6,C1:C6)</f>
+        <v>500006.325</v>
       </c>
     </row>
     <row r="1190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1190" s="0" t="s">
         <v>1187</v>
       </c>
-      <c r="L1190" s="0" t="n">
-        <f aca="false">FORECAST(5,F1:F4,A1:A4)</f>
-        <v>500</v>
+      <c r="L1190" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1191" s="0" t="s">
         <v>1188</v>
       </c>
-      <c r="L1191" s="0" t="n">
-        <f aca="false">FORECAST(7,C1:C6,A1:A6)</f>
-        <v>666691.616666667</v>
+      <c r="L1191" s="0" t="e">
+        <f aca="false">_xlfn.COVARIANCE.S(A1,F1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1192" s="0" t="s">
         <v>1189</v>
       </c>
-      <c r="L1192" s="0" t="e">
-        <f aca="false">FORECAST(5,F1:F4,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1192" s="0" t="n">
+        <f aca="false">SLOPE(F1:F4,A1:A4)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1193" s="0" t="s">
         <v>1190</v>
       </c>
-      <c r="L1193" s="0" t="e">
-        <f aca="false">FORECAST(B1,F1:F4,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1193" s="0" t="n">
+        <f aca="false">SLOPE(C1:C6,A1:A6)</f>
+        <v>142858.95</v>
       </c>
     </row>
     <row r="1194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1194" s="0" t="s">
         <v>1191</v>
       </c>
-      <c r="L1194" s="0" t="n">
-        <f aca="false">_xlfn.FORECAST.LINEAR(10,F1:F4,A1:A4)</f>
-        <v>1000</v>
+      <c r="L1194" s="0" t="e">
+        <f aca="false">SLOPE(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1195" s="0" t="s">
         <v>1192</v>
       </c>
-      <c r="L1195" s="0" t="n">
-        <f aca="false">_xlfn.FORECAST.LINEAR(0,C1:C6,A1:A6)</f>
-        <v>-333321.033333333</v>
+      <c r="L1195" s="0" t="e">
+        <f aca="false">SLOPE(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1196" s="0" t="s">
         <v>1193</v>
       </c>
-      <c r="L1196" s="0" t="e">
-        <f aca="false">_xlfn.FORECAST.LINEAR(5,F1:F4,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1196" s="0" t="n">
+        <f aca="false">INTERCEPT(F1:F4,A1:A4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15838,26 +15880,26 @@
         <v>1194</v>
       </c>
       <c r="L1197" s="0" t="n">
-        <f aca="false">_xlfn.FORECAST.LINEAR(2.5,F1:F4,A1:A4)</f>
-        <v>250</v>
+        <f aca="false">INTERCEPT(C1:C6,A1:A6)</f>
+        <v>-333321.033333333</v>
       </c>
     </row>
     <row r="1198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1198" s="0" t="s">
         <v>1195</v>
       </c>
-      <c r="L1198" s="0" t="n">
-        <f aca="false">TREND(F1:F4,A1:A4,5)</f>
-        <v>500</v>
+      <c r="L1198" s="0" t="e">
+        <f aca="false">INTERCEPT(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1199" s="0" t="s">
         <v>1196</v>
       </c>
-      <c r="L1199" s="0" t="n">
-        <f aca="false">SUM(TREND(F1:F4,A1:A4,A5:A6))</f>
-        <v>1100</v>
+      <c r="L1199" s="0" t="e">
+        <f aca="false">INTERCEPT(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15865,8 +15907,8 @@
         <v>1197</v>
       </c>
       <c r="L1200" s="0" t="n">
-        <f aca="false">INDEX(TREND(F1:F4),2)</f>
-        <v>200</v>
+        <f aca="false">RSQ(F1:F4,A1:A4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15874,26 +15916,26 @@
         <v>1198</v>
       </c>
       <c r="L1201" s="0" t="n">
-        <f aca="false">TREND(F1:F4,A1:A4,5,FALSE())</f>
-        <v>500</v>
+        <f aca="false">RSQ(C1:C6,A1:A6)</f>
+        <v>0.428601425843957</v>
       </c>
     </row>
     <row r="1202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1202" s="0" t="s">
         <v>1199</v>
       </c>
-      <c r="L1202" s="0" t="n">
-        <f aca="false">TREND(A1:A4,F1:F4,250)</f>
-        <v>2.5</v>
+      <c r="L1202" s="0" t="e">
+        <f aca="false">RSQ(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1203" s="0" t="s">
         <v>1200</v>
       </c>
-      <c r="L1203" s="0" t="n">
-        <f aca="false">GEOMEAN(1,2,4)</f>
-        <v>2</v>
+      <c r="L1203" s="0" t="e">
+        <f aca="false">RSQ(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15901,17 +15943,17 @@
         <v>1201</v>
       </c>
       <c r="L1204" s="0" t="n">
-        <f aca="false">GEOMEAN(A1:A6)</f>
-        <v>2.99379516552391</v>
+        <f aca="false">FORECAST(5,F1:F4,A1:A4)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="1205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1205" s="0" t="s">
         <v>1202</v>
       </c>
-      <c r="L1205" s="0" t="e">
-        <f aca="false">GEOMEAN(C1:C3)</f>
-        <v>#VALUE!</v>
+      <c r="L1205" s="0" t="n">
+        <f aca="false">FORECAST(7,C1:C6,A1:A6)</f>
+        <v>666691.616666667</v>
       </c>
     </row>
     <row r="1206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15919,17 +15961,17 @@
         <v>1203</v>
       </c>
       <c r="L1206" s="0" t="e">
-        <f aca="false">GEOMEAN(B1:B2)</f>
-        <v>#NUM!</v>
+        <f aca="false">FORECAST(5,F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1207" s="0" t="s">
         <v>1204</v>
       </c>
-      <c r="L1207" s="0" t="n">
-        <f aca="false">HARMEAN(1,2,4)</f>
-        <v>1.71428571428571</v>
+      <c r="L1207" s="0" t="e">
+        <f aca="false">FORECAST(B1,F1:F4,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15937,17 +15979,17 @@
         <v>1205</v>
       </c>
       <c r="L1208" s="0" t="n">
-        <f aca="false">HARMEAN(A1:A3)</f>
-        <v>1.63636363636364</v>
+        <f aca="false">_xlfn.FORECAST.LINEAR(10,F1:F4,A1:A4)</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="1209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1209" s="0" t="s">
         <v>1206</v>
       </c>
-      <c r="L1209" s="0" t="e">
-        <f aca="false">HARMEAN(C1:C3)</f>
-        <v>#VALUE!</v>
+      <c r="L1209" s="0" t="n">
+        <f aca="false">_xlfn.FORECAST.LINEAR(0,C1:C6,A1:A6)</f>
+        <v>-333321.033333333</v>
       </c>
     </row>
     <row r="1210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15955,8 +15997,8 @@
         <v>1207</v>
       </c>
       <c r="L1210" s="0" t="e">
-        <f aca="false">HARMEAN(B1:B2)</f>
-        <v>#NUM!</v>
+        <f aca="false">_xlfn.FORECAST.LINEAR(5,F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15964,8 +16006,8 @@
         <v>1208</v>
       </c>
       <c r="L1211" s="0" t="n">
-        <f aca="false">DEVSQ(A1:A6)</f>
-        <v>17.5</v>
+        <f aca="false">_xlfn.FORECAST.LINEAR(2.5,F1:F4,A1:A4)</f>
+        <v>250</v>
       </c>
     </row>
     <row r="1212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15973,8 +16015,8 @@
         <v>1209</v>
       </c>
       <c r="L1212" s="0" t="n">
-        <f aca="false">DEVSQ(1,2,3)</f>
-        <v>2</v>
+        <f aca="false">TREND(F1:F4,A1:A4,5)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="1213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15982,17 +16024,17 @@
         <v>1210</v>
       </c>
       <c r="L1213" s="0" t="n">
-        <f aca="false">DEVSQ(C1:C4)</f>
-        <v>7171.1875</v>
+        <f aca="false">SUM(TREND(F1:F4,A1:A4,A5:A6))</f>
+        <v>1100</v>
       </c>
     </row>
     <row r="1214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1214" s="0" t="s">
         <v>1211</v>
       </c>
-      <c r="L1214" s="0" t="e">
-        <f aca="false">DEVSQ(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1214" s="0" t="n">
+        <f aca="false">INDEX(TREND(F1:F4),2)</f>
+        <v>200</v>
       </c>
     </row>
     <row r="1215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16000,8 +16042,8 @@
         <v>1212</v>
       </c>
       <c r="L1215" s="0" t="n">
-        <f aca="false">AVEDEV(A1:A6)</f>
-        <v>1.5</v>
+        <f aca="false">TREND(F1:F4,A1:A4,5,FALSE())</f>
+        <v>500</v>
       </c>
     </row>
     <row r="1216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16009,8 +16051,8 @@
         <v>1213</v>
       </c>
       <c r="L1216" s="0" t="n">
-        <f aca="false">AVEDEV(1,2,3,4)</f>
-        <v>1</v>
+        <f aca="false">TREND(A1:A4,F1:F4,250)</f>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16018,179 +16060,179 @@
         <v>1214</v>
       </c>
       <c r="L1217" s="0" t="n">
-        <f aca="false">AVEDEV(C1:C4)</f>
-        <v>36.4375</v>
+        <f aca="false">GEOMEAN(1,2,4)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1218" s="0" t="s">
         <v>1215</v>
       </c>
-      <c r="L1218" s="0" t="e">
-        <f aca="false">AVEDEV(B1:B3)</f>
-        <v>#NUM!</v>
+      <c r="L1218" s="0" t="n">
+        <f aca="false">GEOMEAN(A1:A6)</f>
+        <v>2.99379516552391</v>
       </c>
     </row>
     <row r="1219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1219" s="0" t="s">
         <v>1216</v>
       </c>
-      <c r="L1219" s="7" t="n">
-        <f aca="false">PMT(0.08/12,10,10000)</f>
-        <v>-1037.03208935915</v>
+      <c r="L1219" s="0" t="e">
+        <f aca="false">GEOMEAN(C1:C3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1220" s="0" t="s">
         <v>1217</v>
       </c>
-      <c r="L1220" s="7" t="n">
-        <f aca="false">PMT(0,10,1000)</f>
-        <v>-100</v>
+      <c r="L1220" s="0" t="e">
+        <f aca="false">GEOMEAN(B1:B2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1221" s="0" t="s">
         <v>1218</v>
       </c>
-      <c r="L1221" s="7" t="n">
-        <f aca="false">PMT(0.05,5,1000,0,1)</f>
-        <v>-219.975998217398</v>
+      <c r="L1221" s="0" t="n">
+        <f aca="false">HARMEAN(1,2,4)</f>
+        <v>1.71428571428571</v>
       </c>
     </row>
     <row r="1222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1222" s="0" t="s">
         <v>1219</v>
       </c>
-      <c r="L1222" s="7" t="e">
-        <f aca="false">PMT(0.05,0,100)</f>
-        <v>#NUM!</v>
+      <c r="L1222" s="0" t="n">
+        <f aca="false">HARMEAN(A1:A3)</f>
+        <v>1.63636363636364</v>
       </c>
     </row>
     <row r="1223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1223" s="0" t="s">
         <v>1220</v>
       </c>
-      <c r="L1223" s="7" t="n">
-        <f aca="false">PMT(0.06,12,-5000,1000)</f>
-        <v>537.108117522654</v>
+      <c r="L1223" s="0" t="e">
+        <f aca="false">HARMEAN(C1:C3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1224" s="0" t="s">
         <v>1221</v>
       </c>
-      <c r="L1224" s="7" t="n">
-        <f aca="false">FV(0.06/12,10,-200,-500,1)</f>
-        <v>2581.40337406014</v>
+      <c r="L1224" s="0" t="e">
+        <f aca="false">HARMEAN(B1:B2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1225" s="0" t="s">
         <v>1222</v>
       </c>
-      <c r="L1225" s="7" t="n">
-        <f aca="false">FV(0,10,-100)</f>
-        <v>1000</v>
+      <c r="L1225" s="0" t="n">
+        <f aca="false">DEVSQ(A1:A6)</f>
+        <v>17.5</v>
       </c>
     </row>
     <row r="1226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1226" s="0" t="s">
         <v>1223</v>
       </c>
-      <c r="L1226" s="7" t="n">
-        <f aca="false">FV(0.05,5,-100,0,0)</f>
-        <v>552.563125000001</v>
+      <c r="L1226" s="0" t="n">
+        <f aca="false">DEVSQ(1,2,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1227" s="0" t="s">
         <v>1224</v>
       </c>
-      <c r="L1227" s="7" t="n">
-        <f aca="false">FV(0.1,2,0,-100)</f>
-        <v>121</v>
+      <c r="L1227" s="0" t="n">
+        <f aca="false">DEVSQ(C1:C4)</f>
+        <v>7171.1875</v>
       </c>
     </row>
     <row r="1228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1228" s="0" t="s">
         <v>1225</v>
       </c>
-      <c r="L1228" s="7" t="n">
-        <f aca="false">PV(0.08/12,240,500)</f>
-        <v>-59777.1458511878</v>
+      <c r="L1228" s="0" t="e">
+        <f aca="false">DEVSQ(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1229" s="0" t="s">
         <v>1226</v>
       </c>
-      <c r="L1229" s="7" t="n">
-        <f aca="false">PV(0,5,-10)</f>
-        <v>50</v>
+      <c r="L1229" s="0" t="n">
+        <f aca="false">AVEDEV(A1:A6)</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1230" s="0" t="s">
         <v>1227</v>
       </c>
-      <c r="L1230" s="7" t="n">
-        <f aca="false">PV(0.05,10,-100,0,1)</f>
-        <v>810.782167564406</v>
+      <c r="L1230" s="0" t="n">
+        <f aca="false">AVEDEV(1,2,3,4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1231" s="0" t="s">
         <v>1228</v>
       </c>
-      <c r="L1231" s="7" t="n">
-        <f aca="false">PV(0.05,10,0,1000)</f>
-        <v>-613.913253540759</v>
+      <c r="L1231" s="0" t="n">
+        <f aca="false">AVEDEV(C1:C4)</f>
+        <v>36.4375</v>
       </c>
     </row>
     <row r="1232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1232" s="0" t="s">
         <v>1229</v>
       </c>
-      <c r="L1232" s="0" t="n">
-        <f aca="false">NPER(0.12/12,-100,-1000,10000)</f>
-        <v>60.0821228537617</v>
+      <c r="L1232" s="0" t="e">
+        <f aca="false">AVEDEV(B1:B3)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1233" s="0" t="s">
         <v>1230</v>
       </c>
-      <c r="L1233" s="0" t="n">
-        <f aca="false">NPER(0,-100,1000)</f>
-        <v>10</v>
+      <c r="L1233" s="7" t="n">
+        <f aca="false">PMT(0.08/12,10,10000)</f>
+        <v>-1037.03208935915</v>
       </c>
     </row>
     <row r="1234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1234" s="0" t="s">
         <v>1231</v>
       </c>
-      <c r="L1234" s="0" t="n">
-        <f aca="false">NPER(0.05,-100,1000,0,1)</f>
-        <v>13.2532278981381</v>
+      <c r="L1234" s="7" t="n">
+        <f aca="false">PMT(0,10,1000)</f>
+        <v>-100</v>
       </c>
     </row>
     <row r="1235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1235" s="0" t="s">
         <v>1232</v>
       </c>
-      <c r="L1235" s="0" t="e">
-        <f aca="false">NPER(0.01,0,100)</f>
-        <v>#NUM!</v>
+      <c r="L1235" s="7" t="n">
+        <f aca="false">PMT(0.05,5,1000,0,1)</f>
+        <v>-219.975998217398</v>
       </c>
     </row>
     <row r="1236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1236" s="0" t="s">
         <v>1233</v>
       </c>
-      <c r="L1236" s="7" t="n">
-        <f aca="false">IPMT(0.1/12,1,36,8000)</f>
-        <v>-66.6666666666667</v>
+      <c r="L1236" s="7" t="e">
+        <f aca="false">PMT(0.05,0,100)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16198,8 +16240,8 @@
         <v>1234</v>
       </c>
       <c r="L1237" s="7" t="n">
-        <f aca="false">IPMT(0.1/12,3,36,8000)</f>
-        <v>-63.4621895664547</v>
+        <f aca="false">PMT(0.06,12,-5000,1000)</f>
+        <v>537.108117522654</v>
       </c>
     </row>
     <row r="1238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16207,8 +16249,8 @@
         <v>1235</v>
       </c>
       <c r="L1238" s="7" t="n">
-        <f aca="false">IPMT(0.1,3,3,8000)</f>
-        <v>-292.447129909365</v>
+        <f aca="false">FV(0.06/12,10,-200,-500,1)</f>
+        <v>2581.40337406014</v>
       </c>
     </row>
     <row r="1239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16216,17 +16258,17 @@
         <v>1236</v>
       </c>
       <c r="L1239" s="7" t="n">
-        <f aca="false">IPMT(0.1/12,1,36,8000,0,1)</f>
-        <v>0</v>
+        <f aca="false">FV(0,10,-100)</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="1240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1240" s="0" t="s">
         <v>1237</v>
       </c>
-      <c r="L1240" s="7" t="e">
-        <f aca="false">IPMT(0.05,0,3,1000)</f>
-        <v>#VALUE!</v>
+      <c r="L1240" s="7" t="n">
+        <f aca="false">FV(0.05,5,-100,0,0)</f>
+        <v>552.563125000001</v>
       </c>
     </row>
     <row r="1241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16234,8 +16276,8 @@
         <v>1238</v>
       </c>
       <c r="L1241" s="7" t="n">
-        <f aca="false">IPMT(0.05,2,3,1000,0,1)</f>
-        <v>-32.5138778747026</v>
+        <f aca="false">FV(0.1,2,0,-100)</f>
+        <v>121</v>
       </c>
     </row>
     <row r="1242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16243,8 +16285,8 @@
         <v>1239</v>
       </c>
       <c r="L1242" s="7" t="n">
-        <f aca="false">PPMT(0.1/12,1,24,2000)</f>
-        <v>-75.6231860083664</v>
+        <f aca="false">PV(0.08/12,240,500)</f>
+        <v>-59777.1458511878</v>
       </c>
     </row>
     <row r="1243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16252,8 +16294,8 @@
         <v>1240</v>
       </c>
       <c r="L1243" s="7" t="n">
-        <f aca="false">PPMT(0.08,10,10,200000)</f>
-        <v>-27598.0534624214</v>
+        <f aca="false">PV(0,5,-10)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="1244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16261,125 +16303,125 @@
         <v>1241</v>
       </c>
       <c r="L1244" s="7" t="n">
-        <f aca="false">PPMT(0.05,2,3,1000,0,1)</f>
-        <v>-317.208564631245</v>
+        <f aca="false">PV(0.05,10,-100,0,1)</f>
+        <v>810.782167564406</v>
       </c>
     </row>
     <row r="1245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1245" s="0" t="s">
         <v>1242</v>
       </c>
-      <c r="L1245" s="7" t="e">
-        <f aca="false">PPMT(0.05,4,3,1000)</f>
-        <v>#VALUE!</v>
+      <c r="L1245" s="7" t="n">
+        <f aca="false">PV(0.05,10,0,1000)</f>
+        <v>-613.913253540759</v>
       </c>
     </row>
     <row r="1246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1246" s="0" t="s">
         <v>1243</v>
       </c>
-      <c r="L1246" s="7" t="n">
-        <f aca="false">NPV(0.1,-10000,3000,4200,6800)</f>
-        <v>1188.44341233522</v>
+      <c r="L1246" s="0" t="n">
+        <f aca="false">NPER(0.12/12,-100,-1000,10000)</f>
+        <v>60.0821228537617</v>
       </c>
     </row>
     <row r="1247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1247" s="0" t="s">
         <v>1244</v>
       </c>
-      <c r="L1247" s="7" t="n">
-        <f aca="false">NPV(0.1,A1:A3)</f>
-        <v>4.81592787377911</v>
+      <c r="L1247" s="0" t="n">
+        <f aca="false">NPER(0,-100,1000)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="1248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1248" s="0" t="s">
         <v>1245</v>
       </c>
-      <c r="L1248" s="7" t="e">
-        <f aca="false">NPV(-1,1,2)</f>
-        <v>#NUM!</v>
+      <c r="L1248" s="0" t="n">
+        <f aca="false">NPER(0.05,-100,1000,0,1)</f>
+        <v>13.2532278981381</v>
       </c>
     </row>
     <row r="1249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1249" s="0" t="s">
         <v>1246</v>
       </c>
-      <c r="L1249" s="7" t="n">
-        <f aca="false">NPV(0.08,F1:F4)</f>
-        <v>796.221970077581</v>
+      <c r="L1249" s="0" t="e">
+        <f aca="false">NPER(0.01,0,100)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1250" s="0" t="s">
         <v>1247</v>
       </c>
-      <c r="L1250" s="0" t="n">
-        <f aca="false">ROUND(IRR({-70000,12000,15000,18000,21000,26000}),6)</f>
-        <v>0.086631</v>
+      <c r="L1250" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,1,36,8000)</f>
+        <v>-66.6666666666667</v>
       </c>
     </row>
     <row r="1251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1251" s="0" t="s">
         <v>1248</v>
       </c>
-      <c r="L1251" s="0" t="n">
-        <f aca="false">ROUND(IRR({-100,110}),6)</f>
-        <v>0.1</v>
+      <c r="L1251" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,3,36,8000)</f>
+        <v>-63.4621895664547</v>
       </c>
     </row>
     <row r="1252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1252" s="0" t="s">
         <v>1249</v>
       </c>
-      <c r="L1252" s="6" t="e">
-        <f aca="false">IRR({1,2,3})</f>
-        <v>#N/A</v>
+      <c r="L1252" s="7" t="n">
+        <f aca="false">IPMT(0.1,3,3,8000)</f>
+        <v>-292.447129909365</v>
       </c>
     </row>
     <row r="1253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1253" s="0" t="s">
         <v>1250</v>
       </c>
-      <c r="L1253" s="0" t="n">
-        <f aca="false">ROUND(IRR({-1000,300,400,500},0.2),6)</f>
-        <v>0.088963</v>
+      <c r="L1253" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,1,36,8000,0,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1254" s="0" t="s">
         <v>1251</v>
       </c>
-      <c r="L1254" s="0" t="n">
-        <f aca="false">ROUND(RATE(48,-200,8000),6)</f>
-        <v>0.007701</v>
+      <c r="L1254" s="7" t="e">
+        <f aca="false">IPMT(0.05,0,3,1000)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1255" s="0" t="s">
         <v>1252</v>
       </c>
-      <c r="L1255" s="0" t="n">
-        <f aca="false">ROUND(RATE(10,0,-100,200),6)</f>
-        <v>0.071773</v>
+      <c r="L1255" s="7" t="n">
+        <f aca="false">IPMT(0.05,2,3,1000,0,1)</f>
+        <v>-32.5138778747026</v>
       </c>
     </row>
     <row r="1256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1256" s="0" t="s">
         <v>1253</v>
       </c>
-      <c r="L1256" s="6" t="e">
-        <f aca="false">RATE(0,-100,1000)</f>
-        <v>#VALUE!</v>
+      <c r="L1256" s="7" t="n">
+        <f aca="false">PPMT(0.1/12,1,24,2000)</f>
+        <v>-75.6231860083664</v>
       </c>
     </row>
     <row r="1257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1257" s="0" t="s">
         <v>1254</v>
       </c>
-      <c r="L1257" s="0" t="n">
-        <f aca="false">ROUND(RATE(12,-100,1000),6)</f>
-        <v>0.029229</v>
+      <c r="L1257" s="7" t="n">
+        <f aca="false">PPMT(0.08,10,10,200000)</f>
+        <v>-27598.0534624214</v>
       </c>
     </row>
     <row r="1258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16387,26 +16429,26 @@
         <v>1255</v>
       </c>
       <c r="L1258" s="7" t="n">
-        <f aca="false">SLN(30000,7500,10)</f>
-        <v>2250</v>
+        <f aca="false">PPMT(0.05,2,3,1000,0,1)</f>
+        <v>-317.208564631245</v>
       </c>
     </row>
     <row r="1259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1259" s="0" t="s">
         <v>1256</v>
       </c>
-      <c r="L1259" s="7" t="n">
-        <f aca="false">SLN(100,0,4)</f>
-        <v>25</v>
+      <c r="L1259" s="7" t="e">
+        <f aca="false">PPMT(0.05,4,3,1000)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1260" s="0" t="s">
         <v>1257</v>
       </c>
-      <c r="L1260" s="7" t="e">
-        <f aca="false">SLN(100,10,0)</f>
-        <v>#DIV/0!</v>
+      <c r="L1260" s="7" t="n">
+        <f aca="false">NPV(0.1,-10000,3000,4200,6800)</f>
+        <v>1188.44341233522</v>
       </c>
     </row>
     <row r="1261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16414,17 +16456,17 @@
         <v>1258</v>
       </c>
       <c r="L1261" s="7" t="n">
-        <f aca="false">SLN(F1,0,4)</f>
-        <v>25</v>
+        <f aca="false">NPV(0.1,A1:A3)</f>
+        <v>4.81592787377911</v>
       </c>
     </row>
     <row r="1262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1262" s="0" t="s">
         <v>1259</v>
       </c>
-      <c r="L1262" s="7" t="n">
-        <f aca="false">SYD(30000,7500,10,1)</f>
-        <v>4090.90909090909</v>
+      <c r="L1262" s="7" t="e">
+        <f aca="false">NPV(-1,1,2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16432,80 +16474,80 @@
         <v>1260</v>
       </c>
       <c r="L1263" s="7" t="n">
-        <f aca="false">SYD(30000,7500,10,10)</f>
-        <v>409.090909090909</v>
+        <f aca="false">NPV(0.08,F1:F4)</f>
+        <v>796.221970077581</v>
       </c>
     </row>
     <row r="1264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1264" s="0" t="s">
         <v>1261</v>
       </c>
-      <c r="L1264" s="7" t="n">
-        <f aca="false">SYD(100,0,4,5)</f>
-        <v>0</v>
+      <c r="L1264" s="0" t="n">
+        <f aca="false">ROUND(IRR({-70000,12000,15000,18000,21000,26000}),6)</f>
+        <v>0.086631</v>
       </c>
     </row>
     <row r="1265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1265" s="0" t="s">
         <v>1262</v>
       </c>
-      <c r="L1265" s="7" t="n">
-        <f aca="false">SYD(100,0,4,0)</f>
-        <v>50</v>
+      <c r="L1265" s="0" t="n">
+        <f aca="false">ROUND(IRR({-100,110}),6)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1266" s="0" t="s">
         <v>1263</v>
       </c>
-      <c r="L1266" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,1,7)</f>
-        <v>186083.333333333</v>
+      <c r="L1266" s="6" t="e">
+        <f aca="false">IRR({1,2,3})</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1267" s="0" t="s">
         <v>1264</v>
       </c>
-      <c r="L1267" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,2,7)</f>
-        <v>259639.416666667</v>
+      <c r="L1267" s="0" t="n">
+        <f aca="false">ROUND(IRR({-1000,300,400,500},0.2),6)</f>
+        <v>0.088963</v>
       </c>
     </row>
     <row r="1268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1268" s="0" t="s">
         <v>1265</v>
       </c>
-      <c r="L1268" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,7,7)</f>
-        <v>15845.0984738481</v>
+      <c r="L1268" s="0" t="n">
+        <f aca="false">ROUND(RATE(48,-200,8000),6)</f>
+        <v>0.007701</v>
       </c>
     </row>
     <row r="1269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1269" s="0" t="s">
         <v>1266</v>
       </c>
-      <c r="L1269" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,1)</f>
-        <v>319000</v>
+      <c r="L1269" s="0" t="n">
+        <f aca="false">ROUND(RATE(10,0,-100,200),6)</f>
+        <v>0.071773</v>
       </c>
     </row>
     <row r="1270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1270" s="0" t="s">
         <v>1267</v>
       </c>
-      <c r="L1270" s="7" t="n">
-        <f aca="false">DB(1000,100,5,6)</f>
-        <v>0</v>
+      <c r="L1270" s="6" t="e">
+        <f aca="false">RATE(0,-100,1000)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1271" s="0" t="s">
         <v>1268</v>
       </c>
-      <c r="L1271" s="7" t="n">
-        <f aca="false">DDB(2400,300,10*365,1)</f>
-        <v>1.31506849315065</v>
+      <c r="L1271" s="0" t="n">
+        <f aca="false">ROUND(RATE(12,-100,1000),6)</f>
+        <v>0.029229</v>
       </c>
     </row>
     <row r="1272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16513,8 +16555,8 @@
         <v>1269</v>
       </c>
       <c r="L1272" s="7" t="n">
-        <f aca="false">DDB(2400,300,10,1,2)</f>
-        <v>480</v>
+        <f aca="false">SLN(30000,7500,10)</f>
+        <v>2250</v>
       </c>
     </row>
     <row r="1273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16522,52 +16564,52 @@
         <v>1270</v>
       </c>
       <c r="L1273" s="7" t="n">
-        <f aca="false">DDB(2400,300,10,2,2)</f>
-        <v>384</v>
+        <f aca="false">SLN(100,0,4)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="1274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1274" s="0" t="s">
         <v>1271</v>
       </c>
-      <c r="L1274" s="7" t="n">
-        <f aca="false">DDB(2400,300,10,10)</f>
-        <v>22.1225472000002</v>
+      <c r="L1274" s="7" t="e">
+        <f aca="false">SLN(100,10,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1275" s="0" t="s">
         <v>1272</v>
       </c>
-      <c r="L1275" s="7" t="e">
-        <f aca="false">DDB(100,0,5,6)</f>
-        <v>#VALUE!</v>
+      <c r="L1275" s="7" t="n">
+        <f aca="false">SLN(F1,0,4)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="1276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1276" s="0" t="s">
         <v>1273</v>
       </c>
-      <c r="L1276" s="6" t="n">
-        <f aca="false">EFFECT(0.0525,4)</f>
-        <v>0.0535426673707582</v>
+      <c r="L1276" s="7" t="n">
+        <f aca="false">SYD(30000,7500,10,1)</f>
+        <v>4090.90909090909</v>
       </c>
     </row>
     <row r="1277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1277" s="0" t="s">
         <v>1274</v>
       </c>
-      <c r="L1277" s="6" t="n">
-        <f aca="false">EFFECT(0.1,1)</f>
-        <v>0.1</v>
+      <c r="L1277" s="7" t="n">
+        <f aca="false">SYD(30000,7500,10,10)</f>
+        <v>409.090909090909</v>
       </c>
     </row>
     <row r="1278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1278" s="0" t="s">
         <v>1275</v>
       </c>
-      <c r="L1278" s="6" t="n">
-        <f aca="false">EFFECT(0,4)</f>
+      <c r="L1278" s="7" t="n">
+        <f aca="false">SYD(100,0,4,5)</f>
         <v>0</v>
       </c>
     </row>
@@ -16575,189 +16617,189 @@
       <c r="K1279" s="0" t="s">
         <v>1276</v>
       </c>
-      <c r="L1279" s="6" t="e">
-        <f aca="false">EFFECT(0.1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1279" s="7" t="n">
+        <f aca="false">SYD(100,0,4,0)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="1280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1280" s="0" t="s">
         <v>1277</v>
       </c>
-      <c r="L1280" s="6" t="n">
-        <f aca="false">NOMINAL(0.053543,4)</f>
-        <v>0.052500319868356</v>
+      <c r="L1280" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,1,7)</f>
+        <v>186083.333333333</v>
       </c>
     </row>
     <row r="1281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1281" s="0" t="s">
         <v>1278</v>
       </c>
-      <c r="L1281" s="6" t="n">
-        <f aca="false">NOMINAL(0.1,1)</f>
-        <v>0.1</v>
+      <c r="L1281" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,2,7)</f>
+        <v>259639.416666667</v>
       </c>
     </row>
     <row r="1282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1282" s="0" t="s">
         <v>1279</v>
       </c>
-      <c r="L1282" s="6" t="e">
-        <f aca="false">NOMINAL(0,4)</f>
-        <v>#VALUE!</v>
+      <c r="L1282" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,7,7)</f>
+        <v>15845.0984738481</v>
       </c>
     </row>
     <row r="1283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1283" s="0" t="s">
         <v>1280</v>
       </c>
-      <c r="L1283" s="6" t="e">
-        <f aca="false">NOMINAL(0.1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1283" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,1)</f>
+        <v>319000</v>
       </c>
     </row>
     <row r="1284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1284" s="0" t="s">
         <v>1281</v>
       </c>
-      <c r="L1284" s="0" t="n">
-        <f aca="false">ROUND(MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12),6)</f>
-        <v>0.126094</v>
+      <c r="L1284" s="7" t="n">
+        <f aca="false">DB(1000,100,5,6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1285" s="0" t="s">
         <v>1282</v>
       </c>
-      <c r="L1285" s="6" t="e">
-        <f aca="false">MIRR({1,2,3},0.1,0.1)</f>
-        <v>#VALUE!</v>
+      <c r="L1285" s="7" t="n">
+        <f aca="false">DDB(2400,300,10*365,1)</f>
+        <v>1.31506849315065</v>
       </c>
     </row>
     <row r="1286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1286" s="0" t="s">
         <v>1283</v>
       </c>
-      <c r="L1286" s="0" t="n">
-        <f aca="false">ROUND(MIRR({-100,50,60},0.05,0.05),6)</f>
-        <v>0.06066</v>
+      <c r="L1286" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,1,2)</f>
+        <v>480</v>
       </c>
     </row>
     <row r="1287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1287" s="0" t="s">
         <v>1284</v>
       </c>
-      <c r="L1287" s="6" t="e">
-        <f aca="false">MIRR({-100,-50},0.1,0.1)</f>
-        <v>#VALUE!</v>
+      <c r="L1287" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,2,2)</f>
+        <v>384</v>
       </c>
     </row>
     <row r="1288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1288" s="0" t="s">
         <v>1285</v>
       </c>
-      <c r="L1288" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
-        <v>b</v>
+      <c r="L1288" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,10)</f>
+        <v>22.1225472000002</v>
       </c>
     </row>
     <row r="1289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1289" s="0" t="s">
         <v>1286</v>
       </c>
-      <c r="L1289" s="0" t="n">
-        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
-        <v>2</v>
+      <c r="L1289" s="7" t="e">
+        <f aca="false">DDB(100,0,5,6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1290" s="0" t="s">
         <v>1287</v>
       </c>
-      <c r="L1290" s="0" t="e">
-        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
-        <v>#N/A</v>
+      <c r="L1290" s="6" t="n">
+        <f aca="false">EFFECT(0.0525,4)</f>
+        <v>0.0535426673707582</v>
       </c>
     </row>
     <row r="1291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1291" s="0" t="s">
         <v>1288</v>
       </c>
-      <c r="L1291" s="0" t="n">
-        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
-        <v>1</v>
+      <c r="L1291" s="6" t="n">
+        <f aca="false">EFFECT(0.1,1)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1292" s="0" t="s">
         <v>1289</v>
       </c>
-      <c r="L1292" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A1,"x")</f>
-        <v>x</v>
+      <c r="L1292" s="6" t="n">
+        <f aca="false">EFFECT(0,4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1293" s="0" t="s">
         <v>1290</v>
       </c>
-      <c r="L1293" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
-        <v>b</v>
+      <c r="L1293" s="6" t="e">
+        <f aca="false">EFFECT(0.1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1294" s="0" t="s">
         <v>1291</v>
       </c>
-      <c r="L1294" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
-        <v>z</v>
+      <c r="L1294" s="6" t="n">
+        <f aca="false">NOMINAL(0.053543,4)</f>
+        <v>0.052500319868356</v>
       </c>
     </row>
     <row r="1295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1295" s="0" t="s">
         <v>1292</v>
       </c>
-      <c r="L1295" s="0" t="e">
-        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
-        <v>#N/A</v>
+      <c r="L1295" s="6" t="n">
+        <f aca="false">NOMINAL(0.1,1)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1296" s="0" t="s">
         <v>1293</v>
       </c>
-      <c r="L1296" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
-        <v>2</v>
+      <c r="L1296" s="6" t="e">
+        <f aca="false">NOMINAL(0,4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1297" s="0" t="s">
         <v>1294</v>
       </c>
-      <c r="L1297" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
-        <v>three</v>
+      <c r="L1297" s="6" t="e">
+        <f aca="false">NOMINAL(0.1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1298" s="0" t="s">
         <v>1295</v>
       </c>
-      <c r="L1298" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(H2,"x")</f>
-        <v>x</v>
+      <c r="L1298" s="0" t="n">
+        <f aca="false">ROUND(MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12),6)</f>
+        <v>0.126094</v>
       </c>
     </row>
     <row r="1299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1299" s="0" t="s">
         <v>1296</v>
       </c>
-      <c r="L1299" s="0" t="e">
-        <f aca="false">_xlfn.IFNA(H1,"x")</f>
-        <v>#DIV/0!</v>
+      <c r="L1299" s="6" t="e">
+        <f aca="false">MIRR({1,2,3},0.1,0.1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16765,52 +16807,52 @@
         <v>1297</v>
       </c>
       <c r="L1300" s="0" t="n">
-        <f aca="false">_xlfn.IFNA(5,"x")</f>
-        <v>5</v>
+        <f aca="false">ROUND(MIRR({-100,50,60},0.05,0.05),6)</f>
+        <v>0.06066</v>
       </c>
     </row>
     <row r="1301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1301" s="0" t="s">
         <v>1298</v>
       </c>
-      <c r="L1301" s="0" t="n">
-        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
-        <v>0</v>
+      <c r="L1301" s="6" t="e">
+        <f aca="false">MIRR({-100,-50},0.1,0.1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1302" s="0" t="s">
         <v>1299</v>
       </c>
-      <c r="L1302" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
-        <v>1</v>
+      <c r="L1302" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1303" s="0" t="s">
         <v>1300</v>
       </c>
-      <c r="L1303" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
-        <v>0</v>
+      <c r="L1303" s="0" t="n">
+        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1304" s="0" t="s">
         <v>1301</v>
       </c>
-      <c r="L1304" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
-        <v>1</v>
+      <c r="L1304" s="0" t="e">
+        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1305" s="0" t="s">
         <v>1302</v>
       </c>
-      <c r="L1305" s="1" t="b">
-        <f aca="false">_xlfn.XOR(1,0,0)</f>
+      <c r="L1305" s="0" t="n">
+        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
         <v>1</v>
       </c>
     </row>
@@ -16818,90 +16860,90 @@
       <c r="K1306" s="0" t="s">
         <v>1303</v>
       </c>
-      <c r="L1306" s="1" t="e">
-        <f aca="false">_xlfn.XOR(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1306" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1,"x")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="1307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1307" s="0" t="s">
         <v>1304</v>
       </c>
-      <c r="L1307" s="1" t="b">
-        <f aca="false">ISLOGICAL(TRUE())</f>
-        <v>1</v>
+      <c r="L1307" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1308" s="0" t="s">
         <v>1305</v>
       </c>
-      <c r="L1308" s="1" t="b">
-        <f aca="false">ISLOGICAL(1)</f>
-        <v>0</v>
+      <c r="L1308" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
+        <v>z</v>
       </c>
     </row>
     <row r="1309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1309" s="0" t="s">
         <v>1306</v>
       </c>
-      <c r="L1309" s="1" t="b">
-        <f aca="false">ISLOGICAL("TRUE")</f>
-        <v>0</v>
+      <c r="L1309" s="0" t="e">
+        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1310" s="0" t="s">
         <v>1307</v>
       </c>
-      <c r="L1310" s="1" t="b">
-        <f aca="false">ISLOGICAL(1=1)</f>
-        <v>1</v>
+      <c r="L1310" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1311" s="0" t="s">
         <v>1308</v>
       </c>
-      <c r="L1311" s="1" t="b">
-        <f aca="false">ISEVEN(2)</f>
-        <v>1</v>
+      <c r="L1311" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
+        <v>three</v>
       </c>
     </row>
     <row r="1312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1312" s="0" t="s">
         <v>1309</v>
       </c>
-      <c r="L1312" s="1" t="b">
-        <f aca="false">ISEVEN(3)</f>
-        <v>0</v>
+      <c r="L1312" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(H2,"x")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="1313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1313" s="0" t="s">
         <v>1310</v>
       </c>
-      <c r="L1313" s="1" t="b">
-        <f aca="false">ISEVEN(-2.9)</f>
-        <v>1</v>
+      <c r="L1313" s="0" t="e">
+        <f aca="false">_xlfn.IFNA(H1,"x")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1314" s="0" t="s">
         <v>1311</v>
       </c>
-      <c r="L1314" s="1" t="e">
-        <f aca="false">ISEVEN("a")</f>
-        <v>#VALUE!</v>
+      <c r="L1314" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(5,"x")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1315" s="0" t="s">
         <v>1312</v>
       </c>
-      <c r="L1315" s="1" t="b">
-        <f aca="false">ISEVEN(A2)</f>
-        <v>1</v>
+      <c r="L1315" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16909,8 +16951,8 @@
         <v>1313</v>
       </c>
       <c r="L1316" s="1" t="b">
-        <f aca="false">ISODD(2)</f>
-        <v>0</v>
+        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16918,8 +16960,8 @@
         <v>1314</v>
       </c>
       <c r="L1317" s="1" t="b">
-        <f aca="false">ISODD(3)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16927,7 +16969,7 @@
         <v>1315</v>
       </c>
       <c r="L1318" s="1" t="b">
-        <f aca="false">ISODD(-3.5)</f>
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
         <v>1</v>
       </c>
     </row>
@@ -16935,35 +16977,35 @@
       <c r="K1319" s="0" t="s">
         <v>1316</v>
       </c>
-      <c r="L1319" s="1" t="e">
-        <f aca="false">ISODD("a")</f>
-        <v>#VALUE!</v>
+      <c r="L1319" s="1" t="b">
+        <f aca="false">_xlfn.XOR(1,0,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1320" s="0" t="s">
         <v>1317</v>
       </c>
-      <c r="L1320" s="1" t="b">
-        <f aca="false">ISODD(A1)</f>
-        <v>1</v>
+      <c r="L1320" s="1" t="e">
+        <f aca="false">_xlfn.XOR(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1321" s="0" t="s">
         <v>1318</v>
       </c>
-      <c r="L1321" s="0" t="n">
-        <f aca="false">N(5)</f>
-        <v>5</v>
+      <c r="L1321" s="1" t="b">
+        <f aca="false">ISLOGICAL(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1322" s="0" t="s">
         <v>1319</v>
       </c>
-      <c r="L1322" s="0" t="n">
-        <f aca="false">N("a")</f>
+      <c r="L1322" s="1" t="b">
+        <f aca="false">ISLOGICAL(1)</f>
         <v>0</v>
       </c>
     </row>
@@ -16971,89 +17013,89 @@
       <c r="K1323" s="0" t="s">
         <v>1320</v>
       </c>
-      <c r="L1323" s="0" t="n">
-        <f aca="false">N(TRUE())</f>
-        <v>1</v>
+      <c r="L1323" s="1" t="b">
+        <f aca="false">ISLOGICAL("TRUE")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1324" s="0" t="s">
         <v>1321</v>
       </c>
-      <c r="L1324" s="0" t="e">
-        <f aca="false">N(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1324" s="1" t="b">
+        <f aca="false">ISLOGICAL(1=1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1325" s="0" t="s">
         <v>1322</v>
       </c>
-      <c r="L1325" s="0" t="n">
-        <f aca="false">N(B1)</f>
-        <v>0</v>
+      <c r="L1325" s="1" t="b">
+        <f aca="false">ISEVEN(2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1326" s="0" t="s">
         <v>1323</v>
       </c>
-      <c r="L1326" s="0" t="n">
-        <f aca="false">N(A3)</f>
-        <v>3</v>
+      <c r="L1326" s="1" t="b">
+        <f aca="false">ISEVEN(3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1327" s="0" t="s">
         <v>1324</v>
       </c>
-      <c r="L1327" s="0" t="str">
-        <f aca="false">T("a")</f>
-        <v>a</v>
+      <c r="L1327" s="1" t="b">
+        <f aca="false">ISEVEN(-2.9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1328" s="0" t="s">
         <v>1325</v>
       </c>
-      <c r="L1328" s="0" t="str">
-        <f aca="false">T(5)</f>
-        <v/>
+      <c r="L1328" s="1" t="e">
+        <f aca="false">ISEVEN("a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1329" s="0" t="s">
         <v>1326</v>
       </c>
-      <c r="L1329" s="0" t="str">
-        <f aca="false">T(B1)</f>
-        <v>apple</v>
+      <c r="L1329" s="1" t="b">
+        <f aca="false">ISEVEN(A2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1330" s="0" t="s">
         <v>1327</v>
       </c>
-      <c r="L1330" s="0" t="e">
-        <f aca="false">T(H2)</f>
-        <v>#N/A</v>
+      <c r="L1330" s="1" t="b">
+        <f aca="false">ISODD(2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1331" s="0" t="s">
         <v>1328</v>
       </c>
-      <c r="L1331" s="0" t="str">
-        <f aca="false">T(TRUE())</f>
-        <v/>
+      <c r="L1331" s="1" t="b">
+        <f aca="false">ISODD(3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1332" s="0" t="s">
         <v>1329</v>
       </c>
-      <c r="L1332" s="0" t="n">
-        <f aca="false">TYPE(1)</f>
+      <c r="L1332" s="1" t="b">
+        <f aca="false">ISODD(-3.5)</f>
         <v>1</v>
       </c>
     </row>
@@ -17061,17 +17103,17 @@
       <c r="K1333" s="0" t="s">
         <v>1330</v>
       </c>
-      <c r="L1333" s="0" t="n">
-        <f aca="false">TYPE("a")</f>
-        <v>2</v>
+      <c r="L1333" s="1" t="e">
+        <f aca="false">ISODD("a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1334" s="0" t="s">
         <v>1331</v>
       </c>
-      <c r="L1334" s="0" t="n">
-        <f aca="false">TYPE(TRUE())</f>
+      <c r="L1334" s="1" t="b">
+        <f aca="false">ISODD(A1)</f>
         <v>1</v>
       </c>
     </row>
@@ -17080,8 +17122,8 @@
         <v>1332</v>
       </c>
       <c r="L1335" s="0" t="n">
-        <f aca="false">TYPE(H1)</f>
-        <v>16</v>
+        <f aca="false">N(5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17089,26 +17131,26 @@
         <v>1333</v>
       </c>
       <c r="L1336" s="0" t="n">
-        <f aca="false">TYPE({1,2})</f>
-        <v>64</v>
+        <f aca="false">N("a")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1337" s="0" t="s">
         <v>1334</v>
       </c>
-      <c r="L1337" s="0" t="e">
-        <f aca="false">TYPE(A1:A2)</f>
-        <v>#VALUE!</v>
+      <c r="L1337" s="0" t="n">
+        <f aca="false">N(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1338" s="0" t="s">
         <v>1335</v>
       </c>
-      <c r="L1338" s="0" t="n">
-        <f aca="false">TYPE(A1)</f>
-        <v>1</v>
+      <c r="L1338" s="0" t="e">
+        <f aca="false">N(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17116,8 +17158,8 @@
         <v>1336</v>
       </c>
       <c r="L1339" s="0" t="n">
-        <f aca="false">TYPE(B1)</f>
-        <v>2</v>
+        <f aca="false">N(B1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17125,17 +17167,17 @@
         <v>1337</v>
       </c>
       <c r="L1340" s="0" t="n">
-        <f aca="true">CELL("row",A5)</f>
-        <v>5</v>
+        <f aca="false">N(A3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1341" s="0" t="s">
         <v>1338</v>
       </c>
-      <c r="L1341" s="0" t="n">
-        <f aca="true">CELL("col",C1)</f>
-        <v>3</v>
+      <c r="L1341" s="0" t="str">
+        <f aca="false">T("a")</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17143,26 +17185,26 @@
         <v>1339</v>
       </c>
       <c r="L1342" s="0" t="str">
-        <f aca="true">CELL("address",B2)</f>
-        <v>$B$2</v>
+        <f aca="false">T(5)</f>
+        <v/>
       </c>
     </row>
     <row r="1343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1343" s="0" t="s">
         <v>1340</v>
       </c>
-      <c r="L1343" s="0" t="n">
-        <f aca="true">CELL("contents",A3)</f>
-        <v>3</v>
+      <c r="L1343" s="0" t="str">
+        <f aca="false">T(B1)</f>
+        <v>apple</v>
       </c>
     </row>
     <row r="1344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1344" s="0" t="s">
         <v>1341</v>
       </c>
-      <c r="L1344" s="0" t="str">
-        <f aca="true">CELL("type",B1)</f>
-        <v>l</v>
+      <c r="L1344" s="0" t="e">
+        <f aca="false">T(H2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17170,314 +17212,314 @@
         <v>1342</v>
       </c>
       <c r="L1345" s="0" t="str">
-        <f aca="true">CELL("type",A1)</f>
-        <v>v</v>
+        <f aca="false">T(TRUE())</f>
+        <v/>
       </c>
     </row>
     <row r="1346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1346" s="0" t="s">
         <v>1343</v>
       </c>
-      <c r="L1346" s="0" t="str">
-        <f aca="true">CELL("type",J9)</f>
-        <v>b</v>
+      <c r="L1346" s="0" t="n">
+        <f aca="false">TYPE(1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1347" s="0" t="s">
         <v>1344</v>
       </c>
-      <c r="L1347" s="1" t="b">
-        <f aca="false">ISERR(H1)</f>
-        <v>1</v>
+      <c r="L1347" s="0" t="n">
+        <f aca="false">TYPE("a")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1348" s="0" t="s">
         <v>1345</v>
       </c>
-      <c r="L1348" s="1" t="b">
-        <f aca="false">ISERR(H2)</f>
-        <v>0</v>
+      <c r="L1348" s="0" t="n">
+        <f aca="false">TYPE(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1349" s="0" t="s">
         <v>1346</v>
       </c>
-      <c r="L1349" s="1" t="b">
-        <f aca="false">ISERR(1)</f>
-        <v>0</v>
+      <c r="L1349" s="0" t="n">
+        <f aca="false">TYPE(H1)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="1350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1350" s="0" t="s">
         <v>1347</v>
       </c>
-      <c r="L1350" s="1" t="b">
-        <f aca="false">ISERR(1/0)</f>
-        <v>1</v>
+      <c r="L1350" s="0" t="n">
+        <f aca="false">TYPE({1,2})</f>
+        <v>64</v>
       </c>
     </row>
     <row r="1351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1351" s="0" t="s">
         <v>1348</v>
       </c>
-      <c r="L1351" s="1" t="b">
-        <f aca="false">ISNONTEXT(1)</f>
-        <v>1</v>
+      <c r="L1351" s="0" t="e">
+        <f aca="false">TYPE(A1:A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1352" s="0" t="s">
         <v>1349</v>
       </c>
-      <c r="L1352" s="1" t="b">
-        <f aca="false">ISNONTEXT("a")</f>
-        <v>0</v>
+      <c r="L1352" s="0" t="n">
+        <f aca="false">TYPE(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1353" s="0" t="s">
         <v>1350</v>
       </c>
-      <c r="L1353" s="1" t="b">
-        <f aca="false">ISNONTEXT(J9)</f>
-        <v>1</v>
+      <c r="L1353" s="0" t="n">
+        <f aca="false">TYPE(B1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1354" s="0" t="s">
         <v>1351</v>
       </c>
-      <c r="L1354" s="1" t="b">
-        <f aca="false">ISNONTEXT(H1)</f>
-        <v>1</v>
+      <c r="L1354" s="0" t="n">
+        <f aca="true">CELL("row",A5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1355" s="0" t="s">
         <v>1352</v>
       </c>
-      <c r="L1355" s="1" t="b">
-        <f aca="false">ISREF(A1)</f>
-        <v>1</v>
+      <c r="L1355" s="0" t="n">
+        <f aca="true">CELL("col",C1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1356" s="0" t="s">
         <v>1353</v>
       </c>
-      <c r="L1356" s="1" t="b">
-        <f aca="false">ISREF(1)</f>
-        <v>0</v>
+      <c r="L1356" s="0" t="str">
+        <f aca="true">CELL("address",B2)</f>
+        <v>$B$2</v>
       </c>
     </row>
     <row r="1357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1357" s="0" t="s">
         <v>1354</v>
       </c>
-      <c r="L1357" s="1" t="b">
-        <f aca="false">ISREF(A1:B2)</f>
-        <v>1</v>
+      <c r="L1357" s="0" t="n">
+        <f aca="true">CELL("contents",A3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1358" s="0" t="s">
         <v>1355</v>
       </c>
-      <c r="L1358" s="1" t="b">
-        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
-        <v>1</v>
+      <c r="L1358" s="0" t="str">
+        <f aca="true">CELL("type",B1)</f>
+        <v>l</v>
       </c>
     </row>
     <row r="1359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1359" s="0" t="s">
         <v>1356</v>
       </c>
-      <c r="L1359" s="1" t="b">
-        <f aca="false">ISREF("A1")</f>
-        <v>0</v>
+      <c r="L1359" s="0" t="str">
+        <f aca="true">CELL("type",A1)</f>
+        <v>v</v>
       </c>
     </row>
     <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1360" s="0" t="s">
         <v>1357</v>
       </c>
-      <c r="L1360" s="0" t="n">
-        <f aca="false">SEARCH("an","banana")</f>
-        <v>2</v>
+      <c r="L1360" s="0" t="str">
+        <f aca="true">CELL("type",J9)</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1361" s="0" t="s">
         <v>1358</v>
       </c>
-      <c r="L1361" s="0" t="n">
-        <f aca="false">SEARCH("AN","banana",3)</f>
-        <v>4</v>
+      <c r="L1361" s="1" t="b">
+        <f aca="false">ISERR(H1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1362" s="0" t="s">
         <v>1359</v>
       </c>
-      <c r="L1362" s="0" t="n">
-        <f aca="false">SEARCH("b?n","banana")</f>
-        <v>1</v>
+      <c r="L1362" s="1" t="b">
+        <f aca="false">ISERR(H2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1363" s="0" t="s">
         <v>1360</v>
       </c>
-      <c r="L1363" s="0" t="e">
-        <f aca="false">SEARCH("z","banana")</f>
-        <v>#VALUE!</v>
+      <c r="L1363" s="1" t="b">
+        <f aca="false">ISERR(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1364" s="0" t="s">
         <v>1361</v>
       </c>
-      <c r="L1364" s="0" t="n">
-        <f aca="false">SEARCH("a*a","banana")</f>
-        <v>2</v>
+      <c r="L1364" s="1" t="b">
+        <f aca="false">ISERR(1/0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1365" s="0" t="s">
         <v>1362</v>
       </c>
-      <c r="L1365" s="0" t="n">
-        <f aca="false">SEARCH("~?","what?")</f>
-        <v>5</v>
+      <c r="L1365" s="1" t="b">
+        <f aca="false">ISNONTEXT(1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1366" s="0" t="s">
         <v>1363</v>
       </c>
-      <c r="L1366" s="0" t="str">
-        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
-        <v>abXYef</v>
+      <c r="L1366" s="1" t="b">
+        <f aca="false">ISNONTEXT("a")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1367" s="0" t="s">
         <v>1364</v>
       </c>
-      <c r="L1367" s="0" t="str">
-        <f aca="false">REPLACE("abc",5,1,"Z")</f>
-        <v>abcZ</v>
+      <c r="L1367" s="1" t="b">
+        <f aca="false">ISNONTEXT(J9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1368" s="0" t="s">
         <v>1365</v>
       </c>
-      <c r="L1368" s="0" t="str">
-        <f aca="false">REPLACE("abc",1,0,"Z")</f>
-        <v>Zabc</v>
+      <c r="L1368" s="1" t="b">
+        <f aca="false">ISNONTEXT(H1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1369" s="0" t="s">
         <v>1366</v>
       </c>
-      <c r="L1369" s="0" t="e">
-        <f aca="false">REPLACE("abc",0,1,"Z")</f>
-        <v>#VALUE!</v>
+      <c r="L1369" s="1" t="b">
+        <f aca="false">ISREF(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1370" s="0" t="s">
         <v>1367</v>
       </c>
-      <c r="L1370" s="0" t="str">
-        <f aca="false">REPLACE(B1,1,1,"A")</f>
-        <v>Apple</v>
+      <c r="L1370" s="1" t="b">
+        <f aca="false">ISREF(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1371" s="0" t="s">
         <v>1368</v>
       </c>
-      <c r="L1371" s="0" t="str">
-        <f aca="false">REPT("ab",3)</f>
-        <v>ababab</v>
+      <c r="L1371" s="1" t="b">
+        <f aca="false">ISREF(A1:B2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1372" s="0" t="s">
         <v>1369</v>
       </c>
-      <c r="L1372" s="0" t="str">
-        <f aca="false">REPT("x",0)</f>
-        <v/>
+      <c r="L1372" s="1" t="b">
+        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1373" s="0" t="s">
         <v>1370</v>
       </c>
-      <c r="L1373" s="0" t="e">
-        <f aca="false">REPT("x",-1)</f>
-        <v>#VALUE!</v>
+      <c r="L1373" s="1" t="b">
+        <f aca="false">ISREF("A1")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1374" s="0" t="s">
         <v>1371</v>
       </c>
-      <c r="L1374" s="0" t="str">
-        <f aca="false">REPT(A1,3)</f>
-        <v>111</v>
+      <c r="L1374" s="0" t="n">
+        <f aca="false">SEARCH("an","banana")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1375" s="0" t="s">
         <v>1372</v>
       </c>
-      <c r="L1375" s="0" t="str">
-        <f aca="false">REPT("-",2.9)</f>
-        <v>--</v>
+      <c r="L1375" s="0" t="n">
+        <f aca="false">SEARCH("AN","banana",3)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1376" s="0" t="s">
         <v>1373</v>
       </c>
-      <c r="L1376" s="0" t="str">
-        <f aca="false">PROPER("hello world")</f>
-        <v>Hello World</v>
+      <c r="L1376" s="0" t="n">
+        <f aca="false">SEARCH("b?n","banana")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1377" s="0" t="s">
         <v>1374</v>
       </c>
-      <c r="L1377" s="0" t="str">
-        <f aca="false">PROPER("o'neil mc-donald")</f>
-        <v>O'Neil Mc-Donald</v>
+      <c r="L1377" s="0" t="e">
+        <f aca="false">SEARCH("z","banana")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1378" s="0" t="s">
         <v>1375</v>
       </c>
-      <c r="L1378" s="0" t="str">
-        <f aca="false">PROPER("2nd place")</f>
-        <v>2Nd Place</v>
+      <c r="L1378" s="0" t="n">
+        <f aca="false">SEARCH("a*a","banana")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1379" s="0" t="s">
         <v>1376</v>
       </c>
-      <c r="L1379" s="0" t="str">
-        <f aca="false">PROPER(B1)</f>
-        <v>Apple</v>
+      <c r="L1379" s="0" t="n">
+        <f aca="false">SEARCH("~?","what?")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17485,8 +17527,8 @@
         <v>1377</v>
       </c>
       <c r="L1380" s="0" t="str">
-        <f aca="false">PROPER("ÀB cD")</f>
-        <v>Àb Cd</v>
+        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
+        <v>abXYef</v>
       </c>
     </row>
     <row r="1381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17494,8 +17536,8 @@
         <v>1378</v>
       </c>
       <c r="L1381" s="0" t="str">
-        <f aca="false">CHAR(65)</f>
-        <v>A</v>
+        <f aca="false">REPLACE("abc",5,1,"Z")</f>
+        <v>abcZ</v>
       </c>
     </row>
     <row r="1382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17503,26 +17545,26 @@
         <v>1379</v>
       </c>
       <c r="L1382" s="0" t="str">
-        <f aca="false">CHAR(97)</f>
-        <v>a</v>
+        <f aca="false">REPLACE("abc",1,0,"Z")</f>
+        <v>Zabc</v>
       </c>
     </row>
     <row r="1383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1383" s="0" t="s">
         <v>1380</v>
       </c>
-      <c r="L1383" s="0" t="str">
-        <f aca="false">CHAR(0)</f>
-        <v>_x0000_</v>
+      <c r="L1383" s="0" t="e">
+        <f aca="false">REPLACE("abc",0,1,"Z")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1384" s="0" t="s">
         <v>1381</v>
       </c>
-      <c r="L1384" s="0" t="e">
-        <f aca="false">CHAR(256)</f>
-        <v>#VALUE!</v>
+      <c r="L1384" s="0" t="str">
+        <f aca="false">REPLACE(B1,1,1,"A")</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="1385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17530,8 +17572,8 @@
         <v>1382</v>
       </c>
       <c r="L1385" s="0" t="str">
-        <f aca="false">CHAR(169)</f>
-        <v>�</v>
+        <f aca="false">REPT("ab",3)</f>
+        <v>ababab</v>
       </c>
     </row>
     <row r="1386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17539,89 +17581,89 @@
         <v>1383</v>
       </c>
       <c r="L1386" s="0" t="str">
-        <f aca="false">CHAR(233)</f>
-        <v>�</v>
+        <f aca="false">REPT("x",0)</f>
+        <v/>
       </c>
     </row>
     <row r="1387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1387" s="0" t="s">
         <v>1384</v>
       </c>
-      <c r="L1387" s="0" t="n">
-        <f aca="false">CODE("A")</f>
-        <v>65</v>
+      <c r="L1387" s="0" t="e">
+        <f aca="false">REPT("x",-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1388" s="0" t="s">
         <v>1385</v>
       </c>
-      <c r="L1388" s="0" t="n">
-        <f aca="false">CODE("apple")</f>
-        <v>97</v>
+      <c r="L1388" s="0" t="str">
+        <f aca="false">REPT(A1,3)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="1389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1389" s="0" t="s">
         <v>1386</v>
       </c>
-      <c r="L1389" s="0" t="n">
-        <f aca="false">CODE("")</f>
-        <v>0</v>
+      <c r="L1389" s="0" t="str">
+        <f aca="false">REPT("-",2.9)</f>
+        <v>--</v>
       </c>
     </row>
     <row r="1390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1390" s="0" t="s">
         <v>1387</v>
       </c>
-      <c r="L1390" s="0" t="n">
-        <f aca="false">CODE("é")</f>
-        <v>195</v>
+      <c r="L1390" s="0" t="str">
+        <f aca="false">PROPER("hello world")</f>
+        <v>Hello World</v>
       </c>
     </row>
     <row r="1391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1391" s="0" t="s">
         <v>1388</v>
       </c>
-      <c r="L1391" s="0" t="n">
-        <f aca="false">CODE(B1)</f>
-        <v>97</v>
+      <c r="L1391" s="0" t="str">
+        <f aca="false">PROPER("o'neil mc-donald")</f>
+        <v>O'Neil Mc-Donald</v>
       </c>
     </row>
     <row r="1392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1392" s="0" t="s">
         <v>1389</v>
       </c>
-      <c r="L1392" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE("A")</f>
-        <v>65</v>
+      <c r="L1392" s="0" t="str">
+        <f aca="false">PROPER("2nd place")</f>
+        <v>2Nd Place</v>
       </c>
     </row>
     <row r="1393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1393" s="0" t="s">
         <v>1390</v>
       </c>
-      <c r="L1393" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE("€")</f>
-        <v>8364</v>
+      <c r="L1393" s="0" t="str">
+        <f aca="false">PROPER(B1)</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="1394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1394" s="0" t="s">
         <v>1391</v>
       </c>
-      <c r="L1394" s="0" t="e">
-        <f aca="false">_xlfn.UNICODE("")</f>
-        <v>#VALUE!</v>
+      <c r="L1394" s="0" t="str">
+        <f aca="false">PROPER("ÀB cD")</f>
+        <v>Àb Cd</v>
       </c>
     </row>
     <row r="1395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1395" s="0" t="s">
         <v>1392</v>
       </c>
-      <c r="L1395" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE(B2)</f>
-        <v>98</v>
+      <c r="L1395" s="0" t="str">
+        <f aca="false">CHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="1396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17629,8 +17671,8 @@
         <v>1393</v>
       </c>
       <c r="L1396" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(65)</f>
-        <v>A</v>
+        <f aca="false">CHAR(97)</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17638,17 +17680,17 @@
         <v>1394</v>
       </c>
       <c r="L1397" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(8364)</f>
-        <v>€</v>
+        <f aca="false">CHAR(0)</f>
+        <v>_x0000_</v>
       </c>
     </row>
     <row r="1398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1398" s="0" t="s">
         <v>1395</v>
       </c>
-      <c r="L1398" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(0)</f>
-        <v>_x0000_</v>
+      <c r="L1398" s="0" t="e">
+        <f aca="false">CHAR(256)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17656,8 +17698,8 @@
         <v>1396</v>
       </c>
       <c r="L1399" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(97)</f>
-        <v>a</v>
+        <f aca="false">CHAR(169)</f>
+        <v>�</v>
       </c>
     </row>
     <row r="1400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17665,44 +17707,44 @@
         <v>1397</v>
       </c>
       <c r="L1400" s="0" t="str">
-        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
-        <v>ab</v>
+        <f aca="false">CHAR(233)</f>
+        <v>�</v>
       </c>
     </row>
     <row r="1401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1401" s="0" t="s">
         <v>1398</v>
       </c>
-      <c r="L1401" s="0" t="str">
-        <f aca="false">CLEAN(B1)</f>
-        <v>apple</v>
+      <c r="L1401" s="0" t="n">
+        <f aca="false">CODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="1402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1402" s="0" t="s">
         <v>1399</v>
       </c>
-      <c r="L1402" s="0" t="str">
-        <f aca="false">CLEAN("  x ")</f>
-        <v>  x </v>
+      <c r="L1402" s="0" t="n">
+        <f aca="false">CODE("apple")</f>
+        <v>97</v>
       </c>
     </row>
     <row r="1403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1403" s="0" t="s">
         <v>1400</v>
       </c>
-      <c r="L1403" s="0" t="str">
-        <f aca="false">CLEAN(A1)</f>
-        <v>1</v>
+      <c r="L1403" s="0" t="n">
+        <f aca="false">CODE("")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1404" s="0" t="s">
         <v>1401</v>
       </c>
-      <c r="L1404" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
-        <v>#VALUE!</v>
+      <c r="L1404" s="0" t="n">
+        <f aca="false">CODE("é")</f>
+        <v>195</v>
       </c>
     </row>
     <row r="1405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17710,8 +17752,8 @@
         <v>1402</v>
       </c>
       <c r="L1405" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
-        <v>1234.5</v>
+        <f aca="false">CODE(B1)</f>
+        <v>97</v>
       </c>
     </row>
     <row r="1406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17719,17 +17761,17 @@
         <v>1403</v>
       </c>
       <c r="L1406" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
-        <v>0.05</v>
+        <f aca="false">_xlfn.UNICODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="1407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1407" s="0" t="s">
         <v>1404</v>
       </c>
-      <c r="L1407" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("")</f>
-        <v>#VALUE!</v>
+      <c r="L1407" s="0" t="n">
+        <f aca="false">_xlfn.UNICODE("€")</f>
+        <v>8364</v>
       </c>
     </row>
     <row r="1408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17737,7 +17779,7 @@
         <v>1405</v>
       </c>
       <c r="L1408" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
+        <f aca="false">_xlfn.UNICODE("")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -17746,26 +17788,26 @@
         <v>1406</v>
       </c>
       <c r="L1409" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
-        <v>0.0001</v>
+        <f aca="false">_xlfn.UNICODE(B2)</f>
+        <v>98</v>
       </c>
     </row>
     <row r="1410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1410" s="0" t="s">
         <v>1407</v>
       </c>
-      <c r="L1410" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
-        <v>#VALUE!</v>
+      <c r="L1410" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="1411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1411" s="0" t="s">
         <v>1408</v>
       </c>
-      <c r="L1411" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
-        <v>12</v>
+      <c r="L1411" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(8364)</f>
+        <v>€</v>
       </c>
     </row>
     <row r="1412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17773,8 +17815,8 @@
         <v>1409</v>
       </c>
       <c r="L1412" s="0" t="str">
-        <f aca="false">FIXED(1234.567,1)</f>
-        <v>1,234.6</v>
+        <f aca="false">_xlfn.UNICHAR(0)</f>
+        <v>_x0000_</v>
       </c>
     </row>
     <row r="1413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17782,8 +17824,8 @@
         <v>1410</v>
       </c>
       <c r="L1413" s="0" t="str">
-        <f aca="false">FIXED(1234.567,-1)</f>
-        <v>1,230</v>
+        <f aca="false">_xlfn.UNICHAR(97)</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17791,8 +17833,8 @@
         <v>1411</v>
       </c>
       <c r="L1414" s="0" t="str">
-        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
-        <v>-1234.57</v>
+        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
+        <v>ab</v>
       </c>
     </row>
     <row r="1415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17800,8 +17842,8 @@
         <v>1412</v>
       </c>
       <c r="L1415" s="0" t="str">
-        <f aca="false">FIXED(0.5,0)</f>
-        <v>1</v>
+        <f aca="false">CLEAN(B1)</f>
+        <v>apple</v>
       </c>
     </row>
     <row r="1416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17809,8 +17851,8 @@
         <v>1413</v>
       </c>
       <c r="L1416" s="0" t="str">
-        <f aca="false">FIXED(1234567)</f>
-        <v>1,234,567.00</v>
+        <f aca="false">CLEAN("  x ")</f>
+        <v>  x </v>
       </c>
     </row>
     <row r="1417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17818,71 +17860,71 @@
         <v>1414</v>
       </c>
       <c r="L1417" s="0" t="str">
-        <f aca="false">FIXED(A1)</f>
-        <v>1.00</v>
+        <f aca="false">CLEAN(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1418" s="0" t="s">
         <v>1415</v>
       </c>
-      <c r="L1418" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
-        <v>apple,banana,cherry</v>
+      <c r="L1418" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1419" s="0" t="s">
         <v>1416</v>
       </c>
-      <c r="L1419" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
-        <v>1-2-3</v>
+      <c r="L1419" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
+        <v>1234.5</v>
       </c>
     </row>
     <row r="1420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1420" s="0" t="s">
         <v>1417</v>
       </c>
-      <c r="L1420" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
-        <v>a, b</v>
+      <c r="L1420" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="1421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1421" s="0" t="s">
         <v>1418</v>
       </c>
-      <c r="L1421" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
-        <v>a,,b</v>
+      <c r="L1421" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1422" s="0" t="s">
         <v>1419</v>
       </c>
-      <c r="L1422" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
-        <v>applebanana!</v>
+      <c r="L1422" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1423" s="0" t="s">
         <v>1420</v>
       </c>
-      <c r="L1423" s="0" t="e">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
-        <v>#DIV/0!</v>
+      <c r="L1423" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="1424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1424" s="0" t="s">
         <v>1421</v>
       </c>
-      <c r="L1424" s="0" t="n">
-        <f aca="false">DATEVALUE("2024-01-15")</f>
-        <v>45306</v>
+      <c r="L1424" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17890,125 +17932,125 @@
         <v>1422</v>
       </c>
       <c r="L1425" s="0" t="n">
-        <f aca="false">DATEVALUE("1/15/2024")</f>
-        <v>45306</v>
+        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1426" s="0" t="s">
         <v>1423</v>
       </c>
-      <c r="L1426" s="0" t="n">
-        <f aca="false">DATEVALUE("2024-12-31")</f>
-        <v>45657</v>
+      <c r="L1426" s="0" t="str">
+        <f aca="false">FIXED(1234.567,1)</f>
+        <v>1,234.6</v>
       </c>
     </row>
     <row r="1427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1427" s="0" t="s">
         <v>1424</v>
       </c>
-      <c r="L1427" s="0" t="e">
-        <f aca="false">DATEVALUE("abc")</f>
-        <v>#VALUE!</v>
+      <c r="L1427" s="0" t="str">
+        <f aca="false">FIXED(1234.567,-1)</f>
+        <v>1,230</v>
       </c>
     </row>
     <row r="1428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1428" s="0" t="s">
         <v>1425</v>
       </c>
-      <c r="L1428" s="0" t="e">
-        <f aca="false">DATEVALUE(5)</f>
-        <v>#VALUE!</v>
+      <c r="L1428" s="0" t="str">
+        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
+        <v>-1234.57</v>
       </c>
     </row>
     <row r="1429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1429" s="0" t="s">
         <v>1426</v>
       </c>
-      <c r="L1429" s="0" t="n">
-        <f aca="false">TIMEVALUE("12:00")</f>
-        <v>0.5</v>
+      <c r="L1429" s="0" t="str">
+        <f aca="false">FIXED(0.5,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1430" s="0" t="s">
         <v>1427</v>
       </c>
-      <c r="L1430" s="0" t="n">
-        <f aca="false">TIMEVALUE("6:00 PM")</f>
-        <v>0.75</v>
+      <c r="L1430" s="0" t="str">
+        <f aca="false">FIXED(1234567)</f>
+        <v>1,234,567.00</v>
       </c>
     </row>
     <row r="1431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1431" s="0" t="s">
         <v>1428</v>
       </c>
-      <c r="L1431" s="0" t="n">
-        <f aca="false">TIMEVALUE("18:30:30")</f>
-        <v>0.771180555555556</v>
+      <c r="L1431" s="0" t="str">
+        <f aca="false">FIXED(A1)</f>
+        <v>1.00</v>
       </c>
     </row>
     <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1432" s="0" t="s">
         <v>1429</v>
       </c>
-      <c r="L1432" s="0" t="e">
-        <f aca="false">TIMEVALUE("xx")</f>
-        <v>#VALUE!</v>
+      <c r="L1432" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
+        <v>apple,banana,cherry</v>
       </c>
     </row>
     <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1433" s="0" t="s">
         <v>1430</v>
       </c>
-      <c r="L1433" s="0" t="n">
-        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
-        <v>0.25</v>
+      <c r="L1433" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
+        <v>1-2-3</v>
       </c>
     </row>
     <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1434" s="0" t="s">
         <v>1431</v>
       </c>
-      <c r="L1434" s="8" t="n">
-        <f aca="false">TIME(12,0,0)</f>
-        <v>0.5</v>
+      <c r="L1434" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
+        <v>a, b</v>
       </c>
     </row>
     <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1435" s="0" t="s">
         <v>1432</v>
       </c>
-      <c r="L1435" s="8" t="n">
-        <f aca="false">TIME(25,0,0)</f>
-        <v>0.0416666666666667</v>
+      <c r="L1435" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
+        <v>a,,b</v>
       </c>
     </row>
     <row r="1436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1436" s="0" t="s">
         <v>1433</v>
       </c>
-      <c r="L1436" s="8" t="n">
-        <f aca="false">TIME(0,90,0)</f>
-        <v>0.0625</v>
+      <c r="L1436" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
+        <v>applebanana!</v>
       </c>
     </row>
     <row r="1437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1437" s="0" t="s">
         <v>1434</v>
       </c>
-      <c r="L1437" s="8" t="n">
-        <f aca="false">TIME(1,2,3)</f>
-        <v>0.0430902777777778</v>
+      <c r="L1437" s="0" t="e">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1438" s="0" t="s">
         <v>1435</v>
       </c>
-      <c r="L1438" s="8" t="e">
-        <f aca="false">TIME(-1,0,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1438" s="0" t="n">
+        <f aca="false">DATEVALUE("2024-01-15")</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18016,8 +18058,8 @@
         <v>1436</v>
       </c>
       <c r="L1439" s="0" t="n">
-        <f aca="false">HOUR(E3)</f>
-        <v>18</v>
+        <f aca="false">DATEVALUE("1/15/2024")</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18025,26 +18067,26 @@
         <v>1437</v>
       </c>
       <c r="L1440" s="0" t="n">
-        <f aca="false">HOUR(0.5)</f>
-        <v>12</v>
+        <f aca="false">DATEVALUE("2024-12-31")</f>
+        <v>45657</v>
       </c>
     </row>
     <row r="1441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1441" s="0" t="s">
         <v>1438</v>
       </c>
-      <c r="L1441" s="0" t="n">
-        <f aca="false">HOUR("18:30")</f>
-        <v>18</v>
+      <c r="L1441" s="0" t="e">
+        <f aca="false">DATEVALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1442" s="0" t="s">
         <v>1439</v>
       </c>
-      <c r="L1442" s="0" t="n">
-        <f aca="false">HOUR(-1)</f>
-        <v>0</v>
+      <c r="L1442" s="0" t="e">
+        <f aca="false">DATEVALUE(5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18052,8 +18094,8 @@
         <v>1440</v>
       </c>
       <c r="L1443" s="0" t="n">
-        <f aca="false">MINUTE(E3)</f>
-        <v>0</v>
+        <f aca="false">TIMEVALUE("12:00")</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18061,8 +18103,8 @@
         <v>1441</v>
       </c>
       <c r="L1444" s="0" t="n">
-        <f aca="false">MINUTE("18:30:45")</f>
-        <v>30</v>
+        <f aca="false">TIMEVALUE("6:00 PM")</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18070,17 +18112,17 @@
         <v>1442</v>
       </c>
       <c r="L1445" s="0" t="n">
-        <f aca="false">MINUTE(0.7712)</f>
-        <v>30</v>
+        <f aca="false">TIMEVALUE("18:30:30")</f>
+        <v>0.771180555555556</v>
       </c>
     </row>
     <row r="1446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1446" s="0" t="s">
         <v>1443</v>
       </c>
-      <c r="L1446" s="0" t="n">
-        <f aca="false">MINUTE(-1)</f>
-        <v>0</v>
+      <c r="L1446" s="0" t="e">
+        <f aca="false">TIMEVALUE("xx")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18088,53 +18130,53 @@
         <v>1444</v>
       </c>
       <c r="L1447" s="0" t="n">
-        <f aca="false">SECOND("18:30:45")</f>
-        <v>45</v>
+        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="1448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1448" s="0" t="s">
         <v>1445</v>
       </c>
-      <c r="L1448" s="0" t="n">
-        <f aca="false">SECOND(0.5)</f>
-        <v>0</v>
+      <c r="L1448" s="8" t="n">
+        <f aca="false">TIME(12,0,0)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1449" s="0" t="s">
         <v>1446</v>
       </c>
-      <c r="L1449" s="0" t="n">
-        <f aca="false">SECOND(TIME(1,2,3))</f>
-        <v>3</v>
+      <c r="L1449" s="8" t="n">
+        <f aca="false">TIME(25,0,0)</f>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="1450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1450" s="0" t="s">
         <v>1447</v>
       </c>
-      <c r="L1450" s="0" t="n">
-        <f aca="false">SECOND(-1)</f>
-        <v>0</v>
+      <c r="L1450" s="8" t="n">
+        <f aca="false">TIME(0,90,0)</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="1451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1451" s="0" t="s">
         <v>1448</v>
       </c>
-      <c r="L1451" s="0" t="n">
-        <f aca="false">EDATE(E1,1)</f>
-        <v>45337</v>
+      <c r="L1451" s="8" t="n">
+        <f aca="false">TIME(1,2,3)</f>
+        <v>0.0430902777777778</v>
       </c>
     </row>
     <row r="1452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1452" s="0" t="s">
         <v>1449</v>
       </c>
-      <c r="L1452" s="0" t="n">
-        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
-        <v>45351</v>
+      <c r="L1452" s="8" t="e">
+        <f aca="false">TIME(-1,0,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18142,8 +18184,8 @@
         <v>1450</v>
       </c>
       <c r="L1453" s="0" t="n">
-        <f aca="false">EDATE(E1,-1)</f>
-        <v>45275</v>
+        <f aca="false">HOUR(E3)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="1454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18151,8 +18193,8 @@
         <v>1451</v>
       </c>
       <c r="L1454" s="0" t="n">
-        <f aca="false">EDATE(E1,0)</f>
-        <v>45306</v>
+        <f aca="false">HOUR(0.5)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18160,8 +18202,8 @@
         <v>1452</v>
       </c>
       <c r="L1455" s="0" t="n">
-        <f aca="false">EDATE(E1,12)</f>
-        <v>45672</v>
+        <f aca="false">HOUR("18:30")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="1456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18169,8 +18211,8 @@
         <v>1453</v>
       </c>
       <c r="L1456" s="0" t="n">
-        <f aca="false">EOMONTH(E1,0)</f>
-        <v>45322</v>
+        <f aca="false">HOUR(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18178,8 +18220,8 @@
         <v>1454</v>
       </c>
       <c r="L1457" s="0" t="n">
-        <f aca="false">EOMONTH(E1,1)</f>
-        <v>45351</v>
+        <f aca="false">MINUTE(E3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18187,8 +18229,8 @@
         <v>1455</v>
       </c>
       <c r="L1458" s="0" t="n">
-        <f aca="false">EOMONTH(E1,-1)</f>
-        <v>45291</v>
+        <f aca="false">MINUTE("18:30:45")</f>
+        <v>30</v>
       </c>
     </row>
     <row r="1459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18196,8 +18238,8 @@
         <v>1456</v>
       </c>
       <c r="L1459" s="0" t="n">
-        <f aca="false">EOMONTH(E2,2)</f>
-        <v>45716</v>
+        <f aca="false">MINUTE(0.7712)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="1460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18205,8 +18247,8 @@
         <v>1457</v>
       </c>
       <c r="L1460" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
-        <v>23</v>
+        <f aca="false">MINUTE(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18214,8 +18256,8 @@
         <v>1458</v>
       </c>
       <c r="L1461" s="0" t="n">
-        <f aca="false">NETWORKDAYS(E1,E2)</f>
-        <v>252</v>
+        <f aca="false">SECOND("18:30:45")</f>
+        <v>45</v>
       </c>
     </row>
     <row r="1462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18223,8 +18265,8 @@
         <v>1459</v>
       </c>
       <c r="L1462" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
-        <v>22</v>
+        <f aca="false">SECOND(0.5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18232,8 +18274,8 @@
         <v>1460</v>
       </c>
       <c r="L1463" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
-        <v>-23</v>
+        <f aca="false">SECOND(TIME(1,2,3))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18241,8 +18283,8 @@
         <v>1461</v>
       </c>
       <c r="L1464" s="0" t="n">
-        <f aca="false">NETWORKDAYS(E1,E1)</f>
-        <v>1</v>
+        <f aca="false">SECOND(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18250,8 +18292,8 @@
         <v>1462</v>
       </c>
       <c r="L1465" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
-        <v>27</v>
+        <f aca="false">EDATE(E1,1)</f>
+        <v>45337</v>
       </c>
     </row>
     <row r="1466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18259,8 +18301,8 @@
         <v>1463</v>
       </c>
       <c r="L1466" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
-        <v>23</v>
+        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
+        <v>45351</v>
       </c>
     </row>
     <row r="1467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18268,8 +18310,8 @@
         <v>1464</v>
       </c>
       <c r="L1467" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
-        <v>22</v>
+        <f aca="false">EDATE(E1,-1)</f>
+        <v>45275</v>
       </c>
     </row>
     <row r="1468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18277,17 +18319,17 @@
         <v>1465</v>
       </c>
       <c r="L1468" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
-        <v>22</v>
+        <f aca="false">EDATE(E1,0)</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1469" s="0" t="s">
         <v>1466</v>
       </c>
-      <c r="L1469" s="0" t="e">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
-        <v>#VALUE!</v>
+      <c r="L1469" s="0" t="n">
+        <f aca="false">EDATE(E1,12)</f>
+        <v>45672</v>
       </c>
     </row>
     <row r="1470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18295,8 +18337,8 @@
         <v>1467</v>
       </c>
       <c r="L1470" s="0" t="n">
-        <f aca="false">WORKDAY(E1,1)</f>
-        <v>45307</v>
+        <f aca="false">EOMONTH(E1,0)</f>
+        <v>45322</v>
       </c>
     </row>
     <row r="1471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18304,8 +18346,8 @@
         <v>1468</v>
       </c>
       <c r="L1471" s="0" t="n">
-        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
-        <v>45313</v>
+        <f aca="false">EOMONTH(E1,1)</f>
+        <v>45351</v>
       </c>
     </row>
     <row r="1472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18313,8 +18355,8 @@
         <v>1469</v>
       </c>
       <c r="L1472" s="0" t="n">
-        <f aca="false">WORKDAY(E1,-1)</f>
-        <v>45303</v>
+        <f aca="false">EOMONTH(E1,-1)</f>
+        <v>45291</v>
       </c>
     </row>
     <row r="1473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18322,8 +18364,8 @@
         <v>1470</v>
       </c>
       <c r="L1473" s="0" t="n">
-        <f aca="false">WORKDAY(E1,5,E1+1)</f>
-        <v>45314</v>
+        <f aca="false">EOMONTH(E2,2)</f>
+        <v>45716</v>
       </c>
     </row>
     <row r="1474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18331,44 +18373,44 @@
         <v>1471</v>
       </c>
       <c r="L1474" s="0" t="n">
-        <f aca="false">WORKDAY(E1,0)</f>
-        <v>45306</v>
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
+        <v>23</v>
       </c>
     </row>
     <row r="1475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1475" s="0" t="s">
         <v>1472</v>
       </c>
-      <c r="L1475" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
-        <v>45307</v>
+      <c r="L1475" s="0" t="n">
+        <f aca="false">NETWORKDAYS(E1,E2)</f>
+        <v>252</v>
       </c>
     </row>
     <row r="1476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1476" s="0" t="s">
         <v>1473</v>
       </c>
-      <c r="L1476" s="3" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
-        <v>45313</v>
+      <c r="L1476" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1477" s="0" t="s">
         <v>1474</v>
       </c>
-      <c r="L1477" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
-        <v>45313</v>
+      <c r="L1477" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
+        <v>-23</v>
       </c>
     </row>
     <row r="1478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1478" s="0" t="s">
         <v>1475</v>
       </c>
-      <c r="L1478" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
-        <v>45303</v>
+      <c r="L1478" s="0" t="n">
+        <f aca="false">NETWORKDAYS(E1,E1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18376,8 +18418,8 @@
         <v>1476</v>
       </c>
       <c r="L1479" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
-        <v>4</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="1480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18385,8 +18427,8 @@
         <v>1477</v>
       </c>
       <c r="L1480" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
-        <v>48</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
+        <v>23</v>
       </c>
     </row>
     <row r="1481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18394,8 +18436,8 @@
         <v>1478</v>
       </c>
       <c r="L1481" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
-        <v>1461</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18403,17 +18445,17 @@
         <v>1479</v>
       </c>
       <c r="L1482" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
-        <v>5</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1483" s="0" t="s">
         <v>1480</v>
       </c>
-      <c r="L1483" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
-        <v>6</v>
+      <c r="L1483" s="0" t="e">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18421,26 +18463,26 @@
         <v>1481</v>
       </c>
       <c r="L1484" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
-        <v>209</v>
+        <f aca="false">WORKDAY(E1,1)</f>
+        <v>45307</v>
       </c>
     </row>
     <row r="1485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1485" s="0" t="s">
         <v>1482</v>
       </c>
-      <c r="L1485" s="0" t="e">
-        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
-        <v>#VALUE!</v>
+      <c r="L1485" s="0" t="n">
+        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1486" s="0" t="s">
         <v>1483</v>
       </c>
-      <c r="L1486" s="0" t="e">
-        <f aca="false">DATEDIF(E1,E2,"X")</f>
-        <v>#VALUE!</v>
+      <c r="L1486" s="0" t="n">
+        <f aca="false">WORKDAY(E1,-1)</f>
+        <v>45303</v>
       </c>
     </row>
     <row r="1487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18448,8 +18490,8 @@
         <v>1484</v>
       </c>
       <c r="L1487" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
-        <v>0.5</v>
+        <f aca="false">WORKDAY(E1,5,E1+1)</f>
+        <v>45314</v>
       </c>
     </row>
     <row r="1488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18457,44 +18499,44 @@
         <v>1485</v>
       </c>
       <c r="L1488" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
-        <v>0.495890410958904</v>
+        <f aca="false">WORKDAY(E1,0)</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1489" s="0" t="s">
         <v>1486</v>
       </c>
-      <c r="L1489" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
-        <v>0.502777777777778</v>
+      <c r="L1489" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
+        <v>45307</v>
       </c>
     </row>
     <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1490" s="0" t="s">
         <v>1487</v>
       </c>
-      <c r="L1490" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
-        <v>0.495890410958904</v>
+      <c r="L1490" s="3" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1491" s="0" t="s">
         <v>1488</v>
       </c>
-      <c r="L1491" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
-        <v>0.5</v>
+      <c r="L1491" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1492" s="0" t="s">
         <v>1489</v>
       </c>
-      <c r="L1492" s="0" t="n">
-        <f aca="false">YEARFRAC(E1,E2)</f>
-        <v>0.961111111111111</v>
+      <c r="L1492" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
+        <v>45303</v>
       </c>
     </row>
     <row r="1493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18502,8 +18544,8 @@
         <v>1490</v>
       </c>
       <c r="L1493" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
-        <v>3.99835796387521</v>
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18511,17 +18553,17 @@
         <v>1491</v>
       </c>
       <c r="L1494" s="0" t="n">
-        <f aca="false">YEARFRAC(E2,E1)</f>
-        <v>0.961111111111111</v>
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
+        <v>48</v>
       </c>
     </row>
     <row r="1495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1495" s="0" t="s">
         <v>1492</v>
       </c>
-      <c r="L1495" s="0" t="e">
-        <f aca="false">YEARFRAC(E1,E2,5)</f>
-        <v>#VALUE!</v>
+      <c r="L1495" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
+        <v>1461</v>
       </c>
     </row>
     <row r="1496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18529,8 +18571,8 @@
         <v>1493</v>
       </c>
       <c r="L1496" s="0" t="n">
-        <f aca="false">WEEKNUM(E1,1)</f>
-        <v>3</v>
+        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18538,8 +18580,8 @@
         <v>1494</v>
       </c>
       <c r="L1497" s="0" t="n">
-        <f aca="false">WEEKNUM(E1,2)</f>
-        <v>3</v>
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18547,35 +18589,35 @@
         <v>1495</v>
       </c>
       <c r="L1498" s="0" t="n">
-        <f aca="false">WEEKNUM(E2,1)</f>
-        <v>1</v>
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
+        <v>209</v>
       </c>
     </row>
     <row r="1499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1499" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="L1499" s="0" t="n">
-        <f aca="false">WEEKNUM(E2,21)</f>
-        <v>1</v>
+      <c r="L1499" s="0" t="e">
+        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1500" s="0" t="s">
         <v>1497</v>
       </c>
-      <c r="L1500" s="0" t="n">
-        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
-        <v>1</v>
+      <c r="L1500" s="0" t="e">
+        <f aca="false">DATEDIF(E1,E2,"X")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1501" s="0" t="s">
         <v>1498</v>
       </c>
-      <c r="L1501" s="0" t="e">
-        <f aca="false">WEEKNUM(E1,3)</f>
-        <v>#VALUE!</v>
+      <c r="L1501" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18583,8 +18625,8 @@
         <v>1499</v>
       </c>
       <c r="L1502" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
-        <v>3</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
+        <v>0.495890410958904</v>
       </c>
     </row>
     <row r="1503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18592,8 +18634,8 @@
         <v>1500</v>
       </c>
       <c r="L1503" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
-        <v>1</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
+        <v>0.502777777777778</v>
       </c>
     </row>
     <row r="1504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18601,8 +18643,8 @@
         <v>1501</v>
       </c>
       <c r="L1504" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
-        <v>53</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
+        <v>0.495890410958904</v>
       </c>
     </row>
     <row r="1505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18610,8 +18652,8 @@
         <v>1502</v>
       </c>
       <c r="L1505" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
-        <v>53</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18619,8 +18661,8 @@
         <v>1503</v>
       </c>
       <c r="L1506" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
-        <v>53</v>
+        <f aca="false">YEARFRAC(E1,E2)</f>
+        <v>0.961111111111111</v>
       </c>
     </row>
     <row r="1507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18628,8 +18670,8 @@
         <v>1504</v>
       </c>
       <c r="L1507" s="0" t="n">
-        <f aca="false">ROWS(A1:A6)</f>
-        <v>6</v>
+        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
+        <v>3.99835796387521</v>
       </c>
     </row>
     <row r="1508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18637,17 +18679,17 @@
         <v>1505</v>
       </c>
       <c r="L1508" s="0" t="n">
-        <f aca="false">ROWS(A1:C3)</f>
-        <v>3</v>
+        <f aca="false">YEARFRAC(E2,E1)</f>
+        <v>0.961111111111111</v>
       </c>
     </row>
     <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1509" s="0" t="s">
         <v>1506</v>
       </c>
-      <c r="L1509" s="0" t="n">
-        <f aca="false">ROWS(A:A)</f>
-        <v>1048576</v>
+      <c r="L1509" s="0" t="e">
+        <f aca="false">YEARFRAC(E1,E2,5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18655,8 +18697,8 @@
         <v>1507</v>
       </c>
       <c r="L1510" s="0" t="n">
-        <f aca="false">ROWS({1,2;3,4})</f>
-        <v>2</v>
+        <f aca="false">WEEKNUM(E1,1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18664,7 +18706,7 @@
         <v>1508</v>
       </c>
       <c r="L1511" s="0" t="n">
-        <f aca="false">COLUMNS(A1:C3)</f>
+        <f aca="false">WEEKNUM(E1,2)</f>
         <v>3</v>
       </c>
     </row>
@@ -18673,8 +18715,8 @@
         <v>1509</v>
       </c>
       <c r="L1512" s="0" t="n">
-        <f aca="false">COLUMNS(A:C)</f>
-        <v>3</v>
+        <f aca="false">WEEKNUM(E2,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18682,8 +18724,8 @@
         <v>1510</v>
       </c>
       <c r="L1513" s="0" t="n">
-        <f aca="false">COLUMNS(1:1)</f>
-        <v>16384</v>
+        <f aca="false">WEEKNUM(E2,21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18691,53 +18733,53 @@
         <v>1511</v>
       </c>
       <c r="L1514" s="0" t="n">
-        <f aca="false">COLUMNS({1,2;3,4})</f>
-        <v>2</v>
+        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1515" s="0" t="s">
         <v>1512</v>
       </c>
-      <c r="L1515" s="0" t="str">
-        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1515" s="0" t="e">
+        <f aca="false">WEEKNUM(E1,3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1516" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="L1516" s="0" t="str">
-        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1516" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1517" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="L1517" s="0" t="e">
-        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
-        <v>#N/A</v>
+      <c r="L1517" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1518" s="0" t="s">
         <v>1515</v>
       </c>
-      <c r="L1518" s="0" t="str">
-        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
-        <v>fig</v>
+      <c r="L1518" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1519" s="0" t="s">
         <v>1516</v>
       </c>
-      <c r="L1519" s="0" t="str">
-        <f aca="false">LOOKUP(2,A1:B6)</f>
-        <v>banana</v>
+      <c r="L1519" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18745,8 +18787,8 @@
         <v>1517</v>
       </c>
       <c r="L1520" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18754,8 +18796,8 @@
         <v>1518</v>
       </c>
       <c r="L1521" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
-        <v>3</v>
+        <f aca="false">ROWS(A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18763,7 +18805,7 @@
         <v>1519</v>
       </c>
       <c r="L1522" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
+        <f aca="false">ROWS(A1:C3)</f>
         <v>3</v>
       </c>
     </row>
@@ -18772,8 +18814,8 @@
         <v>1520</v>
       </c>
       <c r="L1523" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
-        <v>4</v>
+        <f aca="false">ROWS(A:A)</f>
+        <v>1048576</v>
       </c>
     </row>
     <row r="1524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18781,17 +18823,17 @@
         <v>1521</v>
       </c>
       <c r="L1524" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
-        <v>3</v>
+        <f aca="false">ROWS({1,2;3,4})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1525" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="L1525" s="0" t="e">
-        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
-        <v>#N/A</v>
+      <c r="L1525" s="0" t="n">
+        <f aca="false">COLUMNS(A1:C3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18799,7 +18841,7 @@
         <v>1523</v>
       </c>
       <c r="L1526" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
+        <f aca="false">COLUMNS(A:C)</f>
         <v>3</v>
       </c>
     </row>
@@ -18807,18 +18849,18 @@
       <c r="K1527" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="L1527" s="0" t="e">
-        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
-        <v>#VALUE!</v>
+      <c r="L1527" s="0" t="n">
+        <f aca="false">COLUMNS(1:1)</f>
+        <v>16384</v>
       </c>
     </row>
     <row r="1528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1528" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="L1528" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1528" s="0" t="n">
+        <f aca="false">COLUMNS({1,2;3,4})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18826,53 +18868,53 @@
         <v>1526</v>
       </c>
       <c r="L1529" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
-        <v>none</v>
+        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1530" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="L1530" s="0" t="e">
-        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
-        <v>#N/A</v>
+      <c r="L1530" s="0" t="str">
+        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1531" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="L1531" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
-        <v>cherry</v>
+      <c r="L1531" s="0" t="e">
+        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1532" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="L1532" s="0" t="n">
-        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
-        <v>6</v>
+      <c r="L1532" s="0" t="str">
+        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
+        <v>fig</v>
       </c>
     </row>
     <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1533" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="L1533" s="0" t="n">
-        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
-        <v>100</v>
+      <c r="L1533" s="0" t="str">
+        <f aca="false">LOOKUP(2,A1:B6)</f>
+        <v>banana</v>
       </c>
     </row>
     <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1534" s="0" t="s">
         <v>1531</v>
       </c>
-      <c r="L1534" s="0" t="e">
-        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
-        <v>#VALUE!</v>
+      <c r="L1534" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18880,8 +18922,8 @@
         <v>1532</v>
       </c>
       <c r="L1535" s="0" t="n">
-        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
-        <v>6</v>
+        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18889,8 +18931,8 @@
         <v>1533</v>
       </c>
       <c r="L1536" s="0" t="n">
-        <f aca="true">INDIRECT("A1")</f>
-        <v>1</v>
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18898,8 +18940,8 @@
         <v>1534</v>
       </c>
       <c r="L1537" s="0" t="n">
-        <f aca="true">INDIRECT("A"&amp;3)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18907,17 +18949,17 @@
         <v>1535</v>
       </c>
       <c r="L1538" s="0" t="n">
-        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
-        <v>6</v>
+        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1539" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="L1539" s="0" t="n">
-        <f aca="true">INDIRECT("Other!A1")</f>
-        <v>7</v>
+      <c r="L1539" s="0" t="e">
+        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18925,8 +18967,8 @@
         <v>1537</v>
       </c>
       <c r="L1540" s="0" t="n">
-        <f aca="true">INDIRECT("R2C1",FALSE())</f>
-        <v>2</v>
+        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18934,17 +18976,17 @@
         <v>1538</v>
       </c>
       <c r="L1541" s="0" t="e">
-        <f aca="true">INDIRECT("zzz")</f>
-        <v>#REF!</v>
+        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1542" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="L1542" s="0" t="e">
-        <f aca="true">INDIRECT(B1)</f>
-        <v>#REF!</v>
+      <c r="L1542" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18952,26 +18994,26 @@
         <v>1540</v>
       </c>
       <c r="L1543" s="0" t="str">
-        <f aca="true">OFFSET(A1,2,1)</f>
-        <v>cherry</v>
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
+        <v>none</v>
       </c>
     </row>
     <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1544" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="L1544" s="0" t="n">
-        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
-        <v>6</v>
+      <c r="L1544" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1545" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="L1545" s="0" t="e">
-        <f aca="true">OFFSET(A1,-1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1545" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18979,8 +19021,8 @@
         <v>1543</v>
       </c>
       <c r="L1546" s="0" t="n">
-        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
-        <v>5</v>
+        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18988,8 +19030,8 @@
         <v>1544</v>
       </c>
       <c r="L1547" s="0" t="n">
-        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
-        <v>3</v>
+        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18997,7 +19039,7 @@
         <v>1545</v>
       </c>
       <c r="L1548" s="0" t="e">
-        <f aca="true">OFFSET(A1,0,0,0,1)</f>
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -19005,81 +19047,81 @@
       <c r="K1549" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="L1549" s="0" t="str">
-        <f aca="false">ADDRESS(1,1)</f>
-        <v>$A$1</v>
+      <c r="L1549" s="0" t="n">
+        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1550" s="0" t="s">
         <v>1547</v>
       </c>
-      <c r="L1550" s="0" t="str">
-        <f aca="false">ADDRESS(5,3,4)</f>
-        <v>C5</v>
+      <c r="L1550" s="0" t="n">
+        <f aca="true">INDIRECT("A1")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1551" s="0" t="s">
         <v>1548</v>
       </c>
-      <c r="L1551" s="0" t="str">
-        <f aca="false">ADDRESS(2,28,2)</f>
-        <v>AB$2</v>
+      <c r="L1551" s="0" t="n">
+        <f aca="true">INDIRECT("A"&amp;3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1552" s="0" t="s">
         <v>1549</v>
       </c>
-      <c r="L1552" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
-        <v>R1C1</v>
+      <c r="L1552" s="0" t="n">
+        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1553" s="0" t="s">
         <v>1550</v>
       </c>
-      <c r="L1553" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
-        <v>'My Sheet'.$A$1</v>
+      <c r="L1553" s="0" t="n">
+        <f aca="true">INDIRECT("Other!A1")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1554" s="0" t="s">
         <v>1551</v>
       </c>
-      <c r="L1554" s="0" t="e">
-        <f aca="false">ADDRESS(0,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1554" s="0" t="n">
+        <f aca="true">INDIRECT("R2C1",FALSE())</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1555" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="L1555" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,5)</f>
-        <v>$A$1</v>
+      <c r="L1555" s="0" t="e">
+        <f aca="true">INDIRECT("zzz")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="1556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1556" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="L1556" s="0" t="n">
-        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
-        <v>6</v>
+      <c r="L1556" s="0" t="e">
+        <f aca="true">INDIRECT(B1)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="1557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1557" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="L1557" s="0" t="n">
-        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
-        <v>2</v>
+      <c r="L1557" s="0" t="str">
+        <f aca="true">OFFSET(A1,2,1)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19087,7 +19129,7 @@
         <v>1555</v>
       </c>
       <c r="L1558" s="0" t="n">
-        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
+        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
         <v>6</v>
       </c>
     </row>
@@ -19095,9 +19137,9 @@
       <c r="K1559" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="L1559" s="0" t="n">
-        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
-        <v>3</v>
+      <c r="L1559" s="0" t="e">
+        <f aca="true">OFFSET(A1,-1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19105,26 +19147,26 @@
         <v>1557</v>
       </c>
       <c r="L1560" s="0" t="n">
-        <f aca="false">TRANSPOSE(A1:A3)</f>
-        <v>1</v>
+        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1561" s="0" t="s">
         <v>1558</v>
       </c>
-      <c r="L1561" s="0" t="str">
-        <f aca="false">HYPERLINK("http://x.y","click")</f>
-        <v>click</v>
+      <c r="L1561" s="0" t="n">
+        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1562" s="0" t="s">
         <v>1559</v>
       </c>
-      <c r="L1562" s="0" t="str">
-        <f aca="false">HYPERLINK("http://x.y")</f>
-        <v>http://x.y</v>
+      <c r="L1562" s="0" t="e">
+        <f aca="true">OFFSET(A1,0,0,0,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19132,15 +19174,141 @@
         <v>1560</v>
       </c>
       <c r="L1563" s="0" t="str">
-        <f aca="false">HYPERLINK(B1,"go")</f>
-        <v>go</v>
+        <f aca="false">ADDRESS(1,1)</f>
+        <v>$A$1</v>
       </c>
     </row>
     <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1564" s="0" t="s">
         <v>1561</v>
       </c>
-      <c r="L1564" s="0" t="n">
+      <c r="L1564" s="0" t="str">
+        <f aca="false">ADDRESS(5,3,4)</f>
+        <v>C5</v>
+      </c>
+    </row>
+    <row r="1565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1565" s="0" t="s">
+        <v>1562</v>
+      </c>
+      <c r="L1565" s="0" t="str">
+        <f aca="false">ADDRESS(2,28,2)</f>
+        <v>AB$2</v>
+      </c>
+    </row>
+    <row r="1566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1566" s="0" t="s">
+        <v>1563</v>
+      </c>
+      <c r="L1566" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
+        <v>R1C1</v>
+      </c>
+    </row>
+    <row r="1567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1567" s="0" t="s">
+        <v>1564</v>
+      </c>
+      <c r="L1567" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
+        <v>'My Sheet'.$A$1</v>
+      </c>
+    </row>
+    <row r="1568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1568" s="0" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L1568" s="0" t="e">
+        <f aca="false">ADDRESS(0,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1569" s="0" t="s">
+        <v>1566</v>
+      </c>
+      <c r="L1569" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,5)</f>
+        <v>$A$1</v>
+      </c>
+    </row>
+    <row r="1570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1570" s="0" t="s">
+        <v>1567</v>
+      </c>
+      <c r="L1570" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1571" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L1571" s="0" t="n">
+        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1572" s="0" t="s">
+        <v>1569</v>
+      </c>
+      <c r="L1572" s="0" t="n">
+        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1573" s="0" t="s">
+        <v>1570</v>
+      </c>
+      <c r="L1573" s="0" t="n">
+        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1574" s="0" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L1574" s="0" t="n">
+        <f aca="false">TRANSPOSE(A1:A3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1575" s="0" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L1575" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y","click")</f>
+        <v>click</v>
+      </c>
+    </row>
+    <row r="1576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1576" s="0" t="s">
+        <v>1573</v>
+      </c>
+      <c r="L1576" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y")</f>
+        <v>http://x.y</v>
+      </c>
+    </row>
+    <row r="1577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1577" s="0" t="s">
+        <v>1574</v>
+      </c>
+      <c r="L1577" s="0" t="str">
+        <f aca="false">HYPERLINK(B1,"go")</f>
+        <v>go</v>
+      </c>
+    </row>
+    <row r="1578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1578" s="0" t="s">
+        <v>1575</v>
+      </c>
+      <c r="L1578" s="0" t="n">
         <f aca="false">HYPERLINK("u",A2)</f>
         <v>2</v>
       </c>
@@ -19169,7 +19337,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/formulas/formula-suite.xlsx
+++ b/testdata/formulas/formula-suite.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="1577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="1621">
   <si>
     <t xml:space="preserve">apple</t>
   </si>
@@ -4749,6 +4749,138 @@
   </si>
   <si>
     <t xml:space="preserve">=HYPERLINK("u",A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(SEQUENCE(4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SEQUENCE(3,4,10,5),2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(SEQUENCE(5,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(SEQUENCE(5,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(SEQUENCE(2,2,0.5,0.25))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEQUENCE(1,1,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEQUENCE(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SEQUENCE(-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(RANDARRAY(3,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(RANDARRAY(3,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(RANDARRAY(4,4,5,5))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANDARRAY(1,1,2,2,TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MIN(RANDARRAY(10,1,1,3,TRUE))&gt;=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=RANDARRAY(2,2,5,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORT(C1:C6),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORT(C1:C6,1,-1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(",",TRUE,SORT(B1:B6,1,-1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORT(A1:C6,3,1),2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORT(F1:G4,1,-1),1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORT({3,1,2},1,1,TRUE),1,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SORT(A1:A6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SORT(A1:A6,1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORTBY(B1:B6,C1:C6),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORTBY(B1:B6,C1:C6,-1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(",",TRUE,SORTBY(G1:G4,F1:F4,-1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SORTBY(A1:A6,{1;1;2;2;3;3},-1,A1:A6,1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SORTBY(A1:A6,A1:A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SORTBY(A1:A6,A1:A6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(FILTER(A1:A6,A1:A6&gt;3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(FILTER(B1:B6,C1:C6&gt;0))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(FILTER(B1:B6,A1:A6=4),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN("-",TRUE,FILTER(F1:F4,G1:G4&lt;&gt;"two hundred"))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FILTER(A1:A6,A1:A6&gt;10,"none")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FILTER(A1:A6,A1:A6&gt;10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=FILTER(A1:A6,A1:A3&gt;1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(UNIQUE({1;2;2;3;1}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(UNIQUE({1;2;2;3;1}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(UNIQUE({1;2;2;3;1},FALSE,TRUE))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TEXTJOIN(",",TRUE,UNIQUE({"a";"B";"A";"b"}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(UNIQUE({1,1,2},TRUE))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(UNIQUE(A1:A6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=UNIQUE({1;1},FALSE,TRUE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(TRANSPOSE(SEQUENCE(3)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(XLOOKUP(3,A1:A6,B1:C6),1,2)</t>
   </si>
   <si>
     <t xml:space="preserve">remote</t>
@@ -4992,7 +5124,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1578"/>
+  <dimension ref="A1:L1622"/>
   <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10220,7 +10352,7 @@
       </c>
       <c r="L568" s="4" t="n">
         <f aca="true">NOW()</f>
-        <v>46310.9071510982</v>
+        <v>46310.9747491907</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19311,6 +19443,402 @@
       <c r="L1578" s="0" t="n">
         <f aca="false">HYPERLINK("u",A2)</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="1579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1579" s="0" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L1579" s="0" t="n">
+        <f aca="false">SUM(_xlfn.SEQUENCE(4))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1580" s="0" t="s">
+        <v>1577</v>
+      </c>
+      <c r="L1580" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.SEQUENCE(3,4,10,5),2,3)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1581" s="0" t="s">
+        <v>1578</v>
+      </c>
+      <c r="L1581" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.SEQUENCE(5,2))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1582" s="0" t="s">
+        <v>1579</v>
+      </c>
+      <c r="L1582" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.SEQUENCE(5,2))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1583" s="0" t="s">
+        <v>1580</v>
+      </c>
+      <c r="L1583" s="0" t="n">
+        <f aca="false">SUM(_xlfn.SEQUENCE(2,2,0.5,0.25))</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1584" s="0" t="s">
+        <v>1581</v>
+      </c>
+      <c r="L1584" s="0" t="n">
+        <f aca="false">_xlfn.SEQUENCE(1,1,7)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1585" s="0" t="s">
+        <v>1582</v>
+      </c>
+      <c r="L1585" s="0" t="e">
+        <f aca="false">_xlfn.SEQUENCE(0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1586" s="0" t="s">
+        <v>1583</v>
+      </c>
+      <c r="L1586" s="0" t="e">
+        <f aca="false">_xlfn.SEQUENCE(-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1587" s="0" t="s">
+        <v>1584</v>
+      </c>
+      <c r="L1587" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.RANDARRAY(3,2))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1588" s="0" t="s">
+        <v>1585</v>
+      </c>
+      <c r="L1588" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.RANDARRAY(3,2))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1589" s="0" t="s">
+        <v>1586</v>
+      </c>
+      <c r="L1589" s="0" t="n">
+        <f aca="false">SUM(_xlfn.RANDARRAY(4,4,5,5))</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1590" s="0" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L1590" s="0" t="n">
+        <f aca="false">_xlfn.RANDARRAY(1,1,2,2,TRUE())</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1591" s="0" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L1591" s="1" t="b">
+        <f aca="false">MIN(_xlfn.RANDARRAY(10,1,1,3,TRUE()))&gt;=1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1592" s="0" t="s">
+        <v>1589</v>
+      </c>
+      <c r="L1592" s="0" t="e">
+        <f aca="false">_xlfn.RANDARRAY(2,2,5,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1593" s="0" t="s">
+        <v>1590</v>
+      </c>
+      <c r="L1593" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6),1)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1594" s="0" t="s">
+        <v>1591</v>
+      </c>
+      <c r="L1594" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6,1,-1),1)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="1595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1595" s="0" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L1595" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn._xlws.SORT(B1:B6,1,-1))</f>
+        <v>fig,elderberry,date,cherry,banana,apple</v>
+      </c>
+    </row>
+    <row r="1596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1596" s="0" t="s">
+        <v>1593</v>
+      </c>
+      <c r="L1596" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(A1:C6,3,1),2,2)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1597" s="0" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L1597" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(F1:G4,1,-1),1,2)</f>
+        <v>four hundred</v>
+      </c>
+    </row>
+    <row r="1598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1598" s="0" t="s">
+        <v>1595</v>
+      </c>
+      <c r="L1598" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT({3,1,2},1,1,TRUE()),1,3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1599" s="0" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1599" s="0" t="e">
+        <f aca="false">_xlfn._xlws.SORT(A1:A6,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1600" s="0" t="s">
+        <v>1597</v>
+      </c>
+      <c r="L1600" s="0" t="e">
+        <f aca="false">_xlfn._xlws.SORT(A1:A6,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1601" s="0" t="s">
+        <v>1598</v>
+      </c>
+      <c r="L1601" s="0" t="str">
+        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6),1)</f>
+        <v>banana</v>
+      </c>
+    </row>
+    <row r="1602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1602" s="0" t="s">
+        <v>1599</v>
+      </c>
+      <c r="L1602" s="0" t="str">
+        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6,-1),1)</f>
+        <v>fig</v>
+      </c>
+    </row>
+    <row r="1603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1603" s="0" t="s">
+        <v>1600</v>
+      </c>
+      <c r="L1603" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.SORTBY(G1:G4,F1:F4,-1))</f>
+        <v>four hundred,three hundred,two hundred,one hundred</v>
+      </c>
+    </row>
+    <row r="1604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1604" s="0" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L1604" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.SORTBY(A1:A6,{1;1;2;2;3;3},-1,A1:A6,1),1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1605" s="0" t="s">
+        <v>1602</v>
+      </c>
+      <c r="L1605" s="0" t="e">
+        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1606" s="0" t="s">
+        <v>1603</v>
+      </c>
+      <c r="L1606" s="0" t="e">
+        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A6,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1607" s="0" t="s">
+        <v>1604</v>
+      </c>
+      <c r="L1607" s="0" t="n">
+        <f aca="false">SUM(_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;3))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1608" s="0" t="s">
+        <v>1605</v>
+      </c>
+      <c r="L1608" s="0" t="n">
+        <f aca="false">ROWS(_xlfn._xlws.FILTER(B1:B6,C1:C6&gt;0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1609" s="0" t="s">
+        <v>1606</v>
+      </c>
+      <c r="L1609" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.FILTER(B1:B6,A1:A6=4),1)</f>
+        <v>date</v>
+      </c>
+    </row>
+    <row r="1610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1610" s="0" t="s">
+        <v>1607</v>
+      </c>
+      <c r="L1610" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),_xlfn._xlws.FILTER(F1:F4,G1:G4&lt;&gt;"two hundred"))</f>
+        <v>100-300-400</v>
+      </c>
+    </row>
+    <row r="1611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1611" s="0" t="s">
+        <v>1608</v>
+      </c>
+      <c r="L1611" s="0" t="str">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10,"none")</f>
+        <v>none</v>
+      </c>
+    </row>
+    <row r="1612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1612" s="0" t="s">
+        <v>1609</v>
+      </c>
+      <c r="L1612" s="0" t="e">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1613" s="0" t="s">
+        <v>1610</v>
+      </c>
+      <c r="L1613" s="0" t="e">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A3&gt;1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1614" s="0" t="s">
+        <v>1611</v>
+      </c>
+      <c r="L1614" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1615" s="0" t="s">
+        <v>1612</v>
+      </c>
+      <c r="L1615" s="0" t="n">
+        <f aca="false">SUM(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1616" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="L1616" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1},FALSE(),TRUE()))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1617" s="0" t="s">
+        <v>1614</v>
+      </c>
+      <c r="L1617" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE({"a";"B";"A";"b"}))</f>
+        <v>a,B</v>
+      </c>
+    </row>
+    <row r="1618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1618" s="0" t="s">
+        <v>1615</v>
+      </c>
+      <c r="L1618" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.UNIQUE({1,1,2},TRUE()))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1619" s="0" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L1619" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE(A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1620" s="0" t="s">
+        <v>1617</v>
+      </c>
+      <c r="L1620" s="0" t="e">
+        <f aca="false">_xlfn.UNIQUE({1;1},FALSE(),TRUE())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1621" s="0" t="s">
+        <v>1618</v>
+      </c>
+      <c r="L1621" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(_xlfn.SEQUENCE(3)))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1622" s="0" t="s">
+        <v>1619</v>
+      </c>
+      <c r="L1622" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.XLOOKUP(3,A1:A6,B1:C6),1,2)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19337,7 +19865,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1576</v>
+        <v>1620</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/formulas/formula-suite.xlsx
+++ b/testdata/formulas/formula-suite.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="1637">
   <si>
     <t xml:space="preserve">apple</t>
   </si>
@@ -2445,6 +2445,54 @@
   </si>
   <si>
     <t xml:space="preserve">=SUM(A1:A3)*Other!A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(A1:C3 B2:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=A1:A6 A3:C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(A1:A3 C4:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ISERROR(A1 C2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM((A1:A3,C1:C2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNT((A1,A3,C1:C6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MAX((A1:A2,C1,F1:F4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AVERAGE((A1:A2,A5:A6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AREAS(A1:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AREAS((A1:A3,C1,F1:F4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AREAS(A1:C3 B2:C6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AREAS((A1,B1))+AREAS(Other!A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(Data:Other!A1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COUNT(Data:Other!A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM($A:A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(2:$3)</t>
   </si>
   <si>
     <t xml:space="preserve">=#DIV/0!</t>
@@ -5124,7 +5172,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1622"/>
+  <dimension ref="A1:L1638"/>
   <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10280,7 +10328,7 @@
       </c>
       <c r="L560" s="3" t="n">
         <f aca="true">TODAY()</f>
-        <v>46310</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10352,7 +10400,7 @@
       </c>
       <c r="L568" s="4" t="n">
         <f aca="true">NOW()</f>
-        <v>46310.9747491907</v>
+        <v>46312.7703913421</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12447,18 +12495,18 @@
       <c r="K801" s="0" t="s">
         <v>808</v>
       </c>
-      <c r="L801" s="0" t="e">
-        <f aca="false">#DIV/0!</f>
-        <v>#DIV/0!</v>
+      <c r="L801" s="0" t="n">
+        <f aca="false">SUM(A1:C3 B2:C6)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K802" s="0" t="s">
         <v>809</v>
       </c>
-      <c r="L802" s="0" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
+      <c r="L802" s="0" t="n">
+        <f aca="false">A1:A6 A3:C3</f>
+        <v>3</v>
       </c>
     </row>
     <row r="803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12466,521 +12514,521 @@
         <v>810</v>
       </c>
       <c r="L803" s="0" t="e">
-        <f aca="false">#VALUE!</f>
-        <v>#VALUE!</v>
+        <f aca="false">SUM(A1:A3 C4:C6)</f>
+        <v>#NULL!</v>
       </c>
     </row>
     <row r="804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K804" s="0" t="s">
         <v>811</v>
       </c>
-      <c r="L804" s="0" t="e">
-        <f aca="false">#REF!</f>
-        <v>#REF!</v>
+      <c r="L804" s="1" t="b">
+        <f aca="false">ISERROR(A1 C2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K805" s="0" t="s">
         <v>812</v>
       </c>
-      <c r="L805" s="0" t="e">
-        <f aca="false">#NAME?</f>
-        <v>#NAME?</v>
+      <c r="L805" s="0" t="n">
+        <f aca="false">SUM((A1:A3~C1:C2))</f>
+        <v>14.5</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K806" s="0" t="s">
         <v>813</v>
       </c>
-      <c r="L806" s="0" t="e">
-        <f aca="false">#NUM!</f>
-        <v>#NUM!</v>
+      <c r="L806" s="0" t="n">
+        <f aca="false">COUNT((A1~A3~C1:C6))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K807" s="0" t="s">
         <v>814</v>
       </c>
-      <c r="L807" s="0" t="e">
-        <f aca="false">#NULL!</f>
-        <v>#NULL!</v>
+      <c r="L807" s="0" t="n">
+        <f aca="false">MAX((A1:A2~C1~F1:F4))</f>
+        <v>400</v>
       </c>
     </row>
     <row r="808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K808" s="0" t="s">
         <v>815</v>
       </c>
-      <c r="L808" s="0" t="str">
-        <f aca="false">IFERROR(#DIV/0!,"e")</f>
-        <v>e</v>
+      <c r="L808" s="0" t="n">
+        <f aca="false">AVERAGE((A1:A2~A5:A6))</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K809" s="0" t="s">
         <v>816</v>
       </c>
-      <c r="L809" s="0" t="str">
-        <f aca="false">IFERROR(#N/A,"e")</f>
-        <v>e</v>
+      <c r="L809" s="0" t="n">
+        <f aca="false">AREAS(A1:C6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K810" s="0" t="s">
         <v>817</v>
       </c>
-      <c r="L810" s="0" t="str">
-        <f aca="false">IFERROR(#VALUE!,"e")</f>
-        <v>e</v>
+      <c r="L810" s="0" t="n">
+        <f aca="false">AREAS((A1:A3~C1~F1:F4))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K811" s="0" t="s">
         <v>818</v>
       </c>
-      <c r="L811" s="0" t="str">
-        <f aca="false">IFERROR(#REF!,"e")</f>
-        <v>e</v>
+      <c r="L811" s="0" t="n">
+        <f aca="false">AREAS(A1:C3 B2:C6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K812" s="0" t="s">
         <v>819</v>
       </c>
-      <c r="L812" s="0" t="str">
-        <f aca="false">IFERROR(#NAME?,"e")</f>
-        <v>e</v>
+      <c r="L812" s="0" t="n">
+        <f aca="false">AREAS((A1~B1))+AREAS(Other!A1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K813" s="0" t="s">
         <v>820</v>
       </c>
-      <c r="L813" s="0" t="str">
-        <f aca="false">IFERROR(#NUM!,"e")</f>
-        <v>e</v>
+      <c r="L813" s="0" t="n">
+        <f aca="false">SUM(Data:Other!A1)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K814" s="0" t="s">
         <v>821</v>
       </c>
-      <c r="L814" s="0" t="str">
-        <f aca="false">IFERROR(#NULL!,"e")</f>
-        <v>e</v>
+      <c r="L814" s="0" t="n">
+        <f aca="false">COUNT(Data:Other!A1:A2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K815" s="0" t="s">
         <v>822</v>
       </c>
-      <c r="L815" s="1" t="b">
-        <f aca="false">ISERROR(#DIV/0!)</f>
-        <v>1</v>
+      <c r="L815" s="0" t="n">
+        <f aca="false">SUM($A:A)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K816" s="0" t="s">
         <v>823</v>
       </c>
-      <c r="L816" s="1" t="b">
-        <f aca="false">ISERROR(#N/A)</f>
-        <v>1</v>
+      <c r="L816" s="0" t="e">
+        <f aca="false">SUM(2:$3)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K817" s="0" t="s">
         <v>824</v>
       </c>
-      <c r="L817" s="1" t="b">
-        <f aca="false">ISERROR(#VALUE!)</f>
-        <v>1</v>
+      <c r="L817" s="0" t="e">
+        <f aca="false">#DIV/0!</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K818" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="L818" s="1" t="b">
-        <f aca="false">ISERROR(#REF!)</f>
-        <v>1</v>
+      <c r="L818" s="0" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K819" s="0" t="s">
         <v>826</v>
       </c>
-      <c r="L819" s="1" t="b">
-        <f aca="false">ISERROR(#NAME?)</f>
-        <v>1</v>
+      <c r="L819" s="0" t="e">
+        <f aca="false">#VALUE!</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K820" s="0" t="s">
         <v>827</v>
       </c>
-      <c r="L820" s="1" t="b">
-        <f aca="false">ISERROR(#NUM!)</f>
-        <v>1</v>
+      <c r="L820" s="0" t="e">
+        <f aca="false">#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K821" s="0" t="s">
         <v>828</v>
       </c>
-      <c r="L821" s="1" t="b">
-        <f aca="false">ISERROR(#NULL!)</f>
-        <v>1</v>
+      <c r="L821" s="0" t="e">
+        <f aca="false">#NAME?</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K822" s="0" t="s">
         <v>829</v>
       </c>
-      <c r="L822" s="1" t="b">
-        <f aca="false">ISNA(#N/A)</f>
-        <v>1</v>
+      <c r="L822" s="0" t="e">
+        <f aca="false">#NUM!</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K823" s="0" t="s">
         <v>830</v>
       </c>
-      <c r="L823" s="1" t="b">
-        <f aca="false">ISNA(#DIV/0!)</f>
-        <v>0</v>
+      <c r="L823" s="0" t="e">
+        <f aca="false">#NULL!</f>
+        <v>#NULL!</v>
       </c>
     </row>
     <row r="824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K824" s="0" t="s">
         <v>831</v>
       </c>
-      <c r="L824" s="1" t="b">
-        <f aca="false">ISNA(#VALUE!)</f>
-        <v>0</v>
+      <c r="L824" s="0" t="str">
+        <f aca="false">IFERROR(#DIV/0!,"e")</f>
+        <v>e</v>
       </c>
     </row>
     <row r="825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K825" s="0" t="s">
         <v>832</v>
       </c>
-      <c r="L825" s="1" t="b">
-        <f aca="false">ISNA(#REF!)</f>
-        <v>0</v>
+      <c r="L825" s="0" t="str">
+        <f aca="false">IFERROR(#N/A,"e")</f>
+        <v>e</v>
       </c>
     </row>
     <row r="826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K826" s="0" t="s">
         <v>833</v>
       </c>
-      <c r="L826" s="1" t="b">
-        <f aca="false">ISNA(#NAME?)</f>
-        <v>0</v>
+      <c r="L826" s="0" t="str">
+        <f aca="false">IFERROR(#VALUE!,"e")</f>
+        <v>e</v>
       </c>
     </row>
     <row r="827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K827" s="0" t="s">
         <v>834</v>
       </c>
-      <c r="L827" s="1" t="b">
-        <f aca="false">ISNA(#NUM!)</f>
-        <v>0</v>
+      <c r="L827" s="0" t="str">
+        <f aca="false">IFERROR(#REF!,"e")</f>
+        <v>e</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K828" s="0" t="s">
         <v>835</v>
       </c>
-      <c r="L828" s="1" t="b">
+      <c r="L828" s="0" t="str">
+        <f aca="false">IFERROR(#NAME?,"e")</f>
+        <v>e</v>
+      </c>
+    </row>
+    <row r="829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K829" s="0" t="s">
+        <v>836</v>
+      </c>
+      <c r="L829" s="0" t="str">
+        <f aca="false">IFERROR(#NUM!,"e")</f>
+        <v>e</v>
+      </c>
+    </row>
+    <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K830" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="L830" s="0" t="str">
+        <f aca="false">IFERROR(#NULL!,"e")</f>
+        <v>e</v>
+      </c>
+    </row>
+    <row r="831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K831" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="L831" s="1" t="b">
+        <f aca="false">ISERROR(#DIV/0!)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K832" s="0" t="s">
+        <v>839</v>
+      </c>
+      <c r="L832" s="1" t="b">
+        <f aca="false">ISERROR(#N/A)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K833" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="L833" s="1" t="b">
+        <f aca="false">ISERROR(#VALUE!)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K834" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="L834" s="1" t="b">
+        <f aca="false">ISERROR(#REF!)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K835" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="L835" s="1" t="b">
+        <f aca="false">ISERROR(#NAME?)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K836" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="L836" s="1" t="b">
+        <f aca="false">ISERROR(#NUM!)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K837" s="0" t="s">
+        <v>844</v>
+      </c>
+      <c r="L837" s="1" t="b">
+        <f aca="false">ISERROR(#NULL!)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K838" s="0" t="s">
+        <v>845</v>
+      </c>
+      <c r="L838" s="1" t="b">
+        <f aca="false">ISNA(#N/A)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K839" s="0" t="s">
+        <v>846</v>
+      </c>
+      <c r="L839" s="1" t="b">
+        <f aca="false">ISNA(#DIV/0!)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K840" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="L840" s="1" t="b">
+        <f aca="false">ISNA(#VALUE!)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K841" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="L841" s="1" t="b">
+        <f aca="false">ISNA(#REF!)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K842" s="0" t="s">
+        <v>849</v>
+      </c>
+      <c r="L842" s="1" t="b">
+        <f aca="false">ISNA(#NAME?)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K843" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="L843" s="1" t="b">
+        <f aca="false">ISNA(#NUM!)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K844" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="L844" s="1" t="b">
         <f aca="false">ISNA(#NULL!)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K829" s="0" t="s">
+    <row r="845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K845" s="0" t="s">
         <v>735</v>
       </c>
-      <c r="L829" s="0" t="e">
+      <c r="L845" s="0" t="e">
         <f aca="false">1/0</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K830" s="0" t="s">
+    <row r="846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K846" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="L830" s="0" t="e">
+      <c r="L846" s="0" t="e">
         <f aca="false">SQRT(-1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K831" s="0" t="s">
+    <row r="847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K847" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="L831" s="0" t="e">
+      <c r="L847" s="0" t="e">
         <f aca="false">VLOOKUP(999,F1:G4,2,FALSE())</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K832" s="0" t="s">
-        <v>836</v>
-      </c>
-      <c r="L832" s="0" t="e">
+    <row r="848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K848" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="L848" s="0" t="e">
         <f aca="false">unknownfn(1)</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K833" s="0" t="s">
+    <row r="849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K849" s="0" t="s">
         <v>513</v>
       </c>
-      <c r="L833" s="0" t="e">
+      <c r="L849" s="0" t="e">
         <f aca="false">INDEX(A1:A6,10)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K834" s="0" t="s">
+    <row r="850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K850" s="0" t="s">
         <v>458</v>
       </c>
-      <c r="L834" s="0" t="e">
+      <c r="L850" s="0" t="e">
         <f aca="false">VALUE("abc")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K835" s="0" t="s">
+    <row r="851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K851" s="0" t="s">
         <v>307</v>
       </c>
-      <c r="L835" s="0" t="e">
+      <c r="L851" s="0" t="e">
         <f aca="false">NA()</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K836" s="0" t="s">
-        <v>837</v>
-      </c>
-      <c r="L836" s="0" t="e">
+    <row r="852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K852" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="L852" s="0" t="e">
         <f aca="false">H1</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K837" s="0" t="s">
+    <row r="853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K853" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="L837" s="0" t="e">
+      <c r="L853" s="0" t="e">
         <f aca="false">H2</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K838" s="0" t="s">
+    <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K854" s="0" t="s">
         <v>770</v>
       </c>
-      <c r="L838" s="0" t="e">
+      <c r="L854" s="0" t="e">
         <f aca="false">H1+H2</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K839" s="0" t="s">
+    <row r="855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K855" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="L839" s="0" t="e">
+      <c r="L855" s="0" t="e">
         <f aca="false">SUM(H1:H2)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K840" s="0" t="s">
-        <v>838</v>
-      </c>
-      <c r="L840" s="0" t="str">
+    <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K856" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="L856" s="0" t="str">
         <f aca="false">IF(ISERROR(H1),"bad","ok")</f>
         <v>bad</v>
       </c>
     </row>
-    <row r="841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K841" s="0" t="s">
-        <v>839</v>
-      </c>
-      <c r="L841" s="0" t="str">
+    <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K857" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="L857" s="0" t="str">
         <f aca="false">IF(ISNA(H2),"na",IF(ISERROR(H2),"err","ok"))</f>
         <v>na</v>
       </c>
     </row>
-    <row r="842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K842" s="0" t="s">
-        <v>840</v>
-      </c>
-      <c r="L842" s="1" t="b">
+    <row r="858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K858" s="0" t="s">
+        <v>856</v>
+      </c>
+      <c r="L858" s="1" t="b">
         <f aca="false">ISERROR(unknownfn(1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K843" s="0" t="s">
+    <row r="859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K859" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="L843" s="0" t="str">
+      <c r="L859" s="0" t="str">
         <f aca="false">IFERROR(unknownfn(1),"x")</f>
         <v>x</v>
-      </c>
-    </row>
-    <row r="844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K844" s="0" t="s">
-        <v>841</v>
-      </c>
-      <c r="L844" s="1" t="b">
-        <f aca="false">ISNA(unknownfn(1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K845" s="0" t="s">
-        <v>842</v>
-      </c>
-      <c r="L845" s="0" t="e">
-        <f aca="false">#VALUE!+1</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K846" s="0" t="s">
-        <v>843</v>
-      </c>
-      <c r="L846" s="0" t="e">
-        <f aca="false">ABS(#NUM!)</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K847" s="0" t="s">
-        <v>844</v>
-      </c>
-      <c r="L847" s="0" t="e">
-        <f aca="false">#N/A&amp;"x"</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K848" s="0" t="s">
-        <v>845</v>
-      </c>
-      <c r="L848" s="0" t="e">
-        <f aca="false">MAX(#REF!,1)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K849" s="0" t="s">
-        <v>846</v>
-      </c>
-      <c r="L849" s="0" t="e">
-        <f aca="false">CHOOSE(2,1,#NAME?)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K850" s="0" t="s">
-        <v>847</v>
-      </c>
-      <c r="L850" s="0" t="e">
-        <f aca="false">SQRT(-1)+1</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K851" s="0" t="s">
-        <v>848</v>
-      </c>
-      <c r="L851" s="0" t="str">
-        <f aca="false">IFERROR(SQRT(-1),"nan")</f>
-        <v>nan</v>
-      </c>
-    </row>
-    <row r="852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K852" s="0" t="s">
-        <v>849</v>
-      </c>
-      <c r="L852" s="1" t="b">
-        <f aca="false">ISNA(SQRT(-1))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K853" s="0" t="s">
-        <v>850</v>
-      </c>
-      <c r="L853" s="0" t="e">
-        <f aca="false">LEN(#N/A)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K854" s="0" t="s">
-        <v>851</v>
-      </c>
-      <c r="L854" s="0" t="e">
-        <f aca="false">unknownfn(H1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K855" s="0" t="s">
-        <v>852</v>
-      </c>
-      <c r="L855" s="0" t="e">
-        <f aca="false">SUM(unknownfn(1),1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K856" s="0" t="s">
-        <v>853</v>
-      </c>
-      <c r="L856" s="0" t="e">
-        <f aca="false">MATCH(1,B1:B6,0)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K857" s="0" t="s">
-        <v>854</v>
-      </c>
-      <c r="L857" s="0" t="e">
-        <f aca="false">nope!a1</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K858" s="0" t="s">
-        <v>855</v>
-      </c>
-      <c r="L858" s="0" t="e">
-        <f aca="false">#N/A+#DIV/0!</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K859" s="0" t="s">
-        <v>856</v>
-      </c>
-      <c r="L859" s="0" t="e">
-        <f aca="false">#DIV/0!+#N/A</f>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K860" s="0" t="s">
         <v>857</v>
       </c>
-      <c r="L860" s="0" t="e">
-        <f aca="false">IF(#N/A,1,2)</f>
-        <v>#N/A</v>
+      <c r="L860" s="1" t="b">
+        <f aca="false">ISNA(unknownfn(1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12988,8 +13036,8 @@
         <v>858</v>
       </c>
       <c r="L861" s="0" t="e">
-        <f aca="false">-#NUM!</f>
-        <v>#NUM!</v>
+        <f aca="false">#VALUE!+1</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12997,152 +13045,152 @@
         <v>859</v>
       </c>
       <c r="L862" s="0" t="e">
-        <f aca="false">1/0+NA()</f>
-        <v>#DIV/0!</v>
+        <f aca="false">ABS(#NUM!)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K863" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="L863" s="0" t="n">
-        <f aca="false">TRUNC(8.9)</f>
-        <v>8</v>
+      <c r="L863" s="0" t="e">
+        <f aca="false">#N/A&amp;"x"</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K864" s="0" t="s">
         <v>861</v>
       </c>
-      <c r="L864" s="0" t="n">
-        <f aca="false">TRUNC(-8.9)</f>
-        <v>-8</v>
+      <c r="L864" s="0" t="e">
+        <f aca="false">MAX(#REF!,1)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K865" s="0" t="s">
         <v>862</v>
       </c>
-      <c r="L865" s="0" t="n">
-        <f aca="false">TRUNC(3.14159,2)</f>
-        <v>3.14</v>
+      <c r="L865" s="0" t="e">
+        <f aca="false">CHOOSE(2,1,#NAME?)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K866" s="0" t="s">
         <v>863</v>
       </c>
-      <c r="L866" s="0" t="n">
-        <f aca="false">TRUNC(1234.5,-2)</f>
-        <v>1200</v>
+      <c r="L866" s="0" t="e">
+        <f aca="false">SQRT(-1)+1</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K867" s="0" t="s">
         <v>864</v>
       </c>
-      <c r="L867" s="0" t="n">
-        <f aca="false">TRUNC(C1)</f>
-        <v>10</v>
+      <c r="L867" s="0" t="str">
+        <f aca="false">IFERROR(SQRT(-1),"nan")</f>
+        <v>nan</v>
       </c>
     </row>
     <row r="868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K868" s="0" t="s">
         <v>865</v>
       </c>
-      <c r="L868" s="0" t="n">
-        <f aca="false">_xlfn.CEILING.MATH(6.3)</f>
-        <v>7</v>
+      <c r="L868" s="1" t="b">
+        <f aca="false">ISNA(SQRT(-1))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K869" s="0" t="s">
         <v>866</v>
       </c>
-      <c r="L869" s="0" t="n">
-        <f aca="false">_xlfn.CEILING.MATH(-5.5,2)</f>
-        <v>-4</v>
+      <c r="L869" s="0" t="e">
+        <f aca="false">LEN(#N/A)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K870" s="0" t="s">
         <v>867</v>
       </c>
-      <c r="L870" s="0" t="n">
-        <f aca="false">_xlfn.CEILING.MATH(-5.5,2,1)</f>
-        <v>-6</v>
+      <c r="L870" s="0" t="e">
+        <f aca="false">unknownfn(H1)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K871" s="0" t="s">
         <v>868</v>
       </c>
-      <c r="L871" s="0" t="n">
-        <f aca="false">_xlfn.CEILING.MATH(6.3,0)</f>
-        <v>0</v>
+      <c r="L871" s="0" t="e">
+        <f aca="false">SUM(unknownfn(1),1)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K872" s="0" t="s">
         <v>869</v>
       </c>
-      <c r="L872" s="0" t="n">
-        <f aca="false">_xlfn.CEILING.MATH(24.3,5)</f>
-        <v>25</v>
+      <c r="L872" s="0" t="e">
+        <f aca="false">MATCH(1,B1:B6,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K873" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="L873" s="0" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(6.7)</f>
-        <v>6</v>
+      <c r="L873" s="0" t="e">
+        <f aca="false">nope!a1</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K874" s="0" t="s">
         <v>871</v>
       </c>
-      <c r="L874" s="0" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(-5.5,2)</f>
-        <v>-6</v>
+      <c r="L874" s="0" t="e">
+        <f aca="false">#N/A+#DIV/0!</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K875" s="0" t="s">
         <v>872</v>
       </c>
-      <c r="L875" s="0" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(-5.5,2,1)</f>
-        <v>-4</v>
+      <c r="L875" s="0" t="e">
+        <f aca="false">#DIV/0!+#N/A</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K876" s="0" t="s">
         <v>873</v>
       </c>
-      <c r="L876" s="0" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(24.3,5)</f>
-        <v>20</v>
+      <c r="L876" s="0" t="e">
+        <f aca="false">IF(#N/A,1,2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K877" s="0" t="s">
         <v>874</v>
       </c>
-      <c r="L877" s="0" t="n">
-        <f aca="false">FLOOR(3.7,2)</f>
-        <v>2</v>
+      <c r="L877" s="0" t="e">
+        <f aca="false">-#NUM!</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K878" s="0" t="s">
         <v>875</v>
       </c>
-      <c r="L878" s="0" t="n">
-        <f aca="false">FLOOR(-2.5,2)</f>
-        <v>-4</v>
+      <c r="L878" s="0" t="e">
+        <f aca="false">1/0+NA()</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13150,26 +13198,26 @@
         <v>876</v>
       </c>
       <c r="L879" s="0" t="n">
-        <f aca="false">FLOOR(-2.5,-2)</f>
-        <v>-2</v>
+        <f aca="false">TRUNC(8.9)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K880" s="0" t="s">
         <v>877</v>
       </c>
-      <c r="L880" s="0" t="e">
-        <f aca="false">FLOOR(2.5,-2)</f>
-        <v>#VALUE!</v>
+      <c r="L880" s="0" t="n">
+        <f aca="false">TRUNC(-8.9)</f>
+        <v>-8</v>
       </c>
     </row>
     <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K881" s="0" t="s">
         <v>878</v>
       </c>
-      <c r="L881" s="0" t="e">
-        <f aca="false">FLOOR(3,0)</f>
-        <v>#VALUE!</v>
+      <c r="L881" s="0" t="n">
+        <f aca="false">TRUNC(3.14159,2)</f>
+        <v>3.14</v>
       </c>
     </row>
     <row r="882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13177,8 +13225,8 @@
         <v>879</v>
       </c>
       <c r="L882" s="0" t="n">
-        <f aca="false">MROUND(10,3)</f>
-        <v>9</v>
+        <f aca="false">TRUNC(1234.5,-2)</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13186,8 +13234,8 @@
         <v>880</v>
       </c>
       <c r="L883" s="0" t="n">
-        <f aca="false">MROUND(-10,-3)</f>
-        <v>-9</v>
+        <f aca="false">TRUNC(C1)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13195,8 +13243,8 @@
         <v>881</v>
       </c>
       <c r="L884" s="0" t="n">
-        <f aca="false">MROUND(1.3,0.2)</f>
-        <v>1.4</v>
+        <f aca="false">_xlfn.CEILING.MATH(6.3)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13204,8 +13252,8 @@
         <v>882</v>
       </c>
       <c r="L885" s="0" t="n">
-        <f aca="false">MROUND(5,-2)</f>
-        <v>6</v>
+        <f aca="false">_xlfn.CEILING.MATH(-5.5,2)</f>
+        <v>-4</v>
       </c>
     </row>
     <row r="886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13213,8 +13261,8 @@
         <v>883</v>
       </c>
       <c r="L886" s="0" t="n">
-        <f aca="false">MROUND(7,0)</f>
-        <v>0</v>
+        <f aca="false">_xlfn.CEILING.MATH(-5.5,2,1)</f>
+        <v>-6</v>
       </c>
     </row>
     <row r="887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13222,8 +13270,8 @@
         <v>884</v>
       </c>
       <c r="L887" s="0" t="n">
-        <f aca="false">EXP(0)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.CEILING.MATH(6.3,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13231,8 +13279,8 @@
         <v>885</v>
       </c>
       <c r="L888" s="0" t="n">
-        <f aca="false">EXP(1)</f>
-        <v>2.71828182845905</v>
+        <f aca="false">_xlfn.CEILING.MATH(24.3,5)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13240,8 +13288,8 @@
         <v>886</v>
       </c>
       <c r="L889" s="0" t="n">
-        <f aca="false">EXP(-1)</f>
-        <v>0.367879441171442</v>
+        <f aca="false">_xlfn.FLOOR.MATH(6.7)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13249,17 +13297,17 @@
         <v>887</v>
       </c>
       <c r="L890" s="0" t="n">
-        <f aca="false">EXP(A2)</f>
-        <v>7.38905609893065</v>
+        <f aca="false">_xlfn.FLOOR.MATH(-5.5,2)</f>
+        <v>-6</v>
       </c>
     </row>
     <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K891" s="0" t="s">
         <v>888</v>
       </c>
-      <c r="L891" s="0" t="e">
-        <f aca="false">EXP(B1)</f>
-        <v>#VALUE!</v>
+      <c r="L891" s="0" t="n">
+        <f aca="false">_xlfn.FLOOR.MATH(-5.5,2,1)</f>
+        <v>-4</v>
       </c>
     </row>
     <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13267,8 +13315,8 @@
         <v>889</v>
       </c>
       <c r="L892" s="0" t="n">
-        <f aca="false">LN(1)</f>
-        <v>0</v>
+        <f aca="false">_xlfn.FLOOR.MATH(24.3,5)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13276,7 +13324,7 @@
         <v>890</v>
       </c>
       <c r="L893" s="0" t="n">
-        <f aca="false">LN(EXP(2))</f>
+        <f aca="false">FLOOR(3.7,2)</f>
         <v>2</v>
       </c>
     </row>
@@ -13284,36 +13332,36 @@
       <c r="K894" s="0" t="s">
         <v>891</v>
       </c>
-      <c r="L894" s="0" t="e">
-        <f aca="false">LN(0)</f>
-        <v>#VALUE!</v>
+      <c r="L894" s="0" t="n">
+        <f aca="false">FLOOR(-2.5,2)</f>
+        <v>-4</v>
       </c>
     </row>
     <row r="895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K895" s="0" t="s">
         <v>892</v>
       </c>
-      <c r="L895" s="0" t="e">
-        <f aca="false">LN(-1)</f>
-        <v>#VALUE!</v>
+      <c r="L895" s="0" t="n">
+        <f aca="false">FLOOR(-2.5,-2)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K896" s="0" t="s">
         <v>893</v>
       </c>
-      <c r="L896" s="0" t="n">
-        <f aca="false">LN(A6)</f>
-        <v>1.79175946922806</v>
+      <c r="L896" s="0" t="e">
+        <f aca="false">FLOOR(2.5,-2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K897" s="0" t="s">
         <v>894</v>
       </c>
-      <c r="L897" s="0" t="n">
-        <f aca="false">LOG(100)</f>
-        <v>2</v>
+      <c r="L897" s="0" t="e">
+        <f aca="false">FLOOR(3,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13321,8 +13369,8 @@
         <v>895</v>
       </c>
       <c r="L898" s="0" t="n">
-        <f aca="false">LOG(8,2)</f>
-        <v>3</v>
+        <f aca="false">MROUND(10,3)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13330,26 +13378,26 @@
         <v>896</v>
       </c>
       <c r="L899" s="0" t="n">
-        <f aca="false">LOG(10,10)</f>
-        <v>1</v>
+        <f aca="false">MROUND(-10,-3)</f>
+        <v>-9</v>
       </c>
     </row>
     <row r="900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K900" s="0" t="s">
         <v>897</v>
       </c>
-      <c r="L900" s="0" t="e">
-        <f aca="false">LOG(5,1)</f>
-        <v>#VALUE!</v>
+      <c r="L900" s="0" t="n">
+        <f aca="false">MROUND(1.3,0.2)</f>
+        <v>1.4</v>
       </c>
     </row>
     <row r="901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K901" s="0" t="s">
         <v>898</v>
       </c>
-      <c r="L901" s="0" t="e">
-        <f aca="false">LOG(-1)</f>
-        <v>#VALUE!</v>
+      <c r="L901" s="0" t="n">
+        <f aca="false">MROUND(5,-2)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13357,8 +13405,8 @@
         <v>899</v>
       </c>
       <c r="L902" s="0" t="n">
-        <f aca="false">LOG10(1000)</f>
-        <v>3</v>
+        <f aca="false">MROUND(7,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13366,17 +13414,17 @@
         <v>900</v>
       </c>
       <c r="L903" s="0" t="n">
-        <f aca="false">LOG10(0.01)</f>
-        <v>-2</v>
+        <f aca="false">EXP(0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K904" s="0" t="s">
         <v>901</v>
       </c>
-      <c r="L904" s="0" t="e">
-        <f aca="false">LOG10(0)</f>
-        <v>#VALUE!</v>
+      <c r="L904" s="0" t="n">
+        <f aca="false">EXP(1)</f>
+        <v>2.71828182845905</v>
       </c>
     </row>
     <row r="905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13384,8 +13432,8 @@
         <v>902</v>
       </c>
       <c r="L905" s="0" t="n">
-        <f aca="false">LOG10(A4)</f>
-        <v>0.602059991327962</v>
+        <f aca="false">EXP(-1)</f>
+        <v>0.367879441171442</v>
       </c>
     </row>
     <row r="906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13393,17 +13441,17 @@
         <v>903</v>
       </c>
       <c r="L906" s="0" t="n">
-        <f aca="false">SIGN(-5)</f>
-        <v>-1</v>
+        <f aca="false">EXP(A2)</f>
+        <v>7.38905609893065</v>
       </c>
     </row>
     <row r="907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K907" s="0" t="s">
         <v>904</v>
       </c>
-      <c r="L907" s="0" t="n">
-        <f aca="false">SIGN(0)</f>
-        <v>0</v>
+      <c r="L907" s="0" t="e">
+        <f aca="false">EXP(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13411,8 +13459,8 @@
         <v>905</v>
       </c>
       <c r="L908" s="0" t="n">
-        <f aca="false">SIGN(C1)</f>
-        <v>1</v>
+        <f aca="false">LN(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13420,8 +13468,8 @@
         <v>906</v>
       </c>
       <c r="L909" s="0" t="n">
-        <f aca="false">SIGN(C2)</f>
-        <v>-1</v>
+        <f aca="false">LN(EXP(2))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13429,7 +13477,7 @@
         <v>907</v>
       </c>
       <c r="L910" s="0" t="e">
-        <f aca="false">SIGN(B1)</f>
+        <f aca="false">LN(0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -13437,9 +13485,9 @@
       <c r="K911" s="0" t="s">
         <v>908</v>
       </c>
-      <c r="L911" s="1" t="b">
-        <f aca="true">AND(RAND()&gt;=0,RAND()&lt;1)</f>
-        <v>1</v>
+      <c r="L911" s="0" t="e">
+        <f aca="false">LN(-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13447,26 +13495,26 @@
         <v>909</v>
       </c>
       <c r="L912" s="0" t="n">
-        <f aca="true">INT(RAND())</f>
-        <v>0</v>
+        <f aca="false">LN(A6)</f>
+        <v>1.79175946922806</v>
       </c>
     </row>
     <row r="913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K913" s="0" t="s">
         <v>910</v>
       </c>
-      <c r="L913" s="1" t="b">
-        <f aca="true">RAND()&lt;&gt;RAND()</f>
-        <v>1</v>
+      <c r="L913" s="0" t="n">
+        <f aca="false">LOG(100)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K914" s="0" t="s">
         <v>911</v>
       </c>
-      <c r="L914" s="0" t="str">
-        <f aca="true">IF(RAND()&lt;1,"ok","bad")</f>
-        <v>ok</v>
+      <c r="L914" s="0" t="n">
+        <f aca="false">LOG(8,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13474,17 +13522,17 @@
         <v>912</v>
       </c>
       <c r="L915" s="0" t="n">
-        <f aca="false">RANDBETWEEN(5,5)</f>
-        <v>5</v>
+        <f aca="false">LOG(10,10)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K916" s="0" t="s">
         <v>913</v>
       </c>
-      <c r="L916" s="1" t="b">
-        <f aca="false">AND(RANDBETWEEN(1,6)&gt;=1,RANDBETWEEN(1,6)&lt;=6)</f>
-        <v>1</v>
+      <c r="L916" s="0" t="e">
+        <f aca="false">LOG(5,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13492,7 +13540,7 @@
         <v>914</v>
       </c>
       <c r="L917" s="0" t="e">
-        <f aca="false">RANDBETWEEN(3,1)</f>
+        <f aca="false">LOG(-1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -13501,8 +13549,8 @@
         <v>915</v>
       </c>
       <c r="L918" s="0" t="n">
-        <f aca="false">RANDBETWEEN(-2,-2)</f>
-        <v>-2</v>
+        <f aca="false">LOG10(1000)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13510,17 +13558,17 @@
         <v>916</v>
       </c>
       <c r="L919" s="0" t="n">
-        <f aca="false">SUMSQ(3,4)</f>
-        <v>25</v>
+        <f aca="false">LOG10(0.01)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K920" s="0" t="s">
         <v>917</v>
       </c>
-      <c r="L920" s="0" t="n">
-        <f aca="false">SUMSQ(A1:A3)</f>
-        <v>14</v>
+      <c r="L920" s="0" t="e">
+        <f aca="false">LOG10(0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13528,8 +13576,8 @@
         <v>918</v>
       </c>
       <c r="L921" s="0" t="n">
-        <f aca="false">SUMSQ(C1:C3)</f>
-        <v>114.25</v>
+        <f aca="false">LOG10(A4)</f>
+        <v>0.602059991327962</v>
       </c>
     </row>
     <row r="922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13537,17 +13585,17 @@
         <v>919</v>
       </c>
       <c r="L922" s="0" t="n">
-        <f aca="false">SUMSQ(A1:A2,B1:B3)</f>
-        <v>5</v>
+        <f aca="false">SIGN(-5)</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K923" s="0" t="s">
         <v>920</v>
       </c>
-      <c r="L923" s="0" t="e">
-        <f aca="false">SUMSQ(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L923" s="0" t="n">
+        <f aca="false">SIGN(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13555,8 +13603,8 @@
         <v>921</v>
       </c>
       <c r="L924" s="0" t="n">
-        <f aca="false">SQRTPI(1)</f>
-        <v>1.77245385090552</v>
+        <f aca="false">SIGN(C1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13564,26 +13612,26 @@
         <v>922</v>
       </c>
       <c r="L925" s="0" t="n">
-        <f aca="false">SQRTPI(2)</f>
-        <v>2.506628274631</v>
+        <f aca="false">SIGN(C2)</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K926" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="L926" s="0" t="n">
-        <f aca="false">SQRTPI(0)</f>
-        <v>0</v>
+      <c r="L926" s="0" t="e">
+        <f aca="false">SIGN(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K927" s="0" t="s">
         <v>924</v>
       </c>
-      <c r="L927" s="0" t="e">
-        <f aca="false">SQRTPI(-1)</f>
-        <v>#VALUE!</v>
+      <c r="L927" s="1" t="b">
+        <f aca="true">AND(RAND()&gt;=0,RAND()&lt;1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13591,16 +13639,16 @@
         <v>925</v>
       </c>
       <c r="L928" s="0" t="n">
-        <f aca="false">FACT(5)</f>
-        <v>120</v>
+        <f aca="true">INT(RAND())</f>
+        <v>0</v>
       </c>
     </row>
     <row r="929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K929" s="0" t="s">
         <v>926</v>
       </c>
-      <c r="L929" s="0" t="n">
-        <f aca="false">FACT(0)</f>
+      <c r="L929" s="1" t="b">
+        <f aca="true">RAND()&lt;&gt;RAND()</f>
         <v>1</v>
       </c>
     </row>
@@ -13608,36 +13656,36 @@
       <c r="K930" s="0" t="s">
         <v>927</v>
       </c>
-      <c r="L930" s="0" t="n">
-        <f aca="false">FACT(5.9)</f>
-        <v>120</v>
+      <c r="L930" s="0" t="str">
+        <f aca="true">IF(RAND()&lt;1,"ok","bad")</f>
+        <v>ok</v>
       </c>
     </row>
     <row r="931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K931" s="0" t="s">
         <v>928</v>
       </c>
-      <c r="L931" s="0" t="e">
-        <f aca="false">FACT(-1)</f>
-        <v>#VALUE!</v>
+      <c r="L931" s="0" t="n">
+        <f aca="false">RANDBETWEEN(5,5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K932" s="0" t="s">
         <v>929</v>
       </c>
-      <c r="L932" s="0" t="e">
-        <f aca="false">FACT(171)</f>
-        <v>#VALUE!</v>
+      <c r="L932" s="1" t="b">
+        <f aca="false">AND(RANDBETWEEN(1,6)&gt;=1,RANDBETWEEN(1,6)&lt;=6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K933" s="0" t="s">
         <v>930</v>
       </c>
-      <c r="L933" s="0" t="n">
-        <f aca="false">FACTDOUBLE(6)</f>
-        <v>48</v>
+      <c r="L933" s="0" t="e">
+        <f aca="false">RANDBETWEEN(3,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13645,8 +13693,8 @@
         <v>931</v>
       </c>
       <c r="L934" s="0" t="n">
-        <f aca="false">FACTDOUBLE(7)</f>
-        <v>105</v>
+        <f aca="false">RANDBETWEEN(-2,-2)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13654,17 +13702,17 @@
         <v>932</v>
       </c>
       <c r="L935" s="0" t="n">
-        <f aca="false">FACTDOUBLE(0)</f>
-        <v>1</v>
+        <f aca="false">SUMSQ(3,4)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K936" s="0" t="s">
         <v>933</v>
       </c>
-      <c r="L936" s="0" t="e">
-        <f aca="false">FACTDOUBLE(-2)</f>
-        <v>#VALUE!</v>
+      <c r="L936" s="0" t="n">
+        <f aca="false">SUMSQ(A1:A3)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13672,8 +13720,8 @@
         <v>934</v>
       </c>
       <c r="L937" s="0" t="n">
-        <f aca="false">COMBIN(8,2)</f>
-        <v>28</v>
+        <f aca="false">SUMSQ(C1:C3)</f>
+        <v>114.25</v>
       </c>
     </row>
     <row r="938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13681,26 +13729,26 @@
         <v>935</v>
       </c>
       <c r="L938" s="0" t="n">
-        <f aca="false">COMBIN(5,0)</f>
-        <v>1</v>
+        <f aca="false">SUMSQ(A1:A2,B1:B3)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K939" s="0" t="s">
         <v>936</v>
       </c>
-      <c r="L939" s="0" t="n">
-        <f aca="false">COMBIN(5,5)</f>
-        <v>1</v>
+      <c r="L939" s="0" t="e">
+        <f aca="false">SUMSQ(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K940" s="0" t="s">
         <v>937</v>
       </c>
-      <c r="L940" s="0" t="e">
-        <f aca="false">COMBIN(3,5)</f>
-        <v>#VALUE!</v>
+      <c r="L940" s="0" t="n">
+        <f aca="false">SQRTPI(1)</f>
+        <v>1.77245385090552</v>
       </c>
     </row>
     <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13708,8 +13756,8 @@
         <v>938</v>
       </c>
       <c r="L941" s="0" t="n">
-        <f aca="false">COMBIN(10.9,2.5)</f>
-        <v>45</v>
+        <f aca="false">SQRTPI(2)</f>
+        <v>2.506628274631</v>
       </c>
     </row>
     <row r="942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13717,17 +13765,17 @@
         <v>939</v>
       </c>
       <c r="L942" s="0" t="n">
-        <f aca="false">PERMUT(5,2)</f>
-        <v>20</v>
+        <f aca="false">SQRTPI(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K943" s="0" t="s">
         <v>940</v>
       </c>
-      <c r="L943" s="0" t="n">
-        <f aca="false">PERMUT(3,3)</f>
-        <v>6</v>
+      <c r="L943" s="0" t="e">
+        <f aca="false">SQRTPI(-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13735,17 +13783,17 @@
         <v>941</v>
       </c>
       <c r="L944" s="0" t="n">
-        <f aca="false">PERMUT(3,0)</f>
-        <v>1</v>
+        <f aca="false">FACT(5)</f>
+        <v>120</v>
       </c>
     </row>
     <row r="945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K945" s="0" t="s">
         <v>942</v>
       </c>
-      <c r="L945" s="0" t="e">
-        <f aca="false">PERMUT(2,3)</f>
-        <v>#VALUE!</v>
+      <c r="L945" s="0" t="n">
+        <f aca="false">FACT(0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13753,35 +13801,35 @@
         <v>943</v>
       </c>
       <c r="L946" s="0" t="n">
-        <f aca="false">GCD(24,36)</f>
-        <v>12</v>
+        <f aca="false">FACT(5.9)</f>
+        <v>120</v>
       </c>
     </row>
     <row r="947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K947" s="0" t="s">
         <v>944</v>
       </c>
-      <c r="L947" s="0" t="n">
-        <f aca="false">GCD(5,0)</f>
-        <v>5</v>
+      <c r="L947" s="0" t="e">
+        <f aca="false">FACT(-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K948" s="0" t="s">
         <v>945</v>
       </c>
-      <c r="L948" s="0" t="n">
-        <f aca="false">GCD(A1:A6)</f>
-        <v>1</v>
+      <c r="L948" s="0" t="e">
+        <f aca="false">FACT(171)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K949" s="0" t="s">
         <v>946</v>
       </c>
-      <c r="L949" s="0" t="e">
-        <f aca="false">GCD(-1,2)</f>
-        <v>#VALUE!</v>
+      <c r="L949" s="0" t="n">
+        <f aca="false">FACTDOUBLE(6)</f>
+        <v>48</v>
       </c>
     </row>
     <row r="950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13789,8 +13837,8 @@
         <v>947</v>
       </c>
       <c r="L950" s="0" t="n">
-        <f aca="false">GCD(7.9,14)</f>
-        <v>7</v>
+        <f aca="false">FACTDOUBLE(7)</f>
+        <v>105</v>
       </c>
     </row>
     <row r="951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13798,17 +13846,17 @@
         <v>948</v>
       </c>
       <c r="L951" s="0" t="n">
-        <f aca="false">LCM(4,6)</f>
-        <v>12</v>
+        <f aca="false">FACTDOUBLE(0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K952" s="0" t="s">
         <v>949</v>
       </c>
-      <c r="L952" s="0" t="n">
-        <f aca="false">LCM(A1:A6)</f>
-        <v>60</v>
+      <c r="L952" s="0" t="e">
+        <f aca="false">FACTDOUBLE(-2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13816,17 +13864,17 @@
         <v>950</v>
       </c>
       <c r="L953" s="0" t="n">
-        <f aca="false">LCM(0,5)</f>
-        <v>0</v>
+        <f aca="false">COMBIN(8,2)</f>
+        <v>28</v>
       </c>
     </row>
     <row r="954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K954" s="0" t="s">
         <v>951</v>
       </c>
-      <c r="L954" s="0" t="e">
-        <f aca="false">LCM(-1,2)</f>
-        <v>#VALUE!</v>
+      <c r="L954" s="0" t="n">
+        <f aca="false">COMBIN(5,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13834,26 +13882,26 @@
         <v>952</v>
       </c>
       <c r="L955" s="0" t="n">
-        <f aca="false">QUOTIENT(7,2)</f>
-        <v>3</v>
+        <f aca="false">COMBIN(5,5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K956" s="0" t="s">
         <v>953</v>
       </c>
-      <c r="L956" s="0" t="n">
-        <f aca="false">QUOTIENT(-7,2)</f>
-        <v>-3</v>
+      <c r="L956" s="0" t="e">
+        <f aca="false">COMBIN(3,5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K957" s="0" t="s">
         <v>954</v>
       </c>
-      <c r="L957" s="0" t="e">
-        <f aca="false">QUOTIENT(5,0)</f>
-        <v>#VALUE!</v>
+      <c r="L957" s="0" t="n">
+        <f aca="false">COMBIN(10.9,2.5)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13861,8 +13909,8 @@
         <v>955</v>
       </c>
       <c r="L958" s="0" t="n">
-        <f aca="false">QUOTIENT(C1,A2)</f>
-        <v>5</v>
+        <f aca="false">PERMUT(5,2)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13870,8 +13918,8 @@
         <v>956</v>
       </c>
       <c r="L959" s="0" t="n">
-        <f aca="false">EVEN(3)</f>
-        <v>4</v>
+        <f aca="false">PERMUT(3,3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13879,17 +13927,17 @@
         <v>957</v>
       </c>
       <c r="L960" s="0" t="n">
-        <f aca="false">EVEN(-1)</f>
-        <v>-2</v>
+        <f aca="false">PERMUT(3,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K961" s="0" t="s">
         <v>958</v>
       </c>
-      <c r="L961" s="0" t="n">
-        <f aca="false">EVEN(2)</f>
-        <v>2</v>
+      <c r="L961" s="0" t="e">
+        <f aca="false">PERMUT(2,3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13897,8 +13945,8 @@
         <v>959</v>
       </c>
       <c r="L962" s="0" t="n">
-        <f aca="false">EVEN(1.5)</f>
-        <v>2</v>
+        <f aca="false">GCD(24,36)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13906,8 +13954,8 @@
         <v>960</v>
       </c>
       <c r="L963" s="0" t="n">
-        <f aca="false">EVEN(0)</f>
-        <v>0</v>
+        <f aca="false">GCD(5,0)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13915,17 +13963,17 @@
         <v>961</v>
       </c>
       <c r="L964" s="0" t="n">
-        <f aca="false">ODD(2)</f>
-        <v>3</v>
+        <f aca="false">GCD(A1:A6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K965" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="L965" s="0" t="n">
-        <f aca="false">ODD(-2)</f>
-        <v>-3</v>
+      <c r="L965" s="0" t="e">
+        <f aca="false">GCD(-1,2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13933,8 +13981,8 @@
         <v>963</v>
       </c>
       <c r="L966" s="0" t="n">
-        <f aca="false">ODD(3)</f>
-        <v>3</v>
+        <f aca="false">GCD(7.9,14)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13942,8 +13990,8 @@
         <v>964</v>
       </c>
       <c r="L967" s="0" t="n">
-        <f aca="false">ODD(1.5)</f>
-        <v>3</v>
+        <f aca="false">LCM(4,6)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13951,8 +13999,8 @@
         <v>965</v>
       </c>
       <c r="L968" s="0" t="n">
-        <f aca="false">ODD(0)</f>
-        <v>1</v>
+        <f aca="false">LCM(A1:A6)</f>
+        <v>60</v>
       </c>
     </row>
     <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13960,7 +14008,7 @@
         <v>966</v>
       </c>
       <c r="L969" s="0" t="n">
-        <f aca="false">SIN(0)</f>
+        <f aca="false">LCM(0,5)</f>
         <v>0</v>
       </c>
     </row>
@@ -13968,9 +14016,9 @@
       <c r="K970" s="0" t="s">
         <v>967</v>
       </c>
-      <c r="L970" s="0" t="n">
-        <f aca="false">SIN(PI()/2)</f>
-        <v>1</v>
+      <c r="L970" s="0" t="e">
+        <f aca="false">LCM(-1,2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13978,26 +14026,26 @@
         <v>968</v>
       </c>
       <c r="L971" s="0" t="n">
-        <f aca="false">SIN(1)</f>
-        <v>0.841470984807897</v>
+        <f aca="false">QUOTIENT(7,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K972" s="0" t="s">
         <v>969</v>
       </c>
-      <c r="L972" s="0" t="e">
-        <f aca="false">SIN(B1)</f>
-        <v>#VALUE!</v>
+      <c r="L972" s="0" t="n">
+        <f aca="false">QUOTIENT(-7,2)</f>
+        <v>-3</v>
       </c>
     </row>
     <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K973" s="0" t="s">
         <v>970</v>
       </c>
-      <c r="L973" s="0" t="n">
-        <f aca="false">COS(0)</f>
-        <v>1</v>
+      <c r="L973" s="0" t="e">
+        <f aca="false">QUOTIENT(5,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14005,8 +14053,8 @@
         <v>971</v>
       </c>
       <c r="L974" s="0" t="n">
-        <f aca="false">COS(PI())</f>
-        <v>-1</v>
+        <f aca="false">QUOTIENT(C1,A2)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14014,17 +14062,17 @@
         <v>972</v>
       </c>
       <c r="L975" s="0" t="n">
-        <f aca="false">COS(1)</f>
-        <v>0.54030230586814</v>
+        <f aca="false">EVEN(3)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K976" s="0" t="s">
         <v>973</v>
       </c>
-      <c r="L976" s="0" t="e">
-        <f aca="false">COS(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L976" s="0" t="n">
+        <f aca="false">EVEN(-1)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14032,8 +14080,8 @@
         <v>974</v>
       </c>
       <c r="L977" s="0" t="n">
-        <f aca="false">TAN(0)</f>
-        <v>0</v>
+        <f aca="false">EVEN(2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14041,8 +14089,8 @@
         <v>975</v>
       </c>
       <c r="L978" s="0" t="n">
-        <f aca="false">TAN(1)</f>
-        <v>1.5574077246549</v>
+        <f aca="false">EVEN(1.5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14050,8 +14098,8 @@
         <v>976</v>
       </c>
       <c r="L979" s="0" t="n">
-        <f aca="false">TAN(-1)</f>
-        <v>-1.5574077246549</v>
+        <f aca="false">EVEN(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14059,8 +14107,8 @@
         <v>977</v>
       </c>
       <c r="L980" s="0" t="n">
-        <f aca="false">TAN(A2)</f>
-        <v>-2.18503986326152</v>
+        <f aca="false">ODD(2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14068,8 +14116,8 @@
         <v>978</v>
       </c>
       <c r="L981" s="0" t="n">
-        <f aca="false">ASIN(1)</f>
-        <v>1.5707963267949</v>
+        <f aca="false">ODD(-2)</f>
+        <v>-3</v>
       </c>
     </row>
     <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14077,17 +14125,17 @@
         <v>979</v>
       </c>
       <c r="L982" s="0" t="n">
-        <f aca="false">ASIN(0.5)</f>
-        <v>0.523598775598299</v>
+        <f aca="false">ODD(3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K983" s="0" t="s">
         <v>980</v>
       </c>
-      <c r="L983" s="0" t="e">
-        <f aca="false">ASIN(2)</f>
-        <v>#NUM!</v>
+      <c r="L983" s="0" t="n">
+        <f aca="false">ODD(1.5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14095,8 +14143,8 @@
         <v>981</v>
       </c>
       <c r="L984" s="0" t="n">
-        <f aca="false">ASIN(-1)</f>
-        <v>-1.5707963267949</v>
+        <f aca="false">ODD(0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14104,7 +14152,7 @@
         <v>982</v>
       </c>
       <c r="L985" s="0" t="n">
-        <f aca="false">ACOS(1)</f>
+        <f aca="false">SIN(0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14113,8 +14161,8 @@
         <v>983</v>
       </c>
       <c r="L986" s="0" t="n">
-        <f aca="false">ACOS(-1)</f>
-        <v>3.14159265358979</v>
+        <f aca="false">SIN(PI()/2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14122,8 +14170,8 @@
         <v>984</v>
       </c>
       <c r="L987" s="0" t="n">
-        <f aca="false">ACOS(0.5)</f>
-        <v>1.0471975511966</v>
+        <f aca="false">SIN(1)</f>
+        <v>0.841470984807897</v>
       </c>
     </row>
     <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14131,8 +14179,8 @@
         <v>985</v>
       </c>
       <c r="L988" s="0" t="e">
-        <f aca="false">ACOS(2)</f>
-        <v>#NUM!</v>
+        <f aca="false">SIN(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14140,8 +14188,8 @@
         <v>986</v>
       </c>
       <c r="L989" s="0" t="n">
-        <f aca="false">ATAN(1)</f>
-        <v>0.785398163397448</v>
+        <f aca="false">COS(0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14149,8 +14197,8 @@
         <v>987</v>
       </c>
       <c r="L990" s="0" t="n">
-        <f aca="false">ATAN(0)</f>
-        <v>0</v>
+        <f aca="false">COS(PI())</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14158,17 +14206,17 @@
         <v>988</v>
       </c>
       <c r="L991" s="0" t="n">
-        <f aca="false">ATAN(-1)</f>
-        <v>-0.785398163397448</v>
+        <f aca="false">COS(1)</f>
+        <v>0.54030230586814</v>
       </c>
     </row>
     <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K992" s="0" t="s">
         <v>989</v>
       </c>
-      <c r="L992" s="0" t="n">
-        <f aca="false">ATAN(1000000)</f>
-        <v>1.5707953267949</v>
+      <c r="L992" s="0" t="e">
+        <f aca="false">COS(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14176,8 +14224,8 @@
         <v>990</v>
       </c>
       <c r="L993" s="0" t="n">
-        <f aca="false">ATAN2(1,1)</f>
-        <v>0.785398163397448</v>
+        <f aca="false">TAN(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14185,8 +14233,8 @@
         <v>991</v>
       </c>
       <c r="L994" s="0" t="n">
-        <f aca="false">ATAN2(-1,-1)</f>
-        <v>-2.35619449019235</v>
+        <f aca="false">TAN(1)</f>
+        <v>1.5574077246549</v>
       </c>
     </row>
     <row r="995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14194,8 +14242,8 @@
         <v>992</v>
       </c>
       <c r="L995" s="0" t="n">
-        <f aca="false">ATAN2(0,0)</f>
-        <v>0</v>
+        <f aca="false">TAN(-1)</f>
+        <v>-1.5574077246549</v>
       </c>
     </row>
     <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14203,8 +14251,8 @@
         <v>993</v>
       </c>
       <c r="L996" s="0" t="n">
-        <f aca="false">ATAN2(1,0)</f>
-        <v>0</v>
+        <f aca="false">TAN(A2)</f>
+        <v>-2.18503986326152</v>
       </c>
     </row>
     <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14212,8 +14260,8 @@
         <v>994</v>
       </c>
       <c r="L997" s="0" t="n">
-        <f aca="false">SINH(1)</f>
-        <v>1.1752011936438</v>
+        <f aca="false">ASIN(1)</f>
+        <v>1.5707963267949</v>
       </c>
     </row>
     <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14221,26 +14269,26 @@
         <v>995</v>
       </c>
       <c r="L998" s="0" t="n">
-        <f aca="false">SINH(0)</f>
-        <v>0</v>
+        <f aca="false">ASIN(0.5)</f>
+        <v>0.523598775598299</v>
       </c>
     </row>
     <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K999" s="0" t="s">
         <v>996</v>
       </c>
-      <c r="L999" s="0" t="n">
-        <f aca="false">SINH(-2)</f>
-        <v>-3.62686040784702</v>
+      <c r="L999" s="0" t="e">
+        <f aca="false">ASIN(2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1000" s="0" t="s">
         <v>997</v>
       </c>
-      <c r="L1000" s="0" t="e">
-        <f aca="false">SINH(B1)</f>
-        <v>#VALUE!</v>
+      <c r="L1000" s="0" t="n">
+        <f aca="false">ASIN(-1)</f>
+        <v>-1.5707963267949</v>
       </c>
     </row>
     <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14248,8 +14296,8 @@
         <v>998</v>
       </c>
       <c r="L1001" s="0" t="n">
-        <f aca="false">COSH(0)</f>
-        <v>1</v>
+        <f aca="false">ACOS(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14257,8 +14305,8 @@
         <v>999</v>
       </c>
       <c r="L1002" s="0" t="n">
-        <f aca="false">COSH(1)</f>
-        <v>1.54308063481524</v>
+        <f aca="false">ACOS(-1)</f>
+        <v>3.14159265358979</v>
       </c>
     </row>
     <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14266,8 +14314,8 @@
         <v>1000</v>
       </c>
       <c r="L1003" s="0" t="n">
-        <f aca="false">COSH(-2)</f>
-        <v>3.76219569108363</v>
+        <f aca="false">ACOS(0.5)</f>
+        <v>1.0471975511966</v>
       </c>
     </row>
     <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14275,8 +14323,8 @@
         <v>1001</v>
       </c>
       <c r="L1004" s="0" t="e">
-        <f aca="false">COSH(H2)</f>
-        <v>#N/A</v>
+        <f aca="false">ACOS(2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14284,8 +14332,8 @@
         <v>1002</v>
       </c>
       <c r="L1005" s="0" t="n">
-        <f aca="false">TANH(0)</f>
-        <v>0</v>
+        <f aca="false">ATAN(1)</f>
+        <v>0.785398163397448</v>
       </c>
     </row>
     <row r="1006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14293,8 +14341,8 @@
         <v>1003</v>
       </c>
       <c r="L1006" s="0" t="n">
-        <f aca="false">TANH(1)</f>
-        <v>0.761594155955765</v>
+        <f aca="false">ATAN(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14302,8 +14350,8 @@
         <v>1004</v>
       </c>
       <c r="L1007" s="0" t="n">
-        <f aca="false">TANH(-0.5)</f>
-        <v>-0.46211715726001</v>
+        <f aca="false">ATAN(-1)</f>
+        <v>-0.785398163397448</v>
       </c>
     </row>
     <row r="1008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14311,8 +14359,8 @@
         <v>1005</v>
       </c>
       <c r="L1008" s="0" t="n">
-        <f aca="false">TANH(100)</f>
-        <v>1</v>
+        <f aca="false">ATAN(1000000)</f>
+        <v>1.5707953267949</v>
       </c>
     </row>
     <row r="1009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14320,8 +14368,8 @@
         <v>1006</v>
       </c>
       <c r="L1009" s="0" t="n">
-        <f aca="false">DEGREES(PI())</f>
-        <v>180</v>
+        <f aca="false">ATAN2(1,1)</f>
+        <v>0.785398163397448</v>
       </c>
     </row>
     <row r="1010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14329,8 +14377,8 @@
         <v>1007</v>
       </c>
       <c r="L1010" s="0" t="n">
-        <f aca="false">DEGREES(1)</f>
-        <v>57.2957795130823</v>
+        <f aca="false">ATAN2(-1,-1)</f>
+        <v>-2.35619449019235</v>
       </c>
     </row>
     <row r="1011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14338,7 +14386,7 @@
         <v>1008</v>
       </c>
       <c r="L1011" s="0" t="n">
-        <f aca="false">DEGREES(0)</f>
+        <f aca="false">ATAN2(0,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -14346,9 +14394,9 @@
       <c r="K1012" s="0" t="s">
         <v>1009</v>
       </c>
-      <c r="L1012" s="0" t="e">
-        <f aca="false">DEGREES(B1)</f>
-        <v>#VALUE!</v>
+      <c r="L1012" s="0" t="n">
+        <f aca="false">ATAN2(1,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14356,8 +14404,8 @@
         <v>1010</v>
       </c>
       <c r="L1013" s="0" t="n">
-        <f aca="false">RADIANS(180)</f>
-        <v>3.14159265358979</v>
+        <f aca="false">SINH(1)</f>
+        <v>1.1752011936438</v>
       </c>
     </row>
     <row r="1014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14365,8 +14413,8 @@
         <v>1011</v>
       </c>
       <c r="L1014" s="0" t="n">
-        <f aca="false">RADIANS(90)</f>
-        <v>1.5707963267949</v>
+        <f aca="false">SINH(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14374,17 +14422,17 @@
         <v>1012</v>
       </c>
       <c r="L1015" s="0" t="n">
-        <f aca="false">RADIANS(0)</f>
-        <v>0</v>
+        <f aca="false">SINH(-2)</f>
+        <v>-3.62686040784702</v>
       </c>
     </row>
     <row r="1016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1016" s="0" t="s">
         <v>1013</v>
       </c>
-      <c r="L1016" s="0" t="n">
-        <f aca="false">RADIANS(-45)</f>
-        <v>-0.785398163397448</v>
+      <c r="L1016" s="0" t="e">
+        <f aca="false">SINH(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14392,8 +14440,8 @@
         <v>1014</v>
       </c>
       <c r="L1017" s="0" t="n">
-        <f aca="false">SUMX2MY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
-        <v>-55</v>
+        <f aca="false">COSH(0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14401,17 +14449,17 @@
         <v>1015</v>
       </c>
       <c r="L1018" s="0" t="n">
-        <f aca="false">SUMX2MY2(A1:A3,A4:A6)</f>
-        <v>-63</v>
+        <f aca="false">COSH(1)</f>
+        <v>1.54308063481524</v>
       </c>
     </row>
     <row r="1019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1019" s="0" t="s">
         <v>1016</v>
       </c>
-      <c r="L1019" s="0" t="e">
-        <f aca="false">SUMX2MY2(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1019" s="0" t="n">
+        <f aca="false">COSH(-2)</f>
+        <v>3.76219569108363</v>
       </c>
     </row>
     <row r="1020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14419,8 +14467,8 @@
         <v>1017</v>
       </c>
       <c r="L1020" s="0" t="e">
-        <f aca="false">SUMX2MY2(A1:A3,H1:H3)</f>
-        <v>#DIV/0!</v>
+        <f aca="false">COSH(H2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14428,8 +14476,8 @@
         <v>1018</v>
       </c>
       <c r="L1021" s="0" t="n">
-        <f aca="false">SUMX2PY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
-        <v>521</v>
+        <f aca="false">TANH(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14437,17 +14485,17 @@
         <v>1019</v>
       </c>
       <c r="L1022" s="0" t="n">
-        <f aca="false">SUMX2PY2(A1:A3,A4:A6)</f>
-        <v>91</v>
+        <f aca="false">TANH(1)</f>
+        <v>0.761594155955765</v>
       </c>
     </row>
     <row r="1023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1023" s="0" t="s">
         <v>1020</v>
       </c>
-      <c r="L1023" s="0" t="e">
-        <f aca="false">SUMX2PY2(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1023" s="0" t="n">
+        <f aca="false">TANH(-0.5)</f>
+        <v>-0.46211715726001</v>
       </c>
     </row>
     <row r="1024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14455,8 +14503,8 @@
         <v>1021</v>
       </c>
       <c r="L1024" s="0" t="n">
-        <f aca="false">SUMX2PY2(F1:F2,A1:A2)</f>
-        <v>50005</v>
+        <f aca="false">TANH(100)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14464,8 +14512,8 @@
         <v>1022</v>
       </c>
       <c r="L1025" s="0" t="n">
-        <f aca="false">SUBTOTAL(9,A1:A6)</f>
-        <v>21</v>
+        <f aca="false">DEGREES(PI())</f>
+        <v>180</v>
       </c>
     </row>
     <row r="1026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14473,8 +14521,8 @@
         <v>1023</v>
       </c>
       <c r="L1026" s="0" t="n">
-        <f aca="false">SUBTOTAL(109,A1:A6,C1:C6)</f>
-        <v>1000132.75</v>
+        <f aca="false">DEGREES(1)</f>
+        <v>57.2957795130823</v>
       </c>
     </row>
     <row r="1027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14482,17 +14530,17 @@
         <v>1024</v>
       </c>
       <c r="L1027" s="0" t="n">
-        <f aca="false">SUBTOTAL(1,C1:C6)</f>
-        <v>166685.291666667</v>
+        <f aca="false">DEGREES(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1028" s="0" t="s">
         <v>1025</v>
       </c>
-      <c r="L1028" s="0" t="n">
-        <f aca="false">SUBTOTAL(2,A1:B6)</f>
-        <v>6</v>
+      <c r="L1028" s="0" t="e">
+        <f aca="false">DEGREES(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14500,8 +14548,8 @@
         <v>1026</v>
       </c>
       <c r="L1029" s="0" t="n">
-        <f aca="false">SUBTOTAL(103,A1:B6)</f>
-        <v>12</v>
+        <f aca="false">RADIANS(180)</f>
+        <v>3.14159265358979</v>
       </c>
     </row>
     <row r="1030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14509,8 +14557,8 @@
         <v>1027</v>
       </c>
       <c r="L1030" s="0" t="n">
-        <f aca="false">SUBTOTAL(4,C1:C6)</f>
-        <v>1000000</v>
+        <f aca="false">RADIANS(90)</f>
+        <v>1.5707963267949</v>
       </c>
     </row>
     <row r="1031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14518,8 +14566,8 @@
         <v>1028</v>
       </c>
       <c r="L1031" s="0" t="n">
-        <f aca="false">SUBTOTAL(105,C1:C6)</f>
-        <v>-2</v>
+        <f aca="false">RADIANS(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14527,8 +14575,8 @@
         <v>1029</v>
       </c>
       <c r="L1032" s="0" t="n">
-        <f aca="false">SUBTOTAL(6,A1:A4)</f>
-        <v>24</v>
+        <f aca="false">RADIANS(-45)</f>
+        <v>-0.785398163397448</v>
       </c>
     </row>
     <row r="1033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14536,8 +14584,8 @@
         <v>1030</v>
       </c>
       <c r="L1033" s="0" t="n">
-        <f aca="false">SUBTOTAL(7,A1:A6)</f>
-        <v>1.87082869338697</v>
+        <f aca="false">SUMX2MY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>-55</v>
       </c>
     </row>
     <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14545,35 +14593,35 @@
         <v>1031</v>
       </c>
       <c r="L1034" s="0" t="n">
-        <f aca="false">SUBTOTAL(108,A1:A6)</f>
-        <v>1.70782512765993</v>
+        <f aca="false">SUMX2MY2(A1:A3,A4:A6)</f>
+        <v>-63</v>
       </c>
     </row>
     <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1035" s="0" t="s">
         <v>1032</v>
       </c>
-      <c r="L1035" s="0" t="n">
-        <f aca="false">SUBTOTAL(10,F1:F4)</f>
-        <v>16666.6666666667</v>
+      <c r="L1035" s="0" t="e">
+        <f aca="false">SUMX2MY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1036" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="L1036" s="0" t="n">
-        <f aca="false">SUBTOTAL(111,F1:F4)</f>
-        <v>12500</v>
+      <c r="L1036" s="0" t="e">
+        <f aca="false">SUMX2MY2(A1:A3,H1:H3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1037" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="L1037" s="0" t="e">
-        <f aca="false">SUBTOTAL(9,A1:A3,H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1037" s="0" t="n">
+        <f aca="false">SUMX2PY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>521</v>
       </c>
     </row>
     <row r="1038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14581,17 +14629,17 @@
         <v>1035</v>
       </c>
       <c r="L1038" s="0" t="n">
-        <f aca="false">SUBTOTAL(9.9,A1:A3)</f>
-        <v>6</v>
+        <f aca="false">SUMX2PY2(A1:A3,A4:A6)</f>
+        <v>91</v>
       </c>
     </row>
     <row r="1039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1039" s="0" t="s">
         <v>1036</v>
       </c>
-      <c r="L1039" s="0" t="n">
-        <f aca="false">SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
-        <v>79</v>
+      <c r="L1039" s="0" t="e">
+        <f aca="false">SUMX2PY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14599,17 +14647,17 @@
         <v>1037</v>
       </c>
       <c r="L1040" s="0" t="n">
-        <f aca="false">SUMXMY2(A1:A3,A4:A6)</f>
-        <v>27</v>
+        <f aca="false">SUMX2PY2(F1:F2,A1:A2)</f>
+        <v>50005</v>
       </c>
     </row>
     <row r="1041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1041" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="L1041" s="0" t="e">
-        <f aca="false">SUMXMY2(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1041" s="0" t="n">
+        <f aca="false">SUBTOTAL(9,A1:A6)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="1042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14617,8 +14665,8 @@
         <v>1039</v>
       </c>
       <c r="L1042" s="0" t="n">
-        <f aca="false">SUMXMY2(F1:F2,A1:A2)</f>
-        <v>49005</v>
+        <f aca="false">SUBTOTAL(109,A1:A6,C1:C6)</f>
+        <v>1000132.75</v>
       </c>
     </row>
     <row r="1043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14626,8 +14674,8 @@
         <v>1040</v>
       </c>
       <c r="L1043" s="0" t="n">
-        <f aca="false">COUNTBLANK(D1:D6)</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(1,C1:C6)</f>
+        <v>166685.291666667</v>
       </c>
     </row>
     <row r="1044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14635,8 +14683,8 @@
         <v>1041</v>
       </c>
       <c r="L1044" s="0" t="n">
-        <f aca="false">COUNTBLANK(A1:A6)</f>
-        <v>0</v>
+        <f aca="false">SUBTOTAL(2,A1:B6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14644,8 +14692,8 @@
         <v>1042</v>
       </c>
       <c r="L1045" s="0" t="n">
-        <f aca="false">COUNTBLANK(D3:D4)</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(103,A1:B6)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14653,8 +14701,8 @@
         <v>1043</v>
       </c>
       <c r="L1046" s="0" t="n">
-        <f aca="false">COUNTBLANK(J1:J4)</f>
-        <v>4</v>
+        <f aca="false">SUBTOTAL(4,C1:C6)</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="1047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14662,8 +14710,8 @@
         <v>1044</v>
       </c>
       <c r="L1047" s="0" t="n">
-        <f aca="false">SUMIFS(A1:A6,B1:B6,"*a*")</f>
-        <v>7</v>
+        <f aca="false">SUBTOTAL(105,C1:C6)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="1048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14671,8 +14719,8 @@
         <v>1045</v>
       </c>
       <c r="L1048" s="0" t="n">
-        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",A1:A6,"&lt;5")</f>
-        <v>7</v>
+        <f aca="false">SUBTOTAL(6,A1:A4)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="1049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14680,17 +14728,17 @@
         <v>1046</v>
       </c>
       <c r="L1049" s="0" t="n">
-        <f aca="false">SUMIFS(C1:C6,A1:A6,"&gt;=3")</f>
-        <v>1000103.25</v>
+        <f aca="false">SUBTOTAL(7,A1:A6)</f>
+        <v>1.87082869338697</v>
       </c>
     </row>
     <row r="1050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1050" s="0" t="s">
         <v>1047</v>
       </c>
-      <c r="L1050" s="0" t="e">
-        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",B1:B3,"x")</f>
-        <v>#VALUE!</v>
+      <c r="L1050" s="0" t="n">
+        <f aca="false">SUBTOTAL(108,A1:A6)</f>
+        <v>1.70782512765993</v>
       </c>
     </row>
     <row r="1051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14698,8 +14746,8 @@
         <v>1048</v>
       </c>
       <c r="L1051" s="0" t="n">
-        <f aca="false">SUMIFS(F1:F4,A1:A4,2)</f>
-        <v>200</v>
+        <f aca="false">SUBTOTAL(10,F1:F4)</f>
+        <v>16666.6666666667</v>
       </c>
     </row>
     <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14707,17 +14755,17 @@
         <v>1049</v>
       </c>
       <c r="L1052" s="0" t="n">
-        <f aca="false">SUMIFS(A1:A2,H1:H2,"#N/A")</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(111,F1:F4)</f>
+        <v>12500</v>
       </c>
     </row>
     <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1053" s="0" t="s">
         <v>1050</v>
       </c>
-      <c r="L1053" s="0" t="n">
-        <f aca="false">COUNTIFS(A1:A6,"&gt;2")</f>
-        <v>4</v>
+      <c r="L1053" s="0" t="e">
+        <f aca="false">SUBTOTAL(9,A1:A3,H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14725,8 +14773,8 @@
         <v>1051</v>
       </c>
       <c r="L1054" s="0" t="n">
-        <f aca="false">COUNTIFS(A1:A6,"&gt;2",C1:C6,"&lt;50")</f>
-        <v>2</v>
+        <f aca="false">SUBTOTAL(9.9,A1:A3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14734,26 +14782,26 @@
         <v>1052</v>
       </c>
       <c r="L1055" s="0" t="n">
-        <f aca="false">COUNTIFS(B1:B6,"?????")</f>
-        <v>1</v>
+        <f aca="false">SUMXMY2({2,3,9,1,8,7,5},{6,5,11,7,5,4,4})</f>
+        <v>79</v>
       </c>
     </row>
     <row r="1056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1056" s="0" t="s">
         <v>1053</v>
       </c>
-      <c r="L1056" s="0" t="e">
-        <f aca="false">COUNTIFS(A1:A6,"&gt;2",B1:B5,"a*")</f>
-        <v>#VALUE!</v>
+      <c r="L1056" s="0" t="n">
+        <f aca="false">SUMXMY2(A1:A3,A4:A6)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="1057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1057" s="0" t="s">
         <v>1054</v>
       </c>
-      <c r="L1057" s="0" t="n">
-        <f aca="false">COUNTIFS(D1:D6,"")</f>
-        <v>2</v>
+      <c r="L1057" s="0" t="e">
+        <f aca="false">SUMXMY2(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14761,8 +14809,8 @@
         <v>1055</v>
       </c>
       <c r="L1058" s="0" t="n">
-        <f aca="false">COUNTIFS(A1:A6,"&lt;&gt;3",A1:A6,"&lt;&gt;4")</f>
-        <v>4</v>
+        <f aca="false">SUMXMY2(F1:F2,A1:A2)</f>
+        <v>49005</v>
       </c>
     </row>
     <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14770,8 +14818,8 @@
         <v>1056</v>
       </c>
       <c r="L1059" s="0" t="n">
-        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;2")</f>
-        <v>4.5</v>
+        <f aca="false">COUNTBLANK(D1:D6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14779,17 +14827,17 @@
         <v>1057</v>
       </c>
       <c r="L1060" s="0" t="n">
-        <f aca="false">AVERAGEIFS(C1:C6,A1:A6,"&lt;=3")</f>
-        <v>2.83333333333333</v>
+        <f aca="false">COUNTBLANK(A1:A6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1061" s="0" t="s">
         <v>1058</v>
       </c>
-      <c r="L1061" s="0" t="e">
-        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;10")</f>
-        <v>#DIV/0!</v>
+      <c r="L1061" s="0" t="n">
+        <f aca="false">COUNTBLANK(D3:D4)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14797,8 +14845,8 @@
         <v>1059</v>
       </c>
       <c r="L1062" s="0" t="n">
-        <f aca="false">AVERAGEIFS(A1:A6,B1:B6,"*e*")</f>
-        <v>3.25</v>
+        <f aca="false">COUNTBLANK(J1:J4)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14806,8 +14854,8 @@
         <v>1060</v>
       </c>
       <c r="L1063" s="0" t="n">
-        <f aca="false">AVERAGEIF(A1:A6,"&gt;3")</f>
-        <v>5</v>
+        <f aca="false">SUMIFS(A1:A6,B1:B6,"*a*")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14815,26 +14863,26 @@
         <v>1061</v>
       </c>
       <c r="L1064" s="0" t="n">
-        <f aca="false">AVERAGEIF(B1:B6,"*e*",A1:A6)</f>
-        <v>3.25</v>
+        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",A1:A6,"&lt;5")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1065" s="0" t="s">
         <v>1062</v>
       </c>
-      <c r="L1065" s="0" t="e">
-        <f aca="false">AVERAGEIF(A1:A6,"&gt;10")</f>
-        <v>#DIV/0!</v>
+      <c r="L1065" s="0" t="n">
+        <f aca="false">SUMIFS(C1:C6,A1:A6,"&gt;=3")</f>
+        <v>1000103.25</v>
       </c>
     </row>
     <row r="1066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1066" s="0" t="s">
         <v>1063</v>
       </c>
-      <c r="L1066" s="0" t="n">
-        <f aca="false">AVERAGEIF(C1:C6,"&lt;&gt;0")</f>
-        <v>200022.35</v>
+      <c r="L1066" s="0" t="e">
+        <f aca="false">SUMIFS(A1:A6,A1:A6,"&gt;2",B1:B3,"x")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14842,8 +14890,8 @@
         <v>1064</v>
       </c>
       <c r="L1067" s="0" t="n">
-        <f aca="false">AVERAGEIF(F1:F4,"&gt;=200")</f>
-        <v>300</v>
+        <f aca="false">SUMIFS(F1:F4,A1:A4,2)</f>
+        <v>200</v>
       </c>
     </row>
     <row r="1068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14851,8 +14899,8 @@
         <v>1065</v>
       </c>
       <c r="L1068" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&lt;=4")</f>
-        <v>100</v>
+        <f aca="false">SUMIFS(A1:A2,H1:H2,"#N/A")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14860,8 +14908,8 @@
         <v>1066</v>
       </c>
       <c r="L1069" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(A1:A6,B1:B6,"*e*")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14869,8 +14917,8 @@
         <v>1067</v>
       </c>
       <c r="L1070" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(A1:A6,A1:A6,"&gt;10")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2",C1:C6,"&lt;50")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14878,17 +14926,17 @@
         <v>1068</v>
       </c>
       <c r="L1071" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&gt;=2",A1:A6,"&lt;=3")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(B1:B6,"?????")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1072" s="0" t="s">
         <v>1069</v>
       </c>
-      <c r="L1072" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&lt;=4")</f>
-        <v>-2</v>
+      <c r="L1072" s="0" t="e">
+        <f aca="false">COUNTIFS(A1:A6,"&gt;2",B1:B5,"a*")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14896,8 +14944,8 @@
         <v>1070</v>
       </c>
       <c r="L1073" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(A1:A6,B1:B6,"*e*")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(D1:D6,"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14905,8 +14953,8 @@
         <v>1071</v>
       </c>
       <c r="L1074" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(A1:A6,A1:A6,"&gt;10")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(A1:A6,"&lt;&gt;3",A1:A6,"&lt;&gt;4")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14914,8 +14962,8 @@
         <v>1072</v>
       </c>
       <c r="L1075" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&gt;=3")</f>
-        <v>0</v>
+        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;2")</f>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14923,17 +14971,17 @@
         <v>1073</v>
       </c>
       <c r="L1076" s="0" t="n">
-        <f aca="false">MEDIAN(A1:A6)</f>
-        <v>3.5</v>
+        <f aca="false">AVERAGEIFS(C1:C6,A1:A6,"&lt;=3")</f>
+        <v>2.83333333333333</v>
       </c>
     </row>
     <row r="1077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1077" s="0" t="s">
         <v>1074</v>
       </c>
-      <c r="L1077" s="0" t="n">
-        <f aca="false">MEDIAN(1,2,3)</f>
-        <v>2</v>
+      <c r="L1077" s="0" t="e">
+        <f aca="false">AVERAGEIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14941,35 +14989,35 @@
         <v>1075</v>
       </c>
       <c r="L1078" s="0" t="n">
-        <f aca="false">MEDIAN(C1:C6)</f>
-        <v>6.875</v>
+        <f aca="false">AVERAGEIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>3.25</v>
       </c>
     </row>
     <row r="1079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1079" s="0" t="s">
         <v>1076</v>
       </c>
-      <c r="L1079" s="0" t="e">
-        <f aca="false">MEDIAN(B1:B3)</f>
-        <v>#VALUE!</v>
+      <c r="L1079" s="0" t="n">
+        <f aca="false">AVERAGEIF(A1:A6,"&gt;3")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1080" s="0" t="s">
         <v>1077</v>
       </c>
-      <c r="L1080" s="0" t="e">
-        <f aca="false">MEDIAN(A1:A2,H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1080" s="0" t="n">
+        <f aca="false">AVERAGEIF(B1:B6,"*e*",A1:A6)</f>
+        <v>3.25</v>
       </c>
     </row>
     <row r="1081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1081" s="0" t="s">
         <v>1078</v>
       </c>
-      <c r="L1081" s="0" t="n">
-        <f aca="false">MEDIAN(A1:A5)</f>
-        <v>3</v>
+      <c r="L1081" s="0" t="e">
+        <f aca="false">AVERAGEIF(A1:A6,"&gt;10")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14977,17 +15025,17 @@
         <v>1079</v>
       </c>
       <c r="L1082" s="0" t="n">
-        <f aca="false">MODE(1,2,2,3,3,3)</f>
-        <v>3</v>
+        <f aca="false">AVERAGEIF(C1:C6,"&lt;&gt;0")</f>
+        <v>200022.35</v>
       </c>
     </row>
     <row r="1083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1083" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="L1083" s="0" t="e">
-        <f aca="false">MODE(A1:A6)</f>
-        <v>#VALUE!</v>
+      <c r="L1083" s="0" t="n">
+        <f aca="false">AVERAGEIF(F1:F4,"&gt;=200")</f>
+        <v>300</v>
       </c>
     </row>
     <row r="1084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14995,8 +15043,8 @@
         <v>1081</v>
       </c>
       <c r="L1084" s="0" t="n">
-        <f aca="false">MODE(2,2,3,3)</f>
-        <v>2</v>
+        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&lt;=4")</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15004,8 +15052,8 @@
         <v>1082</v>
       </c>
       <c r="L1085" s="0" t="n">
-        <f aca="false">MODE({1,2,2,3})</f>
-        <v>2</v>
+        <f aca="false">_xlfn.MAXIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15013,17 +15061,17 @@
         <v>1083</v>
       </c>
       <c r="L1086" s="0" t="n">
-        <f aca="false">_xlfn.MODE.SNGL(1,2,2,3,3,3)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.MAXIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1087" s="0" t="s">
         <v>1084</v>
       </c>
-      <c r="L1087" s="0" t="e">
-        <f aca="false">_xlfn.MODE.SNGL(A1:A6)</f>
-        <v>#VALUE!</v>
+      <c r="L1087" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C1:C6,A1:A6,"&gt;=2",A1:A6,"&lt;=3")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15031,8 +15079,8 @@
         <v>1085</v>
       </c>
       <c r="L1088" s="0" t="n">
-        <f aca="false">_xlfn.MODE.SNGL(2,2,3,3)</f>
-        <v>2</v>
+        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&lt;=4")</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="1089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15040,8 +15088,8 @@
         <v>1086</v>
       </c>
       <c r="L1089" s="0" t="n">
-        <f aca="false">_xlfn.MODE.SNGL(B1:B3,5,5)</f>
-        <v>5</v>
+        <f aca="false">_xlfn.MINIFS(A1:A6,B1:B6,"*e*")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15049,17 +15097,17 @@
         <v>1087</v>
       </c>
       <c r="L1090" s="0" t="n">
-        <f aca="false">VAR(A1:A6)</f>
-        <v>3.5</v>
+        <f aca="false">_xlfn.MINIFS(A1:A6,A1:A6,"&gt;10")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1091" s="0" t="s">
         <v>1088</v>
       </c>
-      <c r="L1091" s="0" t="e">
-        <f aca="false">VAR(5)</f>
-        <v>#DIV/0!</v>
+      <c r="L1091" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C1:C6,A1:A6,"&gt;=3")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15067,17 +15115,17 @@
         <v>1089</v>
       </c>
       <c r="L1092" s="0" t="n">
-        <f aca="false">VAR(1,2)</f>
-        <v>0.5</v>
+        <f aca="false">MEDIAN(A1:A6)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1093" s="0" t="s">
         <v>1090</v>
       </c>
-      <c r="L1093" s="0" t="e">
-        <f aca="false">VAR(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1093" s="0" t="n">
+        <f aca="false">MEDIAN(1,2,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15085,17 +15133,17 @@
         <v>1091</v>
       </c>
       <c r="L1094" s="0" t="n">
-        <f aca="false">_xlfn.VAR.S(A1:A6)</f>
-        <v>3.5</v>
+        <f aca="false">MEDIAN(C1:C6)</f>
+        <v>6.875</v>
       </c>
     </row>
     <row r="1095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1095" s="0" t="s">
         <v>1092</v>
       </c>
-      <c r="L1095" s="0" t="n">
-        <f aca="false">_xlfn.VAR.S(C1:C4)</f>
-        <v>2390.39583333333</v>
+      <c r="L1095" s="0" t="e">
+        <f aca="false">MEDIAN(B1:B3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15103,7 +15151,7 @@
         <v>1093</v>
       </c>
       <c r="L1096" s="0" t="e">
-        <f aca="false">_xlfn.VAR.S(A1,H1)</f>
+        <f aca="false">MEDIAN(A1:A2,H1)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15111,9 +15159,9 @@
       <c r="K1097" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="L1097" s="0" t="e">
-        <f aca="false">_xlfn.VAR.S(A1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1097" s="0" t="n">
+        <f aca="false">MEDIAN(A1:A5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15121,17 +15169,17 @@
         <v>1095</v>
       </c>
       <c r="L1098" s="0" t="n">
-        <f aca="false">_xlfn.VAR.P(A1:A6)</f>
-        <v>2.91666666666667</v>
+        <f aca="false">MODE(1,2,2,3,3,3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1099" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="L1099" s="0" t="n">
-        <f aca="false">_xlfn.VAR.P(5)</f>
-        <v>0</v>
+      <c r="L1099" s="0" t="e">
+        <f aca="false">MODE(A1:A6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15139,17 +15187,17 @@
         <v>1097</v>
       </c>
       <c r="L1100" s="0" t="n">
-        <f aca="false">_xlfn.VAR.P(C1:C4)</f>
-        <v>1792.796875</v>
+        <f aca="false">MODE(2,2,3,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1101" s="0" t="s">
         <v>1098</v>
       </c>
-      <c r="L1101" s="0" t="e">
-        <f aca="false">_xlfn.VAR.P(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1101" s="0" t="n">
+        <f aca="false">MODE({1,2,2,3})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15157,17 +15205,17 @@
         <v>1099</v>
       </c>
       <c r="L1102" s="0" t="n">
-        <f aca="false">VARP(A1:A6)</f>
-        <v>2.91666666666667</v>
+        <f aca="false">_xlfn.MODE.SNGL(1,2,2,3,3,3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1103" s="0" t="s">
         <v>1100</v>
       </c>
-      <c r="L1103" s="0" t="n">
-        <f aca="false">VARP(5)</f>
-        <v>0</v>
+      <c r="L1103" s="0" t="e">
+        <f aca="false">_xlfn.MODE.SNGL(A1:A6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15175,17 +15223,17 @@
         <v>1101</v>
       </c>
       <c r="L1104" s="0" t="n">
-        <f aca="false">VARP(1,2,3,4)</f>
-        <v>1.25</v>
+        <f aca="false">_xlfn.MODE.SNGL(2,2,3,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1105" s="0" t="s">
         <v>1102</v>
       </c>
-      <c r="L1105" s="0" t="e">
-        <f aca="false">VARP(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1105" s="0" t="n">
+        <f aca="false">_xlfn.MODE.SNGL(B1:B3,5,5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15193,8 +15241,8 @@
         <v>1103</v>
       </c>
       <c r="L1106" s="0" t="n">
-        <f aca="false">STDEV(A1:A6)</f>
-        <v>1.87082869338697</v>
+        <f aca="false">VAR(A1:A6)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15202,7 +15250,7 @@
         <v>1104</v>
       </c>
       <c r="L1107" s="0" t="e">
-        <f aca="false">STDEV(5)</f>
+        <f aca="false">VAR(5)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15211,8 +15259,8 @@
         <v>1105</v>
       </c>
       <c r="L1108" s="0" t="n">
-        <f aca="false">STDEV(1,2)</f>
-        <v>0.707106781186548</v>
+        <f aca="false">VAR(1,2)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15220,7 +15268,7 @@
         <v>1106</v>
       </c>
       <c r="L1109" s="0" t="e">
-        <f aca="false">STDEV(B1:B3)</f>
+        <f aca="false">VAR(B1:B3)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15229,8 +15277,8 @@
         <v>1107</v>
       </c>
       <c r="L1110" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.S(A1:A6)</f>
-        <v>1.87082869338697</v>
+        <f aca="false">_xlfn.VAR.S(A1:A6)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15238,8 +15286,8 @@
         <v>1108</v>
       </c>
       <c r="L1111" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.S(C1:C4)</f>
-        <v>48.8916744787222</v>
+        <f aca="false">_xlfn.VAR.S(C1:C4)</f>
+        <v>2390.39583333333</v>
       </c>
     </row>
     <row r="1112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15247,7 +15295,7 @@
         <v>1109</v>
       </c>
       <c r="L1112" s="0" t="e">
-        <f aca="false">_xlfn.STDEV.S(1)</f>
+        <f aca="false">_xlfn.VAR.S(A1,H1)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15256,7 +15304,7 @@
         <v>1110</v>
       </c>
       <c r="L1113" s="0" t="e">
-        <f aca="false">_xlfn.STDEV.S(A1,H1)</f>
+        <f aca="false">_xlfn.VAR.S(A1)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15265,8 +15313,8 @@
         <v>1111</v>
       </c>
       <c r="L1114" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.P(A1:A6)</f>
-        <v>1.70782512765993</v>
+        <f aca="false">_xlfn.VAR.P(A1:A6)</f>
+        <v>2.91666666666667</v>
       </c>
     </row>
     <row r="1115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15274,7 +15322,7 @@
         <v>1112</v>
       </c>
       <c r="L1115" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.P(5)</f>
+        <f aca="false">_xlfn.VAR.P(5)</f>
         <v>0</v>
       </c>
     </row>
@@ -15283,8 +15331,8 @@
         <v>1113</v>
       </c>
       <c r="L1116" s="0" t="n">
-        <f aca="false">_xlfn.STDEV.P(C1:C4)</f>
-        <v>42.3414321321327</v>
+        <f aca="false">_xlfn.VAR.P(C1:C4)</f>
+        <v>1792.796875</v>
       </c>
     </row>
     <row r="1117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15292,7 +15340,7 @@
         <v>1114</v>
       </c>
       <c r="L1117" s="0" t="e">
-        <f aca="false">_xlfn.STDEV.P(B1:B3)</f>
+        <f aca="false">_xlfn.VAR.P(B1:B3)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15301,8 +15349,8 @@
         <v>1115</v>
       </c>
       <c r="L1118" s="0" t="n">
-        <f aca="false">STDEVP(A1:A6)</f>
-        <v>1.70782512765993</v>
+        <f aca="false">VARP(A1:A6)</f>
+        <v>2.91666666666667</v>
       </c>
     </row>
     <row r="1119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15310,7 +15358,7 @@
         <v>1116</v>
       </c>
       <c r="L1119" s="0" t="n">
-        <f aca="false">STDEVP(5)</f>
+        <f aca="false">VARP(5)</f>
         <v>0</v>
       </c>
     </row>
@@ -15319,8 +15367,8 @@
         <v>1117</v>
       </c>
       <c r="L1120" s="0" t="n">
-        <f aca="false">STDEVP(1,2,3,4)</f>
-        <v>1.1180339887499</v>
+        <f aca="false">VARP(1,2,3,4)</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="1121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15328,7 +15376,7 @@
         <v>1118</v>
       </c>
       <c r="L1121" s="0" t="e">
-        <f aca="false">STDEVP(B1:B3)</f>
+        <f aca="false">VARP(B1:B3)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -15337,8 +15385,8 @@
         <v>1119</v>
       </c>
       <c r="L1122" s="0" t="n">
-        <f aca="false">LARGE(A1:A6,2)</f>
-        <v>5</v>
+        <f aca="false">STDEV(A1:A6)</f>
+        <v>1.87082869338697</v>
       </c>
     </row>
     <row r="1123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15346,8 +15394,8 @@
         <v>1120</v>
       </c>
       <c r="L1123" s="0" t="e">
-        <f aca="false">LARGE(A1:A6,7)</f>
-        <v>#VALUE!</v>
+        <f aca="false">STDEV(5)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15355,8 +15403,8 @@
         <v>1121</v>
       </c>
       <c r="L1124" s="0" t="n">
-        <f aca="false">LARGE(C1:C6,1)</f>
-        <v>1000000</v>
+        <f aca="false">STDEV(1,2)</f>
+        <v>0.707106781186548</v>
       </c>
     </row>
     <row r="1125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15364,8 +15412,8 @@
         <v>1122</v>
       </c>
       <c r="L1125" s="0" t="e">
-        <f aca="false">LARGE(A1:A6,0)</f>
-        <v>#VALUE!</v>
+        <f aca="false">STDEV(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15373,8 +15421,8 @@
         <v>1123</v>
       </c>
       <c r="L1126" s="0" t="n">
-        <f aca="false">LARGE(A1:A6,1.5)</f>
-        <v>5</v>
+        <f aca="false">_xlfn.STDEV.S(A1:A6)</f>
+        <v>1.87082869338697</v>
       </c>
     </row>
     <row r="1127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15382,17 +15430,17 @@
         <v>1124</v>
       </c>
       <c r="L1127" s="0" t="n">
-        <f aca="false">SMALL(A1:A6,1)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.STDEV.S(C1:C4)</f>
+        <v>48.8916744787222</v>
       </c>
     </row>
     <row r="1128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1128" s="0" t="s">
         <v>1125</v>
       </c>
-      <c r="L1128" s="0" t="n">
-        <f aca="false">SMALL(C1:C6,2)</f>
-        <v>0</v>
+      <c r="L1128" s="0" t="e">
+        <f aca="false">_xlfn.STDEV.S(1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15400,8 +15448,8 @@
         <v>1126</v>
       </c>
       <c r="L1129" s="0" t="e">
-        <f aca="false">SMALL(B1:B6,1)</f>
-        <v>#VALUE!</v>
+        <f aca="false">_xlfn.STDEV.S(A1,H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15409,8 +15457,8 @@
         <v>1127</v>
       </c>
       <c r="L1130" s="0" t="n">
-        <f aca="false">SMALL(A1:A6,6)</f>
-        <v>6</v>
+        <f aca="false">_xlfn.STDEV.P(A1:A6)</f>
+        <v>1.70782512765993</v>
       </c>
     </row>
     <row r="1131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15418,8 +15466,8 @@
         <v>1128</v>
       </c>
       <c r="L1131" s="0" t="n">
-        <f aca="false">RANK(3,A1:A6)</f>
-        <v>4</v>
+        <f aca="false">_xlfn.STDEV.P(5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15427,8 +15475,8 @@
         <v>1129</v>
       </c>
       <c r="L1132" s="0" t="n">
-        <f aca="false">RANK(3,A1:A6,1)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.STDEV.P(C1:C4)</f>
+        <v>42.3414321321327</v>
       </c>
     </row>
     <row r="1133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15436,8 +15484,8 @@
         <v>1130</v>
       </c>
       <c r="L1133" s="0" t="e">
-        <f aca="false">RANK(9,A1:A6)</f>
-        <v>#N/A</v>
+        <f aca="false">_xlfn.STDEV.P(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15445,8 +15493,8 @@
         <v>1131</v>
       </c>
       <c r="L1134" s="0" t="n">
-        <f aca="false">RANK(100,C1:C6)</f>
-        <v>2</v>
+        <f aca="false">STDEVP(A1:A6)</f>
+        <v>1.70782512765993</v>
       </c>
     </row>
     <row r="1135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15454,8 +15502,8 @@
         <v>1132</v>
       </c>
       <c r="L1135" s="0" t="n">
-        <f aca="false">_xlfn.RANK.EQ(100,C1:C6)</f>
-        <v>2</v>
+        <f aca="false">STDEVP(5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15463,8 +15511,8 @@
         <v>1133</v>
       </c>
       <c r="L1136" s="0" t="n">
-        <f aca="false">_xlfn.RANK.EQ(1,A1:A6,1)</f>
-        <v>1</v>
+        <f aca="false">STDEVP(1,2,3,4)</f>
+        <v>1.1180339887499</v>
       </c>
     </row>
     <row r="1137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15472,8 +15520,8 @@
         <v>1134</v>
       </c>
       <c r="L1137" s="0" t="e">
-        <f aca="false">_xlfn.RANK.EQ(9,A1:A6)</f>
-        <v>#N/A</v>
+        <f aca="false">STDEVP(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15481,17 +15529,17 @@
         <v>1135</v>
       </c>
       <c r="L1138" s="0" t="n">
-        <f aca="false">_xlfn.RANK.EQ(0,C1:C6,1)</f>
-        <v>2</v>
+        <f aca="false">LARGE(A1:A6,2)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1139" s="0" t="s">
         <v>1136</v>
       </c>
-      <c r="L1139" s="0" t="n">
-        <f aca="false">_xlfn.RANK.AVG(3,A1:A6)</f>
-        <v>4</v>
+      <c r="L1139" s="0" t="e">
+        <f aca="false">LARGE(A1:A6,7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15499,8 +15547,8 @@
         <v>1137</v>
       </c>
       <c r="L1140" s="0" t="n">
-        <f aca="false">_xlfn.RANK.AVG(1,A1:A6,1)</f>
-        <v>1</v>
+        <f aca="false">LARGE(C1:C6,1)</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="1141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15508,8 +15556,8 @@
         <v>1138</v>
       </c>
       <c r="L1141" s="0" t="e">
-        <f aca="false">_xlfn.RANK.AVG(9,A1:A6)</f>
-        <v>#N/A</v>
+        <f aca="false">LARGE(A1:A6,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15517,8 +15565,8 @@
         <v>1139</v>
       </c>
       <c r="L1142" s="0" t="n">
-        <f aca="false">_xlfn.RANK.AVG(100,C1:C6)</f>
-        <v>2</v>
+        <f aca="false">LARGE(A1:A6,1.5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15526,8 +15574,8 @@
         <v>1140</v>
       </c>
       <c r="L1143" s="0" t="n">
-        <f aca="false">PERCENTILE(A1:A6,0.5)</f>
-        <v>3.5</v>
+        <f aca="false">SMALL(A1:A6,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15535,26 +15583,26 @@
         <v>1141</v>
       </c>
       <c r="L1144" s="0" t="n">
-        <f aca="false">PERCENTILE(A1:A6,0.25)</f>
-        <v>2.25</v>
+        <f aca="false">SMALL(C1:C6,2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1145" s="0" t="s">
         <v>1142</v>
       </c>
-      <c r="L1145" s="0" t="n">
-        <f aca="false">PERCENTILE(A1:A6,0)</f>
-        <v>1</v>
+      <c r="L1145" s="0" t="e">
+        <f aca="false">SMALL(B1:B6,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1146" s="0" t="s">
         <v>1143</v>
       </c>
-      <c r="L1146" s="0" t="e">
-        <f aca="false">PERCENTILE(A1:A6,1.5)</f>
-        <v>#VALUE!</v>
+      <c r="L1146" s="0" t="n">
+        <f aca="false">SMALL(A1:A6,6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15562,8 +15610,8 @@
         <v>1144</v>
       </c>
       <c r="L1147" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,0.9)</f>
-        <v>5.5</v>
+        <f aca="false">RANK(3,A1:A6)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15571,26 +15619,26 @@
         <v>1145</v>
       </c>
       <c r="L1148" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.INC(C1:C6,0.5)</f>
-        <v>6.875</v>
+        <f aca="false">RANK(3,A1:A6,1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1149" s="0" t="s">
         <v>1146</v>
       </c>
-      <c r="L1149" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,1)</f>
-        <v>6</v>
+      <c r="L1149" s="0" t="e">
+        <f aca="false">RANK(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1150" s="0" t="s">
         <v>1147</v>
       </c>
-      <c r="L1150" s="0" t="e">
-        <f aca="false">_xlfn.PERCENTILE.INC(B1:B3,0.5)</f>
-        <v>#VALUE!</v>
+      <c r="L1150" s="0" t="n">
+        <f aca="false">RANK(100,C1:C6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15598,8 +15646,8 @@
         <v>1148</v>
       </c>
       <c r="L1151" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.5)</f>
-        <v>3.5</v>
+        <f aca="false">_xlfn.RANK.EQ(100,C1:C6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15607,8 +15655,8 @@
         <v>1149</v>
       </c>
       <c r="L1152" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.25)</f>
-        <v>1.75</v>
+        <f aca="false">_xlfn.RANK.EQ(1,A1:A6,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15616,8 +15664,8 @@
         <v>1150</v>
       </c>
       <c r="L1153" s="0" t="e">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.1)</f>
-        <v>#VALUE!</v>
+        <f aca="false">_xlfn.RANK.EQ(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15625,8 +15673,8 @@
         <v>1151</v>
       </c>
       <c r="L1154" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.8)</f>
-        <v>5.6</v>
+        <f aca="false">_xlfn.RANK.EQ(0,C1:C6,1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15634,8 +15682,8 @@
         <v>1152</v>
       </c>
       <c r="L1155" s="0" t="n">
-        <f aca="false">QUARTILE(A1:A6,1)</f>
-        <v>2.25</v>
+        <f aca="false">_xlfn.RANK.AVG(3,A1:A6)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15643,26 +15691,26 @@
         <v>1153</v>
       </c>
       <c r="L1156" s="0" t="n">
-        <f aca="false">QUARTILE(A1:A6,3)</f>
-        <v>4.75</v>
+        <f aca="false">_xlfn.RANK.AVG(1,A1:A6,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1157" s="0" t="s">
         <v>1154</v>
       </c>
-      <c r="L1157" s="0" t="n">
-        <f aca="false">QUARTILE(A1:A6,0)</f>
-        <v>1</v>
+      <c r="L1157" s="0" t="e">
+        <f aca="false">_xlfn.RANK.AVG(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1158" s="0" t="s">
         <v>1155</v>
       </c>
-      <c r="L1158" s="0" t="e">
-        <f aca="false">QUARTILE(A1:A6,5)</f>
-        <v>#VALUE!</v>
+      <c r="L1158" s="0" t="n">
+        <f aca="false">_xlfn.RANK.AVG(100,C1:C6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15670,7 +15718,7 @@
         <v>1156</v>
       </c>
       <c r="L1159" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,2)</f>
+        <f aca="false">PERCENTILE(A1:A6,0.5)</f>
         <v>3.5</v>
       </c>
     </row>
@@ -15679,8 +15727,8 @@
         <v>1157</v>
       </c>
       <c r="L1160" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.INC(C1:C6,1)</f>
-        <v>0.8125</v>
+        <f aca="false">PERCENTILE(A1:A6,0.25)</f>
+        <v>2.25</v>
       </c>
     </row>
     <row r="1161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15688,8 +15736,8 @@
         <v>1158</v>
       </c>
       <c r="L1161" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,4)</f>
-        <v>6</v>
+        <f aca="false">PERCENTILE(A1:A6,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15697,7 +15745,7 @@
         <v>1159</v>
       </c>
       <c r="L1162" s="0" t="e">
-        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,-1)</f>
+        <f aca="false">PERCENTILE(A1:A6,1.5)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15706,8 +15754,8 @@
         <v>1160</v>
       </c>
       <c r="L1163" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,1)</f>
-        <v>1.75</v>
+        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,0.9)</f>
+        <v>5.5</v>
       </c>
     </row>
     <row r="1164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15715,17 +15763,17 @@
         <v>1161</v>
       </c>
       <c r="L1164" s="0" t="n">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,3)</f>
-        <v>5.25</v>
+        <f aca="false">_xlfn.PERCENTILE.INC(C1:C6,0.5)</f>
+        <v>6.875</v>
       </c>
     </row>
     <row r="1165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1165" s="0" t="s">
         <v>1162</v>
       </c>
-      <c r="L1165" s="0" t="e">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1165" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTILE.INC(A1:A6,1)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15733,7 +15781,7 @@
         <v>1163</v>
       </c>
       <c r="L1166" s="0" t="e">
-        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,4)</f>
+        <f aca="false">_xlfn.PERCENTILE.INC(B1:B3,0.5)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15742,8 +15790,8 @@
         <v>1164</v>
       </c>
       <c r="L1167" s="0" t="n">
-        <f aca="false">PERCENTRANK(A1:A6,3)</f>
-        <v>0.4</v>
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.5)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15751,8 +15799,8 @@
         <v>1165</v>
       </c>
       <c r="L1168" s="0" t="n">
-        <f aca="false">PERCENTRANK(A1:A6,3.5)</f>
-        <v>0.5</v>
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.25)</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="1169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15760,7 +15808,7 @@
         <v>1166</v>
       </c>
       <c r="L1169" s="0" t="e">
-        <f aca="false">PERCENTRANK(A1:A6,7)</f>
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15769,8 +15817,8 @@
         <v>1167</v>
       </c>
       <c r="L1170" s="0" t="n">
-        <f aca="false">PERCENTRANK(A1:A6,1)</f>
-        <v>0</v>
+        <f aca="false">_xlfn.PERCENTILE.EXC(A1:A6,0.8)</f>
+        <v>5.6</v>
       </c>
     </row>
     <row r="1171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15778,8 +15826,8 @@
         <v>1168</v>
       </c>
       <c r="L1171" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,2.5,2)</f>
-        <v>0.3</v>
+        <f aca="false">QUARTILE(A1:A6,1)</f>
+        <v>2.25</v>
       </c>
     </row>
     <row r="1172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15787,26 +15835,26 @@
         <v>1169</v>
       </c>
       <c r="L1172" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,6)</f>
-        <v>1</v>
+        <f aca="false">QUARTILE(A1:A6,3)</f>
+        <v>4.75</v>
       </c>
     </row>
     <row r="1173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1173" s="0" t="s">
         <v>1170</v>
       </c>
-      <c r="L1173" s="0" t="e">
-        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1173" s="0" t="n">
+        <f aca="false">QUARTILE(A1:A6,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1174" s="0" t="s">
         <v>1171</v>
       </c>
-      <c r="L1174" s="0" t="n">
-        <f aca="false">_xlfn.PERCENTRANK.INC(C1:C6,10.5)</f>
-        <v>0.6</v>
+      <c r="L1174" s="0" t="e">
+        <f aca="false">QUARTILE(A1:A6,5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15814,8 +15862,8 @@
         <v>1172</v>
       </c>
       <c r="L1175" s="0" t="n">
-        <f aca="false">CORREL(A1:A4,F1:F4)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,2)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15823,17 +15871,17 @@
         <v>1173</v>
       </c>
       <c r="L1176" s="0" t="n">
-        <f aca="false">CORREL(A1:A4,{4;3;2;1})</f>
-        <v>-1</v>
+        <f aca="false">_xlfn.QUARTILE.INC(C1:C6,1)</f>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="1177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1177" s="0" t="s">
         <v>1174</v>
       </c>
-      <c r="L1177" s="0" t="e">
-        <f aca="false">CORREL(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1177" s="0" t="n">
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,4)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15841,8 +15889,8 @@
         <v>1175</v>
       </c>
       <c r="L1178" s="0" t="e">
-        <f aca="false">CORREL(A1,F1)</f>
-        <v>#DIV/0!</v>
+        <f aca="false">_xlfn.QUARTILE.INC(A1:A6,-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15850,8 +15898,8 @@
         <v>1176</v>
       </c>
       <c r="L1179" s="0" t="n">
-        <f aca="false">CORREL(A1:A6,C1:C6)</f>
-        <v>0.654676581102423</v>
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,1)</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="1180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15859,17 +15907,17 @@
         <v>1177</v>
       </c>
       <c r="L1180" s="0" t="n">
-        <f aca="false">COVAR(A1:A4,F1:F4)</f>
-        <v>125</v>
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,3)</f>
+        <v>5.25</v>
       </c>
     </row>
     <row r="1181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1181" s="0" t="s">
         <v>1178</v>
       </c>
-      <c r="L1181" s="0" t="n">
-        <f aca="false">COVAR(A1:A6,C1:C6)</f>
-        <v>416671.9375</v>
+      <c r="L1181" s="0" t="e">
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15877,7 +15925,7 @@
         <v>1179</v>
       </c>
       <c r="L1182" s="0" t="e">
-        <f aca="false">COVAR(A1:A3,A1:A4)</f>
+        <f aca="false">_xlfn.QUARTILE.EXC(A1:A6,4)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -15885,9 +15933,9 @@
       <c r="K1183" s="0" t="s">
         <v>1180</v>
       </c>
-      <c r="L1183" s="0" t="e">
-        <f aca="false">COVAR(B1:B3,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1183" s="0" t="n">
+        <f aca="false">PERCENTRANK(A1:A6,3)</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="1184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15895,35 +15943,35 @@
         <v>1181</v>
       </c>
       <c r="L1184" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.P(A1:A4,F1:F4)</f>
-        <v>125</v>
+        <f aca="false">PERCENTRANK(A1:A6,3.5)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1185" s="0" t="s">
         <v>1182</v>
       </c>
-      <c r="L1185" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.P(A1:A6,C1:C6)</f>
-        <v>416671.9375</v>
+      <c r="L1185" s="0" t="e">
+        <f aca="false">PERCENTRANK(A1:A6,7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1186" s="0" t="s">
         <v>1183</v>
       </c>
-      <c r="L1186" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.P(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1186" s="0" t="n">
+        <f aca="false">PERCENTRANK(A1:A6,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1187" s="0" t="s">
         <v>1184</v>
       </c>
-      <c r="L1187" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.P(B1:B3,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1187" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,2.5,2)</f>
+        <v>0.3</v>
       </c>
     </row>
     <row r="1188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15931,35 +15979,35 @@
         <v>1185</v>
       </c>
       <c r="L1188" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.S(A1:A4,F1:F4)</f>
-        <v>166.666666666667</v>
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1189" s="0" t="s">
         <v>1186</v>
       </c>
-      <c r="L1189" s="0" t="n">
-        <f aca="false">_xlfn.COVARIANCE.S(A1:A6,C1:C6)</f>
-        <v>500006.325</v>
+      <c r="L1189" s="0" t="e">
+        <f aca="false">_xlfn.PERCENTRANK.INC(A1:A6,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1190" s="0" t="s">
         <v>1187</v>
       </c>
-      <c r="L1190" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.S(A1:A3,A1:A4)</f>
-        <v>#VALUE!</v>
+      <c r="L1190" s="0" t="n">
+        <f aca="false">_xlfn.PERCENTRANK.INC(C1:C6,10.5)</f>
+        <v>0.6</v>
       </c>
     </row>
     <row r="1191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1191" s="0" t="s">
         <v>1188</v>
       </c>
-      <c r="L1191" s="0" t="e">
-        <f aca="false">_xlfn.COVARIANCE.S(A1,F1)</f>
-        <v>#VALUE!</v>
+      <c r="L1191" s="0" t="n">
+        <f aca="false">CORREL(A1:A4,F1:F4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15967,17 +16015,17 @@
         <v>1189</v>
       </c>
       <c r="L1192" s="0" t="n">
-        <f aca="false">SLOPE(F1:F4,A1:A4)</f>
-        <v>100</v>
+        <f aca="false">CORREL(A1:A4,{4;3;2;1})</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="1193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1193" s="0" t="s">
         <v>1190</v>
       </c>
-      <c r="L1193" s="0" t="n">
-        <f aca="false">SLOPE(C1:C6,A1:A6)</f>
-        <v>142858.95</v>
+      <c r="L1193" s="0" t="e">
+        <f aca="false">CORREL(A1:A3,A1:A4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15985,17 +16033,17 @@
         <v>1191</v>
       </c>
       <c r="L1194" s="0" t="e">
-        <f aca="false">SLOPE(F1:F4,A1:A3)</f>
-        <v>#VALUE!</v>
+        <f aca="false">CORREL(A1,F1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1195" s="0" t="s">
         <v>1192</v>
       </c>
-      <c r="L1195" s="0" t="e">
-        <f aca="false">SLOPE(F1:F4,{1;1;1;1})</f>
-        <v>#DIV/0!</v>
+      <c r="L1195" s="0" t="n">
+        <f aca="false">CORREL(A1:A6,C1:C6)</f>
+        <v>0.654676581102423</v>
       </c>
     </row>
     <row r="1196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16003,8 +16051,8 @@
         <v>1193</v>
       </c>
       <c r="L1196" s="0" t="n">
-        <f aca="false">INTERCEPT(F1:F4,A1:A4)</f>
-        <v>0</v>
+        <f aca="false">COVAR(A1:A4,F1:F4)</f>
+        <v>125</v>
       </c>
     </row>
     <row r="1197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16012,8 +16060,8 @@
         <v>1194</v>
       </c>
       <c r="L1197" s="0" t="n">
-        <f aca="false">INTERCEPT(C1:C6,A1:A6)</f>
-        <v>-333321.033333333</v>
+        <f aca="false">COVAR(A1:A6,C1:C6)</f>
+        <v>416671.9375</v>
       </c>
     </row>
     <row r="1198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16021,7 +16069,7 @@
         <v>1195</v>
       </c>
       <c r="L1198" s="0" t="e">
-        <f aca="false">INTERCEPT(F1:F4,A1:A3)</f>
+        <f aca="false">COVAR(A1:A3,A1:A4)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16030,8 +16078,8 @@
         <v>1196</v>
       </c>
       <c r="L1199" s="0" t="e">
-        <f aca="false">INTERCEPT(F1:F4,{1;1;1;1})</f>
-        <v>#DIV/0!</v>
+        <f aca="false">COVAR(B1:B3,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16039,8 +16087,8 @@
         <v>1197</v>
       </c>
       <c r="L1200" s="0" t="n">
-        <f aca="false">RSQ(F1:F4,A1:A4)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A4,F1:F4)</f>
+        <v>125</v>
       </c>
     </row>
     <row r="1201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16048,8 +16096,8 @@
         <v>1198</v>
       </c>
       <c r="L1201" s="0" t="n">
-        <f aca="false">RSQ(C1:C6,A1:A6)</f>
-        <v>0.428601425843957</v>
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A6,C1:C6)</f>
+        <v>416671.9375</v>
       </c>
     </row>
     <row r="1202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16057,7 +16105,7 @@
         <v>1199</v>
       </c>
       <c r="L1202" s="0" t="e">
-        <f aca="false">RSQ(F1:F4,A1:A3)</f>
+        <f aca="false">_xlfn.COVARIANCE.P(A1:A3,A1:A4)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16066,8 +16114,8 @@
         <v>1200</v>
       </c>
       <c r="L1203" s="0" t="e">
-        <f aca="false">RSQ(F1:F4,{1;1;1;1})</f>
-        <v>#DIV/0!</v>
+        <f aca="false">_xlfn.COVARIANCE.P(B1:B3,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16075,8 +16123,8 @@
         <v>1201</v>
       </c>
       <c r="L1204" s="0" t="n">
-        <f aca="false">FORECAST(5,F1:F4,A1:A4)</f>
-        <v>500</v>
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A4,F1:F4)</f>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="1205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16084,8 +16132,8 @@
         <v>1202</v>
       </c>
       <c r="L1205" s="0" t="n">
-        <f aca="false">FORECAST(7,C1:C6,A1:A6)</f>
-        <v>666691.616666667</v>
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A6,C1:C6)</f>
+        <v>500006.325</v>
       </c>
     </row>
     <row r="1206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16093,7 +16141,7 @@
         <v>1203</v>
       </c>
       <c r="L1206" s="0" t="e">
-        <f aca="false">FORECAST(5,F1:F4,A1:A3)</f>
+        <f aca="false">_xlfn.COVARIANCE.S(A1:A3,A1:A4)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16102,7 +16150,7 @@
         <v>1204</v>
       </c>
       <c r="L1207" s="0" t="e">
-        <f aca="false">FORECAST(B1,F1:F4,A1:A4)</f>
+        <f aca="false">_xlfn.COVARIANCE.S(A1,F1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16111,8 +16159,8 @@
         <v>1205</v>
       </c>
       <c r="L1208" s="0" t="n">
-        <f aca="false">_xlfn.FORECAST.LINEAR(10,F1:F4,A1:A4)</f>
-        <v>1000</v>
+        <f aca="false">SLOPE(F1:F4,A1:A4)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16120,8 +16168,8 @@
         <v>1206</v>
       </c>
       <c r="L1209" s="0" t="n">
-        <f aca="false">_xlfn.FORECAST.LINEAR(0,C1:C6,A1:A6)</f>
-        <v>-333321.033333333</v>
+        <f aca="false">SLOPE(C1:C6,A1:A6)</f>
+        <v>142858.95</v>
       </c>
     </row>
     <row r="1210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16129,7 +16177,7 @@
         <v>1207</v>
       </c>
       <c r="L1210" s="0" t="e">
-        <f aca="false">_xlfn.FORECAST.LINEAR(5,F1:F4,A1:A3)</f>
+        <f aca="false">SLOPE(F1:F4,A1:A3)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16137,9 +16185,9 @@
       <c r="K1211" s="0" t="s">
         <v>1208</v>
       </c>
-      <c r="L1211" s="0" t="n">
-        <f aca="false">_xlfn.FORECAST.LINEAR(2.5,F1:F4,A1:A4)</f>
-        <v>250</v>
+      <c r="L1211" s="0" t="e">
+        <f aca="false">SLOPE(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16147,8 +16195,8 @@
         <v>1209</v>
       </c>
       <c r="L1212" s="0" t="n">
-        <f aca="false">TREND(F1:F4,A1:A4,5)</f>
-        <v>500</v>
+        <f aca="false">INTERCEPT(F1:F4,A1:A4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16156,26 +16204,26 @@
         <v>1210</v>
       </c>
       <c r="L1213" s="0" t="n">
-        <f aca="false">SUM(TREND(F1:F4,A1:A4,A5:A6))</f>
-        <v>1100</v>
+        <f aca="false">INTERCEPT(C1:C6,A1:A6)</f>
+        <v>-333321.033333333</v>
       </c>
     </row>
     <row r="1214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1214" s="0" t="s">
         <v>1211</v>
       </c>
-      <c r="L1214" s="0" t="n">
-        <f aca="false">INDEX(TREND(F1:F4),2)</f>
-        <v>200</v>
+      <c r="L1214" s="0" t="e">
+        <f aca="false">INTERCEPT(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1215" s="0" t="s">
         <v>1212</v>
       </c>
-      <c r="L1215" s="0" t="n">
-        <f aca="false">TREND(F1:F4,A1:A4,5,FALSE())</f>
-        <v>500</v>
+      <c r="L1215" s="0" t="e">
+        <f aca="false">INTERCEPT(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16183,8 +16231,8 @@
         <v>1213</v>
       </c>
       <c r="L1216" s="0" t="n">
-        <f aca="false">TREND(A1:A4,F1:F4,250)</f>
-        <v>2.5</v>
+        <f aca="false">RSQ(F1:F4,A1:A4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16192,17 +16240,17 @@
         <v>1214</v>
       </c>
       <c r="L1217" s="0" t="n">
-        <f aca="false">GEOMEAN(1,2,4)</f>
-        <v>2</v>
+        <f aca="false">RSQ(C1:C6,A1:A6)</f>
+        <v>0.428601425843957</v>
       </c>
     </row>
     <row r="1218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1218" s="0" t="s">
         <v>1215</v>
       </c>
-      <c r="L1218" s="0" t="n">
-        <f aca="false">GEOMEAN(A1:A6)</f>
-        <v>2.99379516552391</v>
+      <c r="L1218" s="0" t="e">
+        <f aca="false">RSQ(F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16210,17 +16258,17 @@
         <v>1216</v>
       </c>
       <c r="L1219" s="0" t="e">
-        <f aca="false">GEOMEAN(C1:C3)</f>
-        <v>#VALUE!</v>
+        <f aca="false">RSQ(F1:F4,{1;1;1;1})</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1220" s="0" t="s">
         <v>1217</v>
       </c>
-      <c r="L1220" s="0" t="e">
-        <f aca="false">GEOMEAN(B1:B2)</f>
-        <v>#NUM!</v>
+      <c r="L1220" s="0" t="n">
+        <f aca="false">FORECAST(5,F1:F4,A1:A4)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="1221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16228,17 +16276,17 @@
         <v>1218</v>
       </c>
       <c r="L1221" s="0" t="n">
-        <f aca="false">HARMEAN(1,2,4)</f>
-        <v>1.71428571428571</v>
+        <f aca="false">FORECAST(7,C1:C6,A1:A6)</f>
+        <v>666691.616666667</v>
       </c>
     </row>
     <row r="1222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1222" s="0" t="s">
         <v>1219</v>
       </c>
-      <c r="L1222" s="0" t="n">
-        <f aca="false">HARMEAN(A1:A3)</f>
-        <v>1.63636363636364</v>
+      <c r="L1222" s="0" t="e">
+        <f aca="false">FORECAST(5,F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16246,7 +16294,7 @@
         <v>1220</v>
       </c>
       <c r="L1223" s="0" t="e">
-        <f aca="false">HARMEAN(C1:C3)</f>
+        <f aca="false">FORECAST(B1,F1:F4,A1:A4)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16254,9 +16302,9 @@
       <c r="K1224" s="0" t="s">
         <v>1221</v>
       </c>
-      <c r="L1224" s="0" t="e">
-        <f aca="false">HARMEAN(B1:B2)</f>
-        <v>#NUM!</v>
+      <c r="L1224" s="0" t="n">
+        <f aca="false">_xlfn.FORECAST.LINEAR(10,F1:F4,A1:A4)</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="1225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16264,17 +16312,17 @@
         <v>1222</v>
       </c>
       <c r="L1225" s="0" t="n">
-        <f aca="false">DEVSQ(A1:A6)</f>
-        <v>17.5</v>
+        <f aca="false">_xlfn.FORECAST.LINEAR(0,C1:C6,A1:A6)</f>
+        <v>-333321.033333333</v>
       </c>
     </row>
     <row r="1226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1226" s="0" t="s">
         <v>1223</v>
       </c>
-      <c r="L1226" s="0" t="n">
-        <f aca="false">DEVSQ(1,2,3)</f>
-        <v>2</v>
+      <c r="L1226" s="0" t="e">
+        <f aca="false">_xlfn.FORECAST.LINEAR(5,F1:F4,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16282,17 +16330,17 @@
         <v>1224</v>
       </c>
       <c r="L1227" s="0" t="n">
-        <f aca="false">DEVSQ(C1:C4)</f>
-        <v>7171.1875</v>
+        <f aca="false">_xlfn.FORECAST.LINEAR(2.5,F1:F4,A1:A4)</f>
+        <v>250</v>
       </c>
     </row>
     <row r="1228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1228" s="0" t="s">
         <v>1225</v>
       </c>
-      <c r="L1228" s="0" t="e">
-        <f aca="false">DEVSQ(B1:B3)</f>
-        <v>#DIV/0!</v>
+      <c r="L1228" s="0" t="n">
+        <f aca="false">TREND(F1:F4,A1:A4,5)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="1229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16300,8 +16348,8 @@
         <v>1226</v>
       </c>
       <c r="L1229" s="0" t="n">
-        <f aca="false">AVEDEV(A1:A6)</f>
-        <v>1.5</v>
+        <f aca="false">SUM(TREND(F1:F4,A1:A4,A5:A6))</f>
+        <v>1100</v>
       </c>
     </row>
     <row r="1230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16309,8 +16357,8 @@
         <v>1227</v>
       </c>
       <c r="L1230" s="0" t="n">
-        <f aca="false">AVEDEV(1,2,3,4)</f>
-        <v>1</v>
+        <f aca="false">INDEX(TREND(F1:F4),2)</f>
+        <v>200</v>
       </c>
     </row>
     <row r="1231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16318,52 +16366,52 @@
         <v>1228</v>
       </c>
       <c r="L1231" s="0" t="n">
-        <f aca="false">AVEDEV(C1:C4)</f>
-        <v>36.4375</v>
+        <f aca="false">TREND(F1:F4,A1:A4,5,FALSE())</f>
+        <v>500</v>
       </c>
     </row>
     <row r="1232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1232" s="0" t="s">
         <v>1229</v>
       </c>
-      <c r="L1232" s="0" t="e">
-        <f aca="false">AVEDEV(B1:B3)</f>
-        <v>#NUM!</v>
+      <c r="L1232" s="0" t="n">
+        <f aca="false">TREND(A1:A4,F1:F4,250)</f>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1233" s="0" t="s">
         <v>1230</v>
       </c>
-      <c r="L1233" s="7" t="n">
-        <f aca="false">PMT(0.08/12,10,10000)</f>
-        <v>-1037.03208935915</v>
+      <c r="L1233" s="0" t="n">
+        <f aca="false">GEOMEAN(1,2,4)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1234" s="0" t="s">
         <v>1231</v>
       </c>
-      <c r="L1234" s="7" t="n">
-        <f aca="false">PMT(0,10,1000)</f>
-        <v>-100</v>
+      <c r="L1234" s="0" t="n">
+        <f aca="false">GEOMEAN(A1:A6)</f>
+        <v>2.99379516552391</v>
       </c>
     </row>
     <row r="1235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1235" s="0" t="s">
         <v>1232</v>
       </c>
-      <c r="L1235" s="7" t="n">
-        <f aca="false">PMT(0.05,5,1000,0,1)</f>
-        <v>-219.975998217398</v>
+      <c r="L1235" s="0" t="e">
+        <f aca="false">GEOMEAN(C1:C3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1236" s="0" t="s">
         <v>1233</v>
       </c>
-      <c r="L1236" s="7" t="e">
-        <f aca="false">PMT(0.05,0,100)</f>
+      <c r="L1236" s="0" t="e">
+        <f aca="false">GEOMEAN(B1:B2)</f>
         <v>#NUM!</v>
       </c>
     </row>
@@ -16371,81 +16419,81 @@
       <c r="K1237" s="0" t="s">
         <v>1234</v>
       </c>
-      <c r="L1237" s="7" t="n">
-        <f aca="false">PMT(0.06,12,-5000,1000)</f>
-        <v>537.108117522654</v>
+      <c r="L1237" s="0" t="n">
+        <f aca="false">HARMEAN(1,2,4)</f>
+        <v>1.71428571428571</v>
       </c>
     </row>
     <row r="1238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1238" s="0" t="s">
         <v>1235</v>
       </c>
-      <c r="L1238" s="7" t="n">
-        <f aca="false">FV(0.06/12,10,-200,-500,1)</f>
-        <v>2581.40337406014</v>
+      <c r="L1238" s="0" t="n">
+        <f aca="false">HARMEAN(A1:A3)</f>
+        <v>1.63636363636364</v>
       </c>
     </row>
     <row r="1239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1239" s="0" t="s">
         <v>1236</v>
       </c>
-      <c r="L1239" s="7" t="n">
-        <f aca="false">FV(0,10,-100)</f>
-        <v>1000</v>
+      <c r="L1239" s="0" t="e">
+        <f aca="false">HARMEAN(C1:C3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1240" s="0" t="s">
         <v>1237</v>
       </c>
-      <c r="L1240" s="7" t="n">
-        <f aca="false">FV(0.05,5,-100,0,0)</f>
-        <v>552.563125000001</v>
+      <c r="L1240" s="0" t="e">
+        <f aca="false">HARMEAN(B1:B2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1241" s="0" t="s">
         <v>1238</v>
       </c>
-      <c r="L1241" s="7" t="n">
-        <f aca="false">FV(0.1,2,0,-100)</f>
-        <v>121</v>
+      <c r="L1241" s="0" t="n">
+        <f aca="false">DEVSQ(A1:A6)</f>
+        <v>17.5</v>
       </c>
     </row>
     <row r="1242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1242" s="0" t="s">
         <v>1239</v>
       </c>
-      <c r="L1242" s="7" t="n">
-        <f aca="false">PV(0.08/12,240,500)</f>
-        <v>-59777.1458511878</v>
+      <c r="L1242" s="0" t="n">
+        <f aca="false">DEVSQ(1,2,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1243" s="0" t="s">
         <v>1240</v>
       </c>
-      <c r="L1243" s="7" t="n">
-        <f aca="false">PV(0,5,-10)</f>
-        <v>50</v>
+      <c r="L1243" s="0" t="n">
+        <f aca="false">DEVSQ(C1:C4)</f>
+        <v>7171.1875</v>
       </c>
     </row>
     <row r="1244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1244" s="0" t="s">
         <v>1241</v>
       </c>
-      <c r="L1244" s="7" t="n">
-        <f aca="false">PV(0.05,10,-100,0,1)</f>
-        <v>810.782167564406</v>
+      <c r="L1244" s="0" t="e">
+        <f aca="false">DEVSQ(B1:B3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1245" s="0" t="s">
         <v>1242</v>
       </c>
-      <c r="L1245" s="7" t="n">
-        <f aca="false">PV(0.05,10,0,1000)</f>
-        <v>-613.913253540759</v>
+      <c r="L1245" s="0" t="n">
+        <f aca="false">AVEDEV(A1:A6)</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16453,8 +16501,8 @@
         <v>1243</v>
       </c>
       <c r="L1246" s="0" t="n">
-        <f aca="false">NPER(0.12/12,-100,-1000,10000)</f>
-        <v>60.0821228537617</v>
+        <f aca="false">AVEDEV(1,2,3,4)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16462,26 +16510,26 @@
         <v>1244</v>
       </c>
       <c r="L1247" s="0" t="n">
-        <f aca="false">NPER(0,-100,1000)</f>
-        <v>10</v>
+        <f aca="false">AVEDEV(C1:C4)</f>
+        <v>36.4375</v>
       </c>
     </row>
     <row r="1248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1248" s="0" t="s">
         <v>1245</v>
       </c>
-      <c r="L1248" s="0" t="n">
-        <f aca="false">NPER(0.05,-100,1000,0,1)</f>
-        <v>13.2532278981381</v>
+      <c r="L1248" s="0" t="e">
+        <f aca="false">AVEDEV(B1:B3)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1249" s="0" t="s">
         <v>1246</v>
       </c>
-      <c r="L1249" s="0" t="e">
-        <f aca="false">NPER(0.01,0,100)</f>
-        <v>#NUM!</v>
+      <c r="L1249" s="7" t="n">
+        <f aca="false">PMT(0.08/12,10,10000)</f>
+        <v>-1037.03208935915</v>
       </c>
     </row>
     <row r="1250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16489,8 +16537,8 @@
         <v>1247</v>
       </c>
       <c r="L1250" s="7" t="n">
-        <f aca="false">IPMT(0.1/12,1,36,8000)</f>
-        <v>-66.6666666666667</v>
+        <f aca="false">PMT(0,10,1000)</f>
+        <v>-100</v>
       </c>
     </row>
     <row r="1251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16498,17 +16546,17 @@
         <v>1248</v>
       </c>
       <c r="L1251" s="7" t="n">
-        <f aca="false">IPMT(0.1/12,3,36,8000)</f>
-        <v>-63.4621895664547</v>
+        <f aca="false">PMT(0.05,5,1000,0,1)</f>
+        <v>-219.975998217398</v>
       </c>
     </row>
     <row r="1252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1252" s="0" t="s">
         <v>1249</v>
       </c>
-      <c r="L1252" s="7" t="n">
-        <f aca="false">IPMT(0.1,3,3,8000)</f>
-        <v>-292.447129909365</v>
+      <c r="L1252" s="7" t="e">
+        <f aca="false">PMT(0.05,0,100)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16516,17 +16564,17 @@
         <v>1250</v>
       </c>
       <c r="L1253" s="7" t="n">
-        <f aca="false">IPMT(0.1/12,1,36,8000,0,1)</f>
-        <v>0</v>
+        <f aca="false">PMT(0.06,12,-5000,1000)</f>
+        <v>537.108117522654</v>
       </c>
     </row>
     <row r="1254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1254" s="0" t="s">
         <v>1251</v>
       </c>
-      <c r="L1254" s="7" t="e">
-        <f aca="false">IPMT(0.05,0,3,1000)</f>
-        <v>#VALUE!</v>
+      <c r="L1254" s="7" t="n">
+        <f aca="false">FV(0.06/12,10,-200,-500,1)</f>
+        <v>2581.40337406014</v>
       </c>
     </row>
     <row r="1255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16534,8 +16582,8 @@
         <v>1252</v>
       </c>
       <c r="L1255" s="7" t="n">
-        <f aca="false">IPMT(0.05,2,3,1000,0,1)</f>
-        <v>-32.5138778747026</v>
+        <f aca="false">FV(0,10,-100)</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="1256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16543,8 +16591,8 @@
         <v>1253</v>
       </c>
       <c r="L1256" s="7" t="n">
-        <f aca="false">PPMT(0.1/12,1,24,2000)</f>
-        <v>-75.6231860083664</v>
+        <f aca="false">FV(0.05,5,-100,0,0)</f>
+        <v>552.563125000001</v>
       </c>
     </row>
     <row r="1257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16552,8 +16600,8 @@
         <v>1254</v>
       </c>
       <c r="L1257" s="7" t="n">
-        <f aca="false">PPMT(0.08,10,10,200000)</f>
-        <v>-27598.0534624214</v>
+        <f aca="false">FV(0.1,2,0,-100)</f>
+        <v>121</v>
       </c>
     </row>
     <row r="1258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16561,17 +16609,17 @@
         <v>1255</v>
       </c>
       <c r="L1258" s="7" t="n">
-        <f aca="false">PPMT(0.05,2,3,1000,0,1)</f>
-        <v>-317.208564631245</v>
+        <f aca="false">PV(0.08/12,240,500)</f>
+        <v>-59777.1458511878</v>
       </c>
     </row>
     <row r="1259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1259" s="0" t="s">
         <v>1256</v>
       </c>
-      <c r="L1259" s="7" t="e">
-        <f aca="false">PPMT(0.05,4,3,1000)</f>
-        <v>#VALUE!</v>
+      <c r="L1259" s="7" t="n">
+        <f aca="false">PV(0,5,-10)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="1260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16579,8 +16627,8 @@
         <v>1257</v>
       </c>
       <c r="L1260" s="7" t="n">
-        <f aca="false">NPV(0.1,-10000,3000,4200,6800)</f>
-        <v>1188.44341233522</v>
+        <f aca="false">PV(0.05,10,-100,0,1)</f>
+        <v>810.782167564406</v>
       </c>
     </row>
     <row r="1261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16588,26 +16636,26 @@
         <v>1258</v>
       </c>
       <c r="L1261" s="7" t="n">
-        <f aca="false">NPV(0.1,A1:A3)</f>
-        <v>4.81592787377911</v>
+        <f aca="false">PV(0.05,10,0,1000)</f>
+        <v>-613.913253540759</v>
       </c>
     </row>
     <row r="1262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1262" s="0" t="s">
         <v>1259</v>
       </c>
-      <c r="L1262" s="7" t="e">
-        <f aca="false">NPV(-1,1,2)</f>
-        <v>#NUM!</v>
+      <c r="L1262" s="0" t="n">
+        <f aca="false">NPER(0.12/12,-100,-1000,10000)</f>
+        <v>60.0821228537617</v>
       </c>
     </row>
     <row r="1263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1263" s="0" t="s">
         <v>1260</v>
       </c>
-      <c r="L1263" s="7" t="n">
-        <f aca="false">NPV(0.08,F1:F4)</f>
-        <v>796.221970077581</v>
+      <c r="L1263" s="0" t="n">
+        <f aca="false">NPER(0,-100,1000)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="1264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16615,61 +16663,61 @@
         <v>1261</v>
       </c>
       <c r="L1264" s="0" t="n">
-        <f aca="false">ROUND(IRR({-70000,12000,15000,18000,21000,26000}),6)</f>
-        <v>0.086631</v>
+        <f aca="false">NPER(0.05,-100,1000,0,1)</f>
+        <v>13.2532278981381</v>
       </c>
     </row>
     <row r="1265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1265" s="0" t="s">
         <v>1262</v>
       </c>
-      <c r="L1265" s="0" t="n">
-        <f aca="false">ROUND(IRR({-100,110}),6)</f>
-        <v>0.1</v>
+      <c r="L1265" s="0" t="e">
+        <f aca="false">NPER(0.01,0,100)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1266" s="0" t="s">
         <v>1263</v>
       </c>
-      <c r="L1266" s="6" t="e">
-        <f aca="false">IRR({1,2,3})</f>
-        <v>#N/A</v>
+      <c r="L1266" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,1,36,8000)</f>
+        <v>-66.6666666666667</v>
       </c>
     </row>
     <row r="1267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1267" s="0" t="s">
         <v>1264</v>
       </c>
-      <c r="L1267" s="0" t="n">
-        <f aca="false">ROUND(IRR({-1000,300,400,500},0.2),6)</f>
-        <v>0.088963</v>
+      <c r="L1267" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,3,36,8000)</f>
+        <v>-63.4621895664547</v>
       </c>
     </row>
     <row r="1268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1268" s="0" t="s">
         <v>1265</v>
       </c>
-      <c r="L1268" s="0" t="n">
-        <f aca="false">ROUND(RATE(48,-200,8000),6)</f>
-        <v>0.007701</v>
+      <c r="L1268" s="7" t="n">
+        <f aca="false">IPMT(0.1,3,3,8000)</f>
+        <v>-292.447129909365</v>
       </c>
     </row>
     <row r="1269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1269" s="0" t="s">
         <v>1266</v>
       </c>
-      <c r="L1269" s="0" t="n">
-        <f aca="false">ROUND(RATE(10,0,-100,200),6)</f>
-        <v>0.071773</v>
+      <c r="L1269" s="7" t="n">
+        <f aca="false">IPMT(0.1/12,1,36,8000,0,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1270" s="0" t="s">
         <v>1267</v>
       </c>
-      <c r="L1270" s="6" t="e">
-        <f aca="false">RATE(0,-100,1000)</f>
+      <c r="L1270" s="7" t="e">
+        <f aca="false">IPMT(0.05,0,3,1000)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -16677,9 +16725,9 @@
       <c r="K1271" s="0" t="s">
         <v>1268</v>
       </c>
-      <c r="L1271" s="0" t="n">
-        <f aca="false">ROUND(RATE(12,-100,1000),6)</f>
-        <v>0.029229</v>
+      <c r="L1271" s="7" t="n">
+        <f aca="false">IPMT(0.05,2,3,1000,0,1)</f>
+        <v>-32.5138778747026</v>
       </c>
     </row>
     <row r="1272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16687,8 +16735,8 @@
         <v>1269</v>
       </c>
       <c r="L1272" s="7" t="n">
-        <f aca="false">SLN(30000,7500,10)</f>
-        <v>2250</v>
+        <f aca="false">PPMT(0.1/12,1,24,2000)</f>
+        <v>-75.6231860083664</v>
       </c>
     </row>
     <row r="1273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16696,26 +16744,26 @@
         <v>1270</v>
       </c>
       <c r="L1273" s="7" t="n">
-        <f aca="false">SLN(100,0,4)</f>
-        <v>25</v>
+        <f aca="false">PPMT(0.08,10,10,200000)</f>
+        <v>-27598.0534624214</v>
       </c>
     </row>
     <row r="1274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1274" s="0" t="s">
         <v>1271</v>
       </c>
-      <c r="L1274" s="7" t="e">
-        <f aca="false">SLN(100,10,0)</f>
-        <v>#DIV/0!</v>
+      <c r="L1274" s="7" t="n">
+        <f aca="false">PPMT(0.05,2,3,1000,0,1)</f>
+        <v>-317.208564631245</v>
       </c>
     </row>
     <row r="1275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1275" s="0" t="s">
         <v>1272</v>
       </c>
-      <c r="L1275" s="7" t="n">
-        <f aca="false">SLN(F1,0,4)</f>
-        <v>25</v>
+      <c r="L1275" s="7" t="e">
+        <f aca="false">PPMT(0.05,4,3,1000)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16723,8 +16771,8 @@
         <v>1273</v>
       </c>
       <c r="L1276" s="7" t="n">
-        <f aca="false">SYD(30000,7500,10,1)</f>
-        <v>4090.90909090909</v>
+        <f aca="false">NPV(0.1,-10000,3000,4200,6800)</f>
+        <v>1188.44341233522</v>
       </c>
     </row>
     <row r="1277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16732,17 +16780,17 @@
         <v>1274</v>
       </c>
       <c r="L1277" s="7" t="n">
-        <f aca="false">SYD(30000,7500,10,10)</f>
-        <v>409.090909090909</v>
+        <f aca="false">NPV(0.1,A1:A3)</f>
+        <v>4.81592787377911</v>
       </c>
     </row>
     <row r="1278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1278" s="0" t="s">
         <v>1275</v>
       </c>
-      <c r="L1278" s="7" t="n">
-        <f aca="false">SYD(100,0,4,5)</f>
-        <v>0</v>
+      <c r="L1278" s="7" t="e">
+        <f aca="false">NPV(-1,1,2)</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="1279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16750,80 +16798,80 @@
         <v>1276</v>
       </c>
       <c r="L1279" s="7" t="n">
-        <f aca="false">SYD(100,0,4,0)</f>
-        <v>50</v>
+        <f aca="false">NPV(0.08,F1:F4)</f>
+        <v>796.221970077581</v>
       </c>
     </row>
     <row r="1280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1280" s="0" t="s">
         <v>1277</v>
       </c>
-      <c r="L1280" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,1,7)</f>
-        <v>186083.333333333</v>
+      <c r="L1280" s="0" t="n">
+        <f aca="false">ROUND(IRR({-70000,12000,15000,18000,21000,26000}),6)</f>
+        <v>0.086631</v>
       </c>
     </row>
     <row r="1281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1281" s="0" t="s">
         <v>1278</v>
       </c>
-      <c r="L1281" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,2,7)</f>
-        <v>259639.416666667</v>
+      <c r="L1281" s="0" t="n">
+        <f aca="false">ROUND(IRR({-100,110}),6)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1282" s="0" t="s">
         <v>1279</v>
       </c>
-      <c r="L1282" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,7,7)</f>
-        <v>15845.0984738481</v>
+      <c r="L1282" s="6" t="e">
+        <f aca="false">IRR({1,2,3})</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1283" s="0" t="s">
         <v>1280</v>
       </c>
-      <c r="L1283" s="7" t="n">
-        <f aca="false">DB(1000000,100000,6,1)</f>
-        <v>319000</v>
+      <c r="L1283" s="0" t="n">
+        <f aca="false">ROUND(IRR({-1000,300,400,500},0.2),6)</f>
+        <v>0.088963</v>
       </c>
     </row>
     <row r="1284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1284" s="0" t="s">
         <v>1281</v>
       </c>
-      <c r="L1284" s="7" t="n">
-        <f aca="false">DB(1000,100,5,6)</f>
-        <v>0</v>
+      <c r="L1284" s="0" t="n">
+        <f aca="false">ROUND(RATE(48,-200,8000),6)</f>
+        <v>0.007701</v>
       </c>
     </row>
     <row r="1285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1285" s="0" t="s">
         <v>1282</v>
       </c>
-      <c r="L1285" s="7" t="n">
-        <f aca="false">DDB(2400,300,10*365,1)</f>
-        <v>1.31506849315065</v>
+      <c r="L1285" s="0" t="n">
+        <f aca="false">ROUND(RATE(10,0,-100,200),6)</f>
+        <v>0.071773</v>
       </c>
     </row>
     <row r="1286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1286" s="0" t="s">
         <v>1283</v>
       </c>
-      <c r="L1286" s="7" t="n">
-        <f aca="false">DDB(2400,300,10,1,2)</f>
-        <v>480</v>
+      <c r="L1286" s="6" t="e">
+        <f aca="false">RATE(0,-100,1000)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1287" s="0" t="s">
         <v>1284</v>
       </c>
-      <c r="L1287" s="7" t="n">
-        <f aca="false">DDB(2400,300,10,2,2)</f>
-        <v>384</v>
+      <c r="L1287" s="0" t="n">
+        <f aca="false">ROUND(RATE(12,-100,1000),6)</f>
+        <v>0.029229</v>
       </c>
     </row>
     <row r="1288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16831,233 +16879,233 @@
         <v>1285</v>
       </c>
       <c r="L1288" s="7" t="n">
-        <f aca="false">DDB(2400,300,10,10)</f>
-        <v>22.1225472000002</v>
+        <f aca="false">SLN(30000,7500,10)</f>
+        <v>2250</v>
       </c>
     </row>
     <row r="1289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1289" s="0" t="s">
         <v>1286</v>
       </c>
-      <c r="L1289" s="7" t="e">
-        <f aca="false">DDB(100,0,5,6)</f>
-        <v>#VALUE!</v>
+      <c r="L1289" s="7" t="n">
+        <f aca="false">SLN(100,0,4)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="1290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1290" s="0" t="s">
         <v>1287</v>
       </c>
-      <c r="L1290" s="6" t="n">
-        <f aca="false">EFFECT(0.0525,4)</f>
-        <v>0.0535426673707582</v>
+      <c r="L1290" s="7" t="e">
+        <f aca="false">SLN(100,10,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1291" s="0" t="s">
         <v>1288</v>
       </c>
-      <c r="L1291" s="6" t="n">
-        <f aca="false">EFFECT(0.1,1)</f>
-        <v>0.1</v>
+      <c r="L1291" s="7" t="n">
+        <f aca="false">SLN(F1,0,4)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="1292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1292" s="0" t="s">
         <v>1289</v>
       </c>
-      <c r="L1292" s="6" t="n">
-        <f aca="false">EFFECT(0,4)</f>
-        <v>0</v>
+      <c r="L1292" s="7" t="n">
+        <f aca="false">SYD(30000,7500,10,1)</f>
+        <v>4090.90909090909</v>
       </c>
     </row>
     <row r="1293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1293" s="0" t="s">
         <v>1290</v>
       </c>
-      <c r="L1293" s="6" t="e">
-        <f aca="false">EFFECT(0.1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1293" s="7" t="n">
+        <f aca="false">SYD(30000,7500,10,10)</f>
+        <v>409.090909090909</v>
       </c>
     </row>
     <row r="1294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1294" s="0" t="s">
         <v>1291</v>
       </c>
-      <c r="L1294" s="6" t="n">
-        <f aca="false">NOMINAL(0.053543,4)</f>
-        <v>0.052500319868356</v>
+      <c r="L1294" s="7" t="n">
+        <f aca="false">SYD(100,0,4,5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1295" s="0" t="s">
         <v>1292</v>
       </c>
-      <c r="L1295" s="6" t="n">
-        <f aca="false">NOMINAL(0.1,1)</f>
-        <v>0.1</v>
+      <c r="L1295" s="7" t="n">
+        <f aca="false">SYD(100,0,4,0)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="1296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1296" s="0" t="s">
         <v>1293</v>
       </c>
-      <c r="L1296" s="6" t="e">
-        <f aca="false">NOMINAL(0,4)</f>
-        <v>#VALUE!</v>
+      <c r="L1296" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,1,7)</f>
+        <v>186083.333333333</v>
       </c>
     </row>
     <row r="1297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1297" s="0" t="s">
         <v>1294</v>
       </c>
-      <c r="L1297" s="6" t="e">
-        <f aca="false">NOMINAL(0.1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1297" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,2,7)</f>
+        <v>259639.416666667</v>
       </c>
     </row>
     <row r="1298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1298" s="0" t="s">
         <v>1295</v>
       </c>
-      <c r="L1298" s="0" t="n">
-        <f aca="false">ROUND(MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12),6)</f>
-        <v>0.126094</v>
+      <c r="L1298" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,7,7)</f>
+        <v>15845.0984738481</v>
       </c>
     </row>
     <row r="1299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1299" s="0" t="s">
         <v>1296</v>
       </c>
-      <c r="L1299" s="6" t="e">
-        <f aca="false">MIRR({1,2,3},0.1,0.1)</f>
-        <v>#VALUE!</v>
+      <c r="L1299" s="7" t="n">
+        <f aca="false">DB(1000000,100000,6,1)</f>
+        <v>319000</v>
       </c>
     </row>
     <row r="1300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1300" s="0" t="s">
         <v>1297</v>
       </c>
-      <c r="L1300" s="0" t="n">
-        <f aca="false">ROUND(MIRR({-100,50,60},0.05,0.05),6)</f>
-        <v>0.06066</v>
+      <c r="L1300" s="7" t="n">
+        <f aca="false">DB(1000,100,5,6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1301" s="0" t="s">
         <v>1298</v>
       </c>
-      <c r="L1301" s="6" t="e">
-        <f aca="false">MIRR({-100,-50},0.1,0.1)</f>
-        <v>#VALUE!</v>
+      <c r="L1301" s="7" t="n">
+        <f aca="false">DDB(2400,300,10*365,1)</f>
+        <v>1.31506849315065</v>
       </c>
     </row>
     <row r="1302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1302" s="0" t="s">
         <v>1299</v>
       </c>
-      <c r="L1302" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
-        <v>b</v>
+      <c r="L1302" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,1,2)</f>
+        <v>480</v>
       </c>
     </row>
     <row r="1303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1303" s="0" t="s">
         <v>1300</v>
       </c>
-      <c r="L1303" s="0" t="n">
-        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
-        <v>2</v>
+      <c r="L1303" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,2,2)</f>
+        <v>384</v>
       </c>
     </row>
     <row r="1304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1304" s="0" t="s">
         <v>1301</v>
       </c>
-      <c r="L1304" s="0" t="e">
-        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
-        <v>#N/A</v>
+      <c r="L1304" s="7" t="n">
+        <f aca="false">DDB(2400,300,10,10)</f>
+        <v>22.1225472000002</v>
       </c>
     </row>
     <row r="1305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1305" s="0" t="s">
         <v>1302</v>
       </c>
-      <c r="L1305" s="0" t="n">
-        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
-        <v>1</v>
+      <c r="L1305" s="7" t="e">
+        <f aca="false">DDB(100,0,5,6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1306" s="0" t="s">
         <v>1303</v>
       </c>
-      <c r="L1306" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A1,"x")</f>
-        <v>x</v>
+      <c r="L1306" s="6" t="n">
+        <f aca="false">EFFECT(0.0525,4)</f>
+        <v>0.0535426673707582</v>
       </c>
     </row>
     <row r="1307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1307" s="0" t="s">
         <v>1304</v>
       </c>
-      <c r="L1307" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
-        <v>b</v>
+      <c r="L1307" s="6" t="n">
+        <f aca="false">EFFECT(0.1,1)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1308" s="0" t="s">
         <v>1305</v>
       </c>
-      <c r="L1308" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
-        <v>z</v>
+      <c r="L1308" s="6" t="n">
+        <f aca="false">EFFECT(0,4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1309" s="0" t="s">
         <v>1306</v>
       </c>
-      <c r="L1309" s="0" t="e">
-        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
-        <v>#N/A</v>
+      <c r="L1309" s="6" t="e">
+        <f aca="false">EFFECT(0.1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1310" s="0" t="s">
         <v>1307</v>
       </c>
-      <c r="L1310" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
-        <v>2</v>
+      <c r="L1310" s="6" t="n">
+        <f aca="false">NOMINAL(0.053543,4)</f>
+        <v>0.052500319868356</v>
       </c>
     </row>
     <row r="1311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1311" s="0" t="s">
         <v>1308</v>
       </c>
-      <c r="L1311" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
-        <v>three</v>
+      <c r="L1311" s="6" t="n">
+        <f aca="false">NOMINAL(0.1,1)</f>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1312" s="0" t="s">
         <v>1309</v>
       </c>
-      <c r="L1312" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(H2,"x")</f>
-        <v>x</v>
+      <c r="L1312" s="6" t="e">
+        <f aca="false">NOMINAL(0,4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1313" s="0" t="s">
         <v>1310</v>
       </c>
-      <c r="L1313" s="0" t="e">
-        <f aca="false">_xlfn.IFNA(H1,"x")</f>
-        <v>#DIV/0!</v>
+      <c r="L1313" s="6" t="e">
+        <f aca="false">NOMINAL(0.1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17065,70 +17113,70 @@
         <v>1311</v>
       </c>
       <c r="L1314" s="0" t="n">
-        <f aca="false">_xlfn.IFNA(5,"x")</f>
-        <v>5</v>
+        <f aca="false">ROUND(MIRR({-120000,39000,30000,21000,37000,46000},0.1,0.12),6)</f>
+        <v>0.126094</v>
       </c>
     </row>
     <row r="1315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1315" s="0" t="s">
         <v>1312</v>
       </c>
-      <c r="L1315" s="0" t="n">
-        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
-        <v>0</v>
+      <c r="L1315" s="6" t="e">
+        <f aca="false">MIRR({1,2,3},0.1,0.1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1316" s="0" t="s">
         <v>1313</v>
       </c>
-      <c r="L1316" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
-        <v>1</v>
+      <c r="L1316" s="0" t="n">
+        <f aca="false">ROUND(MIRR({-100,50,60},0.05,0.05),6)</f>
+        <v>0.06066</v>
       </c>
     </row>
     <row r="1317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1317" s="0" t="s">
         <v>1314</v>
       </c>
-      <c r="L1317" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
-        <v>0</v>
+      <c r="L1317" s="6" t="e">
+        <f aca="false">MIRR({-100,-50},0.1,0.1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1318" s="0" t="s">
         <v>1315</v>
       </c>
-      <c r="L1318" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
-        <v>1</v>
+      <c r="L1318" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1319" s="0" t="s">
         <v>1316</v>
       </c>
-      <c r="L1319" s="1" t="b">
-        <f aca="false">_xlfn.XOR(1,0,0)</f>
-        <v>1</v>
+      <c r="L1319" s="0" t="n">
+        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1320" s="0" t="s">
         <v>1317</v>
       </c>
-      <c r="L1320" s="1" t="e">
-        <f aca="false">_xlfn.XOR(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1320" s="0" t="e">
+        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1321" s="0" t="s">
         <v>1318</v>
       </c>
-      <c r="L1321" s="1" t="b">
-        <f aca="false">ISLOGICAL(TRUE())</f>
+      <c r="L1321" s="0" t="n">
+        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
         <v>1</v>
       </c>
     </row>
@@ -17136,90 +17184,90 @@
       <c r="K1322" s="0" t="s">
         <v>1319</v>
       </c>
-      <c r="L1322" s="1" t="b">
-        <f aca="false">ISLOGICAL(1)</f>
-        <v>0</v>
+      <c r="L1322" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1,"x")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="1323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1323" s="0" t="s">
         <v>1320</v>
       </c>
-      <c r="L1323" s="1" t="b">
-        <f aca="false">ISLOGICAL("TRUE")</f>
-        <v>0</v>
+      <c r="L1323" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1324" s="0" t="s">
         <v>1321</v>
       </c>
-      <c r="L1324" s="1" t="b">
-        <f aca="false">ISLOGICAL(1=1)</f>
-        <v>1</v>
+      <c r="L1324" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
+        <v>z</v>
       </c>
     </row>
     <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1325" s="0" t="s">
         <v>1322</v>
       </c>
-      <c r="L1325" s="1" t="b">
-        <f aca="false">ISEVEN(2)</f>
-        <v>1</v>
+      <c r="L1325" s="0" t="e">
+        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1326" s="0" t="s">
         <v>1323</v>
       </c>
-      <c r="L1326" s="1" t="b">
-        <f aca="false">ISEVEN(3)</f>
-        <v>0</v>
+      <c r="L1326" s="0" t="n">
+        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1327" s="0" t="s">
         <v>1324</v>
       </c>
-      <c r="L1327" s="1" t="b">
-        <f aca="false">ISEVEN(-2.9)</f>
-        <v>1</v>
+      <c r="L1327" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
+        <v>three</v>
       </c>
     </row>
     <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1328" s="0" t="s">
         <v>1325</v>
       </c>
-      <c r="L1328" s="1" t="e">
-        <f aca="false">ISEVEN("a")</f>
-        <v>#VALUE!</v>
+      <c r="L1328" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(H2,"x")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1329" s="0" t="s">
         <v>1326</v>
       </c>
-      <c r="L1329" s="1" t="b">
-        <f aca="false">ISEVEN(A2)</f>
-        <v>1</v>
+      <c r="L1329" s="0" t="e">
+        <f aca="false">_xlfn.IFNA(H1,"x")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1330" s="0" t="s">
         <v>1327</v>
       </c>
-      <c r="L1330" s="1" t="b">
-        <f aca="false">ISODD(2)</f>
-        <v>0</v>
+      <c r="L1330" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(5,"x")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1331" s="0" t="s">
         <v>1328</v>
       </c>
-      <c r="L1331" s="1" t="b">
-        <f aca="false">ISODD(3)</f>
-        <v>1</v>
+      <c r="L1331" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17227,7 +17275,7 @@
         <v>1329</v>
       </c>
       <c r="L1332" s="1" t="b">
-        <f aca="false">ISODD(-3.5)</f>
+        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
         <v>1</v>
       </c>
     </row>
@@ -17235,9 +17283,9 @@
       <c r="K1333" s="0" t="s">
         <v>1330</v>
       </c>
-      <c r="L1333" s="1" t="e">
-        <f aca="false">ISODD("a")</f>
-        <v>#VALUE!</v>
+      <c r="L1333" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17245,7 +17293,7 @@
         <v>1331</v>
       </c>
       <c r="L1334" s="1" t="b">
-        <f aca="false">ISODD(A1)</f>
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
         <v>1</v>
       </c>
     </row>
@@ -17253,26 +17301,26 @@
       <c r="K1335" s="0" t="s">
         <v>1332</v>
       </c>
-      <c r="L1335" s="0" t="n">
-        <f aca="false">N(5)</f>
-        <v>5</v>
+      <c r="L1335" s="1" t="b">
+        <f aca="false">_xlfn.XOR(1,0,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1336" s="0" t="s">
         <v>1333</v>
       </c>
-      <c r="L1336" s="0" t="n">
-        <f aca="false">N("a")</f>
-        <v>0</v>
+      <c r="L1336" s="1" t="e">
+        <f aca="false">_xlfn.XOR(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1337" s="0" t="s">
         <v>1334</v>
       </c>
-      <c r="L1337" s="0" t="n">
-        <f aca="false">N(TRUE())</f>
+      <c r="L1337" s="1" t="b">
+        <f aca="false">ISLOGICAL(TRUE())</f>
         <v>1</v>
       </c>
     </row>
@@ -17280,17 +17328,17 @@
       <c r="K1338" s="0" t="s">
         <v>1335</v>
       </c>
-      <c r="L1338" s="0" t="e">
-        <f aca="false">N(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1338" s="1" t="b">
+        <f aca="false">ISLOGICAL(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1339" s="0" t="s">
         <v>1336</v>
       </c>
-      <c r="L1339" s="0" t="n">
-        <f aca="false">N(B1)</f>
+      <c r="L1339" s="1" t="b">
+        <f aca="false">ISLOGICAL("TRUE")</f>
         <v>0</v>
       </c>
     </row>
@@ -17298,80 +17346,80 @@
       <c r="K1340" s="0" t="s">
         <v>1337</v>
       </c>
-      <c r="L1340" s="0" t="n">
-        <f aca="false">N(A3)</f>
-        <v>3</v>
+      <c r="L1340" s="1" t="b">
+        <f aca="false">ISLOGICAL(1=1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1341" s="0" t="s">
         <v>1338</v>
       </c>
-      <c r="L1341" s="0" t="str">
-        <f aca="false">T("a")</f>
-        <v>a</v>
+      <c r="L1341" s="1" t="b">
+        <f aca="false">ISEVEN(2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1342" s="0" t="s">
         <v>1339</v>
       </c>
-      <c r="L1342" s="0" t="str">
-        <f aca="false">T(5)</f>
-        <v/>
+      <c r="L1342" s="1" t="b">
+        <f aca="false">ISEVEN(3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1343" s="0" t="s">
         <v>1340</v>
       </c>
-      <c r="L1343" s="0" t="str">
-        <f aca="false">T(B1)</f>
-        <v>apple</v>
+      <c r="L1343" s="1" t="b">
+        <f aca="false">ISEVEN(-2.9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1344" s="0" t="s">
         <v>1341</v>
       </c>
-      <c r="L1344" s="0" t="e">
-        <f aca="false">T(H2)</f>
-        <v>#N/A</v>
+      <c r="L1344" s="1" t="e">
+        <f aca="false">ISEVEN("a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1345" s="0" t="s">
         <v>1342</v>
       </c>
-      <c r="L1345" s="0" t="str">
-        <f aca="false">T(TRUE())</f>
-        <v/>
+      <c r="L1345" s="1" t="b">
+        <f aca="false">ISEVEN(A2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1346" s="0" t="s">
         <v>1343</v>
       </c>
-      <c r="L1346" s="0" t="n">
-        <f aca="false">TYPE(1)</f>
-        <v>1</v>
+      <c r="L1346" s="1" t="b">
+        <f aca="false">ISODD(2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1347" s="0" t="s">
         <v>1344</v>
       </c>
-      <c r="L1347" s="0" t="n">
-        <f aca="false">TYPE("a")</f>
-        <v>2</v>
+      <c r="L1347" s="1" t="b">
+        <f aca="false">ISODD(3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1348" s="0" t="s">
         <v>1345</v>
       </c>
-      <c r="L1348" s="0" t="n">
-        <f aca="false">TYPE(TRUE())</f>
+      <c r="L1348" s="1" t="b">
+        <f aca="false">ISODD(-3.5)</f>
         <v>1</v>
       </c>
     </row>
@@ -17379,27 +17427,27 @@
       <c r="K1349" s="0" t="s">
         <v>1346</v>
       </c>
-      <c r="L1349" s="0" t="n">
-        <f aca="false">TYPE(H1)</f>
-        <v>16</v>
+      <c r="L1349" s="1" t="e">
+        <f aca="false">ISODD("a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1350" s="0" t="s">
         <v>1347</v>
       </c>
-      <c r="L1350" s="0" t="n">
-        <f aca="false">TYPE({1,2})</f>
-        <v>64</v>
+      <c r="L1350" s="1" t="b">
+        <f aca="false">ISODD(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1351" s="0" t="s">
         <v>1348</v>
       </c>
-      <c r="L1351" s="0" t="e">
-        <f aca="false">TYPE(A1:A2)</f>
-        <v>#VALUE!</v>
+      <c r="L1351" s="0" t="n">
+        <f aca="false">N(5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17407,8 +17455,8 @@
         <v>1349</v>
       </c>
       <c r="L1352" s="0" t="n">
-        <f aca="false">TYPE(A1)</f>
-        <v>1</v>
+        <f aca="false">N("a")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17416,17 +17464,17 @@
         <v>1350</v>
       </c>
       <c r="L1353" s="0" t="n">
-        <f aca="false">TYPE(B1)</f>
-        <v>2</v>
+        <f aca="false">N(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1354" s="0" t="s">
         <v>1351</v>
       </c>
-      <c r="L1354" s="0" t="n">
-        <f aca="true">CELL("row",A5)</f>
-        <v>5</v>
+      <c r="L1354" s="0" t="e">
+        <f aca="false">N(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17434,26 +17482,26 @@
         <v>1352</v>
       </c>
       <c r="L1355" s="0" t="n">
-        <f aca="true">CELL("col",C1)</f>
-        <v>3</v>
+        <f aca="false">N(B1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1356" s="0" t="s">
         <v>1353</v>
       </c>
-      <c r="L1356" s="0" t="str">
-        <f aca="true">CELL("address",B2)</f>
-        <v>$B$2</v>
+      <c r="L1356" s="0" t="n">
+        <f aca="false">N(A3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1357" s="0" t="s">
         <v>1354</v>
       </c>
-      <c r="L1357" s="0" t="n">
-        <f aca="true">CELL("contents",A3)</f>
-        <v>3</v>
+      <c r="L1357" s="0" t="str">
+        <f aca="false">T("a")</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17461,8 +17509,8 @@
         <v>1355</v>
       </c>
       <c r="L1358" s="0" t="str">
-        <f aca="true">CELL("type",B1)</f>
-        <v>l</v>
+        <f aca="false">T(5)</f>
+        <v/>
       </c>
     </row>
     <row r="1359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17470,52 +17518,52 @@
         <v>1356</v>
       </c>
       <c r="L1359" s="0" t="str">
-        <f aca="true">CELL("type",A1)</f>
-        <v>v</v>
+        <f aca="false">T(B1)</f>
+        <v>apple</v>
       </c>
     </row>
     <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1360" s="0" t="s">
         <v>1357</v>
       </c>
-      <c r="L1360" s="0" t="str">
-        <f aca="true">CELL("type",J9)</f>
-        <v>b</v>
+      <c r="L1360" s="0" t="e">
+        <f aca="false">T(H2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1361" s="0" t="s">
         <v>1358</v>
       </c>
-      <c r="L1361" s="1" t="b">
-        <f aca="false">ISERR(H1)</f>
-        <v>1</v>
+      <c r="L1361" s="0" t="str">
+        <f aca="false">T(TRUE())</f>
+        <v/>
       </c>
     </row>
     <row r="1362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1362" s="0" t="s">
         <v>1359</v>
       </c>
-      <c r="L1362" s="1" t="b">
-        <f aca="false">ISERR(H2)</f>
-        <v>0</v>
+      <c r="L1362" s="0" t="n">
+        <f aca="false">TYPE(1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1363" s="0" t="s">
         <v>1360</v>
       </c>
-      <c r="L1363" s="1" t="b">
-        <f aca="false">ISERR(1)</f>
-        <v>0</v>
+      <c r="L1363" s="0" t="n">
+        <f aca="false">TYPE("a")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1364" s="0" t="s">
         <v>1361</v>
       </c>
-      <c r="L1364" s="1" t="b">
-        <f aca="false">ISERR(1/0)</f>
+      <c r="L1364" s="0" t="n">
+        <f aca="false">TYPE(TRUE())</f>
         <v>1</v>
       </c>
     </row>
@@ -17523,35 +17571,35 @@
       <c r="K1365" s="0" t="s">
         <v>1362</v>
       </c>
-      <c r="L1365" s="1" t="b">
-        <f aca="false">ISNONTEXT(1)</f>
-        <v>1</v>
+      <c r="L1365" s="0" t="n">
+        <f aca="false">TYPE(H1)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="1366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1366" s="0" t="s">
         <v>1363</v>
       </c>
-      <c r="L1366" s="1" t="b">
-        <f aca="false">ISNONTEXT("a")</f>
-        <v>0</v>
+      <c r="L1366" s="0" t="n">
+        <f aca="false">TYPE({1,2})</f>
+        <v>64</v>
       </c>
     </row>
     <row r="1367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1367" s="0" t="s">
         <v>1364</v>
       </c>
-      <c r="L1367" s="1" t="b">
-        <f aca="false">ISNONTEXT(J9)</f>
-        <v>1</v>
+      <c r="L1367" s="0" t="e">
+        <f aca="false">TYPE(A1:A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1368" s="0" t="s">
         <v>1365</v>
       </c>
-      <c r="L1368" s="1" t="b">
-        <f aca="false">ISNONTEXT(H1)</f>
+      <c r="L1368" s="0" t="n">
+        <f aca="false">TYPE(A1)</f>
         <v>1</v>
       </c>
     </row>
@@ -17559,243 +17607,243 @@
       <c r="K1369" s="0" t="s">
         <v>1366</v>
       </c>
-      <c r="L1369" s="1" t="b">
-        <f aca="false">ISREF(A1)</f>
-        <v>1</v>
+      <c r="L1369" s="0" t="n">
+        <f aca="false">TYPE(B1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1370" s="0" t="s">
         <v>1367</v>
       </c>
-      <c r="L1370" s="1" t="b">
-        <f aca="false">ISREF(1)</f>
-        <v>0</v>
+      <c r="L1370" s="0" t="n">
+        <f aca="true">CELL("row",A5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1371" s="0" t="s">
         <v>1368</v>
       </c>
-      <c r="L1371" s="1" t="b">
-        <f aca="false">ISREF(A1:B2)</f>
-        <v>1</v>
+      <c r="L1371" s="0" t="n">
+        <f aca="true">CELL("col",C1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1372" s="0" t="s">
         <v>1369</v>
       </c>
-      <c r="L1372" s="1" t="b">
-        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
-        <v>1</v>
+      <c r="L1372" s="0" t="str">
+        <f aca="true">CELL("address",B2)</f>
+        <v>$B$2</v>
       </c>
     </row>
     <row r="1373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1373" s="0" t="s">
         <v>1370</v>
       </c>
-      <c r="L1373" s="1" t="b">
-        <f aca="false">ISREF("A1")</f>
-        <v>0</v>
+      <c r="L1373" s="0" t="n">
+        <f aca="true">CELL("contents",A3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1374" s="0" t="s">
         <v>1371</v>
       </c>
-      <c r="L1374" s="0" t="n">
-        <f aca="false">SEARCH("an","banana")</f>
-        <v>2</v>
+      <c r="L1374" s="0" t="str">
+        <f aca="true">CELL("type",B1)</f>
+        <v>l</v>
       </c>
     </row>
     <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1375" s="0" t="s">
         <v>1372</v>
       </c>
-      <c r="L1375" s="0" t="n">
-        <f aca="false">SEARCH("AN","banana",3)</f>
-        <v>4</v>
+      <c r="L1375" s="0" t="str">
+        <f aca="true">CELL("type",A1)</f>
+        <v>v</v>
       </c>
     </row>
     <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1376" s="0" t="s">
         <v>1373</v>
       </c>
-      <c r="L1376" s="0" t="n">
-        <f aca="false">SEARCH("b?n","banana")</f>
-        <v>1</v>
+      <c r="L1376" s="0" t="str">
+        <f aca="true">CELL("type",J9)</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1377" s="0" t="s">
         <v>1374</v>
       </c>
-      <c r="L1377" s="0" t="e">
-        <f aca="false">SEARCH("z","banana")</f>
-        <v>#VALUE!</v>
+      <c r="L1377" s="1" t="b">
+        <f aca="false">ISERR(H1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1378" s="0" t="s">
         <v>1375</v>
       </c>
-      <c r="L1378" s="0" t="n">
-        <f aca="false">SEARCH("a*a","banana")</f>
-        <v>2</v>
+      <c r="L1378" s="1" t="b">
+        <f aca="false">ISERR(H2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1379" s="0" t="s">
         <v>1376</v>
       </c>
-      <c r="L1379" s="0" t="n">
-        <f aca="false">SEARCH("~?","what?")</f>
-        <v>5</v>
+      <c r="L1379" s="1" t="b">
+        <f aca="false">ISERR(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1380" s="0" t="s">
         <v>1377</v>
       </c>
-      <c r="L1380" s="0" t="str">
-        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
-        <v>abXYef</v>
+      <c r="L1380" s="1" t="b">
+        <f aca="false">ISERR(1/0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1381" s="0" t="s">
         <v>1378</v>
       </c>
-      <c r="L1381" s="0" t="str">
-        <f aca="false">REPLACE("abc",5,1,"Z")</f>
-        <v>abcZ</v>
+      <c r="L1381" s="1" t="b">
+        <f aca="false">ISNONTEXT(1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1382" s="0" t="s">
         <v>1379</v>
       </c>
-      <c r="L1382" s="0" t="str">
-        <f aca="false">REPLACE("abc",1,0,"Z")</f>
-        <v>Zabc</v>
+      <c r="L1382" s="1" t="b">
+        <f aca="false">ISNONTEXT("a")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1383" s="0" t="s">
         <v>1380</v>
       </c>
-      <c r="L1383" s="0" t="e">
-        <f aca="false">REPLACE("abc",0,1,"Z")</f>
-        <v>#VALUE!</v>
+      <c r="L1383" s="1" t="b">
+        <f aca="false">ISNONTEXT(J9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1384" s="0" t="s">
         <v>1381</v>
       </c>
-      <c r="L1384" s="0" t="str">
-        <f aca="false">REPLACE(B1,1,1,"A")</f>
-        <v>Apple</v>
+      <c r="L1384" s="1" t="b">
+        <f aca="false">ISNONTEXT(H1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1385" s="0" t="s">
         <v>1382</v>
       </c>
-      <c r="L1385" s="0" t="str">
-        <f aca="false">REPT("ab",3)</f>
-        <v>ababab</v>
+      <c r="L1385" s="1" t="b">
+        <f aca="false">ISREF(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1386" s="0" t="s">
         <v>1383</v>
       </c>
-      <c r="L1386" s="0" t="str">
-        <f aca="false">REPT("x",0)</f>
-        <v/>
+      <c r="L1386" s="1" t="b">
+        <f aca="false">ISREF(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1387" s="0" t="s">
         <v>1384</v>
       </c>
-      <c r="L1387" s="0" t="e">
-        <f aca="false">REPT("x",-1)</f>
-        <v>#VALUE!</v>
+      <c r="L1387" s="1" t="b">
+        <f aca="false">ISREF(A1:B2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1388" s="0" t="s">
         <v>1385</v>
       </c>
-      <c r="L1388" s="0" t="str">
-        <f aca="false">REPT(A1,3)</f>
-        <v>111</v>
+      <c r="L1388" s="1" t="b">
+        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1389" s="0" t="s">
         <v>1386</v>
       </c>
-      <c r="L1389" s="0" t="str">
-        <f aca="false">REPT("-",2.9)</f>
-        <v>--</v>
+      <c r="L1389" s="1" t="b">
+        <f aca="false">ISREF("A1")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1390" s="0" t="s">
         <v>1387</v>
       </c>
-      <c r="L1390" s="0" t="str">
-        <f aca="false">PROPER("hello world")</f>
-        <v>Hello World</v>
+      <c r="L1390" s="0" t="n">
+        <f aca="false">SEARCH("an","banana")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1391" s="0" t="s">
         <v>1388</v>
       </c>
-      <c r="L1391" s="0" t="str">
-        <f aca="false">PROPER("o'neil mc-donald")</f>
-        <v>O'Neil Mc-Donald</v>
+      <c r="L1391" s="0" t="n">
+        <f aca="false">SEARCH("AN","banana",3)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1392" s="0" t="s">
         <v>1389</v>
       </c>
-      <c r="L1392" s="0" t="str">
-        <f aca="false">PROPER("2nd place")</f>
-        <v>2Nd Place</v>
+      <c r="L1392" s="0" t="n">
+        <f aca="false">SEARCH("b?n","banana")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1393" s="0" t="s">
         <v>1390</v>
       </c>
-      <c r="L1393" s="0" t="str">
-        <f aca="false">PROPER(B1)</f>
-        <v>Apple</v>
+      <c r="L1393" s="0" t="e">
+        <f aca="false">SEARCH("z","banana")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1394" s="0" t="s">
         <v>1391</v>
       </c>
-      <c r="L1394" s="0" t="str">
-        <f aca="false">PROPER("ÀB cD")</f>
-        <v>Àb Cd</v>
+      <c r="L1394" s="0" t="n">
+        <f aca="false">SEARCH("a*a","banana")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1395" s="0" t="s">
         <v>1392</v>
       </c>
-      <c r="L1395" s="0" t="str">
-        <f aca="false">CHAR(65)</f>
-        <v>A</v>
+      <c r="L1395" s="0" t="n">
+        <f aca="false">SEARCH("~?","what?")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17803,8 +17851,8 @@
         <v>1393</v>
       </c>
       <c r="L1396" s="0" t="str">
-        <f aca="false">CHAR(97)</f>
-        <v>a</v>
+        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
+        <v>abXYef</v>
       </c>
     </row>
     <row r="1397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17812,26 +17860,26 @@
         <v>1394</v>
       </c>
       <c r="L1397" s="0" t="str">
-        <f aca="false">CHAR(0)</f>
-        <v>_x0000_</v>
+        <f aca="false">REPLACE("abc",5,1,"Z")</f>
+        <v>abcZ</v>
       </c>
     </row>
     <row r="1398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1398" s="0" t="s">
         <v>1395</v>
       </c>
-      <c r="L1398" s="0" t="e">
-        <f aca="false">CHAR(256)</f>
-        <v>#VALUE!</v>
+      <c r="L1398" s="0" t="str">
+        <f aca="false">REPLACE("abc",1,0,"Z")</f>
+        <v>Zabc</v>
       </c>
     </row>
     <row r="1399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1399" s="0" t="s">
         <v>1396</v>
       </c>
-      <c r="L1399" s="0" t="str">
-        <f aca="false">CHAR(169)</f>
-        <v>�</v>
+      <c r="L1399" s="0" t="e">
+        <f aca="false">REPLACE("abc",0,1,"Z")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17839,89 +17887,89 @@
         <v>1397</v>
       </c>
       <c r="L1400" s="0" t="str">
-        <f aca="false">CHAR(233)</f>
-        <v>�</v>
+        <f aca="false">REPLACE(B1,1,1,"A")</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="1401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1401" s="0" t="s">
         <v>1398</v>
       </c>
-      <c r="L1401" s="0" t="n">
-        <f aca="false">CODE("A")</f>
-        <v>65</v>
+      <c r="L1401" s="0" t="str">
+        <f aca="false">REPT("ab",3)</f>
+        <v>ababab</v>
       </c>
     </row>
     <row r="1402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1402" s="0" t="s">
         <v>1399</v>
       </c>
-      <c r="L1402" s="0" t="n">
-        <f aca="false">CODE("apple")</f>
-        <v>97</v>
+      <c r="L1402" s="0" t="str">
+        <f aca="false">REPT("x",0)</f>
+        <v/>
       </c>
     </row>
     <row r="1403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1403" s="0" t="s">
         <v>1400</v>
       </c>
-      <c r="L1403" s="0" t="n">
-        <f aca="false">CODE("")</f>
-        <v>0</v>
+      <c r="L1403" s="0" t="e">
+        <f aca="false">REPT("x",-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1404" s="0" t="s">
         <v>1401</v>
       </c>
-      <c r="L1404" s="0" t="n">
-        <f aca="false">CODE("é")</f>
-        <v>195</v>
+      <c r="L1404" s="0" t="str">
+        <f aca="false">REPT(A1,3)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="1405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1405" s="0" t="s">
         <v>1402</v>
       </c>
-      <c r="L1405" s="0" t="n">
-        <f aca="false">CODE(B1)</f>
-        <v>97</v>
+      <c r="L1405" s="0" t="str">
+        <f aca="false">REPT("-",2.9)</f>
+        <v>--</v>
       </c>
     </row>
     <row r="1406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1406" s="0" t="s">
         <v>1403</v>
       </c>
-      <c r="L1406" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE("A")</f>
-        <v>65</v>
+      <c r="L1406" s="0" t="str">
+        <f aca="false">PROPER("hello world")</f>
+        <v>Hello World</v>
       </c>
     </row>
     <row r="1407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1407" s="0" t="s">
         <v>1404</v>
       </c>
-      <c r="L1407" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE("€")</f>
-        <v>8364</v>
+      <c r="L1407" s="0" t="str">
+        <f aca="false">PROPER("o'neil mc-donald")</f>
+        <v>O'Neil Mc-Donald</v>
       </c>
     </row>
     <row r="1408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1408" s="0" t="s">
         <v>1405</v>
       </c>
-      <c r="L1408" s="0" t="e">
-        <f aca="false">_xlfn.UNICODE("")</f>
-        <v>#VALUE!</v>
+      <c r="L1408" s="0" t="str">
+        <f aca="false">PROPER("2nd place")</f>
+        <v>2Nd Place</v>
       </c>
     </row>
     <row r="1409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1409" s="0" t="s">
         <v>1406</v>
       </c>
-      <c r="L1409" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE(B2)</f>
-        <v>98</v>
+      <c r="L1409" s="0" t="str">
+        <f aca="false">PROPER(B1)</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="1410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17929,8 +17977,8 @@
         <v>1407</v>
       </c>
       <c r="L1410" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(65)</f>
-        <v>A</v>
+        <f aca="false">PROPER("ÀB cD")</f>
+        <v>Àb Cd</v>
       </c>
     </row>
     <row r="1411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17938,8 +17986,8 @@
         <v>1408</v>
       </c>
       <c r="L1411" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(8364)</f>
-        <v>€</v>
+        <f aca="false">CHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="1412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17947,8 +17995,8 @@
         <v>1409</v>
       </c>
       <c r="L1412" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(0)</f>
-        <v>_x0000_</v>
+        <f aca="false">CHAR(97)</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17956,17 +18004,17 @@
         <v>1410</v>
       </c>
       <c r="L1413" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(97)</f>
-        <v>a</v>
+        <f aca="false">CHAR(0)</f>
+        <v>_x0000_</v>
       </c>
     </row>
     <row r="1414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1414" s="0" t="s">
         <v>1411</v>
       </c>
-      <c r="L1414" s="0" t="str">
-        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
-        <v>ab</v>
+      <c r="L1414" s="0" t="e">
+        <f aca="false">CHAR(256)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17974,8 +18022,8 @@
         <v>1412</v>
       </c>
       <c r="L1415" s="0" t="str">
-        <f aca="false">CLEAN(B1)</f>
-        <v>apple</v>
+        <f aca="false">CHAR(169)</f>
+        <v>�</v>
       </c>
     </row>
     <row r="1416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17983,26 +18031,26 @@
         <v>1413</v>
       </c>
       <c r="L1416" s="0" t="str">
-        <f aca="false">CLEAN("  x ")</f>
-        <v>  x </v>
+        <f aca="false">CHAR(233)</f>
+        <v>�</v>
       </c>
     </row>
     <row r="1417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1417" s="0" t="s">
         <v>1414</v>
       </c>
-      <c r="L1417" s="0" t="str">
-        <f aca="false">CLEAN(A1)</f>
-        <v>1</v>
+      <c r="L1417" s="0" t="n">
+        <f aca="false">CODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="1418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1418" s="0" t="s">
         <v>1415</v>
       </c>
-      <c r="L1418" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
-        <v>#VALUE!</v>
+      <c r="L1418" s="0" t="n">
+        <f aca="false">CODE("apple")</f>
+        <v>97</v>
       </c>
     </row>
     <row r="1419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18010,8 +18058,8 @@
         <v>1416</v>
       </c>
       <c r="L1419" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
-        <v>1234.5</v>
+        <f aca="false">CODE("")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18019,26 +18067,26 @@
         <v>1417</v>
       </c>
       <c r="L1420" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
-        <v>0.05</v>
+        <f aca="false">CODE("é")</f>
+        <v>195</v>
       </c>
     </row>
     <row r="1421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1421" s="0" t="s">
         <v>1418</v>
       </c>
-      <c r="L1421" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("")</f>
-        <v>#VALUE!</v>
+      <c r="L1421" s="0" t="n">
+        <f aca="false">CODE(B1)</f>
+        <v>97</v>
       </c>
     </row>
     <row r="1422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1422" s="0" t="s">
         <v>1419</v>
       </c>
-      <c r="L1422" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
-        <v>#VALUE!</v>
+      <c r="L1422" s="0" t="n">
+        <f aca="false">_xlfn.UNICODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="1423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18046,8 +18094,8 @@
         <v>1420</v>
       </c>
       <c r="L1423" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
-        <v>0.0001</v>
+        <f aca="false">_xlfn.UNICODE("€")</f>
+        <v>8364</v>
       </c>
     </row>
     <row r="1424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18055,7 +18103,7 @@
         <v>1421</v>
       </c>
       <c r="L1424" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
+        <f aca="false">_xlfn.UNICODE("")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18064,8 +18112,8 @@
         <v>1422</v>
       </c>
       <c r="L1425" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
-        <v>12</v>
+        <f aca="false">_xlfn.UNICODE(B2)</f>
+        <v>98</v>
       </c>
     </row>
     <row r="1426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18073,8 +18121,8 @@
         <v>1423</v>
       </c>
       <c r="L1426" s="0" t="str">
-        <f aca="false">FIXED(1234.567,1)</f>
-        <v>1,234.6</v>
+        <f aca="false">_xlfn.UNICHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="1427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18082,8 +18130,8 @@
         <v>1424</v>
       </c>
       <c r="L1427" s="0" t="str">
-        <f aca="false">FIXED(1234.567,-1)</f>
-        <v>1,230</v>
+        <f aca="false">_xlfn.UNICHAR(8364)</f>
+        <v>€</v>
       </c>
     </row>
     <row r="1428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18091,8 +18139,8 @@
         <v>1425</v>
       </c>
       <c r="L1428" s="0" t="str">
-        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
-        <v>-1234.57</v>
+        <f aca="false">_xlfn.UNICHAR(0)</f>
+        <v>_x0000_</v>
       </c>
     </row>
     <row r="1429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18100,8 +18148,8 @@
         <v>1426</v>
       </c>
       <c r="L1429" s="0" t="str">
-        <f aca="false">FIXED(0.5,0)</f>
-        <v>1</v>
+        <f aca="false">_xlfn.UNICHAR(97)</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18109,8 +18157,8 @@
         <v>1427</v>
       </c>
       <c r="L1430" s="0" t="str">
-        <f aca="false">FIXED(1234567)</f>
-        <v>1,234,567.00</v>
+        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
+        <v>ab</v>
       </c>
     </row>
     <row r="1431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18118,8 +18166,8 @@
         <v>1428</v>
       </c>
       <c r="L1431" s="0" t="str">
-        <f aca="false">FIXED(A1)</f>
-        <v>1.00</v>
+        <f aca="false">CLEAN(B1)</f>
+        <v>apple</v>
       </c>
     </row>
     <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18127,8 +18175,8 @@
         <v>1429</v>
       </c>
       <c r="L1432" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
-        <v>apple,banana,cherry</v>
+        <f aca="false">CLEAN("  x ")</f>
+        <v>  x </v>
       </c>
     </row>
     <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18136,35 +18184,35 @@
         <v>1430</v>
       </c>
       <c r="L1433" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
-        <v>1-2-3</v>
+        <f aca="false">CLEAN(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1434" s="0" t="s">
         <v>1431</v>
       </c>
-      <c r="L1434" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
-        <v>a, b</v>
+      <c r="L1434" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1435" s="0" t="s">
         <v>1432</v>
       </c>
-      <c r="L1435" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
-        <v>a,,b</v>
+      <c r="L1435" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
+        <v>1234.5</v>
       </c>
     </row>
     <row r="1436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1436" s="0" t="s">
         <v>1433</v>
       </c>
-      <c r="L1436" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
-        <v>applebanana!</v>
+      <c r="L1436" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="1437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18172,17 +18220,17 @@
         <v>1434</v>
       </c>
       <c r="L1437" s="0" t="e">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
-        <v>#DIV/0!</v>
+        <f aca="false">_xlfn.NUMBERVALUE("")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1438" s="0" t="s">
         <v>1435</v>
       </c>
-      <c r="L1438" s="0" t="n">
-        <f aca="false">DATEVALUE("2024-01-15")</f>
-        <v>45306</v>
+      <c r="L1438" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18190,134 +18238,134 @@
         <v>1436</v>
       </c>
       <c r="L1439" s="0" t="n">
-        <f aca="false">DATEVALUE("1/15/2024")</f>
-        <v>45306</v>
+        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="1440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1440" s="0" t="s">
         <v>1437</v>
       </c>
-      <c r="L1440" s="0" t="n">
-        <f aca="false">DATEVALUE("2024-12-31")</f>
-        <v>45657</v>
+      <c r="L1440" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1441" s="0" t="s">
         <v>1438</v>
       </c>
-      <c r="L1441" s="0" t="e">
-        <f aca="false">DATEVALUE("abc")</f>
-        <v>#VALUE!</v>
+      <c r="L1441" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1442" s="0" t="s">
         <v>1439</v>
       </c>
-      <c r="L1442" s="0" t="e">
-        <f aca="false">DATEVALUE(5)</f>
-        <v>#VALUE!</v>
+      <c r="L1442" s="0" t="str">
+        <f aca="false">FIXED(1234.567,1)</f>
+        <v>1,234.6</v>
       </c>
     </row>
     <row r="1443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1443" s="0" t="s">
         <v>1440</v>
       </c>
-      <c r="L1443" s="0" t="n">
-        <f aca="false">TIMEVALUE("12:00")</f>
-        <v>0.5</v>
+      <c r="L1443" s="0" t="str">
+        <f aca="false">FIXED(1234.567,-1)</f>
+        <v>1,230</v>
       </c>
     </row>
     <row r="1444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1444" s="0" t="s">
         <v>1441</v>
       </c>
-      <c r="L1444" s="0" t="n">
-        <f aca="false">TIMEVALUE("6:00 PM")</f>
-        <v>0.75</v>
+      <c r="L1444" s="0" t="str">
+        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
+        <v>-1234.57</v>
       </c>
     </row>
     <row r="1445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1445" s="0" t="s">
         <v>1442</v>
       </c>
-      <c r="L1445" s="0" t="n">
-        <f aca="false">TIMEVALUE("18:30:30")</f>
-        <v>0.771180555555556</v>
+      <c r="L1445" s="0" t="str">
+        <f aca="false">FIXED(0.5,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1446" s="0" t="s">
         <v>1443</v>
       </c>
-      <c r="L1446" s="0" t="e">
-        <f aca="false">TIMEVALUE("xx")</f>
-        <v>#VALUE!</v>
+      <c r="L1446" s="0" t="str">
+        <f aca="false">FIXED(1234567)</f>
+        <v>1,234,567.00</v>
       </c>
     </row>
     <row r="1447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1447" s="0" t="s">
         <v>1444</v>
       </c>
-      <c r="L1447" s="0" t="n">
-        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
-        <v>0.25</v>
+      <c r="L1447" s="0" t="str">
+        <f aca="false">FIXED(A1)</f>
+        <v>1.00</v>
       </c>
     </row>
     <row r="1448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1448" s="0" t="s">
         <v>1445</v>
       </c>
-      <c r="L1448" s="8" t="n">
-        <f aca="false">TIME(12,0,0)</f>
-        <v>0.5</v>
+      <c r="L1448" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
+        <v>apple,banana,cherry</v>
       </c>
     </row>
     <row r="1449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1449" s="0" t="s">
         <v>1446</v>
       </c>
-      <c r="L1449" s="8" t="n">
-        <f aca="false">TIME(25,0,0)</f>
-        <v>0.0416666666666667</v>
+      <c r="L1449" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
+        <v>1-2-3</v>
       </c>
     </row>
     <row r="1450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1450" s="0" t="s">
         <v>1447</v>
       </c>
-      <c r="L1450" s="8" t="n">
-        <f aca="false">TIME(0,90,0)</f>
-        <v>0.0625</v>
+      <c r="L1450" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
+        <v>a, b</v>
       </c>
     </row>
     <row r="1451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1451" s="0" t="s">
         <v>1448</v>
       </c>
-      <c r="L1451" s="8" t="n">
-        <f aca="false">TIME(1,2,3)</f>
-        <v>0.0430902777777778</v>
+      <c r="L1451" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
+        <v>a,,b</v>
       </c>
     </row>
     <row r="1452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1452" s="0" t="s">
         <v>1449</v>
       </c>
-      <c r="L1452" s="8" t="e">
-        <f aca="false">TIME(-1,0,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1452" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
+        <v>applebanana!</v>
       </c>
     </row>
     <row r="1453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1453" s="0" t="s">
         <v>1450</v>
       </c>
-      <c r="L1453" s="0" t="n">
-        <f aca="false">HOUR(E3)</f>
-        <v>18</v>
+      <c r="L1453" s="0" t="e">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18325,8 +18373,8 @@
         <v>1451</v>
       </c>
       <c r="L1454" s="0" t="n">
-        <f aca="false">HOUR(0.5)</f>
-        <v>12</v>
+        <f aca="false">DATEVALUE("2024-01-15")</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18334,8 +18382,8 @@
         <v>1452</v>
       </c>
       <c r="L1455" s="0" t="n">
-        <f aca="false">HOUR("18:30")</f>
-        <v>18</v>
+        <f aca="false">DATEVALUE("1/15/2024")</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18343,26 +18391,26 @@
         <v>1453</v>
       </c>
       <c r="L1456" s="0" t="n">
-        <f aca="false">HOUR(-1)</f>
-        <v>0</v>
+        <f aca="false">DATEVALUE("2024-12-31")</f>
+        <v>45657</v>
       </c>
     </row>
     <row r="1457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1457" s="0" t="s">
         <v>1454</v>
       </c>
-      <c r="L1457" s="0" t="n">
-        <f aca="false">MINUTE(E3)</f>
-        <v>0</v>
+      <c r="L1457" s="0" t="e">
+        <f aca="false">DATEVALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1458" s="0" t="s">
         <v>1455</v>
       </c>
-      <c r="L1458" s="0" t="n">
-        <f aca="false">MINUTE("18:30:45")</f>
-        <v>30</v>
+      <c r="L1458" s="0" t="e">
+        <f aca="false">DATEVALUE(5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18370,8 +18418,8 @@
         <v>1456</v>
       </c>
       <c r="L1459" s="0" t="n">
-        <f aca="false">MINUTE(0.7712)</f>
-        <v>30</v>
+        <f aca="false">TIMEVALUE("12:00")</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18379,8 +18427,8 @@
         <v>1457</v>
       </c>
       <c r="L1460" s="0" t="n">
-        <f aca="false">MINUTE(-1)</f>
-        <v>0</v>
+        <f aca="false">TIMEVALUE("6:00 PM")</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18388,17 +18436,17 @@
         <v>1458</v>
       </c>
       <c r="L1461" s="0" t="n">
-        <f aca="false">SECOND("18:30:45")</f>
-        <v>45</v>
+        <f aca="false">TIMEVALUE("18:30:30")</f>
+        <v>0.771180555555556</v>
       </c>
     </row>
     <row r="1462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1462" s="0" t="s">
         <v>1459</v>
       </c>
-      <c r="L1462" s="0" t="n">
-        <f aca="false">SECOND(0.5)</f>
-        <v>0</v>
+      <c r="L1462" s="0" t="e">
+        <f aca="false">TIMEVALUE("xx")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18406,53 +18454,53 @@
         <v>1460</v>
       </c>
       <c r="L1463" s="0" t="n">
-        <f aca="false">SECOND(TIME(1,2,3))</f>
-        <v>3</v>
+        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="1464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1464" s="0" t="s">
         <v>1461</v>
       </c>
-      <c r="L1464" s="0" t="n">
-        <f aca="false">SECOND(-1)</f>
-        <v>0</v>
+      <c r="L1464" s="8" t="n">
+        <f aca="false">TIME(12,0,0)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1465" s="0" t="s">
         <v>1462</v>
       </c>
-      <c r="L1465" s="0" t="n">
-        <f aca="false">EDATE(E1,1)</f>
-        <v>45337</v>
+      <c r="L1465" s="8" t="n">
+        <f aca="false">TIME(25,0,0)</f>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="1466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1466" s="0" t="s">
         <v>1463</v>
       </c>
-      <c r="L1466" s="0" t="n">
-        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
-        <v>45351</v>
+      <c r="L1466" s="8" t="n">
+        <f aca="false">TIME(0,90,0)</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="1467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1467" s="0" t="s">
         <v>1464</v>
       </c>
-      <c r="L1467" s="0" t="n">
-        <f aca="false">EDATE(E1,-1)</f>
-        <v>45275</v>
+      <c r="L1467" s="8" t="n">
+        <f aca="false">TIME(1,2,3)</f>
+        <v>0.0430902777777778</v>
       </c>
     </row>
     <row r="1468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1468" s="0" t="s">
         <v>1465</v>
       </c>
-      <c r="L1468" s="0" t="n">
-        <f aca="false">EDATE(E1,0)</f>
-        <v>45306</v>
+      <c r="L1468" s="8" t="e">
+        <f aca="false">TIME(-1,0,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18460,8 +18508,8 @@
         <v>1466</v>
       </c>
       <c r="L1469" s="0" t="n">
-        <f aca="false">EDATE(E1,12)</f>
-        <v>45672</v>
+        <f aca="false">HOUR(E3)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="1470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18469,8 +18517,8 @@
         <v>1467</v>
       </c>
       <c r="L1470" s="0" t="n">
-        <f aca="false">EOMONTH(E1,0)</f>
-        <v>45322</v>
+        <f aca="false">HOUR(0.5)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18478,8 +18526,8 @@
         <v>1468</v>
       </c>
       <c r="L1471" s="0" t="n">
-        <f aca="false">EOMONTH(E1,1)</f>
-        <v>45351</v>
+        <f aca="false">HOUR("18:30")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="1472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18487,8 +18535,8 @@
         <v>1469</v>
       </c>
       <c r="L1472" s="0" t="n">
-        <f aca="false">EOMONTH(E1,-1)</f>
-        <v>45291</v>
+        <f aca="false">HOUR(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18496,8 +18544,8 @@
         <v>1470</v>
       </c>
       <c r="L1473" s="0" t="n">
-        <f aca="false">EOMONTH(E2,2)</f>
-        <v>45716</v>
+        <f aca="false">MINUTE(E3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18505,8 +18553,8 @@
         <v>1471</v>
       </c>
       <c r="L1474" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
-        <v>23</v>
+        <f aca="false">MINUTE("18:30:45")</f>
+        <v>30</v>
       </c>
     </row>
     <row r="1475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18514,8 +18562,8 @@
         <v>1472</v>
       </c>
       <c r="L1475" s="0" t="n">
-        <f aca="false">NETWORKDAYS(E1,E2)</f>
-        <v>252</v>
+        <f aca="false">MINUTE(0.7712)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="1476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18523,8 +18571,8 @@
         <v>1473</v>
       </c>
       <c r="L1476" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
-        <v>22</v>
+        <f aca="false">MINUTE(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18532,8 +18580,8 @@
         <v>1474</v>
       </c>
       <c r="L1477" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
-        <v>-23</v>
+        <f aca="false">SECOND("18:30:45")</f>
+        <v>45</v>
       </c>
     </row>
     <row r="1478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18541,8 +18589,8 @@
         <v>1475</v>
       </c>
       <c r="L1478" s="0" t="n">
-        <f aca="false">NETWORKDAYS(E1,E1)</f>
-        <v>1</v>
+        <f aca="false">SECOND(0.5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18550,8 +18598,8 @@
         <v>1476</v>
       </c>
       <c r="L1479" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
-        <v>27</v>
+        <f aca="false">SECOND(TIME(1,2,3))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18559,8 +18607,8 @@
         <v>1477</v>
       </c>
       <c r="L1480" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
-        <v>23</v>
+        <f aca="false">SECOND(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18568,8 +18616,8 @@
         <v>1478</v>
       </c>
       <c r="L1481" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
-        <v>22</v>
+        <f aca="false">EDATE(E1,1)</f>
+        <v>45337</v>
       </c>
     </row>
     <row r="1482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18577,17 +18625,17 @@
         <v>1479</v>
       </c>
       <c r="L1482" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
-        <v>22</v>
+        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
+        <v>45351</v>
       </c>
     </row>
     <row r="1483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1483" s="0" t="s">
         <v>1480</v>
       </c>
-      <c r="L1483" s="0" t="e">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
-        <v>#VALUE!</v>
+      <c r="L1483" s="0" t="n">
+        <f aca="false">EDATE(E1,-1)</f>
+        <v>45275</v>
       </c>
     </row>
     <row r="1484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18595,8 +18643,8 @@
         <v>1481</v>
       </c>
       <c r="L1484" s="0" t="n">
-        <f aca="false">WORKDAY(E1,1)</f>
-        <v>45307</v>
+        <f aca="false">EDATE(E1,0)</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18604,8 +18652,8 @@
         <v>1482</v>
       </c>
       <c r="L1485" s="0" t="n">
-        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
-        <v>45313</v>
+        <f aca="false">EDATE(E1,12)</f>
+        <v>45672</v>
       </c>
     </row>
     <row r="1486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18613,8 +18661,8 @@
         <v>1483</v>
       </c>
       <c r="L1486" s="0" t="n">
-        <f aca="false">WORKDAY(E1,-1)</f>
-        <v>45303</v>
+        <f aca="false">EOMONTH(E1,0)</f>
+        <v>45322</v>
       </c>
     </row>
     <row r="1487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18622,8 +18670,8 @@
         <v>1484</v>
       </c>
       <c r="L1487" s="0" t="n">
-        <f aca="false">WORKDAY(E1,5,E1+1)</f>
-        <v>45314</v>
+        <f aca="false">EOMONTH(E1,1)</f>
+        <v>45351</v>
       </c>
     </row>
     <row r="1488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18631,44 +18679,44 @@
         <v>1485</v>
       </c>
       <c r="L1488" s="0" t="n">
-        <f aca="false">WORKDAY(E1,0)</f>
-        <v>45306</v>
+        <f aca="false">EOMONTH(E1,-1)</f>
+        <v>45291</v>
       </c>
     </row>
     <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1489" s="0" t="s">
         <v>1486</v>
       </c>
-      <c r="L1489" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
-        <v>45307</v>
+      <c r="L1489" s="0" t="n">
+        <f aca="false">EOMONTH(E2,2)</f>
+        <v>45716</v>
       </c>
     </row>
     <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1490" s="0" t="s">
         <v>1487</v>
       </c>
-      <c r="L1490" s="3" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
-        <v>45313</v>
+      <c r="L1490" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
+        <v>23</v>
       </c>
     </row>
     <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1491" s="0" t="s">
         <v>1488</v>
       </c>
-      <c r="L1491" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
-        <v>45313</v>
+      <c r="L1491" s="0" t="n">
+        <f aca="false">NETWORKDAYS(E1,E2)</f>
+        <v>252</v>
       </c>
     </row>
     <row r="1492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1492" s="0" t="s">
         <v>1489</v>
       </c>
-      <c r="L1492" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
-        <v>45303</v>
+      <c r="L1492" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18676,8 +18724,8 @@
         <v>1490</v>
       </c>
       <c r="L1493" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
-        <v>4</v>
+        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
+        <v>-23</v>
       </c>
     </row>
     <row r="1494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18685,8 +18733,8 @@
         <v>1491</v>
       </c>
       <c r="L1494" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
-        <v>48</v>
+        <f aca="false">NETWORKDAYS(E1,E1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18694,8 +18742,8 @@
         <v>1492</v>
       </c>
       <c r="L1495" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
-        <v>1461</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="1496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18703,8 +18751,8 @@
         <v>1493</v>
       </c>
       <c r="L1496" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
-        <v>5</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
+        <v>23</v>
       </c>
     </row>
     <row r="1497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18712,8 +18760,8 @@
         <v>1494</v>
       </c>
       <c r="L1497" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
-        <v>6</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18721,8 +18769,8 @@
         <v>1495</v>
       </c>
       <c r="L1498" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
-        <v>209</v>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18730,7 +18778,7 @@
         <v>1496</v>
       </c>
       <c r="L1499" s="0" t="e">
-        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18738,9 +18786,9 @@
       <c r="K1500" s="0" t="s">
         <v>1497</v>
       </c>
-      <c r="L1500" s="0" t="e">
-        <f aca="false">DATEDIF(E1,E2,"X")</f>
-        <v>#VALUE!</v>
+      <c r="L1500" s="0" t="n">
+        <f aca="false">WORKDAY(E1,1)</f>
+        <v>45307</v>
       </c>
     </row>
     <row r="1501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18748,8 +18796,8 @@
         <v>1498</v>
       </c>
       <c r="L1501" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
-        <v>0.5</v>
+        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18757,8 +18805,8 @@
         <v>1499</v>
       </c>
       <c r="L1502" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
-        <v>0.495890410958904</v>
+        <f aca="false">WORKDAY(E1,-1)</f>
+        <v>45303</v>
       </c>
     </row>
     <row r="1503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18766,8 +18814,8 @@
         <v>1500</v>
       </c>
       <c r="L1503" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
-        <v>0.502777777777778</v>
+        <f aca="false">WORKDAY(E1,5,E1+1)</f>
+        <v>45314</v>
       </c>
     </row>
     <row r="1504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18775,53 +18823,53 @@
         <v>1501</v>
       </c>
       <c r="L1504" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
-        <v>0.495890410958904</v>
+        <f aca="false">WORKDAY(E1,0)</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1505" s="0" t="s">
         <v>1502</v>
       </c>
-      <c r="L1505" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
-        <v>0.5</v>
+      <c r="L1505" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
+        <v>45307</v>
       </c>
     </row>
     <row r="1506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1506" s="0" t="s">
         <v>1503</v>
       </c>
-      <c r="L1506" s="0" t="n">
-        <f aca="false">YEARFRAC(E1,E2)</f>
-        <v>0.961111111111111</v>
+      <c r="L1506" s="3" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1507" s="0" t="s">
         <v>1504</v>
       </c>
-      <c r="L1507" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
-        <v>3.99835796387521</v>
+      <c r="L1507" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1508" s="0" t="s">
         <v>1505</v>
       </c>
-      <c r="L1508" s="0" t="n">
-        <f aca="false">YEARFRAC(E2,E1)</f>
-        <v>0.961111111111111</v>
+      <c r="L1508" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
+        <v>45303</v>
       </c>
     </row>
     <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1509" s="0" t="s">
         <v>1506</v>
       </c>
-      <c r="L1509" s="0" t="e">
-        <f aca="false">YEARFRAC(E1,E2,5)</f>
-        <v>#VALUE!</v>
+      <c r="L1509" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18829,8 +18877,8 @@
         <v>1507</v>
       </c>
       <c r="L1510" s="0" t="n">
-        <f aca="false">WEEKNUM(E1,1)</f>
-        <v>3</v>
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
+        <v>48</v>
       </c>
     </row>
     <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18838,8 +18886,8 @@
         <v>1508</v>
       </c>
       <c r="L1511" s="0" t="n">
-        <f aca="false">WEEKNUM(E1,2)</f>
-        <v>3</v>
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
+        <v>1461</v>
       </c>
     </row>
     <row r="1512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18847,8 +18895,8 @@
         <v>1509</v>
       </c>
       <c r="L1512" s="0" t="n">
-        <f aca="false">WEEKNUM(E2,1)</f>
-        <v>1</v>
+        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18856,8 +18904,8 @@
         <v>1510</v>
       </c>
       <c r="L1513" s="0" t="n">
-        <f aca="false">WEEKNUM(E2,21)</f>
-        <v>1</v>
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18865,8 +18913,8 @@
         <v>1511</v>
       </c>
       <c r="L1514" s="0" t="n">
-        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
-        <v>1</v>
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
+        <v>209</v>
       </c>
     </row>
     <row r="1515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18874,7 +18922,7 @@
         <v>1512</v>
       </c>
       <c r="L1515" s="0" t="e">
-        <f aca="false">WEEKNUM(E1,3)</f>
+        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18882,9 +18930,9 @@
       <c r="K1516" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="L1516" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
-        <v>3</v>
+      <c r="L1516" s="0" t="e">
+        <f aca="false">DATEDIF(E1,E2,"X")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18892,8 +18940,8 @@
         <v>1514</v>
       </c>
       <c r="L1517" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
-        <v>1</v>
+        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18901,8 +18949,8 @@
         <v>1515</v>
       </c>
       <c r="L1518" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
-        <v>53</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
+        <v>0.495890410958904</v>
       </c>
     </row>
     <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18910,8 +18958,8 @@
         <v>1516</v>
       </c>
       <c r="L1519" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
-        <v>53</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
+        <v>0.502777777777778</v>
       </c>
     </row>
     <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18919,8 +18967,8 @@
         <v>1517</v>
       </c>
       <c r="L1520" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
-        <v>53</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
+        <v>0.495890410958904</v>
       </c>
     </row>
     <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18928,8 +18976,8 @@
         <v>1518</v>
       </c>
       <c r="L1521" s="0" t="n">
-        <f aca="false">ROWS(A1:A6)</f>
-        <v>6</v>
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18937,8 +18985,8 @@
         <v>1519</v>
       </c>
       <c r="L1522" s="0" t="n">
-        <f aca="false">ROWS(A1:C3)</f>
-        <v>3</v>
+        <f aca="false">YEARFRAC(E1,E2)</f>
+        <v>0.961111111111111</v>
       </c>
     </row>
     <row r="1523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18946,8 +18994,8 @@
         <v>1520</v>
       </c>
       <c r="L1523" s="0" t="n">
-        <f aca="false">ROWS(A:A)</f>
-        <v>1048576</v>
+        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
+        <v>3.99835796387521</v>
       </c>
     </row>
     <row r="1524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18955,17 +19003,17 @@
         <v>1521</v>
       </c>
       <c r="L1524" s="0" t="n">
-        <f aca="false">ROWS({1,2;3,4})</f>
-        <v>2</v>
+        <f aca="false">YEARFRAC(E2,E1)</f>
+        <v>0.961111111111111</v>
       </c>
     </row>
     <row r="1525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1525" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="L1525" s="0" t="n">
-        <f aca="false">COLUMNS(A1:C3)</f>
-        <v>3</v>
+      <c r="L1525" s="0" t="e">
+        <f aca="false">YEARFRAC(E1,E2,5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18973,7 +19021,7 @@
         <v>1523</v>
       </c>
       <c r="L1526" s="0" t="n">
-        <f aca="false">COLUMNS(A:C)</f>
+        <f aca="false">WEEKNUM(E1,1)</f>
         <v>3</v>
       </c>
     </row>
@@ -18982,8 +19030,8 @@
         <v>1524</v>
       </c>
       <c r="L1527" s="0" t="n">
-        <f aca="false">COLUMNS(1:1)</f>
-        <v>16384</v>
+        <f aca="false">WEEKNUM(E1,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18991,26 +19039,26 @@
         <v>1525</v>
       </c>
       <c r="L1528" s="0" t="n">
-        <f aca="false">COLUMNS({1,2;3,4})</f>
-        <v>2</v>
+        <f aca="false">WEEKNUM(E2,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1529" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="L1529" s="0" t="str">
-        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1529" s="0" t="n">
+        <f aca="false">WEEKNUM(E2,21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1530" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="L1530" s="0" t="str">
-        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1530" s="0" t="n">
+        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19018,26 +19066,26 @@
         <v>1528</v>
       </c>
       <c r="L1531" s="0" t="e">
-        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
-        <v>#N/A</v>
+        <f aca="false">WEEKNUM(E1,3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1532" s="0" t="s">
         <v>1529</v>
       </c>
-      <c r="L1532" s="0" t="str">
-        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
-        <v>fig</v>
+      <c r="L1532" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1533" s="0" t="s">
         <v>1530</v>
       </c>
-      <c r="L1533" s="0" t="str">
-        <f aca="false">LOOKUP(2,A1:B6)</f>
-        <v>banana</v>
+      <c r="L1533" s="0" t="n">
+        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19045,8 +19093,8 @@
         <v>1531</v>
       </c>
       <c r="L1534" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19054,8 +19102,8 @@
         <v>1532</v>
       </c>
       <c r="L1535" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19063,8 +19111,8 @@
         <v>1533</v>
       </c>
       <c r="L1536" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
-        <v>3</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19072,8 +19120,8 @@
         <v>1534</v>
       </c>
       <c r="L1537" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
-        <v>4</v>
+        <f aca="false">ROWS(A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19081,7 +19129,7 @@
         <v>1535</v>
       </c>
       <c r="L1538" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
+        <f aca="false">ROWS(A1:C3)</f>
         <v>3</v>
       </c>
     </row>
@@ -19089,9 +19137,9 @@
       <c r="K1539" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="L1539" s="0" t="e">
-        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
-        <v>#N/A</v>
+      <c r="L1539" s="0" t="n">
+        <f aca="false">ROWS(A:A)</f>
+        <v>1048576</v>
       </c>
     </row>
     <row r="1540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19099,44 +19147,44 @@
         <v>1537</v>
       </c>
       <c r="L1540" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
-        <v>3</v>
+        <f aca="false">ROWS({1,2;3,4})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1541" s="0" t="s">
         <v>1538</v>
       </c>
-      <c r="L1541" s="0" t="e">
-        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
-        <v>#VALUE!</v>
+      <c r="L1541" s="0" t="n">
+        <f aca="false">COLUMNS(A1:C3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1542" s="0" t="s">
         <v>1539</v>
       </c>
-      <c r="L1542" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1542" s="0" t="n">
+        <f aca="false">COLUMNS(A:C)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1543" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="L1543" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
-        <v>none</v>
+      <c r="L1543" s="0" t="n">
+        <f aca="false">COLUMNS(1:1)</f>
+        <v>16384</v>
       </c>
     </row>
     <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1544" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="L1544" s="0" t="e">
-        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
-        <v>#N/A</v>
+      <c r="L1544" s="0" t="n">
+        <f aca="false">COLUMNS({1,2;3,4})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19144,7 +19192,7 @@
         <v>1542</v>
       </c>
       <c r="L1545" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
+        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
         <v>cherry</v>
       </c>
     </row>
@@ -19152,36 +19200,36 @@
       <c r="K1546" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="L1546" s="0" t="n">
-        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
-        <v>6</v>
+      <c r="L1546" s="0" t="str">
+        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1547" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="L1547" s="0" t="n">
-        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
-        <v>100</v>
+      <c r="L1547" s="0" t="e">
+        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1548" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="L1548" s="0" t="e">
-        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
-        <v>#VALUE!</v>
+      <c r="L1548" s="0" t="str">
+        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
+        <v>fig</v>
       </c>
     </row>
     <row r="1549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1549" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="L1549" s="0" t="n">
-        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
-        <v>6</v>
+      <c r="L1549" s="0" t="str">
+        <f aca="false">LOOKUP(2,A1:B6)</f>
+        <v>banana</v>
       </c>
     </row>
     <row r="1550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19189,8 +19237,8 @@
         <v>1547</v>
       </c>
       <c r="L1550" s="0" t="n">
-        <f aca="true">INDIRECT("A1")</f>
-        <v>1</v>
+        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19198,7 +19246,7 @@
         <v>1548</v>
       </c>
       <c r="L1551" s="0" t="n">
-        <f aca="true">INDIRECT("A"&amp;3)</f>
+        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
         <v>3</v>
       </c>
     </row>
@@ -19207,8 +19255,8 @@
         <v>1549</v>
       </c>
       <c r="L1552" s="0" t="n">
-        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
-        <v>6</v>
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19216,8 +19264,8 @@
         <v>1550</v>
       </c>
       <c r="L1553" s="0" t="n">
-        <f aca="true">INDIRECT("Other!A1")</f>
-        <v>7</v>
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19225,8 +19273,8 @@
         <v>1551</v>
       </c>
       <c r="L1554" s="0" t="n">
-        <f aca="true">INDIRECT("R2C1",FALSE())</f>
-        <v>2</v>
+        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19234,134 +19282,134 @@
         <v>1552</v>
       </c>
       <c r="L1555" s="0" t="e">
-        <f aca="true">INDIRECT("zzz")</f>
-        <v>#REF!</v>
+        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1556" s="0" t="s">
         <v>1553</v>
       </c>
-      <c r="L1556" s="0" t="e">
-        <f aca="true">INDIRECT(B1)</f>
-        <v>#REF!</v>
+      <c r="L1556" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1557" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="L1557" s="0" t="str">
-        <f aca="true">OFFSET(A1,2,1)</f>
-        <v>cherry</v>
+      <c r="L1557" s="0" t="e">
+        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1558" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="L1558" s="0" t="n">
-        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
-        <v>6</v>
+      <c r="L1558" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1559" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="L1559" s="0" t="e">
-        <f aca="true">OFFSET(A1,-1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1559" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
+        <v>none</v>
       </c>
     </row>
     <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1560" s="0" t="s">
         <v>1557</v>
       </c>
-      <c r="L1560" s="0" t="n">
-        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
-        <v>5</v>
+      <c r="L1560" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1561" s="0" t="s">
         <v>1558</v>
       </c>
-      <c r="L1561" s="0" t="n">
-        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
-        <v>3</v>
+      <c r="L1561" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1562" s="0" t="s">
         <v>1559</v>
       </c>
-      <c r="L1562" s="0" t="e">
-        <f aca="true">OFFSET(A1,0,0,0,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1562" s="0" t="n">
+        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1563" s="0" t="s">
         <v>1560</v>
       </c>
-      <c r="L1563" s="0" t="str">
-        <f aca="false">ADDRESS(1,1)</f>
-        <v>$A$1</v>
+      <c r="L1563" s="0" t="n">
+        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1564" s="0" t="s">
         <v>1561</v>
       </c>
-      <c r="L1564" s="0" t="str">
-        <f aca="false">ADDRESS(5,3,4)</f>
-        <v>C5</v>
+      <c r="L1564" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1565" s="0" t="s">
         <v>1562</v>
       </c>
-      <c r="L1565" s="0" t="str">
-        <f aca="false">ADDRESS(2,28,2)</f>
-        <v>AB$2</v>
+      <c r="L1565" s="0" t="n">
+        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1566" s="0" t="s">
         <v>1563</v>
       </c>
-      <c r="L1566" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
-        <v>R1C1</v>
+      <c r="L1566" s="0" t="n">
+        <f aca="true">INDIRECT("A1")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1567" s="0" t="s">
         <v>1564</v>
       </c>
-      <c r="L1567" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
-        <v>'My Sheet'.$A$1</v>
+      <c r="L1567" s="0" t="n">
+        <f aca="true">INDIRECT("A"&amp;3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1568" s="0" t="s">
         <v>1565</v>
       </c>
-      <c r="L1568" s="0" t="e">
-        <f aca="false">ADDRESS(0,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1568" s="0" t="n">
+        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1569" s="0" t="s">
         <v>1566</v>
       </c>
-      <c r="L1569" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,5)</f>
-        <v>$A$1</v>
+      <c r="L1569" s="0" t="n">
+        <f aca="true">INDIRECT("Other!A1")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19369,35 +19417,35 @@
         <v>1567</v>
       </c>
       <c r="L1570" s="0" t="n">
-        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
-        <v>6</v>
+        <f aca="true">INDIRECT("R2C1",FALSE())</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1571" s="0" t="s">
         <v>1568</v>
       </c>
-      <c r="L1571" s="0" t="n">
-        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
-        <v>2</v>
+      <c r="L1571" s="0" t="e">
+        <f aca="true">INDIRECT("zzz")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="1572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1572" s="0" t="s">
         <v>1569</v>
       </c>
-      <c r="L1572" s="0" t="n">
-        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
-        <v>6</v>
+      <c r="L1572" s="0" t="e">
+        <f aca="true">INDIRECT(B1)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="1573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1573" s="0" t="s">
         <v>1570</v>
       </c>
-      <c r="L1573" s="0" t="n">
-        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
-        <v>3</v>
+      <c r="L1573" s="0" t="str">
+        <f aca="true">OFFSET(A1,2,1)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19405,116 +19453,116 @@
         <v>1571</v>
       </c>
       <c r="L1574" s="0" t="n">
-        <f aca="false">TRANSPOSE(A1:A3)</f>
-        <v>1</v>
+        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1575" s="0" t="s">
         <v>1572</v>
       </c>
-      <c r="L1575" s="0" t="str">
-        <f aca="false">HYPERLINK("http://x.y","click")</f>
-        <v>click</v>
+      <c r="L1575" s="0" t="e">
+        <f aca="true">OFFSET(A1,-1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1576" s="0" t="s">
         <v>1573</v>
       </c>
-      <c r="L1576" s="0" t="str">
-        <f aca="false">HYPERLINK("http://x.y")</f>
-        <v>http://x.y</v>
+      <c r="L1576" s="0" t="n">
+        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1577" s="0" t="s">
         <v>1574</v>
       </c>
-      <c r="L1577" s="0" t="str">
-        <f aca="false">HYPERLINK(B1,"go")</f>
-        <v>go</v>
+      <c r="L1577" s="0" t="n">
+        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1578" s="0" t="s">
         <v>1575</v>
       </c>
-      <c r="L1578" s="0" t="n">
-        <f aca="false">HYPERLINK("u",A2)</f>
-        <v>2</v>
+      <c r="L1578" s="0" t="e">
+        <f aca="true">OFFSET(A1,0,0,0,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1579" s="0" t="s">
         <v>1576</v>
       </c>
-      <c r="L1579" s="0" t="n">
-        <f aca="false">SUM(_xlfn.SEQUENCE(4))</f>
-        <v>10</v>
+      <c r="L1579" s="0" t="str">
+        <f aca="false">ADDRESS(1,1)</f>
+        <v>$A$1</v>
       </c>
     </row>
     <row r="1580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1580" s="0" t="s">
         <v>1577</v>
       </c>
-      <c r="L1580" s="0" t="n">
-        <f aca="false">INDEX(_xlfn.SEQUENCE(3,4,10,5),2,3)</f>
-        <v>40</v>
+      <c r="L1580" s="0" t="str">
+        <f aca="false">ADDRESS(5,3,4)</f>
+        <v>C5</v>
       </c>
     </row>
     <row r="1581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1581" s="0" t="s">
         <v>1578</v>
       </c>
-      <c r="L1581" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.SEQUENCE(5,2))</f>
-        <v>5</v>
+      <c r="L1581" s="0" t="str">
+        <f aca="false">ADDRESS(2,28,2)</f>
+        <v>AB$2</v>
       </c>
     </row>
     <row r="1582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1582" s="0" t="s">
         <v>1579</v>
       </c>
-      <c r="L1582" s="0" t="n">
-        <f aca="false">COLUMNS(_xlfn.SEQUENCE(5,2))</f>
-        <v>2</v>
+      <c r="L1582" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
+        <v>R1C1</v>
       </c>
     </row>
     <row r="1583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1583" s="0" t="s">
         <v>1580</v>
       </c>
-      <c r="L1583" s="0" t="n">
-        <f aca="false">SUM(_xlfn.SEQUENCE(2,2,0.5,0.25))</f>
-        <v>3.5</v>
+      <c r="L1583" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
+        <v>'My Sheet'.$A$1</v>
       </c>
     </row>
     <row r="1584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1584" s="0" t="s">
         <v>1581</v>
       </c>
-      <c r="L1584" s="0" t="n">
-        <f aca="false">_xlfn.SEQUENCE(1,1,7)</f>
-        <v>7</v>
+      <c r="L1584" s="0" t="e">
+        <f aca="false">ADDRESS(0,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1585" s="0" t="s">
         <v>1582</v>
       </c>
-      <c r="L1585" s="0" t="e">
-        <f aca="false">_xlfn.SEQUENCE(0)</f>
-        <v>#VALUE!</v>
+      <c r="L1585" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,5)</f>
+        <v>$A$1</v>
       </c>
     </row>
     <row r="1586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1586" s="0" t="s">
         <v>1583</v>
       </c>
-      <c r="L1586" s="0" t="e">
-        <f aca="false">_xlfn.SEQUENCE(-1)</f>
-        <v>#VALUE!</v>
+      <c r="L1586" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19522,8 +19570,8 @@
         <v>1584</v>
       </c>
       <c r="L1587" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.RANDARRAY(3,2))</f>
-        <v>3</v>
+        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19531,8 +19579,8 @@
         <v>1585</v>
       </c>
       <c r="L1588" s="0" t="n">
-        <f aca="false">COLUMNS(_xlfn.RANDARRAY(3,2))</f>
-        <v>2</v>
+        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19540,8 +19588,8 @@
         <v>1586</v>
       </c>
       <c r="L1589" s="0" t="n">
-        <f aca="false">SUM(_xlfn.RANDARRAY(4,4,5,5))</f>
-        <v>80</v>
+        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19549,35 +19597,35 @@
         <v>1587</v>
       </c>
       <c r="L1590" s="0" t="n">
-        <f aca="false">_xlfn.RANDARRAY(1,1,2,2,TRUE())</f>
-        <v>2</v>
+        <f aca="false">TRANSPOSE(A1:A3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1591" s="0" t="s">
         <v>1588</v>
       </c>
-      <c r="L1591" s="1" t="b">
-        <f aca="false">MIN(_xlfn.RANDARRAY(10,1,1,3,TRUE()))&gt;=1</f>
-        <v>1</v>
+      <c r="L1591" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y","click")</f>
+        <v>click</v>
       </c>
     </row>
     <row r="1592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1592" s="0" t="s">
         <v>1589</v>
       </c>
-      <c r="L1592" s="0" t="e">
-        <f aca="false">_xlfn.RANDARRAY(2,2,5,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1592" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y")</f>
+        <v>http://x.y</v>
       </c>
     </row>
     <row r="1593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1593" s="0" t="s">
         <v>1590</v>
       </c>
-      <c r="L1593" s="0" t="n">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6),1)</f>
-        <v>-2</v>
+      <c r="L1593" s="0" t="str">
+        <f aca="false">HYPERLINK(B1,"go")</f>
+        <v>go</v>
       </c>
     </row>
     <row r="1594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19585,35 +19633,35 @@
         <v>1591</v>
       </c>
       <c r="L1594" s="0" t="n">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6,1,-1),1)</f>
-        <v>1000000</v>
+        <f aca="false">HYPERLINK("u",A2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1595" s="0" t="s">
         <v>1592</v>
       </c>
-      <c r="L1595" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn._xlws.SORT(B1:B6,1,-1))</f>
-        <v>fig,elderberry,date,cherry,banana,apple</v>
+      <c r="L1595" s="0" t="n">
+        <f aca="false">SUM(_xlfn.SEQUENCE(4))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="1596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1596" s="0" t="s">
         <v>1593</v>
       </c>
-      <c r="L1596" s="0" t="str">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(A1:C6,3,1),2,2)</f>
-        <v>cherry</v>
+      <c r="L1596" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.SEQUENCE(3,4,10,5),2,3)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="1597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1597" s="0" t="s">
         <v>1594</v>
       </c>
-      <c r="L1597" s="0" t="str">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(F1:G4,1,-1),1,2)</f>
-        <v>four hundred</v>
+      <c r="L1597" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.SEQUENCE(5,2))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19621,53 +19669,53 @@
         <v>1595</v>
       </c>
       <c r="L1598" s="0" t="n">
-        <f aca="false">INDEX(_xlfn._xlws.SORT({3,1,2},1,1,TRUE()),1,3)</f>
-        <v>3</v>
+        <f aca="false">COLUMNS(_xlfn.SEQUENCE(5,2))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1599" s="0" t="s">
         <v>1596</v>
       </c>
-      <c r="L1599" s="0" t="e">
-        <f aca="false">_xlfn._xlws.SORT(A1:A6,2)</f>
-        <v>#VALUE!</v>
+      <c r="L1599" s="0" t="n">
+        <f aca="false">SUM(_xlfn.SEQUENCE(2,2,0.5,0.25))</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1600" s="0" t="s">
         <v>1597</v>
       </c>
-      <c r="L1600" s="0" t="e">
-        <f aca="false">_xlfn._xlws.SORT(A1:A6,1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1600" s="0" t="n">
+        <f aca="false">_xlfn.SEQUENCE(1,1,7)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1601" s="0" t="s">
         <v>1598</v>
       </c>
-      <c r="L1601" s="0" t="str">
-        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6),1)</f>
-        <v>banana</v>
+      <c r="L1601" s="0" t="e">
+        <f aca="false">_xlfn.SEQUENCE(0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1602" s="0" t="s">
         <v>1599</v>
       </c>
-      <c r="L1602" s="0" t="str">
-        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6,-1),1)</f>
-        <v>fig</v>
+      <c r="L1602" s="0" t="e">
+        <f aca="false">_xlfn.SEQUENCE(-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1603" s="0" t="s">
         <v>1600</v>
       </c>
-      <c r="L1603" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.SORTBY(G1:G4,F1:F4,-1))</f>
-        <v>four hundred,three hundred,two hundred,one hundred</v>
+      <c r="L1603" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.RANDARRAY(3,2))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19675,62 +19723,62 @@
         <v>1601</v>
       </c>
       <c r="L1604" s="0" t="n">
-        <f aca="false">INDEX(_xlfn.SORTBY(A1:A6,{1;1;2;2;3;3},-1,A1:A6,1),1)</f>
-        <v>5</v>
+        <f aca="false">COLUMNS(_xlfn.RANDARRAY(3,2))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1605" s="0" t="s">
         <v>1602</v>
       </c>
-      <c r="L1605" s="0" t="e">
-        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1605" s="0" t="n">
+        <f aca="false">SUM(_xlfn.RANDARRAY(4,4,5,5))</f>
+        <v>80</v>
       </c>
     </row>
     <row r="1606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1606" s="0" t="s">
         <v>1603</v>
       </c>
-      <c r="L1606" s="0" t="e">
-        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A6,2)</f>
-        <v>#VALUE!</v>
+      <c r="L1606" s="0" t="n">
+        <f aca="false">_xlfn.RANDARRAY(1,1,2,2,TRUE())</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1607" s="0" t="s">
         <v>1604</v>
       </c>
-      <c r="L1607" s="0" t="n">
-        <f aca="false">SUM(_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;3))</f>
-        <v>15</v>
+      <c r="L1607" s="1" t="b">
+        <f aca="false">MIN(_xlfn.RANDARRAY(10,1,1,3,TRUE()))&gt;=1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1608" s="0" t="s">
         <v>1605</v>
       </c>
-      <c r="L1608" s="0" t="n">
-        <f aca="false">ROWS(_xlfn._xlws.FILTER(B1:B6,C1:C6&gt;0))</f>
-        <v>4</v>
+      <c r="L1608" s="0" t="e">
+        <f aca="false">_xlfn.RANDARRAY(2,2,5,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1609" s="0" t="s">
         <v>1606</v>
       </c>
-      <c r="L1609" s="0" t="str">
-        <f aca="false">INDEX(_xlfn._xlws.FILTER(B1:B6,A1:A6=4),1)</f>
-        <v>date</v>
+      <c r="L1609" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6),1)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="1610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1610" s="0" t="s">
         <v>1607</v>
       </c>
-      <c r="L1610" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),_xlfn._xlws.FILTER(F1:F4,G1:G4&lt;&gt;"two hundred"))</f>
-        <v>100-300-400</v>
+      <c r="L1610" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6,1,-1),1)</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="1611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19738,26 +19786,26 @@
         <v>1608</v>
       </c>
       <c r="L1611" s="0" t="str">
-        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10,"none")</f>
-        <v>none</v>
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn._xlws.SORT(B1:B6,1,-1))</f>
+        <v>fig,elderberry,date,cherry,banana,apple</v>
       </c>
     </row>
     <row r="1612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1612" s="0" t="s">
         <v>1609</v>
       </c>
-      <c r="L1612" s="0" t="e">
-        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10)</f>
-        <v>#N/A</v>
+      <c r="L1612" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(A1:C6,3,1),2,2)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1613" s="0" t="s">
         <v>1610</v>
       </c>
-      <c r="L1613" s="0" t="e">
-        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A3&gt;1)</f>
-        <v>#VALUE!</v>
+      <c r="L1613" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(F1:G4,1,-1),1,2)</f>
+        <v>four hundred</v>
       </c>
     </row>
     <row r="1614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19765,7 +19813,7 @@
         <v>1611</v>
       </c>
       <c r="L1614" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <f aca="false">INDEX(_xlfn._xlws.SORT({3,1,2},1,1,TRUE()),1,3)</f>
         <v>3</v>
       </c>
     </row>
@@ -19773,18 +19821,18 @@
       <c r="K1615" s="0" t="s">
         <v>1612</v>
       </c>
-      <c r="L1615" s="0" t="n">
-        <f aca="false">SUM(_xlfn.UNIQUE({1;2;2;3;1}))</f>
-        <v>6</v>
+      <c r="L1615" s="0" t="e">
+        <f aca="false">_xlfn._xlws.SORT(A1:A6,2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1616" s="0" t="s">
         <v>1613</v>
       </c>
-      <c r="L1616" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1},FALSE(),TRUE()))</f>
-        <v>1</v>
+      <c r="L1616" s="0" t="e">
+        <f aca="false">_xlfn._xlws.SORT(A1:A6,1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19792,51 +19840,195 @@
         <v>1614</v>
       </c>
       <c r="L1617" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE({"a";"B";"A";"b"}))</f>
-        <v>a,B</v>
+        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6),1)</f>
+        <v>banana</v>
       </c>
     </row>
     <row r="1618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1618" s="0" t="s">
         <v>1615</v>
       </c>
-      <c r="L1618" s="0" t="n">
-        <f aca="false">COLUMNS(_xlfn.UNIQUE({1,1,2},TRUE()))</f>
-        <v>2</v>
+      <c r="L1618" s="0" t="str">
+        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6,-1),1)</f>
+        <v>fig</v>
       </c>
     </row>
     <row r="1619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1619" s="0" t="s">
         <v>1616</v>
       </c>
-      <c r="L1619" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.UNIQUE(A1:A6))</f>
-        <v>6</v>
+      <c r="L1619" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.SORTBY(G1:G4,F1:F4,-1))</f>
+        <v>four hundred,three hundred,two hundred,one hundred</v>
       </c>
     </row>
     <row r="1620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1620" s="0" t="s">
         <v>1617</v>
       </c>
-      <c r="L1620" s="0" t="e">
-        <f aca="false">_xlfn.UNIQUE({1;1},FALSE(),TRUE())</f>
-        <v>#N/A</v>
+      <c r="L1620" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.SORTBY(A1:A6,{1;1;2;2;3;3},-1,A1:A6,1),1)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1621" s="0" t="s">
         <v>1618</v>
       </c>
-      <c r="L1621" s="0" t="n">
-        <f aca="false">SUM(TRANSPOSE(_xlfn.SEQUENCE(3)))</f>
-        <v>6</v>
+      <c r="L1621" s="0" t="e">
+        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1622" s="0" t="s">
         <v>1619</v>
       </c>
-      <c r="L1622" s="0" t="n">
+      <c r="L1622" s="0" t="e">
+        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A6,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1623" s="0" t="s">
+        <v>1620</v>
+      </c>
+      <c r="L1623" s="0" t="n">
+        <f aca="false">SUM(_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;3))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1624" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="L1624" s="0" t="n">
+        <f aca="false">ROWS(_xlfn._xlws.FILTER(B1:B6,C1:C6&gt;0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1625" s="0" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L1625" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.FILTER(B1:B6,A1:A6=4),1)</f>
+        <v>date</v>
+      </c>
+    </row>
+    <row r="1626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1626" s="0" t="s">
+        <v>1623</v>
+      </c>
+      <c r="L1626" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),_xlfn._xlws.FILTER(F1:F4,G1:G4&lt;&gt;"two hundred"))</f>
+        <v>100-300-400</v>
+      </c>
+    </row>
+    <row r="1627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1627" s="0" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L1627" s="0" t="str">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10,"none")</f>
+        <v>none</v>
+      </c>
+    </row>
+    <row r="1628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1628" s="0" t="s">
+        <v>1625</v>
+      </c>
+      <c r="L1628" s="0" t="e">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1629" s="0" t="s">
+        <v>1626</v>
+      </c>
+      <c r="L1629" s="0" t="e">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A3&gt;1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1630" s="0" t="s">
+        <v>1627</v>
+      </c>
+      <c r="L1630" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1631" s="0" t="s">
+        <v>1628</v>
+      </c>
+      <c r="L1631" s="0" t="n">
+        <f aca="false">SUM(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1632" s="0" t="s">
+        <v>1629</v>
+      </c>
+      <c r="L1632" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1},FALSE(),TRUE()))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1633" s="0" t="s">
+        <v>1630</v>
+      </c>
+      <c r="L1633" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE({"a";"B";"A";"b"}))</f>
+        <v>a,B</v>
+      </c>
+    </row>
+    <row r="1634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1634" s="0" t="s">
+        <v>1631</v>
+      </c>
+      <c r="L1634" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.UNIQUE({1,1,2},TRUE()))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1635" s="0" t="s">
+        <v>1632</v>
+      </c>
+      <c r="L1635" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE(A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1636" s="0" t="s">
+        <v>1633</v>
+      </c>
+      <c r="L1636" s="0" t="e">
+        <f aca="false">_xlfn.UNIQUE({1;1},FALSE(),TRUE())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1637" s="0" t="s">
+        <v>1634</v>
+      </c>
+      <c r="L1637" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(_xlfn.SEQUENCE(3)))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1638" s="0" t="s">
+        <v>1635</v>
+      </c>
+      <c r="L1638" s="0" t="n">
         <f aca="false">INDEX(_xlfn.XLOOKUP(3,A1:A6,B1:C6),1,2)</f>
         <v>0</v>
       </c>
@@ -19865,7 +20057,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1620</v>
+        <v>1636</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/formulas/formula-suite.xlsx
+++ b/testdata/formulas/formula-suite.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1748">
   <si>
     <t xml:space="preserve">apple</t>
   </si>
@@ -3968,6 +3968,87 @@
     <t xml:space="preserve">=MIRR({-100,-50},0.1,0.1)</t>
   </si>
   <si>
+    <t xml:space="preserve">=SUM(MMULT(A1:A2,TRANSPOSE(A1:A2)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(MMULT({1,2;3,4},{5;6}),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MMULT(A1:A2,A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MMULT({1,2},{3;4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(MINVERSE({4,7;2,6}),1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(MINVERSE({2,0;0,4}),2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINVERSE({1,2;2,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MINVERSE(A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MDETERM({1,2;3,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MDETERM({2,0,0;0,3,0;0,0,4})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MDETERM(A1:A2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MDETERM({3})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(MUNIT(3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(MUNIT(2),1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(MUNIT(4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MUNIT(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(9,6,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(4,6,H1:H2,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(9,4,H1:H2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(14,6,C1:C6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(15,0,A1:A6,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(1,0,F1:F4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(3,0,A1:B6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(12,0,A1:A6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(16,0,A1:A6,0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(19,0,A1:A6,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=AGGREGATE(20,0,A1:A6)</t>
+  </si>
+  <si>
     <t xml:space="preserve">=IFS(A1&gt;5,"a",A1&gt;0,"b")</t>
   </si>
   <si>
@@ -4025,6 +4106,114 @@
     <t xml:space="preserve">=XOR(H1)</t>
   </si>
   <si>
+    <t xml:space="preserve">=LET(x,2,x*3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LET(x,A1:A6,SUM(x))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LET(x,A2,y,x*10,y+1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LET(n,COUNT(C1:C6),n*2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LAMBDA(x,x+1)(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LAMBDA(x,y,x*y)(A2,A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LET(f,LAMBDA(v,v*2),f(A4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=IFERROR(LAMBDA(x,x)(1,2),"err")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(MAP(A1:A3,LAMBDA(v,v*v)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(MAP(A1:A6,LAMBDA(v,v+1)),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(MAP(A1:A6,LAMBDA(v,v)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(MAP(A1:A2,F1:F2,LAMBDA(a,b,a*b)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REDUCE(0,A1:A6,LAMBDA(a,v,a+v))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REDUCE(1,A1:A4,LAMBDA(a,v,a*v))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=REDUCE("x",B1:B2,LAMBDA(a,v,a&amp;v))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(REDUCE(0,A1:A3,LAMBDA(a,v,VSTACK(a,v))))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SCAN(0,A1:A6,LAMBDA(a,v,a+v)),6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(SCAN(0,A1:A3,LAMBDA(a,v,a+v)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(SCAN(1,A1:A4,LAMBDA(a,v,a*v)),4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(SCAN(0,A1:A6,LAMBDA(a,v,a+v)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(BYROW(A1:C2,LAMBDA(rw,COUNT(rw))))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(BYROW(A1:A3,LAMBDA(rw,rw*2)),3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(BYROW(A1:C6,LAMBDA(rw,1)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(BYROW(F1:F4,LAMBDA(rw,rw/100)),4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(BYCOL(A1:C6,LAMBDA(cl,COUNT(cl))))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(BYCOL(A1:C1,LAMBDA(cl,1)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(BYCOL(A1:C6,LAMBDA(cl,MAX(cl))),3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(BYCOL(A1:A6,LAMBDA(cl,SUM(cl))),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(MAKEARRAY(2,3,LAMBDA(i,j,i*j)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(MAKEARRAY(3,3,LAMBDA(i,j,i*10+j)),2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(MAKEARRAY(4,2,LAMBDA(i,j,0)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=MAKEARRAY(0,1,LAMBDA(i,j,1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LAMBDA(x,y,ISOMITTED(y))(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LAMBDA(x,y,ISOMITTED(y))(1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LET(f,LAMBDA(a,b,IF(ISOMITTED(b),a,a+b)),f(5))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=LET(f,LAMBDA(a,b,IF(ISOMITTED(b),a,a+b)),f(5,1))</t>
+  </si>
+  <si>
     <t xml:space="preserve">=ISLOGICAL(TRUE)</t>
   </si>
   <si>
@@ -4929,6 +5118,150 @@
   </si>
   <si>
     <t xml:space="preserve">=INDEX(XLOOKUP(3,A1:A6,B1:C6),1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(TAKE(A1:A6,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(TAKE(A1:A6,-2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TAKE(A1:C6,1,-1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(TAKE(A1:A6,99))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=TAKE(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(DROP(A1:A6,4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(DROP(A1:A6,-4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(DROP(A1:C6,1,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=DROP(A1:A6,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(VSTACK(A1:A2,F1:F4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(VSTACK(A1:A3,F1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(VSTACK(A1:B1,F1),2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(VSTACK(A1,B1:C1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(HSTACK(A1:A2,F1:F2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(HSTACK(A1:A2,F1:F2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(HSTACK(A1:A2,F1),2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(HSTACK(A1:A3,F1:F4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(CHOOSECOLS(A1:C6,1))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(CHOOSECOLS(A1:C6,-1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(CHOOSECOLS(A1:C6,1,3,3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHOOSECOLS(A1:C6,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(CHOOSEROWS(A1:A6,1,6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(CHOOSEROWS(B1:B6,-1),1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(CHOOSEROWS(A1:A6,{1,2,3}))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=CHOOSEROWS(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(EXPAND(A1:A2,5))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(EXPAND(A1:A2,3,2,0),3,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(EXPAND(A1,2),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=EXPAND(A1:A3,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(TOCOL(A1:C2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TOCOL(A1:C2),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TOCOL(A1:C2,0,TRUE),2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(TOCOL(A1:H2,2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(TOROW(A1:B2))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TOROW(A1:B2),1,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(TOROW(A1:B2,0,TRUE),1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(TOROW(A1:A6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=ROWS(WRAPROWS(A1:A6,4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(WRAPROWS(A1:A6,4),2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(WRAPROWS(A1:A6,4,0),2,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WRAPROWS(A1:B2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=COLUMNS(WRAPCOLS(A1:A6,4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(WRAPCOLS(A1:A6,4),2,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(WRAPCOLS(A1:A6,4),4,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=WRAPCOLS(A1:A6,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUM(LEN(B1:B3))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=SUMPRODUCT(LEN(B1:B6))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=INDEX(UNIQUE({1,2,1;3,4,3},TRUE),2,2)</t>
   </si>
   <si>
     <t xml:space="preserve">remote</t>
@@ -5172,7 +5505,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1638"/>
+  <dimension ref="A1:L1749"/>
   <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10400,7 +10733,7 @@
       </c>
       <c r="L568" s="4" t="n">
         <f aca="true">NOW()</f>
-        <v>46312.7703913421</v>
+        <v>46312.7881328226</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17148,9 +17481,9 @@
       <c r="K1318" s="0" t="s">
         <v>1315</v>
       </c>
-      <c r="L1318" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
-        <v>b</v>
+      <c r="L1318" s="0" t="n">
+        <f aca="false">SUM(MMULT(A1:A2,TRANSPOSE(A1:A2)))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="1319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17158,8 +17491,8 @@
         <v>1316</v>
       </c>
       <c r="L1319" s="0" t="n">
-        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
-        <v>2</v>
+        <f aca="false">INDEX(MMULT({1,2;3,4},{5;6}),2)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="1320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17167,8 +17500,8 @@
         <v>1317</v>
       </c>
       <c r="L1320" s="0" t="e">
-        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
-        <v>#N/A</v>
+        <f aca="false">MMULT(A1:A2,A1:A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17176,35 +17509,35 @@
         <v>1318</v>
       </c>
       <c r="L1321" s="0" t="n">
-        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
-        <v>1</v>
+        <f aca="false">MMULT({1,2},{3;4})</f>
+        <v>11</v>
       </c>
     </row>
     <row r="1322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1322" s="0" t="s">
         <v>1319</v>
       </c>
-      <c r="L1322" s="0" t="str">
-        <f aca="false">_xlfn.IFS(A1,"x")</f>
-        <v>x</v>
+      <c r="L1322" s="0" t="n">
+        <f aca="false">INDEX(MINVERSE({4,7;2,6}),1,1)</f>
+        <v>0.6</v>
       </c>
     </row>
     <row r="1323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1323" s="0" t="s">
         <v>1320</v>
       </c>
-      <c r="L1323" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
-        <v>b</v>
+      <c r="L1323" s="0" t="n">
+        <f aca="false">INDEX(MINVERSE({2,0;0,4}),2,2)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="1324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1324" s="0" t="s">
         <v>1321</v>
       </c>
-      <c r="L1324" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
-        <v>z</v>
+      <c r="L1324" s="0" t="e">
+        <f aca="false">MINVERSE({1,2;2,4})</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17212,8 +17545,8 @@
         <v>1322</v>
       </c>
       <c r="L1325" s="0" t="e">
-        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
-        <v>#N/A</v>
+        <f aca="false">MINVERSE(A1:A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17221,35 +17554,35 @@
         <v>1323</v>
       </c>
       <c r="L1326" s="0" t="n">
-        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
-        <v>2</v>
+        <f aca="false">MDETERM({1,2;3,4})</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="1327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1327" s="0" t="s">
         <v>1324</v>
       </c>
-      <c r="L1327" s="0" t="str">
-        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
-        <v>three</v>
+      <c r="L1327" s="0" t="n">
+        <f aca="false">MDETERM({2,0,0;0,3,0;0,0,4})</f>
+        <v>24</v>
       </c>
     </row>
     <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1328" s="0" t="s">
         <v>1325</v>
       </c>
-      <c r="L1328" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(H2,"x")</f>
-        <v>x</v>
+      <c r="L1328" s="0" t="e">
+        <f aca="false">MDETERM(A1:A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1329" s="0" t="s">
         <v>1326</v>
       </c>
-      <c r="L1329" s="0" t="e">
-        <f aca="false">_xlfn.IFNA(H1,"x")</f>
-        <v>#DIV/0!</v>
+      <c r="L1329" s="0" t="n">
+        <f aca="false">MDETERM({3})</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17257,8 +17590,8 @@
         <v>1327</v>
       </c>
       <c r="L1330" s="0" t="n">
-        <f aca="false">_xlfn.IFNA(5,"x")</f>
-        <v>5</v>
+        <f aca="false">SUM(_xlfn.MUNIT(3))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17266,7 +17599,7 @@
         <v>1328</v>
       </c>
       <c r="L1331" s="0" t="n">
-        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
+        <f aca="false">INDEX(_xlfn.MUNIT(2),1,2)</f>
         <v>0</v>
       </c>
     </row>
@@ -17274,44 +17607,44 @@
       <c r="K1332" s="0" t="s">
         <v>1329</v>
       </c>
-      <c r="L1332" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
-        <v>1</v>
+      <c r="L1332" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.MUNIT(4))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1333" s="0" t="s">
         <v>1330</v>
       </c>
-      <c r="L1333" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
-        <v>0</v>
+      <c r="L1333" s="0" t="e">
+        <f aca="false">_xlfn.MUNIT(0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1334" s="0" t="s">
         <v>1331</v>
       </c>
-      <c r="L1334" s="1" t="b">
-        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
-        <v>1</v>
+      <c r="L1334" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(9,6,A1:A6)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="1335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1335" s="0" t="s">
         <v>1332</v>
       </c>
-      <c r="L1335" s="1" t="b">
-        <f aca="false">_xlfn.XOR(1,0,0)</f>
-        <v>1</v>
+      <c r="L1335" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(4,6,H1:H2,A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1336" s="0" t="s">
         <v>1333</v>
       </c>
-      <c r="L1336" s="1" t="e">
-        <f aca="false">_xlfn.XOR(H1)</f>
+      <c r="L1336" s="0" t="e">
+        <f aca="false">_xlfn.AGGREGATE(9,4,H1:H2)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -17319,71 +17652,71 @@
       <c r="K1337" s="0" t="s">
         <v>1334</v>
       </c>
-      <c r="L1337" s="1" t="b">
-        <f aca="false">ISLOGICAL(TRUE())</f>
-        <v>1</v>
+      <c r="L1337" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(14,6,C1:C6,2)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1338" s="0" t="s">
         <v>1335</v>
       </c>
-      <c r="L1338" s="1" t="b">
-        <f aca="false">ISLOGICAL(1)</f>
-        <v>0</v>
+      <c r="L1338" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(15,0,A1:A6,2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1339" s="0" t="s">
         <v>1336</v>
       </c>
-      <c r="L1339" s="1" t="b">
-        <f aca="false">ISLOGICAL("TRUE")</f>
-        <v>0</v>
+      <c r="L1339" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(1,0,F1:F4)</f>
+        <v>250</v>
       </c>
     </row>
     <row r="1340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1340" s="0" t="s">
         <v>1337</v>
       </c>
-      <c r="L1340" s="1" t="b">
-        <f aca="false">ISLOGICAL(1=1)</f>
-        <v>1</v>
+      <c r="L1340" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(3,0,A1:B6)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1341" s="0" t="s">
         <v>1338</v>
       </c>
-      <c r="L1341" s="1" t="b">
-        <f aca="false">ISEVEN(2)</f>
-        <v>1</v>
+      <c r="L1341" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(12,0,A1:A6)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1342" s="0" t="s">
         <v>1339</v>
       </c>
-      <c r="L1342" s="1" t="b">
-        <f aca="false">ISEVEN(3)</f>
-        <v>0</v>
+      <c r="L1342" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(16,0,A1:A6,0.5)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1343" s="0" t="s">
         <v>1340</v>
       </c>
-      <c r="L1343" s="1" t="b">
-        <f aca="false">ISEVEN(-2.9)</f>
-        <v>1</v>
+      <c r="L1343" s="0" t="n">
+        <f aca="false">_xlfn.AGGREGATE(19,0,A1:A6,1)</f>
+        <v>1.75</v>
       </c>
     </row>
     <row r="1344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1344" s="0" t="s">
         <v>1341</v>
       </c>
-      <c r="L1344" s="1" t="e">
-        <f aca="false">ISEVEN("a")</f>
+      <c r="L1344" s="0" t="e">
+        <f aca="false">_xlfn.AGGREGATE(20,0,A1:A6)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -17391,35 +17724,35 @@
       <c r="K1345" s="0" t="s">
         <v>1342</v>
       </c>
-      <c r="L1345" s="1" t="b">
-        <f aca="false">ISEVEN(A2)</f>
-        <v>1</v>
+      <c r="L1345" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1&gt;5,"a",A1&gt;0,"b")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1346" s="0" t="s">
         <v>1343</v>
       </c>
-      <c r="L1346" s="1" t="b">
-        <f aca="false">ISODD(2)</f>
-        <v>0</v>
+      <c r="L1346" s="0" t="n">
+        <f aca="false">_xlfn.IFS(FALSE(),1,TRUE(),2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1347" s="0" t="s">
         <v>1344</v>
       </c>
-      <c r="L1347" s="1" t="b">
-        <f aca="false">ISODD(3)</f>
-        <v>1</v>
+      <c r="L1347" s="0" t="e">
+        <f aca="false">_xlfn.IFS(FALSE(),1,FALSE(),2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1348" s="0" t="s">
         <v>1345</v>
       </c>
-      <c r="L1348" s="1" t="b">
-        <f aca="false">ISODD(-3.5)</f>
+      <c r="L1348" s="0" t="n">
+        <f aca="false">_xlfn.IFS(TRUE(),1,1/0,2)</f>
         <v>1</v>
       </c>
     </row>
@@ -17427,36 +17760,36 @@
       <c r="K1349" s="0" t="s">
         <v>1346</v>
       </c>
-      <c r="L1349" s="1" t="e">
-        <f aca="false">ISODD("a")</f>
-        <v>#VALUE!</v>
+      <c r="L1349" s="0" t="str">
+        <f aca="false">_xlfn.IFS(A1,"x")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="1350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1350" s="0" t="s">
         <v>1347</v>
       </c>
-      <c r="L1350" s="1" t="b">
-        <f aca="false">ISODD(A1)</f>
-        <v>1</v>
+      <c r="L1350" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(2,1,"a",2,"b","z")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1351" s="0" t="s">
         <v>1348</v>
       </c>
-      <c r="L1351" s="0" t="n">
-        <f aca="false">N(5)</f>
-        <v>5</v>
+      <c r="L1351" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(9,1,"a",2,"b","z")</f>
+        <v>z</v>
       </c>
     </row>
     <row r="1352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1352" s="0" t="s">
         <v>1349</v>
       </c>
-      <c r="L1352" s="0" t="n">
-        <f aca="false">N("a")</f>
-        <v>0</v>
+      <c r="L1352" s="0" t="e">
+        <f aca="false">_xlfn.SWITCH(9,1,"a")</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17464,88 +17797,88 @@
         <v>1350</v>
       </c>
       <c r="L1353" s="0" t="n">
-        <f aca="false">N(TRUE())</f>
-        <v>1</v>
+        <f aca="false">_xlfn.SWITCH("B","a",1,"b",2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1354" s="0" t="s">
         <v>1351</v>
       </c>
-      <c r="L1354" s="0" t="e">
-        <f aca="false">N(H1)</f>
-        <v>#DIV/0!</v>
+      <c r="L1354" s="0" t="str">
+        <f aca="false">_xlfn.SWITCH(A3,1,"one",3,"three")</f>
+        <v>three</v>
       </c>
     </row>
     <row r="1355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1355" s="0" t="s">
         <v>1352</v>
       </c>
-      <c r="L1355" s="0" t="n">
-        <f aca="false">N(B1)</f>
-        <v>0</v>
+      <c r="L1355" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(H2,"x")</f>
+        <v>x</v>
       </c>
     </row>
     <row r="1356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1356" s="0" t="s">
         <v>1353</v>
       </c>
-      <c r="L1356" s="0" t="n">
-        <f aca="false">N(A3)</f>
-        <v>3</v>
+      <c r="L1356" s="0" t="e">
+        <f aca="false">_xlfn.IFNA(H1,"x")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1357" s="0" t="s">
         <v>1354</v>
       </c>
-      <c r="L1357" s="0" t="str">
-        <f aca="false">T("a")</f>
-        <v>a</v>
+      <c r="L1357" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(5,"x")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1358" s="0" t="s">
         <v>1355</v>
       </c>
-      <c r="L1358" s="0" t="str">
-        <f aca="false">T(5)</f>
-        <v/>
+      <c r="L1358" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(MATCH(9,A1:A6,0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1359" s="0" t="s">
         <v>1356</v>
       </c>
-      <c r="L1359" s="0" t="str">
-        <f aca="false">T(B1)</f>
-        <v>apple</v>
+      <c r="L1359" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),FALSE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1360" s="0" t="s">
         <v>1357</v>
       </c>
-      <c r="L1360" s="0" t="e">
-        <f aca="false">T(H2)</f>
-        <v>#N/A</v>
+      <c r="L1360" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE())</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1361" s="0" t="s">
         <v>1358</v>
       </c>
-      <c r="L1361" s="0" t="str">
-        <f aca="false">T(TRUE())</f>
-        <v/>
+      <c r="L1361" s="1" t="b">
+        <f aca="false">_xlfn.XOR(TRUE(),TRUE(),TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1362" s="0" t="s">
         <v>1359</v>
       </c>
-      <c r="L1362" s="0" t="n">
-        <f aca="false">TYPE(1)</f>
+      <c r="L1362" s="1" t="b">
+        <f aca="false">_xlfn.XOR(1,0,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -17553,9 +17886,9 @@
       <c r="K1363" s="0" t="s">
         <v>1360</v>
       </c>
-      <c r="L1363" s="0" t="n">
-        <f aca="false">TYPE("a")</f>
-        <v>2</v>
+      <c r="L1363" s="1" t="e">
+        <f aca="false">_xlfn.XOR(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17563,8 +17896,8 @@
         <v>1361</v>
       </c>
       <c r="L1364" s="0" t="n">
-        <f aca="false">TYPE(TRUE())</f>
-        <v>1</v>
+        <f aca="false">_xlfn.LET(_xlpm.x,2,_xlpm.x*3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17572,8 +17905,8 @@
         <v>1362</v>
       </c>
       <c r="L1365" s="0" t="n">
-        <f aca="false">TYPE(H1)</f>
-        <v>16</v>
+        <f aca="false">_xlfn.LET(_xlpm.x,A1:A6,SUM(_xlpm.x))</f>
+        <v>21</v>
       </c>
     </row>
     <row r="1366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17581,242 +17914,242 @@
         <v>1363</v>
       </c>
       <c r="L1366" s="0" t="n">
-        <f aca="false">TYPE({1,2})</f>
-        <v>64</v>
+        <f aca="false">_xlfn.LET(_xlpm.x,A2,_xlpm.y,_xlpm.x*10,_xlpm.y+1)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="1367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1367" s="0" t="s">
         <v>1364</v>
       </c>
-      <c r="L1367" s="0" t="e">
-        <f aca="false">TYPE(A1:A2)</f>
-        <v>#VALUE!</v>
+      <c r="L1367" s="0" t="n">
+        <f aca="false">_xlfn.LET(_xlpm.n,COUNT(C1:C6),_xlpm.n*2)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1368" s="0" t="s">
         <v>1365</v>
       </c>
-      <c r="L1368" s="0" t="n">
-        <f aca="false">TYPE(A1)</f>
-        <v>1</v>
+      <c r="L1368" s="0" t="e">
+        <f aca="false">_xlfn.lambda(_xlpm.x,_xlpm.x+1)(2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1369" s="0" t="s">
         <v>1366</v>
       </c>
-      <c r="L1369" s="0" t="n">
-        <f aca="false">TYPE(B1)</f>
-        <v>2</v>
+      <c r="L1369" s="0" t="e">
+        <f aca="false">_xlfn.lambda(_xlpm.x,_xlpm.y,_xlpm.x*_xlpm.y)(A2,A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1370" s="0" t="s">
         <v>1367</v>
       </c>
-      <c r="L1370" s="0" t="n">
-        <f aca="true">CELL("row",A5)</f>
-        <v>5</v>
+      <c r="L1370" s="0" t="e">
+        <f aca="false">_xlfn.LET(_xlpm.f,_xlfn.lambda(_xlpm.v,_xlpm.v*2),_xlpm.f(A4))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1371" s="0" t="s">
         <v>1368</v>
       </c>
-      <c r="L1371" s="0" t="n">
-        <f aca="true">CELL("col",C1)</f>
-        <v>3</v>
+      <c r="L1371" s="0" t="e">
+        <f aca="false">IFERROR(_xlfn.lambda(_xlpm.x,_xlpm.x)(1,2),"err")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1372" s="0" t="s">
         <v>1369</v>
       </c>
-      <c r="L1372" s="0" t="str">
-        <f aca="true">CELL("address",B2)</f>
-        <v>$B$2</v>
+      <c r="L1372" s="0" t="e">
+        <f aca="false">SUM(_xlfn.map(A1:A3,_xlfn.lambda(_xlpm.v,_xlpm.v*_xlpm.v)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1373" s="0" t="s">
         <v>1370</v>
       </c>
-      <c r="L1373" s="0" t="n">
-        <f aca="true">CELL("contents",A3)</f>
-        <v>3</v>
+      <c r="L1373" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.map(A1:A6,_xlfn.lambda(_xlpm.v,_xlpm.v+1)),6)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1374" s="0" t="s">
         <v>1371</v>
       </c>
-      <c r="L1374" s="0" t="str">
-        <f aca="true">CELL("type",B1)</f>
-        <v>l</v>
+      <c r="L1374" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.map(A1:A6,_xlfn.lambda(_xlpm.v,_xlpm.v)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1375" s="0" t="s">
         <v>1372</v>
       </c>
-      <c r="L1375" s="0" t="str">
-        <f aca="true">CELL("type",A1)</f>
-        <v>v</v>
+      <c r="L1375" s="0" t="e">
+        <f aca="false">SUM(_xlfn.map(A1:A2,F1:F2,_xlfn.lambda(_xlpm.a,_xlpm.b,_xlpm.a*_xlpm.b)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1376" s="0" t="s">
         <v>1373</v>
       </c>
-      <c r="L1376" s="0" t="str">
-        <f aca="true">CELL("type",J9)</f>
-        <v>b</v>
+      <c r="L1376" s="0" t="e">
+        <f aca="false">_xlfn.reduce(0,A1:A6,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a+_xlpm.v))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1377" s="0" t="s">
         <v>1374</v>
       </c>
-      <c r="L1377" s="1" t="b">
-        <f aca="false">ISERR(H1)</f>
-        <v>1</v>
+      <c r="L1377" s="0" t="e">
+        <f aca="false">_xlfn.reduce(1,A1:A4,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a*_xlpm.v))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1378" s="0" t="s">
         <v>1375</v>
       </c>
-      <c r="L1378" s="1" t="b">
-        <f aca="false">ISERR(H2)</f>
-        <v>0</v>
+      <c r="L1378" s="0" t="e">
+        <f aca="false">_xlfn.reduce("x",B1:B2,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a&amp;_xlpm.v))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1379" s="0" t="s">
         <v>1376</v>
       </c>
-      <c r="L1379" s="1" t="b">
-        <f aca="false">ISERR(1)</f>
-        <v>0</v>
+      <c r="L1379" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.reduce(0,A1:A3,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlfn.vstack(_xlpm.a,_xlpm.v))))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1380" s="0" t="s">
         <v>1377</v>
       </c>
-      <c r="L1380" s="1" t="b">
-        <f aca="false">ISERR(1/0)</f>
-        <v>1</v>
+      <c r="L1380" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.scan(0,A1:A6,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a+_xlpm.v)),6)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1381" s="0" t="s">
         <v>1378</v>
       </c>
-      <c r="L1381" s="1" t="b">
-        <f aca="false">ISNONTEXT(1)</f>
-        <v>1</v>
+      <c r="L1381" s="0" t="e">
+        <f aca="false">SUM(_xlfn.scan(0,A1:A3,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a+_xlpm.v)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1382" s="0" t="s">
         <v>1379</v>
       </c>
-      <c r="L1382" s="1" t="b">
-        <f aca="false">ISNONTEXT("a")</f>
-        <v>0</v>
+      <c r="L1382" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.scan(1,A1:A4,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a*_xlpm.v)),4)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1383" s="0" t="s">
         <v>1380</v>
       </c>
-      <c r="L1383" s="1" t="b">
-        <f aca="false">ISNONTEXT(J9)</f>
-        <v>1</v>
+      <c r="L1383" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.scan(0,A1:A6,_xlfn.lambda(_xlpm.a,_xlpm.v,_xlpm.a+_xlpm.v)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1384" s="0" t="s">
         <v>1381</v>
       </c>
-      <c r="L1384" s="1" t="b">
-        <f aca="false">ISNONTEXT(H1)</f>
-        <v>1</v>
+      <c r="L1384" s="0" t="e">
+        <f aca="false">SUM(_xlfn.byrow(A1:C2,_xlfn.lambda(_xlpm.rw,COUNT(_xlpm.rw))))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1385" s="0" t="s">
         <v>1382</v>
       </c>
-      <c r="L1385" s="1" t="b">
-        <f aca="false">ISREF(A1)</f>
-        <v>1</v>
+      <c r="L1385" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.byrow(A1:A3,_xlfn.lambda(_xlpm.rw,_xlpm.rw*2)),3)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1386" s="0" t="s">
         <v>1383</v>
       </c>
-      <c r="L1386" s="1" t="b">
-        <f aca="false">ISREF(1)</f>
-        <v>0</v>
+      <c r="L1386" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.byrow(A1:C6,_xlfn.lambda(_xlpm.rw,1)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1387" s="0" t="s">
         <v>1384</v>
       </c>
-      <c r="L1387" s="1" t="b">
-        <f aca="false">ISREF(A1:B2)</f>
-        <v>1</v>
+      <c r="L1387" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.byrow(F1:F4,_xlfn.lambda(_xlpm.rw,_xlpm.rw/100)),4)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1388" s="0" t="s">
         <v>1385</v>
       </c>
-      <c r="L1388" s="1" t="b">
-        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
-        <v>1</v>
+      <c r="L1388" s="0" t="e">
+        <f aca="false">SUM(_xlfn.bycol(A1:C6,_xlfn.lambda(_xlpm.cl,COUNT(_xlpm.cl))))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1389" s="0" t="s">
         <v>1386</v>
       </c>
-      <c r="L1389" s="1" t="b">
-        <f aca="false">ISREF("A1")</f>
-        <v>0</v>
+      <c r="L1389" s="0" t="e">
+        <f aca="false">COLUMNS(_xlfn.bycol(A1:C1,_xlfn.lambda(_xlpm.cl,1)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1390" s="0" t="s">
         <v>1387</v>
       </c>
-      <c r="L1390" s="0" t="n">
-        <f aca="false">SEARCH("an","banana")</f>
-        <v>2</v>
+      <c r="L1390" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.bycol(A1:C6,_xlfn.lambda(_xlpm.cl,MAX(_xlpm.cl))),3)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1391" s="0" t="s">
         <v>1388</v>
       </c>
-      <c r="L1391" s="0" t="n">
-        <f aca="false">SEARCH("AN","banana",3)</f>
-        <v>4</v>
+      <c r="L1391" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.bycol(A1:A6,_xlfn.lambda(_xlpm.cl,SUM(_xlpm.cl))),1)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1392" s="0" t="s">
         <v>1389</v>
       </c>
-      <c r="L1392" s="0" t="n">
-        <f aca="false">SEARCH("b?n","banana")</f>
-        <v>1</v>
+      <c r="L1392" s="0" t="e">
+        <f aca="false">SUM(_xlfn.makearray(2,3,_xlfn.lambda(_xlpm.i,_xlpm.j,_xlpm.i*_xlpm.j)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17824,53 +18157,53 @@
         <v>1390</v>
       </c>
       <c r="L1393" s="0" t="e">
-        <f aca="false">SEARCH("z","banana")</f>
-        <v>#VALUE!</v>
+        <f aca="false">INDEX(_xlfn.makearray(3,3,_xlfn.lambda(_xlpm.i,_xlpm.j,_xlpm.i*10+_xlpm.j)),2,3)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1394" s="0" t="s">
         <v>1391</v>
       </c>
-      <c r="L1394" s="0" t="n">
-        <f aca="false">SEARCH("a*a","banana")</f>
-        <v>2</v>
+      <c r="L1394" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.makearray(4,2,_xlfn.lambda(_xlpm.i,_xlpm.j,0)))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1395" s="0" t="s">
         <v>1392</v>
       </c>
-      <c r="L1395" s="0" t="n">
-        <f aca="false">SEARCH("~?","what?")</f>
-        <v>5</v>
+      <c r="L1395" s="0" t="e">
+        <f aca="false">_xlfn.makearray(0,1,_xlfn.lambda(_xlpm.i,_xlpm.j,1))</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="1396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1396" s="0" t="s">
         <v>1393</v>
       </c>
-      <c r="L1396" s="0" t="str">
-        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
-        <v>abXYef</v>
+      <c r="L1396" s="0" t="e">
+        <f aca="false">_xlfn.lambda(_xlpm.x,_xlpm.y,_xlfn.isomitted(_xlpm.y))(1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1397" s="0" t="s">
         <v>1394</v>
       </c>
-      <c r="L1397" s="0" t="str">
-        <f aca="false">REPLACE("abc",5,1,"Z")</f>
-        <v>abcZ</v>
+      <c r="L1397" s="0" t="e">
+        <f aca="false">_xlfn.lambda(_xlpm.x,_xlpm.y,_xlfn.isomitted(_xlpm.y))(1,2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1398" s="0" t="s">
         <v>1395</v>
       </c>
-      <c r="L1398" s="0" t="str">
-        <f aca="false">REPLACE("abc",1,0,"Z")</f>
-        <v>Zabc</v>
+      <c r="L1398" s="0" t="e">
+        <f aca="false">_xlfn.LET(_xlpm.f,_xlfn.lambda(_xlpm.a,_xlpm.b,IF(_xlfn.isomitted(_xlpm.b),_xlpm.a,_xlpm.a+_xlpm.b)),_xlpm.f(5))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17878,7 +18211,7 @@
         <v>1396</v>
       </c>
       <c r="L1399" s="0" t="e">
-        <f aca="false">REPLACE("abc",0,1,"Z")</f>
+        <f aca="false">_xlfn.LET(_xlpm.f,_xlfn.lambda(_xlpm.a,_xlpm.b,IF(_xlfn.isomitted(_xlpm.b),_xlpm.a,_xlpm.a+_xlpm.b)),_xlpm.f(5,1))</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -17886,162 +18219,162 @@
       <c r="K1400" s="0" t="s">
         <v>1397</v>
       </c>
-      <c r="L1400" s="0" t="str">
-        <f aca="false">REPLACE(B1,1,1,"A")</f>
-        <v>Apple</v>
+      <c r="L1400" s="1" t="b">
+        <f aca="false">ISLOGICAL(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1401" s="0" t="s">
         <v>1398</v>
       </c>
-      <c r="L1401" s="0" t="str">
-        <f aca="false">REPT("ab",3)</f>
-        <v>ababab</v>
+      <c r="L1401" s="1" t="b">
+        <f aca="false">ISLOGICAL(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1402" s="0" t="s">
         <v>1399</v>
       </c>
-      <c r="L1402" s="0" t="str">
-        <f aca="false">REPT("x",0)</f>
-        <v/>
+      <c r="L1402" s="1" t="b">
+        <f aca="false">ISLOGICAL("TRUE")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1403" s="0" t="s">
         <v>1400</v>
       </c>
-      <c r="L1403" s="0" t="e">
-        <f aca="false">REPT("x",-1)</f>
-        <v>#VALUE!</v>
+      <c r="L1403" s="1" t="b">
+        <f aca="false">ISLOGICAL(1=1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1404" s="0" t="s">
         <v>1401</v>
       </c>
-      <c r="L1404" s="0" t="str">
-        <f aca="false">REPT(A1,3)</f>
-        <v>111</v>
+      <c r="L1404" s="1" t="b">
+        <f aca="false">ISEVEN(2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1405" s="0" t="s">
         <v>1402</v>
       </c>
-      <c r="L1405" s="0" t="str">
-        <f aca="false">REPT("-",2.9)</f>
-        <v>--</v>
+      <c r="L1405" s="1" t="b">
+        <f aca="false">ISEVEN(3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1406" s="0" t="s">
         <v>1403</v>
       </c>
-      <c r="L1406" s="0" t="str">
-        <f aca="false">PROPER("hello world")</f>
-        <v>Hello World</v>
+      <c r="L1406" s="1" t="b">
+        <f aca="false">ISEVEN(-2.9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1407" s="0" t="s">
         <v>1404</v>
       </c>
-      <c r="L1407" s="0" t="str">
-        <f aca="false">PROPER("o'neil mc-donald")</f>
-        <v>O'Neil Mc-Donald</v>
+      <c r="L1407" s="1" t="e">
+        <f aca="false">ISEVEN("a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1408" s="0" t="s">
         <v>1405</v>
       </c>
-      <c r="L1408" s="0" t="str">
-        <f aca="false">PROPER("2nd place")</f>
-        <v>2Nd Place</v>
+      <c r="L1408" s="1" t="b">
+        <f aca="false">ISEVEN(A2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1409" s="0" t="s">
         <v>1406</v>
       </c>
-      <c r="L1409" s="0" t="str">
-        <f aca="false">PROPER(B1)</f>
-        <v>Apple</v>
+      <c r="L1409" s="1" t="b">
+        <f aca="false">ISODD(2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1410" s="0" t="s">
         <v>1407</v>
       </c>
-      <c r="L1410" s="0" t="str">
-        <f aca="false">PROPER("ÀB cD")</f>
-        <v>Àb Cd</v>
+      <c r="L1410" s="1" t="b">
+        <f aca="false">ISODD(3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1411" s="0" t="s">
         <v>1408</v>
       </c>
-      <c r="L1411" s="0" t="str">
-        <f aca="false">CHAR(65)</f>
-        <v>A</v>
+      <c r="L1411" s="1" t="b">
+        <f aca="false">ISODD(-3.5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1412" s="0" t="s">
         <v>1409</v>
       </c>
-      <c r="L1412" s="0" t="str">
-        <f aca="false">CHAR(97)</f>
-        <v>a</v>
+      <c r="L1412" s="1" t="e">
+        <f aca="false">ISODD("a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1413" s="0" t="s">
         <v>1410</v>
       </c>
-      <c r="L1413" s="0" t="str">
-        <f aca="false">CHAR(0)</f>
-        <v>_x0000_</v>
+      <c r="L1413" s="1" t="b">
+        <f aca="false">ISODD(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1414" s="0" t="s">
         <v>1411</v>
       </c>
-      <c r="L1414" s="0" t="e">
-        <f aca="false">CHAR(256)</f>
-        <v>#VALUE!</v>
+      <c r="L1414" s="0" t="n">
+        <f aca="false">N(5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1415" s="0" t="s">
         <v>1412</v>
       </c>
-      <c r="L1415" s="0" t="str">
-        <f aca="false">CHAR(169)</f>
-        <v>�</v>
+      <c r="L1415" s="0" t="n">
+        <f aca="false">N("a")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1416" s="0" t="s">
         <v>1413</v>
       </c>
-      <c r="L1416" s="0" t="str">
-        <f aca="false">CHAR(233)</f>
-        <v>�</v>
+      <c r="L1416" s="0" t="n">
+        <f aca="false">N(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1417" s="0" t="s">
         <v>1414</v>
       </c>
-      <c r="L1417" s="0" t="n">
-        <f aca="false">CODE("A")</f>
-        <v>65</v>
+      <c r="L1417" s="0" t="e">
+        <f aca="false">N(H1)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18049,8 +18382,8 @@
         <v>1415</v>
       </c>
       <c r="L1418" s="0" t="n">
-        <f aca="false">CODE("apple")</f>
-        <v>97</v>
+        <f aca="false">N(B1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18058,53 +18391,53 @@
         <v>1416</v>
       </c>
       <c r="L1419" s="0" t="n">
-        <f aca="false">CODE("")</f>
-        <v>0</v>
+        <f aca="false">N(A3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1420" s="0" t="s">
         <v>1417</v>
       </c>
-      <c r="L1420" s="0" t="n">
-        <f aca="false">CODE("é")</f>
-        <v>195</v>
+      <c r="L1420" s="0" t="str">
+        <f aca="false">T("a")</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1421" s="0" t="s">
         <v>1418</v>
       </c>
-      <c r="L1421" s="0" t="n">
-        <f aca="false">CODE(B1)</f>
-        <v>97</v>
+      <c r="L1421" s="0" t="str">
+        <f aca="false">T(5)</f>
+        <v/>
       </c>
     </row>
     <row r="1422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1422" s="0" t="s">
         <v>1419</v>
       </c>
-      <c r="L1422" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE("A")</f>
-        <v>65</v>
+      <c r="L1422" s="0" t="str">
+        <f aca="false">T(B1)</f>
+        <v>apple</v>
       </c>
     </row>
     <row r="1423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1423" s="0" t="s">
         <v>1420</v>
       </c>
-      <c r="L1423" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE("€")</f>
-        <v>8364</v>
+      <c r="L1423" s="0" t="e">
+        <f aca="false">T(H2)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1424" s="0" t="s">
         <v>1421</v>
       </c>
-      <c r="L1424" s="0" t="e">
-        <f aca="false">_xlfn.UNICODE("")</f>
-        <v>#VALUE!</v>
+      <c r="L1424" s="0" t="str">
+        <f aca="false">T(TRUE())</f>
+        <v/>
       </c>
     </row>
     <row r="1425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18112,98 +18445,98 @@
         <v>1422</v>
       </c>
       <c r="L1425" s="0" t="n">
-        <f aca="false">_xlfn.UNICODE(B2)</f>
-        <v>98</v>
+        <f aca="false">TYPE(1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1426" s="0" t="s">
         <v>1423</v>
       </c>
-      <c r="L1426" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(65)</f>
-        <v>A</v>
+      <c r="L1426" s="0" t="n">
+        <f aca="false">TYPE("a")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1427" s="0" t="s">
         <v>1424</v>
       </c>
-      <c r="L1427" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(8364)</f>
-        <v>€</v>
+      <c r="L1427" s="0" t="n">
+        <f aca="false">TYPE(TRUE())</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1428" s="0" t="s">
         <v>1425</v>
       </c>
-      <c r="L1428" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(0)</f>
-        <v>_x0000_</v>
+      <c r="L1428" s="0" t="n">
+        <f aca="false">TYPE(H1)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="1429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1429" s="0" t="s">
         <v>1426</v>
       </c>
-      <c r="L1429" s="0" t="str">
-        <f aca="false">_xlfn.UNICHAR(97)</f>
-        <v>a</v>
+      <c r="L1429" s="0" t="n">
+        <f aca="false">TYPE({1,2})</f>
+        <v>64</v>
       </c>
     </row>
     <row r="1430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1430" s="0" t="s">
         <v>1427</v>
       </c>
-      <c r="L1430" s="0" t="str">
-        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
-        <v>ab</v>
+      <c r="L1430" s="0" t="e">
+        <f aca="false">TYPE(A1:A2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1431" s="0" t="s">
         <v>1428</v>
       </c>
-      <c r="L1431" s="0" t="str">
-        <f aca="false">CLEAN(B1)</f>
-        <v>apple</v>
+      <c r="L1431" s="0" t="n">
+        <f aca="false">TYPE(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1432" s="0" t="s">
         <v>1429</v>
       </c>
-      <c r="L1432" s="0" t="str">
-        <f aca="false">CLEAN("  x ")</f>
-        <v>  x </v>
+      <c r="L1432" s="0" t="n">
+        <f aca="false">TYPE(B1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1433" s="0" t="s">
         <v>1430</v>
       </c>
-      <c r="L1433" s="0" t="str">
-        <f aca="false">CLEAN(A1)</f>
-        <v>1</v>
+      <c r="L1433" s="0" t="n">
+        <f aca="true">CELL("row",A5)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1434" s="0" t="s">
         <v>1431</v>
       </c>
-      <c r="L1434" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
-        <v>#VALUE!</v>
+      <c r="L1434" s="0" t="n">
+        <f aca="true">CELL("col",C1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1435" s="0" t="s">
         <v>1432</v>
       </c>
-      <c r="L1435" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
-        <v>1234.5</v>
+      <c r="L1435" s="0" t="str">
+        <f aca="true">CELL("address",B2)</f>
+        <v>$B$2</v>
       </c>
     </row>
     <row r="1436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18211,161 +18544,161 @@
         <v>1433</v>
       </c>
       <c r="L1436" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
-        <v>0.05</v>
+        <f aca="true">CELL("contents",A3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1437" s="0" t="s">
         <v>1434</v>
       </c>
-      <c r="L1437" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("")</f>
-        <v>#VALUE!</v>
+      <c r="L1437" s="0" t="str">
+        <f aca="true">CELL("type",B1)</f>
+        <v>l</v>
       </c>
     </row>
     <row r="1438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1438" s="0" t="s">
         <v>1435</v>
       </c>
-      <c r="L1438" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
-        <v>#VALUE!</v>
+      <c r="L1438" s="0" t="str">
+        <f aca="true">CELL("type",A1)</f>
+        <v>v</v>
       </c>
     </row>
     <row r="1439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1439" s="0" t="s">
         <v>1436</v>
       </c>
-      <c r="L1439" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
-        <v>0.0001</v>
+      <c r="L1439" s="0" t="str">
+        <f aca="true">CELL("type",J9)</f>
+        <v>b</v>
       </c>
     </row>
     <row r="1440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1440" s="0" t="s">
         <v>1437</v>
       </c>
-      <c r="L1440" s="0" t="e">
-        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
-        <v>#VALUE!</v>
+      <c r="L1440" s="1" t="b">
+        <f aca="false">ISERR(H1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1441" s="0" t="s">
         <v>1438</v>
       </c>
-      <c r="L1441" s="0" t="n">
-        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
-        <v>12</v>
+      <c r="L1441" s="1" t="b">
+        <f aca="false">ISERR(H2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1442" s="0" t="s">
         <v>1439</v>
       </c>
-      <c r="L1442" s="0" t="str">
-        <f aca="false">FIXED(1234.567,1)</f>
-        <v>1,234.6</v>
+      <c r="L1442" s="1" t="b">
+        <f aca="false">ISERR(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1443" s="0" t="s">
         <v>1440</v>
       </c>
-      <c r="L1443" s="0" t="str">
-        <f aca="false">FIXED(1234.567,-1)</f>
-        <v>1,230</v>
+      <c r="L1443" s="1" t="b">
+        <f aca="false">ISERR(1/0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1444" s="0" t="s">
         <v>1441</v>
       </c>
-      <c r="L1444" s="0" t="str">
-        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
-        <v>-1234.57</v>
+      <c r="L1444" s="1" t="b">
+        <f aca="false">ISNONTEXT(1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1445" s="0" t="s">
         <v>1442</v>
       </c>
-      <c r="L1445" s="0" t="str">
-        <f aca="false">FIXED(0.5,0)</f>
-        <v>1</v>
+      <c r="L1445" s="1" t="b">
+        <f aca="false">ISNONTEXT("a")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1446" s="0" t="s">
         <v>1443</v>
       </c>
-      <c r="L1446" s="0" t="str">
-        <f aca="false">FIXED(1234567)</f>
-        <v>1,234,567.00</v>
+      <c r="L1446" s="1" t="b">
+        <f aca="false">ISNONTEXT(J9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1447" s="0" t="s">
         <v>1444</v>
       </c>
-      <c r="L1447" s="0" t="str">
-        <f aca="false">FIXED(A1)</f>
-        <v>1.00</v>
+      <c r="L1447" s="1" t="b">
+        <f aca="false">ISNONTEXT(H1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1448" s="0" t="s">
         <v>1445</v>
       </c>
-      <c r="L1448" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
-        <v>apple,banana,cherry</v>
+      <c r="L1448" s="1" t="b">
+        <f aca="false">ISREF(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1449" s="0" t="s">
         <v>1446</v>
       </c>
-      <c r="L1449" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
-        <v>1-2-3</v>
+      <c r="L1449" s="1" t="b">
+        <f aca="false">ISREF(1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1450" s="0" t="s">
         <v>1447</v>
       </c>
-      <c r="L1450" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
-        <v>a, b</v>
+      <c r="L1450" s="1" t="b">
+        <f aca="false">ISREF(A1:B2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1451" s="0" t="s">
         <v>1448</v>
       </c>
-      <c r="L1451" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
-        <v>a,,b</v>
+      <c r="L1451" s="1" t="b">
+        <f aca="false">ISREF(INDEX(A1:A3,2))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1452" s="0" t="s">
         <v>1449</v>
       </c>
-      <c r="L1452" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
-        <v>applebanana!</v>
+      <c r="L1452" s="1" t="b">
+        <f aca="false">ISREF("A1")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1453" s="0" t="s">
         <v>1450</v>
       </c>
-      <c r="L1453" s="0" t="e">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
-        <v>#DIV/0!</v>
+      <c r="L1453" s="0" t="n">
+        <f aca="false">SEARCH("an","banana")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18373,8 +18706,8 @@
         <v>1451</v>
       </c>
       <c r="L1454" s="0" t="n">
-        <f aca="false">DATEVALUE("2024-01-15")</f>
-        <v>45306</v>
+        <f aca="false">SEARCH("AN","banana",3)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18382,62 +18715,62 @@
         <v>1452</v>
       </c>
       <c r="L1455" s="0" t="n">
-        <f aca="false">DATEVALUE("1/15/2024")</f>
-        <v>45306</v>
+        <f aca="false">SEARCH("b?n","banana")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1456" s="0" t="s">
         <v>1453</v>
       </c>
-      <c r="L1456" s="0" t="n">
-        <f aca="false">DATEVALUE("2024-12-31")</f>
-        <v>45657</v>
+      <c r="L1456" s="0" t="e">
+        <f aca="false">SEARCH("z","banana")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1457" s="0" t="s">
         <v>1454</v>
       </c>
-      <c r="L1457" s="0" t="e">
-        <f aca="false">DATEVALUE("abc")</f>
-        <v>#VALUE!</v>
+      <c r="L1457" s="0" t="n">
+        <f aca="false">SEARCH("a*a","banana")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1458" s="0" t="s">
         <v>1455</v>
       </c>
-      <c r="L1458" s="0" t="e">
-        <f aca="false">DATEVALUE(5)</f>
-        <v>#VALUE!</v>
+      <c r="L1458" s="0" t="n">
+        <f aca="false">SEARCH("~?","what?")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1459" s="0" t="s">
         <v>1456</v>
       </c>
-      <c r="L1459" s="0" t="n">
-        <f aca="false">TIMEVALUE("12:00")</f>
-        <v>0.5</v>
+      <c r="L1459" s="0" t="str">
+        <f aca="false">REPLACE("abcdef",3,2,"XY")</f>
+        <v>abXYef</v>
       </c>
     </row>
     <row r="1460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1460" s="0" t="s">
         <v>1457</v>
       </c>
-      <c r="L1460" s="0" t="n">
-        <f aca="false">TIMEVALUE("6:00 PM")</f>
-        <v>0.75</v>
+      <c r="L1460" s="0" t="str">
+        <f aca="false">REPLACE("abc",5,1,"Z")</f>
+        <v>abcZ</v>
       </c>
     </row>
     <row r="1461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1461" s="0" t="s">
         <v>1458</v>
       </c>
-      <c r="L1461" s="0" t="n">
-        <f aca="false">TIMEVALUE("18:30:30")</f>
-        <v>0.771180555555556</v>
+      <c r="L1461" s="0" t="str">
+        <f aca="false">REPLACE("abc",1,0,"Z")</f>
+        <v>Zabc</v>
       </c>
     </row>
     <row r="1462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18445,7 +18778,7 @@
         <v>1459</v>
       </c>
       <c r="L1462" s="0" t="e">
-        <f aca="false">TIMEVALUE("xx")</f>
+        <f aca="false">REPLACE("abc",0,1,"Z")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18453,153 +18786,153 @@
       <c r="K1463" s="0" t="s">
         <v>1460</v>
       </c>
-      <c r="L1463" s="0" t="n">
-        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
-        <v>0.25</v>
+      <c r="L1463" s="0" t="str">
+        <f aca="false">REPLACE(B1,1,1,"A")</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="1464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1464" s="0" t="s">
         <v>1461</v>
       </c>
-      <c r="L1464" s="8" t="n">
-        <f aca="false">TIME(12,0,0)</f>
-        <v>0.5</v>
+      <c r="L1464" s="0" t="str">
+        <f aca="false">REPT("ab",3)</f>
+        <v>ababab</v>
       </c>
     </row>
     <row r="1465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1465" s="0" t="s">
         <v>1462</v>
       </c>
-      <c r="L1465" s="8" t="n">
-        <f aca="false">TIME(25,0,0)</f>
-        <v>0.0416666666666667</v>
+      <c r="L1465" s="0" t="str">
+        <f aca="false">REPT("x",0)</f>
+        <v/>
       </c>
     </row>
     <row r="1466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1466" s="0" t="s">
         <v>1463</v>
       </c>
-      <c r="L1466" s="8" t="n">
-        <f aca="false">TIME(0,90,0)</f>
-        <v>0.0625</v>
+      <c r="L1466" s="0" t="e">
+        <f aca="false">REPT("x",-1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1467" s="0" t="s">
         <v>1464</v>
       </c>
-      <c r="L1467" s="8" t="n">
-        <f aca="false">TIME(1,2,3)</f>
-        <v>0.0430902777777778</v>
+      <c r="L1467" s="0" t="str">
+        <f aca="false">REPT(A1,3)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="1468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1468" s="0" t="s">
         <v>1465</v>
       </c>
-      <c r="L1468" s="8" t="e">
-        <f aca="false">TIME(-1,0,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1468" s="0" t="str">
+        <f aca="false">REPT("-",2.9)</f>
+        <v>--</v>
       </c>
     </row>
     <row r="1469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1469" s="0" t="s">
         <v>1466</v>
       </c>
-      <c r="L1469" s="0" t="n">
-        <f aca="false">HOUR(E3)</f>
-        <v>18</v>
+      <c r="L1469" s="0" t="str">
+        <f aca="false">PROPER("hello world")</f>
+        <v>Hello World</v>
       </c>
     </row>
     <row r="1470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1470" s="0" t="s">
         <v>1467</v>
       </c>
-      <c r="L1470" s="0" t="n">
-        <f aca="false">HOUR(0.5)</f>
-        <v>12</v>
+      <c r="L1470" s="0" t="str">
+        <f aca="false">PROPER("o'neil mc-donald")</f>
+        <v>O'Neil Mc-Donald</v>
       </c>
     </row>
     <row r="1471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1471" s="0" t="s">
         <v>1468</v>
       </c>
-      <c r="L1471" s="0" t="n">
-        <f aca="false">HOUR("18:30")</f>
-        <v>18</v>
+      <c r="L1471" s="0" t="str">
+        <f aca="false">PROPER("2nd place")</f>
+        <v>2Nd Place</v>
       </c>
     </row>
     <row r="1472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1472" s="0" t="s">
         <v>1469</v>
       </c>
-      <c r="L1472" s="0" t="n">
-        <f aca="false">HOUR(-1)</f>
-        <v>0</v>
+      <c r="L1472" s="0" t="str">
+        <f aca="false">PROPER(B1)</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="1473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1473" s="0" t="s">
         <v>1470</v>
       </c>
-      <c r="L1473" s="0" t="n">
-        <f aca="false">MINUTE(E3)</f>
-        <v>0</v>
+      <c r="L1473" s="0" t="str">
+        <f aca="false">PROPER("ÀB cD")</f>
+        <v>Àb Cd</v>
       </c>
     </row>
     <row r="1474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1474" s="0" t="s">
         <v>1471</v>
       </c>
-      <c r="L1474" s="0" t="n">
-        <f aca="false">MINUTE("18:30:45")</f>
-        <v>30</v>
+      <c r="L1474" s="0" t="str">
+        <f aca="false">CHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="1475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1475" s="0" t="s">
         <v>1472</v>
       </c>
-      <c r="L1475" s="0" t="n">
-        <f aca="false">MINUTE(0.7712)</f>
-        <v>30</v>
+      <c r="L1475" s="0" t="str">
+        <f aca="false">CHAR(97)</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1476" s="0" t="s">
         <v>1473</v>
       </c>
-      <c r="L1476" s="0" t="n">
-        <f aca="false">MINUTE(-1)</f>
-        <v>0</v>
+      <c r="L1476" s="0" t="str">
+        <f aca="false">CHAR(0)</f>
+        <v>_x0000_</v>
       </c>
     </row>
     <row r="1477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1477" s="0" t="s">
         <v>1474</v>
       </c>
-      <c r="L1477" s="0" t="n">
-        <f aca="false">SECOND("18:30:45")</f>
-        <v>45</v>
+      <c r="L1477" s="0" t="e">
+        <f aca="false">CHAR(256)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1478" s="0" t="s">
         <v>1475</v>
       </c>
-      <c r="L1478" s="0" t="n">
-        <f aca="false">SECOND(0.5)</f>
-        <v>0</v>
+      <c r="L1478" s="0" t="str">
+        <f aca="false">CHAR(169)</f>
+        <v>�</v>
       </c>
     </row>
     <row r="1479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1479" s="0" t="s">
         <v>1476</v>
       </c>
-      <c r="L1479" s="0" t="n">
-        <f aca="false">SECOND(TIME(1,2,3))</f>
-        <v>3</v>
+      <c r="L1479" s="0" t="str">
+        <f aca="false">CHAR(233)</f>
+        <v>�</v>
       </c>
     </row>
     <row r="1480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18607,8 +18940,8 @@
         <v>1477</v>
       </c>
       <c r="L1480" s="0" t="n">
-        <f aca="false">SECOND(-1)</f>
-        <v>0</v>
+        <f aca="false">CODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="1481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18616,8 +18949,8 @@
         <v>1478</v>
       </c>
       <c r="L1481" s="0" t="n">
-        <f aca="false">EDATE(E1,1)</f>
-        <v>45337</v>
+        <f aca="false">CODE("apple")</f>
+        <v>97</v>
       </c>
     </row>
     <row r="1482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18625,8 +18958,8 @@
         <v>1479</v>
       </c>
       <c r="L1482" s="0" t="n">
-        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
-        <v>45351</v>
+        <f aca="false">CODE("")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18634,8 +18967,8 @@
         <v>1480</v>
       </c>
       <c r="L1483" s="0" t="n">
-        <f aca="false">EDATE(E1,-1)</f>
-        <v>45275</v>
+        <f aca="false">CODE("é")</f>
+        <v>195</v>
       </c>
     </row>
     <row r="1484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18643,8 +18976,8 @@
         <v>1481</v>
       </c>
       <c r="L1484" s="0" t="n">
-        <f aca="false">EDATE(E1,0)</f>
-        <v>45306</v>
+        <f aca="false">CODE(B1)</f>
+        <v>97</v>
       </c>
     </row>
     <row r="1485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18652,8 +18985,8 @@
         <v>1482</v>
       </c>
       <c r="L1485" s="0" t="n">
-        <f aca="false">EDATE(E1,12)</f>
-        <v>45672</v>
+        <f aca="false">_xlfn.UNICODE("A")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="1486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18661,17 +18994,17 @@
         <v>1483</v>
       </c>
       <c r="L1486" s="0" t="n">
-        <f aca="false">EOMONTH(E1,0)</f>
-        <v>45322</v>
+        <f aca="false">_xlfn.UNICODE("€")</f>
+        <v>8364</v>
       </c>
     </row>
     <row r="1487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1487" s="0" t="s">
         <v>1484</v>
       </c>
-      <c r="L1487" s="0" t="n">
-        <f aca="false">EOMONTH(E1,1)</f>
-        <v>45351</v>
+      <c r="L1487" s="0" t="e">
+        <f aca="false">_xlfn.UNICODE("")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18679,89 +19012,89 @@
         <v>1485</v>
       </c>
       <c r="L1488" s="0" t="n">
-        <f aca="false">EOMONTH(E1,-1)</f>
-        <v>45291</v>
+        <f aca="false">_xlfn.UNICODE(B2)</f>
+        <v>98</v>
       </c>
     </row>
     <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1489" s="0" t="s">
         <v>1486</v>
       </c>
-      <c r="L1489" s="0" t="n">
-        <f aca="false">EOMONTH(E2,2)</f>
-        <v>45716</v>
+      <c r="L1489" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(65)</f>
+        <v>A</v>
       </c>
     </row>
     <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1490" s="0" t="s">
         <v>1487</v>
       </c>
-      <c r="L1490" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
-        <v>23</v>
+      <c r="L1490" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(8364)</f>
+        <v>€</v>
       </c>
     </row>
     <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1491" s="0" t="s">
         <v>1488</v>
       </c>
-      <c r="L1491" s="0" t="n">
-        <f aca="false">NETWORKDAYS(E1,E2)</f>
-        <v>252</v>
+      <c r="L1491" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(0)</f>
+        <v>_x0000_</v>
       </c>
     </row>
     <row r="1492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1492" s="0" t="s">
         <v>1489</v>
       </c>
-      <c r="L1492" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
-        <v>22</v>
+      <c r="L1492" s="0" t="str">
+        <f aca="false">_xlfn.UNICHAR(97)</f>
+        <v>a</v>
       </c>
     </row>
     <row r="1493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1493" s="0" t="s">
         <v>1490</v>
       </c>
-      <c r="L1493" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
-        <v>-23</v>
+      <c r="L1493" s="0" t="str">
+        <f aca="false">CLEAN("a"&amp;CHAR(7)&amp;"b")</f>
+        <v>ab</v>
       </c>
     </row>
     <row r="1494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1494" s="0" t="s">
         <v>1491</v>
       </c>
-      <c r="L1494" s="0" t="n">
-        <f aca="false">NETWORKDAYS(E1,E1)</f>
-        <v>1</v>
+      <c r="L1494" s="0" t="str">
+        <f aca="false">CLEAN(B1)</f>
+        <v>apple</v>
       </c>
     </row>
     <row r="1495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1495" s="0" t="s">
         <v>1492</v>
       </c>
-      <c r="L1495" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
-        <v>27</v>
+      <c r="L1495" s="0" t="str">
+        <f aca="false">CLEAN("  x ")</f>
+        <v>  x </v>
       </c>
     </row>
     <row r="1496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1496" s="0" t="s">
         <v>1493</v>
       </c>
-      <c r="L1496" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
-        <v>23</v>
+      <c r="L1496" s="0" t="str">
+        <f aca="false">CLEAN(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1497" s="0" t="s">
         <v>1494</v>
       </c>
-      <c r="L1497" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
-        <v>22</v>
+      <c r="L1497" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1,234.5")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18769,35 +19102,35 @@
         <v>1495</v>
       </c>
       <c r="L1498" s="0" t="n">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
-        <v>22</v>
+        <f aca="false">_xlfn.NUMBERVALUE("1.234,5",",",".")</f>
+        <v>1234.5</v>
       </c>
     </row>
     <row r="1499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1499" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="L1499" s="0" t="e">
-        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
-        <v>#VALUE!</v>
+      <c r="L1499" s="0" t="n">
+        <f aca="false">_xlfn.NUMBERVALUE("5%")</f>
+        <v>0.05</v>
       </c>
     </row>
     <row r="1500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1500" s="0" t="s">
         <v>1497</v>
       </c>
-      <c r="L1500" s="0" t="n">
-        <f aca="false">WORKDAY(E1,1)</f>
-        <v>45307</v>
+      <c r="L1500" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1501" s="0" t="s">
         <v>1498</v>
       </c>
-      <c r="L1501" s="0" t="n">
-        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
-        <v>45313</v>
+      <c r="L1501" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18805,17 +19138,17 @@
         <v>1499</v>
       </c>
       <c r="L1502" s="0" t="n">
-        <f aca="false">WORKDAY(E1,-1)</f>
-        <v>45303</v>
+        <f aca="false">_xlfn.NUMBERVALUE("1%%")</f>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="1503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1503" s="0" t="s">
         <v>1500</v>
       </c>
-      <c r="L1503" s="0" t="n">
-        <f aca="false">WORKDAY(E1,5,E1+1)</f>
-        <v>45314</v>
+      <c r="L1503" s="0" t="e">
+        <f aca="false">_xlfn.NUMBERVALUE("1.5",".",".")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18823,107 +19156,107 @@
         <v>1501</v>
       </c>
       <c r="L1504" s="0" t="n">
-        <f aca="false">WORKDAY(E1,0)</f>
-        <v>45306</v>
+        <f aca="false">_xlfn.NUMBERVALUE(" 12 ")</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1505" s="0" t="s">
         <v>1502</v>
       </c>
-      <c r="L1505" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
-        <v>45307</v>
+      <c r="L1505" s="0" t="str">
+        <f aca="false">FIXED(1234.567,1)</f>
+        <v>1,234.6</v>
       </c>
     </row>
     <row r="1506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1506" s="0" t="s">
         <v>1503</v>
       </c>
-      <c r="L1506" s="3" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
-        <v>45313</v>
+      <c r="L1506" s="0" t="str">
+        <f aca="false">FIXED(1234.567,-1)</f>
+        <v>1,230</v>
       </c>
     </row>
     <row r="1507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1507" s="0" t="s">
         <v>1504</v>
       </c>
-      <c r="L1507" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
-        <v>45313</v>
+      <c r="L1507" s="0" t="str">
+        <f aca="false">FIXED(-1234.567,2,TRUE())</f>
+        <v>-1234.57</v>
       </c>
     </row>
     <row r="1508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1508" s="0" t="s">
         <v>1505</v>
       </c>
-      <c r="L1508" s="2" t="n">
-        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
-        <v>45303</v>
+      <c r="L1508" s="0" t="str">
+        <f aca="false">FIXED(0.5,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1509" s="0" t="s">
         <v>1506</v>
       </c>
-      <c r="L1509" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
-        <v>4</v>
+      <c r="L1509" s="0" t="str">
+        <f aca="false">FIXED(1234567)</f>
+        <v>1,234,567.00</v>
       </c>
     </row>
     <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1510" s="0" t="s">
         <v>1507</v>
       </c>
-      <c r="L1510" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
-        <v>48</v>
+      <c r="L1510" s="0" t="str">
+        <f aca="false">FIXED(A1)</f>
+        <v>1.00</v>
       </c>
     </row>
     <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1511" s="0" t="s">
         <v>1508</v>
       </c>
-      <c r="L1511" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
-        <v>1461</v>
+      <c r="L1511" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),B1:B3)</f>
+        <v>apple,banana,cherry</v>
       </c>
     </row>
     <row r="1512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1512" s="0" t="s">
         <v>1509</v>
       </c>
-      <c r="L1512" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
-        <v>5</v>
+      <c r="L1512" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",FALSE(),A1:A3)</f>
+        <v>1-2-3</v>
       </c>
     </row>
     <row r="1513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1513" s="0" t="s">
         <v>1510</v>
       </c>
-      <c r="L1513" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
-        <v>6</v>
+      <c r="L1513" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(", ",TRUE(),"a","","b")</f>
+        <v>a, b</v>
       </c>
     </row>
     <row r="1514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1514" s="0" t="s">
         <v>1511</v>
       </c>
-      <c r="L1514" s="0" t="n">
-        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
-        <v>209</v>
+      <c r="L1514" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",FALSE(),"a","","b")</f>
+        <v>a,,b</v>
       </c>
     </row>
     <row r="1515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1515" s="0" t="s">
         <v>1512</v>
       </c>
-      <c r="L1515" s="0" t="e">
-        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
-        <v>#VALUE!</v>
+      <c r="L1515" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("",TRUE(),B1:B2,"!")</f>
+        <v>applebanana!</v>
       </c>
     </row>
     <row r="1516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18931,8 +19264,8 @@
         <v>1513</v>
       </c>
       <c r="L1516" s="0" t="e">
-        <f aca="false">DATEDIF(E1,E2,"X")</f>
-        <v>#VALUE!</v>
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),H1,"a")</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="1517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18940,8 +19273,8 @@
         <v>1514</v>
       </c>
       <c r="L1517" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
-        <v>0.5</v>
+        <f aca="false">DATEVALUE("2024-01-15")</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18949,8 +19282,8 @@
         <v>1515</v>
       </c>
       <c r="L1518" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
-        <v>0.495890410958904</v>
+        <f aca="false">DATEVALUE("1/15/2024")</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18958,26 +19291,26 @@
         <v>1516</v>
       </c>
       <c r="L1519" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
-        <v>0.502777777777778</v>
+        <f aca="false">DATEVALUE("2024-12-31")</f>
+        <v>45657</v>
       </c>
     </row>
     <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1520" s="0" t="s">
         <v>1517</v>
       </c>
-      <c r="L1520" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
-        <v>0.495890410958904</v>
+      <c r="L1520" s="0" t="e">
+        <f aca="false">DATEVALUE("abc")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1521" s="0" t="s">
         <v>1518</v>
       </c>
-      <c r="L1521" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
-        <v>0.5</v>
+      <c r="L1521" s="0" t="e">
+        <f aca="false">DATEVALUE(5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18985,8 +19318,8 @@
         <v>1519</v>
       </c>
       <c r="L1522" s="0" t="n">
-        <f aca="false">YEARFRAC(E1,E2)</f>
-        <v>0.961111111111111</v>
+        <f aca="false">TIMEVALUE("12:00")</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18994,8 +19327,8 @@
         <v>1520</v>
       </c>
       <c r="L1523" s="0" t="n">
-        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
-        <v>3.99835796387521</v>
+        <f aca="false">TIMEVALUE("6:00 PM")</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19003,8 +19336,8 @@
         <v>1521</v>
       </c>
       <c r="L1524" s="0" t="n">
-        <f aca="false">YEARFRAC(E2,E1)</f>
-        <v>0.961111111111111</v>
+        <f aca="false">TIMEVALUE("18:30:30")</f>
+        <v>0.771180555555556</v>
       </c>
     </row>
     <row r="1525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19012,7 +19345,7 @@
         <v>1522</v>
       </c>
       <c r="L1525" s="0" t="e">
-        <f aca="false">YEARFRAC(E1,E2,5)</f>
+        <f aca="false">TIMEVALUE("xx")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -19021,52 +19354,52 @@
         <v>1523</v>
       </c>
       <c r="L1526" s="0" t="n">
-        <f aca="false">WEEKNUM(E1,1)</f>
-        <v>3</v>
+        <f aca="false">TIMEVALUE("2024-01-15 06:00")</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="1527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1527" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="L1527" s="0" t="n">
-        <f aca="false">WEEKNUM(E1,2)</f>
-        <v>3</v>
+      <c r="L1527" s="8" t="n">
+        <f aca="false">TIME(12,0,0)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1528" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="L1528" s="0" t="n">
-        <f aca="false">WEEKNUM(E2,1)</f>
-        <v>1</v>
+      <c r="L1528" s="8" t="n">
+        <f aca="false">TIME(25,0,0)</f>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="1529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1529" s="0" t="s">
         <v>1526</v>
       </c>
-      <c r="L1529" s="0" t="n">
-        <f aca="false">WEEKNUM(E2,21)</f>
-        <v>1</v>
+      <c r="L1529" s="8" t="n">
+        <f aca="false">TIME(0,90,0)</f>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="1530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1530" s="0" t="s">
         <v>1527</v>
       </c>
-      <c r="L1530" s="0" t="n">
-        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
-        <v>1</v>
+      <c r="L1530" s="8" t="n">
+        <f aca="false">TIME(1,2,3)</f>
+        <v>0.0430902777777778</v>
       </c>
     </row>
     <row r="1531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1531" s="0" t="s">
         <v>1528</v>
       </c>
-      <c r="L1531" s="0" t="e">
-        <f aca="false">WEEKNUM(E1,3)</f>
+      <c r="L1531" s="8" t="e">
+        <f aca="false">TIME(-1,0,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -19075,8 +19408,8 @@
         <v>1529</v>
       </c>
       <c r="L1532" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
-        <v>3</v>
+        <f aca="false">HOUR(E3)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19084,8 +19417,8 @@
         <v>1530</v>
       </c>
       <c r="L1533" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
-        <v>1</v>
+        <f aca="false">HOUR(0.5)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19093,8 +19426,8 @@
         <v>1531</v>
       </c>
       <c r="L1534" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
-        <v>53</v>
+        <f aca="false">HOUR("18:30")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19102,8 +19435,8 @@
         <v>1532</v>
       </c>
       <c r="L1535" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
-        <v>53</v>
+        <f aca="false">HOUR(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19111,8 +19444,8 @@
         <v>1533</v>
       </c>
       <c r="L1536" s="0" t="n">
-        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
-        <v>53</v>
+        <f aca="false">MINUTE(E3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19120,8 +19453,8 @@
         <v>1534</v>
       </c>
       <c r="L1537" s="0" t="n">
-        <f aca="false">ROWS(A1:A6)</f>
-        <v>6</v>
+        <f aca="false">MINUTE("18:30:45")</f>
+        <v>30</v>
       </c>
     </row>
     <row r="1538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19129,8 +19462,8 @@
         <v>1535</v>
       </c>
       <c r="L1538" s="0" t="n">
-        <f aca="false">ROWS(A1:C3)</f>
-        <v>3</v>
+        <f aca="false">MINUTE(0.7712)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="1539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19138,8 +19471,8 @@
         <v>1536</v>
       </c>
       <c r="L1539" s="0" t="n">
-        <f aca="false">ROWS(A:A)</f>
-        <v>1048576</v>
+        <f aca="false">MINUTE(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19147,8 +19480,8 @@
         <v>1537</v>
       </c>
       <c r="L1540" s="0" t="n">
-        <f aca="false">ROWS({1,2;3,4})</f>
-        <v>2</v>
+        <f aca="false">SECOND("18:30:45")</f>
+        <v>45</v>
       </c>
     </row>
     <row r="1541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19156,8 +19489,8 @@
         <v>1538</v>
       </c>
       <c r="L1541" s="0" t="n">
-        <f aca="false">COLUMNS(A1:C3)</f>
-        <v>3</v>
+        <f aca="false">SECOND(0.5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19165,7 +19498,7 @@
         <v>1539</v>
       </c>
       <c r="L1542" s="0" t="n">
-        <f aca="false">COLUMNS(A:C)</f>
+        <f aca="false">SECOND(TIME(1,2,3))</f>
         <v>3</v>
       </c>
     </row>
@@ -19174,8 +19507,8 @@
         <v>1540</v>
       </c>
       <c r="L1543" s="0" t="n">
-        <f aca="false">COLUMNS(1:1)</f>
-        <v>16384</v>
+        <f aca="false">SECOND(-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19183,53 +19516,53 @@
         <v>1541</v>
       </c>
       <c r="L1544" s="0" t="n">
-        <f aca="false">COLUMNS({1,2;3,4})</f>
-        <v>2</v>
+        <f aca="false">EDATE(E1,1)</f>
+        <v>45337</v>
       </c>
     </row>
     <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1545" s="0" t="s">
         <v>1542</v>
       </c>
-      <c r="L1545" s="0" t="str">
-        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1545" s="0" t="n">
+        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
+        <v>45351</v>
       </c>
     </row>
     <row r="1546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1546" s="0" t="s">
         <v>1543</v>
       </c>
-      <c r="L1546" s="0" t="str">
-        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1546" s="0" t="n">
+        <f aca="false">EDATE(E1,-1)</f>
+        <v>45275</v>
       </c>
     </row>
     <row r="1547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1547" s="0" t="s">
         <v>1544</v>
       </c>
-      <c r="L1547" s="0" t="e">
-        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
-        <v>#N/A</v>
+      <c r="L1547" s="0" t="n">
+        <f aca="false">EDATE(E1,0)</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1548" s="0" t="s">
         <v>1545</v>
       </c>
-      <c r="L1548" s="0" t="str">
-        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
-        <v>fig</v>
+      <c r="L1548" s="0" t="n">
+        <f aca="false">EDATE(E1,12)</f>
+        <v>45672</v>
       </c>
     </row>
     <row r="1549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1549" s="0" t="s">
         <v>1546</v>
       </c>
-      <c r="L1549" s="0" t="str">
-        <f aca="false">LOOKUP(2,A1:B6)</f>
-        <v>banana</v>
+      <c r="L1549" s="0" t="n">
+        <f aca="false">EOMONTH(E1,0)</f>
+        <v>45322</v>
       </c>
     </row>
     <row r="1550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19237,8 +19570,8 @@
         <v>1547</v>
       </c>
       <c r="L1550" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
-        <v>3</v>
+        <f aca="false">EOMONTH(E1,1)</f>
+        <v>45351</v>
       </c>
     </row>
     <row r="1551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19246,8 +19579,8 @@
         <v>1548</v>
       </c>
       <c r="L1551" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
-        <v>3</v>
+        <f aca="false">EOMONTH(E1,-1)</f>
+        <v>45291</v>
       </c>
     </row>
     <row r="1552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19255,8 +19588,8 @@
         <v>1549</v>
       </c>
       <c r="L1552" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
-        <v>3</v>
+        <f aca="false">EOMONTH(E2,2)</f>
+        <v>45716</v>
       </c>
     </row>
     <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19264,8 +19597,8 @@
         <v>1550</v>
       </c>
       <c r="L1553" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
-        <v>4</v>
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31))</f>
+        <v>23</v>
       </c>
     </row>
     <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19273,17 +19606,17 @@
         <v>1551</v>
       </c>
       <c r="L1554" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
-        <v>3</v>
+        <f aca="false">NETWORKDAYS(E1,E2)</f>
+        <v>252</v>
       </c>
     </row>
     <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1555" s="0" t="s">
         <v>1552</v>
       </c>
-      <c r="L1555" s="0" t="e">
-        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
-        <v>#N/A</v>
+      <c r="L1555" s="0" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,31),DATE(2024,1,15))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19291,62 +19624,62 @@
         <v>1553</v>
       </c>
       <c r="L1556" s="0" t="n">
-        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
-        <v>3</v>
+        <f aca="false">NETWORKDAYS(DATE(2024,1,31),DATE(2024,1,1))</f>
+        <v>-23</v>
       </c>
     </row>
     <row r="1557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1557" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="L1557" s="0" t="e">
-        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
-        <v>#VALUE!</v>
+      <c r="L1557" s="0" t="n">
+        <f aca="false">NETWORKDAYS(E1,E1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1558" s="0" t="s">
         <v>1555</v>
       </c>
-      <c r="L1558" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
-        <v>cherry</v>
+      <c r="L1558" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),11)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="1559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1559" s="0" t="s">
         <v>1556</v>
       </c>
-      <c r="L1559" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
-        <v>none</v>
+      <c r="L1559" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),"0000011")</f>
+        <v>23</v>
       </c>
     </row>
     <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1560" s="0" t="s">
         <v>1557</v>
       </c>
-      <c r="L1560" s="0" t="e">
-        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
-        <v>#N/A</v>
+      <c r="L1560" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),2)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1561" s="0" t="s">
         <v>1558</v>
       </c>
-      <c r="L1561" s="0" t="str">
-        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
-        <v>cherry</v>
+      <c r="L1561" s="0" t="n">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),1,DATE(2024,1,15))</f>
+        <v>22</v>
       </c>
     </row>
     <row r="1562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1562" s="0" t="s">
         <v>1559</v>
       </c>
-      <c r="L1562" s="0" t="n">
-        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
-        <v>6</v>
+      <c r="L1562" s="0" t="e">
+        <f aca="false">NETWORKDAYS.INTL(DATE(2024,1,1),DATE(2024,1,31),99)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19354,17 +19687,17 @@
         <v>1560</v>
       </c>
       <c r="L1563" s="0" t="n">
-        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
-        <v>100</v>
+        <f aca="false">WORKDAY(E1,1)</f>
+        <v>45307</v>
       </c>
     </row>
     <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1564" s="0" t="s">
         <v>1561</v>
       </c>
-      <c r="L1564" s="0" t="e">
-        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
-        <v>#VALUE!</v>
+      <c r="L1564" s="0" t="n">
+        <f aca="false">WORKDAY(DATE(2024,1,19),1)</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19372,8 +19705,8 @@
         <v>1562</v>
       </c>
       <c r="L1565" s="0" t="n">
-        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
-        <v>6</v>
+        <f aca="false">WORKDAY(E1,-1)</f>
+        <v>45303</v>
       </c>
     </row>
     <row r="1566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19381,8 +19714,8 @@
         <v>1563</v>
       </c>
       <c r="L1566" s="0" t="n">
-        <f aca="true">INDIRECT("A1")</f>
-        <v>1</v>
+        <f aca="false">WORKDAY(E1,5,E1+1)</f>
+        <v>45314</v>
       </c>
     </row>
     <row r="1567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19390,62 +19723,62 @@
         <v>1564</v>
       </c>
       <c r="L1567" s="0" t="n">
-        <f aca="true">INDIRECT("A"&amp;3)</f>
-        <v>3</v>
+        <f aca="false">WORKDAY(E1,0)</f>
+        <v>45306</v>
       </c>
     </row>
     <row r="1568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1568" s="0" t="s">
         <v>1565</v>
       </c>
-      <c r="L1568" s="0" t="n">
-        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
-        <v>6</v>
+      <c r="L1568" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,1,11)</f>
+        <v>45307</v>
       </c>
     </row>
     <row r="1569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1569" s="0" t="s">
         <v>1566</v>
       </c>
-      <c r="L1569" s="0" t="n">
-        <f aca="true">INDIRECT("Other!A1")</f>
-        <v>7</v>
+      <c r="L1569" s="3" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2024,1,20),1,11)</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1570" s="0" t="s">
         <v>1567</v>
       </c>
-      <c r="L1570" s="0" t="n">
-        <f aca="true">INDIRECT("R2C1",FALSE())</f>
-        <v>2</v>
+      <c r="L1570" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,5,"0000011")</f>
+        <v>45313</v>
       </c>
     </row>
     <row r="1571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1571" s="0" t="s">
         <v>1568</v>
       </c>
-      <c r="L1571" s="0" t="e">
-        <f aca="true">INDIRECT("zzz")</f>
-        <v>#REF!</v>
+      <c r="L1571" s="2" t="n">
+        <f aca="false">WORKDAY.INTL(E1,-2,2)</f>
+        <v>45303</v>
       </c>
     </row>
     <row r="1572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1572" s="0" t="s">
         <v>1569</v>
       </c>
-      <c r="L1572" s="0" t="e">
-        <f aca="true">INDIRECT(B1)</f>
-        <v>#REF!</v>
+      <c r="L1572" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"Y")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1573" s="0" t="s">
         <v>1570</v>
       </c>
-      <c r="L1573" s="0" t="str">
-        <f aca="true">OFFSET(A1,2,1)</f>
-        <v>cherry</v>
+      <c r="L1573" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"M")</f>
+        <v>48</v>
       </c>
     </row>
     <row r="1574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19453,17 +19786,17 @@
         <v>1571</v>
       </c>
       <c r="L1574" s="0" t="n">
-        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
-        <v>6</v>
+        <f aca="false">DATEDIF(DATE(2020,1,15),E1,"D")</f>
+        <v>1461</v>
       </c>
     </row>
     <row r="1575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1575" s="0" t="s">
         <v>1572</v>
       </c>
-      <c r="L1575" s="0" t="e">
-        <f aca="true">OFFSET(A1,-1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1575" s="0" t="n">
+        <f aca="false">DATEDIF(DATE(2024,1,10),DATE(2024,3,15),"MD")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="1576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19471,8 +19804,8 @@
         <v>1573</v>
       </c>
       <c r="L1576" s="0" t="n">
-        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
-        <v>5</v>
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YM")</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19480,8 +19813,8 @@
         <v>1574</v>
       </c>
       <c r="L1577" s="0" t="n">
-        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
-        <v>3</v>
+        <f aca="false">DATEDIF(DATE(2023,6,20),E1,"YD")</f>
+        <v>209</v>
       </c>
     </row>
     <row r="1578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19489,7 +19822,7 @@
         <v>1575</v>
       </c>
       <c r="L1578" s="0" t="e">
-        <f aca="true">OFFSET(A1,0,0,0,1)</f>
+        <f aca="false">DATEDIF(E1,DATE(2020,1,15),"Y")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -19497,63 +19830,63 @@
       <c r="K1579" s="0" t="s">
         <v>1576</v>
       </c>
-      <c r="L1579" s="0" t="str">
-        <f aca="false">ADDRESS(1,1)</f>
-        <v>$A$1</v>
+      <c r="L1579" s="0" t="e">
+        <f aca="false">DATEDIF(E1,E2,"X")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1580" s="0" t="s">
         <v>1577</v>
       </c>
-      <c r="L1580" s="0" t="str">
-        <f aca="false">ADDRESS(5,3,4)</f>
-        <v>C5</v>
+      <c r="L1580" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2024,7,1))</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1581" s="0" t="s">
         <v>1578</v>
       </c>
-      <c r="L1581" s="0" t="str">
-        <f aca="false">ADDRESS(2,28,2)</f>
-        <v>AB$2</v>
+      <c r="L1581" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),1)</f>
+        <v>0.495890410958904</v>
       </c>
     </row>
     <row r="1582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1582" s="0" t="s">
         <v>1579</v>
       </c>
-      <c r="L1582" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
-        <v>R1C1</v>
+      <c r="L1582" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),2)</f>
+        <v>0.502777777777778</v>
       </c>
     </row>
     <row r="1583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1583" s="0" t="s">
         <v>1580</v>
       </c>
-      <c r="L1583" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
-        <v>'My Sheet'.$A$1</v>
+      <c r="L1583" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),3)</f>
+        <v>0.495890410958904</v>
       </c>
     </row>
     <row r="1584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1584" s="0" t="s">
         <v>1581</v>
       </c>
-      <c r="L1584" s="0" t="e">
-        <f aca="false">ADDRESS(0,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1584" s="0" t="n">
+        <f aca="false">YEARFRAC(DATE(2023,1,1),DATE(2023,7,1),4)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="1585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1585" s="0" t="s">
         <v>1582</v>
       </c>
-      <c r="L1585" s="0" t="str">
-        <f aca="false">ADDRESS(1,1,5)</f>
-        <v>$A$1</v>
+      <c r="L1585" s="0" t="n">
+        <f aca="false">YEARFRAC(E1,E2)</f>
+        <v>0.961111111111111</v>
       </c>
     </row>
     <row r="1586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19561,8 +19894,8 @@
         <v>1583</v>
       </c>
       <c r="L1586" s="0" t="n">
-        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
-        <v>6</v>
+        <f aca="false">YEARFRAC(DATE(2020,1,1),DATE(2024,1,1),1)</f>
+        <v>3.99835796387521</v>
       </c>
     </row>
     <row r="1587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19570,17 +19903,17 @@
         <v>1584</v>
       </c>
       <c r="L1587" s="0" t="n">
-        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
-        <v>2</v>
+        <f aca="false">YEARFRAC(E2,E1)</f>
+        <v>0.961111111111111</v>
       </c>
     </row>
     <row r="1588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1588" s="0" t="s">
         <v>1585</v>
       </c>
-      <c r="L1588" s="0" t="n">
-        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
-        <v>6</v>
+      <c r="L1588" s="0" t="e">
+        <f aca="false">YEARFRAC(E1,E2,5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19588,7 +19921,7 @@
         <v>1586</v>
       </c>
       <c r="L1589" s="0" t="n">
-        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
+        <f aca="false">WEEKNUM(E1,1)</f>
         <v>3</v>
       </c>
     </row>
@@ -19597,44 +19930,44 @@
         <v>1587</v>
       </c>
       <c r="L1590" s="0" t="n">
-        <f aca="false">TRANSPOSE(A1:A3)</f>
-        <v>1</v>
+        <f aca="false">WEEKNUM(E1,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1591" s="0" t="s">
         <v>1588</v>
       </c>
-      <c r="L1591" s="0" t="str">
-        <f aca="false">HYPERLINK("http://x.y","click")</f>
-        <v>click</v>
+      <c r="L1591" s="0" t="n">
+        <f aca="false">WEEKNUM(E2,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1592" s="0" t="s">
         <v>1589</v>
       </c>
-      <c r="L1592" s="0" t="str">
-        <f aca="false">HYPERLINK("http://x.y")</f>
-        <v>http://x.y</v>
+      <c r="L1592" s="0" t="n">
+        <f aca="false">WEEKNUM(E2,21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1593" s="0" t="s">
         <v>1590</v>
       </c>
-      <c r="L1593" s="0" t="str">
-        <f aca="false">HYPERLINK(B1,"go")</f>
-        <v>go</v>
+      <c r="L1593" s="0" t="n">
+        <f aca="false">WEEKNUM(DATE(2024,1,1),21)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1594" s="0" t="s">
         <v>1591</v>
       </c>
-      <c r="L1594" s="0" t="n">
-        <f aca="false">HYPERLINK("u",A2)</f>
-        <v>2</v>
+      <c r="L1594" s="0" t="e">
+        <f aca="false">WEEKNUM(E1,3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19642,8 +19975,8 @@
         <v>1592</v>
       </c>
       <c r="L1595" s="0" t="n">
-        <f aca="false">SUM(_xlfn.SEQUENCE(4))</f>
-        <v>10</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(E1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19651,8 +19984,8 @@
         <v>1593</v>
       </c>
       <c r="L1596" s="0" t="n">
-        <f aca="false">INDEX(_xlfn.SEQUENCE(3,4,10,5),2,3)</f>
-        <v>40</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(E2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19660,8 +19993,8 @@
         <v>1594</v>
       </c>
       <c r="L1597" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.SEQUENCE(5,2))</f>
-        <v>5</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2021,1,3))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19669,8 +20002,8 @@
         <v>1595</v>
       </c>
       <c r="L1598" s="0" t="n">
-        <f aca="false">COLUMNS(_xlfn.SEQUENCE(5,2))</f>
-        <v>2</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2020,12,31))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19678,8 +20011,8 @@
         <v>1596</v>
       </c>
       <c r="L1599" s="0" t="n">
-        <f aca="false">SUM(_xlfn.SEQUENCE(2,2,0.5,0.25))</f>
-        <v>3.5</v>
+        <f aca="false">_xlfn.ISOWEEKNUM(DATE(2016,1,1))</f>
+        <v>53</v>
       </c>
     </row>
     <row r="1600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19687,26 +20020,26 @@
         <v>1597</v>
       </c>
       <c r="L1600" s="0" t="n">
-        <f aca="false">_xlfn.SEQUENCE(1,1,7)</f>
-        <v>7</v>
+        <f aca="false">ROWS(A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1601" s="0" t="s">
         <v>1598</v>
       </c>
-      <c r="L1601" s="0" t="e">
-        <f aca="false">_xlfn.SEQUENCE(0)</f>
-        <v>#VALUE!</v>
+      <c r="L1601" s="0" t="n">
+        <f aca="false">ROWS(A1:C3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1602" s="0" t="s">
         <v>1599</v>
       </c>
-      <c r="L1602" s="0" t="e">
-        <f aca="false">_xlfn.SEQUENCE(-1)</f>
-        <v>#VALUE!</v>
+      <c r="L1602" s="0" t="n">
+        <f aca="false">ROWS(A:A)</f>
+        <v>1048576</v>
       </c>
     </row>
     <row r="1603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19714,8 +20047,8 @@
         <v>1600</v>
       </c>
       <c r="L1603" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.RANDARRAY(3,2))</f>
-        <v>3</v>
+        <f aca="false">ROWS({1,2;3,4})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19723,8 +20056,8 @@
         <v>1601</v>
       </c>
       <c r="L1604" s="0" t="n">
-        <f aca="false">COLUMNS(_xlfn.RANDARRAY(3,2))</f>
-        <v>2</v>
+        <f aca="false">COLUMNS(A1:C3)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19732,8 +20065,8 @@
         <v>1602</v>
       </c>
       <c r="L1605" s="0" t="n">
-        <f aca="false">SUM(_xlfn.RANDARRAY(4,4,5,5))</f>
-        <v>80</v>
+        <f aca="false">COLUMNS(A:C)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19741,44 +20074,44 @@
         <v>1603</v>
       </c>
       <c r="L1606" s="0" t="n">
-        <f aca="false">_xlfn.RANDARRAY(1,1,2,2,TRUE())</f>
-        <v>2</v>
+        <f aca="false">COLUMNS(1:1)</f>
+        <v>16384</v>
       </c>
     </row>
     <row r="1607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1607" s="0" t="s">
         <v>1604</v>
       </c>
-      <c r="L1607" s="1" t="b">
-        <f aca="false">MIN(_xlfn.RANDARRAY(10,1,1,3,TRUE()))&gt;=1</f>
-        <v>1</v>
+      <c r="L1607" s="0" t="n">
+        <f aca="false">COLUMNS({1,2;3,4})</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1608" s="0" t="s">
         <v>1605</v>
       </c>
-      <c r="L1608" s="0" t="e">
-        <f aca="false">_xlfn.RANDARRAY(2,2,5,1)</f>
-        <v>#VALUE!</v>
+      <c r="L1608" s="0" t="str">
+        <f aca="false">LOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1609" s="0" t="s">
         <v>1606</v>
       </c>
-      <c r="L1609" s="0" t="n">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6),1)</f>
-        <v>-2</v>
+      <c r="L1609" s="0" t="str">
+        <f aca="false">LOOKUP(3.5,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1610" s="0" t="s">
         <v>1607</v>
       </c>
-      <c r="L1610" s="0" t="n">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6,1,-1),1)</f>
-        <v>1000000</v>
+      <c r="L1610" s="0" t="e">
+        <f aca="false">LOOKUP(0,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19786,8 +20119,8 @@
         <v>1608</v>
       </c>
       <c r="L1611" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn._xlws.SORT(B1:B6,1,-1))</f>
-        <v>fig,elderberry,date,cherry,banana,apple</v>
+        <f aca="false">LOOKUP(100,A1:A6,B1:B6)</f>
+        <v>fig</v>
       </c>
     </row>
     <row r="1612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19795,17 +20128,17 @@
         <v>1609</v>
       </c>
       <c r="L1612" s="0" t="str">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(A1:C6,3,1),2,2)</f>
-        <v>cherry</v>
+        <f aca="false">LOOKUP(2,A1:B6)</f>
+        <v>banana</v>
       </c>
     </row>
     <row r="1613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1613" s="0" t="s">
         <v>1610</v>
       </c>
-      <c r="L1613" s="0" t="str">
-        <f aca="false">INDEX(_xlfn._xlws.SORT(F1:G4,1,-1),1,2)</f>
-        <v>four hundred</v>
+      <c r="L1613" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3,A1:A6)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19813,7 +20146,7 @@
         <v>1611</v>
       </c>
       <c r="L1614" s="0" t="n">
-        <f aca="false">INDEX(_xlfn._xlws.SORT({3,1,2},1,1,TRUE()),1,3)</f>
+        <f aca="false">_xlfn.XMATCH("cherry",B1:B6)</f>
         <v>3</v>
       </c>
     </row>
@@ -19821,135 +20154,135 @@
       <c r="K1615" s="0" t="s">
         <v>1612</v>
       </c>
-      <c r="L1615" s="0" t="e">
-        <f aca="false">_xlfn._xlws.SORT(A1:A6,2)</f>
-        <v>#VALUE!</v>
+      <c r="L1615" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,-1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1616" s="0" t="s">
         <v>1613</v>
       </c>
-      <c r="L1616" s="0" t="e">
-        <f aca="false">_xlfn._xlws.SORT(A1:A6,1,0)</f>
-        <v>#VALUE!</v>
+      <c r="L1616" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3.5,A1:A6,1)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="1617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1617" s="0" t="s">
         <v>1614</v>
       </c>
-      <c r="L1617" s="0" t="str">
-        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6),1)</f>
-        <v>banana</v>
+      <c r="L1617" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH("ch*",B1:B6,2)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1618" s="0" t="s">
         <v>1615</v>
       </c>
-      <c r="L1618" s="0" t="str">
-        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6,-1),1)</f>
-        <v>fig</v>
+      <c r="L1618" s="0" t="e">
+        <f aca="false">_xlfn.XMATCH(9,A1:A6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1619" s="0" t="s">
         <v>1616</v>
       </c>
-      <c r="L1619" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.SORTBY(G1:G4,F1:F4,-1))</f>
-        <v>four hundred,three hundred,two hundred,one hundred</v>
+      <c r="L1619" s="0" t="n">
+        <f aca="false">_xlfn.XMATCH(3,A1:A6,0,-1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="1620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1620" s="0" t="s">
         <v>1617</v>
       </c>
-      <c r="L1620" s="0" t="n">
-        <f aca="false">INDEX(_xlfn.SORTBY(A1:A6,{1;1;2;2;3;3},-1,A1:A6,1),1)</f>
-        <v>5</v>
+      <c r="L1620" s="0" t="e">
+        <f aca="false">_xlfn.XMATCH(3,A1:C6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1621" s="0" t="s">
         <v>1618</v>
       </c>
-      <c r="L1621" s="0" t="e">
-        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A3)</f>
-        <v>#VALUE!</v>
+      <c r="L1621" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B6)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1622" s="0" t="s">
         <v>1619</v>
       </c>
-      <c r="L1622" s="0" t="e">
-        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A6,2)</f>
-        <v>#VALUE!</v>
+      <c r="L1622" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6,"none")</f>
+        <v>none</v>
       </c>
     </row>
     <row r="1623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1623" s="0" t="s">
         <v>1620</v>
       </c>
-      <c r="L1623" s="0" t="n">
-        <f aca="false">SUM(_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;3))</f>
-        <v>15</v>
+      <c r="L1623" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(9,A1:A6,B1:B6)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="1624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1624" s="0" t="s">
         <v>1621</v>
       </c>
-      <c r="L1624" s="0" t="n">
-        <f aca="false">ROWS(_xlfn._xlws.FILTER(B1:B6,C1:C6&gt;0))</f>
-        <v>4</v>
+      <c r="L1624" s="0" t="str">
+        <f aca="false">_xlfn.XLOOKUP(3.5,A1:A6,B1:B6,,-1)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1625" s="0" t="s">
         <v>1622</v>
       </c>
-      <c r="L1625" s="0" t="str">
-        <f aca="false">INDEX(_xlfn._xlws.FILTER(B1:B6,A1:A6=4),1)</f>
-        <v>date</v>
+      <c r="L1625" s="0" t="n">
+        <f aca="false">_xlfn.XLOOKUP("fig",B1:B6,A1:A6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1626" s="0" t="s">
         <v>1623</v>
       </c>
-      <c r="L1626" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),_xlfn._xlws.FILTER(F1:F4,G1:G4&lt;&gt;"two hundred"))</f>
-        <v>100-300-400</v>
+      <c r="L1626" s="0" t="n">
+        <f aca="false">_xlfn.XLOOKUP(4,A1:A6,C1:C6)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="1627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1627" s="0" t="s">
         <v>1624</v>
       </c>
-      <c r="L1627" s="0" t="str">
-        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10,"none")</f>
-        <v>none</v>
+      <c r="L1627" s="0" t="e">
+        <f aca="false">_xlfn.XLOOKUP(3,A1:A6,B1:B5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="1628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1628" s="0" t="s">
         <v>1625</v>
       </c>
-      <c r="L1628" s="0" t="e">
-        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10)</f>
-        <v>#N/A</v>
+      <c r="L1628" s="0" t="n">
+        <f aca="false">SUM(A1:_xlfn.XLOOKUP(3,A1:A6,A1:A6))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="1629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1629" s="0" t="s">
         <v>1626</v>
       </c>
-      <c r="L1629" s="0" t="e">
-        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A3&gt;1)</f>
-        <v>#VALUE!</v>
+      <c r="L1629" s="0" t="n">
+        <f aca="true">INDIRECT("A1")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="1630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19957,7 +20290,7 @@
         <v>1627</v>
       </c>
       <c r="L1630" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <f aca="true">INDIRECT("A"&amp;3)</f>
         <v>3</v>
       </c>
     </row>
@@ -19966,7 +20299,7 @@
         <v>1628</v>
       </c>
       <c r="L1631" s="0" t="n">
-        <f aca="false">SUM(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <f aca="true">SUM(INDIRECT("A1:A3"))</f>
         <v>6</v>
       </c>
     </row>
@@ -19975,44 +20308,44 @@
         <v>1629</v>
       </c>
       <c r="L1632" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1},FALSE(),TRUE()))</f>
-        <v>1</v>
+        <f aca="true">INDIRECT("Other!A1")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="1633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1633" s="0" t="s">
         <v>1630</v>
       </c>
-      <c r="L1633" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE({"a";"B";"A";"b"}))</f>
-        <v>a,B</v>
+      <c r="L1633" s="0" t="n">
+        <f aca="true">INDIRECT("R2C1",FALSE())</f>
+        <v>2</v>
       </c>
     </row>
     <row r="1634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1634" s="0" t="s">
         <v>1631</v>
       </c>
-      <c r="L1634" s="0" t="n">
-        <f aca="false">COLUMNS(_xlfn.UNIQUE({1,1,2},TRUE()))</f>
-        <v>2</v>
+      <c r="L1634" s="0" t="e">
+        <f aca="true">INDIRECT("zzz")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="1635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1635" s="0" t="s">
         <v>1632</v>
       </c>
-      <c r="L1635" s="0" t="n">
-        <f aca="false">ROWS(_xlfn.UNIQUE(A1:A6))</f>
-        <v>6</v>
+      <c r="L1635" s="0" t="e">
+        <f aca="true">INDIRECT(B1)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="1636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K1636" s="0" t="s">
         <v>1633</v>
       </c>
-      <c r="L1636" s="0" t="e">
-        <f aca="false">_xlfn.UNIQUE({1;1},FALSE(),TRUE())</f>
-        <v>#N/A</v>
+      <c r="L1636" s="0" t="str">
+        <f aca="true">OFFSET(A1,2,1)</f>
+        <v>cherry</v>
       </c>
     </row>
     <row r="1637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20020,7 +20353,7 @@
         <v>1634</v>
       </c>
       <c r="L1637" s="0" t="n">
-        <f aca="false">SUM(TRANSPOSE(_xlfn.SEQUENCE(3)))</f>
+        <f aca="true">SUM(OFFSET(A1,0,0,3,1))</f>
         <v>6</v>
       </c>
     </row>
@@ -20028,9 +20361,1008 @@
       <c r="K1638" s="0" t="s">
         <v>1635</v>
       </c>
-      <c r="L1638" s="0" t="n">
+      <c r="L1638" s="0" t="e">
+        <f aca="true">OFFSET(A1,-1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1639" s="0" t="s">
+        <v>1636</v>
+      </c>
+      <c r="L1639" s="0" t="n">
+        <f aca="true">SUM(OFFSET(A1:A2,1,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1640" s="0" t="s">
+        <v>1637</v>
+      </c>
+      <c r="L1640" s="0" t="n">
+        <f aca="true">ROWS(OFFSET(A1,0,0,3,2))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1641" s="0" t="s">
+        <v>1638</v>
+      </c>
+      <c r="L1641" s="0" t="e">
+        <f aca="true">OFFSET(A1,0,0,0,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1642" s="0" t="s">
+        <v>1639</v>
+      </c>
+      <c r="L1642" s="0" t="str">
+        <f aca="false">ADDRESS(1,1)</f>
+        <v>$A$1</v>
+      </c>
+    </row>
+    <row r="1643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1643" s="0" t="s">
+        <v>1640</v>
+      </c>
+      <c r="L1643" s="0" t="str">
+        <f aca="false">ADDRESS(5,3,4)</f>
+        <v>C5</v>
+      </c>
+    </row>
+    <row r="1644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1644" s="0" t="s">
+        <v>1641</v>
+      </c>
+      <c r="L1644" s="0" t="str">
+        <f aca="false">ADDRESS(2,28,2)</f>
+        <v>AB$2</v>
+      </c>
+    </row>
+    <row r="1645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1645" s="0" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L1645" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,FALSE())</f>
+        <v>R1C1</v>
+      </c>
+    </row>
+    <row r="1646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1646" s="0" t="s">
+        <v>1643</v>
+      </c>
+      <c r="L1646" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,1,TRUE(),"My Sheet")</f>
+        <v>'My Sheet'.$A$1</v>
+      </c>
+    </row>
+    <row r="1647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1647" s="0" t="s">
+        <v>1644</v>
+      </c>
+      <c r="L1647" s="0" t="e">
+        <f aca="false">ADDRESS(0,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1648" s="0" t="s">
+        <v>1645</v>
+      </c>
+      <c r="L1648" s="0" t="str">
+        <f aca="false">ADDRESS(1,1,5)</f>
+        <v>$A$1</v>
+      </c>
+    </row>
+    <row r="1649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1649" s="0" t="s">
+        <v>1646</v>
+      </c>
+      <c r="L1649" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(A1:A3))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1650" s="0" t="s">
+        <v>1647</v>
+      </c>
+      <c r="L1650" s="0" t="n">
+        <f aca="false">INDEX(TRANSPOSE(A1:A3),1,2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1651" s="0" t="s">
+        <v>1648</v>
+      </c>
+      <c r="L1651" s="0" t="n">
+        <f aca="false">COLUMNS(TRANSPOSE(A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1652" s="0" t="s">
+        <v>1649</v>
+      </c>
+      <c r="L1652" s="0" t="n">
+        <f aca="false">ROWS(TRANSPOSE(A1:C1))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1653" s="0" t="s">
+        <v>1650</v>
+      </c>
+      <c r="L1653" s="0" t="n">
+        <f aca="false">TRANSPOSE(A1:A3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1654" s="0" t="s">
+        <v>1651</v>
+      </c>
+      <c r="L1654" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y","click")</f>
+        <v>click</v>
+      </c>
+    </row>
+    <row r="1655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1655" s="0" t="s">
+        <v>1652</v>
+      </c>
+      <c r="L1655" s="0" t="str">
+        <f aca="false">HYPERLINK("http://x.y")</f>
+        <v>http://x.y</v>
+      </c>
+    </row>
+    <row r="1656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1656" s="0" t="s">
+        <v>1653</v>
+      </c>
+      <c r="L1656" s="0" t="str">
+        <f aca="false">HYPERLINK(B1,"go")</f>
+        <v>go</v>
+      </c>
+    </row>
+    <row r="1657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1657" s="0" t="s">
+        <v>1654</v>
+      </c>
+      <c r="L1657" s="0" t="n">
+        <f aca="false">HYPERLINK("u",A2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1658" s="0" t="s">
+        <v>1655</v>
+      </c>
+      <c r="L1658" s="0" t="n">
+        <f aca="false">SUM(_xlfn.SEQUENCE(4))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1659" s="0" t="s">
+        <v>1656</v>
+      </c>
+      <c r="L1659" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.SEQUENCE(3,4,10,5),2,3)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1660" s="0" t="s">
+        <v>1657</v>
+      </c>
+      <c r="L1660" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.SEQUENCE(5,2))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1661" s="0" t="s">
+        <v>1658</v>
+      </c>
+      <c r="L1661" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.SEQUENCE(5,2))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1662" s="0" t="s">
+        <v>1659</v>
+      </c>
+      <c r="L1662" s="0" t="n">
+        <f aca="false">SUM(_xlfn.SEQUENCE(2,2,0.5,0.25))</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="1663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1663" s="0" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L1663" s="0" t="n">
+        <f aca="false">_xlfn.SEQUENCE(1,1,7)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1664" s="0" t="s">
+        <v>1661</v>
+      </c>
+      <c r="L1664" s="0" t="e">
+        <f aca="false">_xlfn.SEQUENCE(0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1665" s="0" t="s">
+        <v>1662</v>
+      </c>
+      <c r="L1665" s="0" t="e">
+        <f aca="false">_xlfn.SEQUENCE(-1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1666" s="0" t="s">
+        <v>1663</v>
+      </c>
+      <c r="L1666" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.RANDARRAY(3,2))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1667" s="0" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L1667" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.RANDARRAY(3,2))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1668" s="0" t="s">
+        <v>1665</v>
+      </c>
+      <c r="L1668" s="0" t="n">
+        <f aca="false">SUM(_xlfn.RANDARRAY(4,4,5,5))</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1669" s="0" t="s">
+        <v>1666</v>
+      </c>
+      <c r="L1669" s="0" t="n">
+        <f aca="false">_xlfn.RANDARRAY(1,1,2,2,TRUE())</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1670" s="0" t="s">
+        <v>1667</v>
+      </c>
+      <c r="L1670" s="1" t="b">
+        <f aca="false">MIN(_xlfn.RANDARRAY(10,1,1,3,TRUE()))&gt;=1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1671" s="0" t="s">
+        <v>1668</v>
+      </c>
+      <c r="L1671" s="0" t="e">
+        <f aca="false">_xlfn.RANDARRAY(2,2,5,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1672" s="0" t="s">
+        <v>1669</v>
+      </c>
+      <c r="L1672" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6),1)</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1673" s="0" t="s">
+        <v>1670</v>
+      </c>
+      <c r="L1673" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(C1:C6,1,-1),1)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="1674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1674" s="0" t="s">
+        <v>1671</v>
+      </c>
+      <c r="L1674" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn._xlws.SORT(B1:B6,1,-1))</f>
+        <v>fig,elderberry,date,cherry,banana,apple</v>
+      </c>
+    </row>
+    <row r="1675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1675" s="0" t="s">
+        <v>1672</v>
+      </c>
+      <c r="L1675" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(A1:C6,3,1),2,2)</f>
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="1676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1676" s="0" t="s">
+        <v>1673</v>
+      </c>
+      <c r="L1676" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.SORT(F1:G4,1,-1),1,2)</f>
+        <v>four hundred</v>
+      </c>
+    </row>
+    <row r="1677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1677" s="0" t="s">
+        <v>1674</v>
+      </c>
+      <c r="L1677" s="0" t="n">
+        <f aca="false">INDEX(_xlfn._xlws.SORT({3,1,2},1,1,TRUE()),1,3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1678" s="0" t="s">
+        <v>1675</v>
+      </c>
+      <c r="L1678" s="0" t="e">
+        <f aca="false">_xlfn._xlws.SORT(A1:A6,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1679" s="0" t="s">
+        <v>1676</v>
+      </c>
+      <c r="L1679" s="0" t="e">
+        <f aca="false">_xlfn._xlws.SORT(A1:A6,1,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1680" s="0" t="s">
+        <v>1677</v>
+      </c>
+      <c r="L1680" s="0" t="str">
+        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6),1)</f>
+        <v>banana</v>
+      </c>
+    </row>
+    <row r="1681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1681" s="0" t="s">
+        <v>1678</v>
+      </c>
+      <c r="L1681" s="0" t="str">
+        <f aca="false">INDEX(_xlfn.SORTBY(B1:B6,C1:C6,-1),1)</f>
+        <v>fig</v>
+      </c>
+    </row>
+    <row r="1682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1682" s="0" t="s">
+        <v>1679</v>
+      </c>
+      <c r="L1682" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.SORTBY(G1:G4,F1:F4,-1))</f>
+        <v>four hundred,three hundred,two hundred,one hundred</v>
+      </c>
+    </row>
+    <row r="1683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1683" s="0" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L1683" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.SORTBY(A1:A6,{1;1;2;2;3;3},-1,A1:A6,1),1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1684" s="0" t="s">
+        <v>1681</v>
+      </c>
+      <c r="L1684" s="0" t="e">
+        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A3)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1685" s="0" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L1685" s="0" t="e">
+        <f aca="false">_xlfn.SORTBY(A1:A6,A1:A6,2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1686" s="0" t="s">
+        <v>1683</v>
+      </c>
+      <c r="L1686" s="0" t="n">
+        <f aca="false">SUM(_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;3))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1687" s="0" t="s">
+        <v>1684</v>
+      </c>
+      <c r="L1687" s="0" t="n">
+        <f aca="false">ROWS(_xlfn._xlws.FILTER(B1:B6,C1:C6&gt;0))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1688" s="0" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L1688" s="0" t="str">
+        <f aca="false">INDEX(_xlfn._xlws.FILTER(B1:B6,A1:A6=4),1)</f>
+        <v>date</v>
+      </c>
+    </row>
+    <row r="1689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1689" s="0" t="s">
+        <v>1686</v>
+      </c>
+      <c r="L1689" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),_xlfn._xlws.FILTER(F1:F4,G1:G4&lt;&gt;"two hundred"))</f>
+        <v>100-300-400</v>
+      </c>
+    </row>
+    <row r="1690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1690" s="0" t="s">
+        <v>1687</v>
+      </c>
+      <c r="L1690" s="0" t="str">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10,"none")</f>
+        <v>none</v>
+      </c>
+    </row>
+    <row r="1691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1691" s="0" t="s">
+        <v>1688</v>
+      </c>
+      <c r="L1691" s="0" t="e">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A6&gt;10)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1692" s="0" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L1692" s="0" t="e">
+        <f aca="false">_xlfn._xlws.FILTER(A1:A6,A1:A3&gt;1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1693" s="0" t="s">
+        <v>1690</v>
+      </c>
+      <c r="L1693" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1694" s="0" t="s">
+        <v>1691</v>
+      </c>
+      <c r="L1694" s="0" t="n">
+        <f aca="false">SUM(_xlfn.UNIQUE({1;2;2;3;1}))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1695" s="0" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L1695" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE({1;2;2;3;1},FALSE(),TRUE()))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1696" s="0" t="s">
+        <v>1693</v>
+      </c>
+      <c r="L1696" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE({"a";"B";"A";"b"}))</f>
+        <v>a,B</v>
+      </c>
+    </row>
+    <row r="1697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1697" s="0" t="s">
+        <v>1694</v>
+      </c>
+      <c r="L1697" s="0" t="n">
+        <f aca="false">COLUMNS(_xlfn.UNIQUE({1,1,2},TRUE()))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1698" s="0" t="s">
+        <v>1695</v>
+      </c>
+      <c r="L1698" s="0" t="n">
+        <f aca="false">ROWS(_xlfn.UNIQUE(A1:A6))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1699" s="0" t="s">
+        <v>1696</v>
+      </c>
+      <c r="L1699" s="0" t="e">
+        <f aca="false">_xlfn.UNIQUE({1;1},FALSE(),TRUE())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="1700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1700" s="0" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L1700" s="0" t="n">
+        <f aca="false">SUM(TRANSPOSE(_xlfn.SEQUENCE(3)))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1701" s="0" t="s">
+        <v>1698</v>
+      </c>
+      <c r="L1701" s="0" t="n">
         <f aca="false">INDEX(_xlfn.XLOOKUP(3,A1:A6,B1:C6),1,2)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="1702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1702" s="0" t="s">
+        <v>1699</v>
+      </c>
+      <c r="L1702" s="0" t="e">
+        <f aca="false">SUM(_xlfn.take(A1:A6,2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1703" s="0" t="s">
+        <v>1700</v>
+      </c>
+      <c r="L1703" s="0" t="e">
+        <f aca="false">SUM(_xlfn.take(A1:A6,-2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1704" s="0" t="s">
+        <v>1701</v>
+      </c>
+      <c r="L1704" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.take(A1:C6,1,-1),1)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1705" s="0" t="s">
+        <v>1702</v>
+      </c>
+      <c r="L1705" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.take(A1:A6,99))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1706" s="0" t="s">
+        <v>1703</v>
+      </c>
+      <c r="L1706" s="0" t="e">
+        <f aca="false">_xlfn.take(A1:A6,0)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1707" s="0" t="s">
+        <v>1704</v>
+      </c>
+      <c r="L1707" s="0" t="e">
+        <f aca="false">SUM(_xlfn.drop(A1:A6,4))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1708" s="0" t="s">
+        <v>1705</v>
+      </c>
+      <c r="L1708" s="0" t="e">
+        <f aca="false">SUM(_xlfn.drop(A1:A6,-4))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1709" s="0" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L1709" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.drop(A1:C6,1,2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1710" s="0" t="s">
+        <v>1707</v>
+      </c>
+      <c r="L1710" s="0" t="e">
+        <f aca="false">_xlfn.drop(A1:A6,6)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1711" s="0" t="s">
+        <v>1708</v>
+      </c>
+      <c r="L1711" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.vstack(A1:A2,F1:F4))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1712" s="0" t="s">
+        <v>1709</v>
+      </c>
+      <c r="L1712" s="0" t="e">
+        <f aca="false">SUM(_xlfn.vstack(A1:A3,F1))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1713" s="0" t="s">
+        <v>1710</v>
+      </c>
+      <c r="L1713" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.vstack(A1:B1,F1),2,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1714" s="0" t="s">
+        <v>1711</v>
+      </c>
+      <c r="L1714" s="0" t="e">
+        <f aca="false">COLUMNS(_xlfn.vstack(A1,B1:C1))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1715" s="0" t="s">
+        <v>1712</v>
+      </c>
+      <c r="L1715" s="0" t="e">
+        <f aca="false">COLUMNS(_xlfn.hstack(A1:A2,F1:F2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1716" s="0" t="s">
+        <v>1713</v>
+      </c>
+      <c r="L1716" s="0" t="e">
+        <f aca="false">SUM(_xlfn.hstack(A1:A2,F1:F2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1717" s="0" t="s">
+        <v>1714</v>
+      </c>
+      <c r="L1717" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.hstack(A1:A2,F1),2,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1718" s="0" t="s">
+        <v>1715</v>
+      </c>
+      <c r="L1718" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.hstack(A1:A3,F1:F4))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1719" s="0" t="s">
+        <v>1716</v>
+      </c>
+      <c r="L1719" s="0" t="e">
+        <f aca="false">SUM(_xlfn.choosecols(A1:C6,1))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1720" s="0" t="s">
+        <v>1717</v>
+      </c>
+      <c r="L1720" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.choosecols(A1:C6,-1),1)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1721" s="0" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L1721" s="0" t="e">
+        <f aca="false">COLUMNS(_xlfn.choosecols(A1:C6,1,3,3))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1722" s="0" t="s">
+        <v>1719</v>
+      </c>
+      <c r="L1722" s="0" t="e">
+        <f aca="false">_xlfn.choosecols(A1:C6,4)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1723" s="0" t="s">
+        <v>1720</v>
+      </c>
+      <c r="L1723" s="0" t="e">
+        <f aca="false">SUM(_xlfn.chooserows(A1:A6,1,6))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1724" s="0" t="s">
+        <v>1721</v>
+      </c>
+      <c r="L1724" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.chooserows(B1:B6,-1),1)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1725" s="0" t="s">
+        <v>1722</v>
+      </c>
+      <c r="L1725" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.chooserows(A1:A6,{1,2,3}))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1726" s="0" t="s">
+        <v>1723</v>
+      </c>
+      <c r="L1726" s="0" t="e">
+        <f aca="false">_xlfn.chooserows(A1:A6,0)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1727" s="0" t="s">
+        <v>1724</v>
+      </c>
+      <c r="L1727" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.expand(A1:A2,5))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1728" s="0" t="s">
+        <v>1725</v>
+      </c>
+      <c r="L1728" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.expand(A1:A2,3,2,0),3,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1729" s="0" t="s">
+        <v>1726</v>
+      </c>
+      <c r="L1729" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.expand(A1,2),2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1730" s="0" t="s">
+        <v>1727</v>
+      </c>
+      <c r="L1730" s="0" t="e">
+        <f aca="false">_xlfn.expand(A1:A3,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1731" s="0" t="s">
+        <v>1728</v>
+      </c>
+      <c r="L1731" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.tocol(A1:C2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1732" s="0" t="s">
+        <v>1729</v>
+      </c>
+      <c r="L1732" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.tocol(A1:C2),2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1733" s="0" t="s">
+        <v>1730</v>
+      </c>
+      <c r="L1733" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.tocol(A1:C2,0,TRUE()),2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1734" s="0" t="s">
+        <v>1731</v>
+      </c>
+      <c r="L1734" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.tocol(A1:H2,2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1735" s="0" t="s">
+        <v>1732</v>
+      </c>
+      <c r="L1735" s="0" t="e">
+        <f aca="false">COLUMNS(_xlfn.torow(A1:B2))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1736" s="0" t="s">
+        <v>1733</v>
+      </c>
+      <c r="L1736" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.torow(A1:B2),1,3)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1737" s="0" t="s">
+        <v>1734</v>
+      </c>
+      <c r="L1737" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.torow(A1:B2,0,TRUE()),1,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1738" s="0" t="s">
+        <v>1735</v>
+      </c>
+      <c r="L1738" s="0" t="e">
+        <f aca="false">SUM(_xlfn.torow(A1:A6))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1739" s="0" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L1739" s="0" t="e">
+        <f aca="false">ROWS(_xlfn.wraprows(A1:A6,4))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1740" s="0" t="s">
+        <v>1737</v>
+      </c>
+      <c r="L1740" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.wraprows(A1:A6,4),2,3)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1741" s="0" t="s">
+        <v>1738</v>
+      </c>
+      <c r="L1741" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.wraprows(A1:A6,4,0),2,3)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1742" s="0" t="s">
+        <v>1739</v>
+      </c>
+      <c r="L1742" s="0" t="e">
+        <f aca="false">_xlfn.wraprows(A1:B2,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1743" s="0" t="s">
+        <v>1740</v>
+      </c>
+      <c r="L1743" s="0" t="e">
+        <f aca="false">COLUMNS(_xlfn.wrapcols(A1:A6,4))</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1744" s="0" t="s">
+        <v>1741</v>
+      </c>
+      <c r="L1744" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.wrapcols(A1:A6,4),2,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1745" s="0" t="s">
+        <v>1742</v>
+      </c>
+      <c r="L1745" s="0" t="e">
+        <f aca="false">INDEX(_xlfn.wrapcols(A1:A6,4),4,2)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1746" s="0" t="s">
+        <v>1743</v>
+      </c>
+      <c r="L1746" s="0" t="e">
+        <f aca="false">_xlfn.wrapcols(A1:A6,0)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="1747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1747" s="0" t="s">
+        <v>1744</v>
+      </c>
+      <c r="L1747" s="0" t="e">
+        <f aca="false">SUM(LEN(B1:B3))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="1748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1748" s="0" t="s">
+        <v>1745</v>
+      </c>
+      <c r="L1748" s="0" t="n">
+        <f aca="false">SUMPRODUCT(LEN(B1:B6))</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1749" s="0" t="s">
+        <v>1746</v>
+      </c>
+      <c r="L1749" s="0" t="n">
+        <f aca="false">INDEX(_xlfn.UNIQUE({1,2,1;3,4,3},TRUE()),2,2)</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -20057,7 +21389,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1636</v>
+        <v>1747</v>
       </c>
     </row>
   </sheetData>
